--- a/Översikt YSTAD.xlsx
+++ b/Översikt YSTAD.xlsx
@@ -584,7 +584,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A 31213-2023</t>
+          <t>A 3253-2025</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>45113</v>
+        <v>45679</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -613,17 +613,22 @@
           <t>YSTAD</t>
         </is>
       </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I2" t="n">
-        <v>6.5</v>
+        <v>2.5</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
@@ -638,7 +643,7 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -650,47 +655,47 @@
         <v>3</v>
       </c>
       <c r="U2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
-          <t>Skogsveronika
-Skärmstarr</t>
+          <t>Lönnlav
+Strävlosta</t>
         </is>
       </c>
       <c r="W2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 31213-2023 artfynd.xlsx", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 3253-2025 artfynd.xlsx", "A 3253-2025")</f>
         <v/>
       </c>
       <c r="X2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 31213-2023 karta.png", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 3253-2025 karta.png", "A 3253-2025")</f>
         <v/>
       </c>
       <c r="Y2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 31213-2023 georefererad karta.tif", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 3253-2025 georefererad karta.tif", "A 3253-2025")</f>
         <v/>
       </c>
       <c r="AA2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 31213-2023 FSC-klagomål.docx", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 3253-2025 FSC-klagomål.docx", "A 3253-2025")</f>
         <v/>
       </c>
       <c r="AB2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 31213-2023 FSC-klagomål mail.docx", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 3253-2025 FSC-klagomål mail.docx", "A 3253-2025")</f>
         <v/>
       </c>
       <c r="AC2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 31213-2023 tillsynsbegäran.docx", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 3253-2025 tillsynsbegäran.docx", "A 3253-2025")</f>
         <v/>
       </c>
       <c r="AD2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 31213-2023 tillsynsbegäran mail.docx", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 3253-2025 tillsynsbegäran mail.docx", "A 3253-2025")</f>
         <v/>
       </c>
     </row>
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 3253-2025</t>
+          <t>A 49546-2025</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -704,10 +709,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>45679</v>
+        <v>45939</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -719,19 +724,14 @@
           <t>YSTAD</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I3" t="n">
-        <v>2.5</v>
+        <v>4.4</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -740,7 +740,7 @@
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -749,59 +749,59 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S3" t="n">
         <v>2</v>
       </c>
       <c r="T3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
-          <t>Lönnlav
-Strävlosta</t>
+          <t>Skogsalm
+Igelkottsröksvamp</t>
         </is>
       </c>
       <c r="W3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 3253-2025 artfynd.xlsx", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 49546-2025 artfynd.xlsx", "A 49546-2025")</f>
         <v/>
       </c>
       <c r="X3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 3253-2025 karta.png", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 49546-2025 karta.png", "A 49546-2025")</f>
         <v/>
       </c>
       <c r="Y3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 3253-2025 georefererad karta.tif", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 49546-2025 georefererad karta.tif", "A 49546-2025")</f>
         <v/>
       </c>
       <c r="AA3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 3253-2025 FSC-klagomål.docx", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 49546-2025 FSC-klagomål.docx", "A 49546-2025")</f>
         <v/>
       </c>
       <c r="AB3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 3253-2025 FSC-klagomål mail.docx", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 49546-2025 FSC-klagomål mail.docx", "A 49546-2025")</f>
         <v/>
       </c>
       <c r="AC3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 3253-2025 tillsynsbegäran.docx", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 49546-2025 tillsynsbegäran.docx", "A 49546-2025")</f>
         <v/>
       </c>
       <c r="AD3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 3253-2025 tillsynsbegäran mail.docx", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 49546-2025 tillsynsbegäran mail.docx", "A 49546-2025")</f>
         <v/>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 49546-2025</t>
+          <t>A 60295-2022</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -811,14 +811,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45939</v>
+        <v>44903</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -831,13 +831,13 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>4.4</v>
+        <v>1.1</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -846,7 +846,7 @@
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -855,59 +855,59 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>2</v>
       </c>
       <c r="T4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>Skogsalm
-Igelkottsröksvamp</t>
+          <t>Klockgroda
+Ätlig groda</t>
         </is>
       </c>
       <c r="W4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 49546-2025 artfynd.xlsx", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 60295-2022 artfynd.xlsx", "A 60295-2022")</f>
         <v/>
       </c>
       <c r="X4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 49546-2025 karta.png", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 60295-2022 karta.png", "A 60295-2022")</f>
         <v/>
       </c>
       <c r="Y4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 49546-2025 georefererad karta.tif", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 60295-2022 georefererad karta.tif", "A 60295-2022")</f>
         <v/>
       </c>
       <c r="AA4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 49546-2025 FSC-klagomål.docx", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 60295-2022 FSC-klagomål.docx", "A 60295-2022")</f>
         <v/>
       </c>
       <c r="AB4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 49546-2025 FSC-klagomål mail.docx", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 60295-2022 FSC-klagomål mail.docx", "A 60295-2022")</f>
         <v/>
       </c>
       <c r="AC4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 49546-2025 tillsynsbegäran.docx", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 60295-2022 tillsynsbegäran.docx", "A 60295-2022")</f>
         <v/>
       </c>
       <c r="AD4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 49546-2025 tillsynsbegäran mail.docx", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 60295-2022 tillsynsbegäran mail.docx", "A 60295-2022")</f>
         <v/>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 60295-2022</t>
+          <t>A 31213-2023</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -917,14 +917,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>44903</v>
+        <v>45113</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -937,16 +937,16 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>1.1</v>
+        <v>6.5</v>
       </c>
       <c r="J5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -961,7 +961,7 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -970,43 +970,43 @@
         <v>2</v>
       </c>
       <c r="T5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="U5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>Klockgroda
-Ätlig groda</t>
+          <t>Skogsveronika
+Skärmstarr</t>
         </is>
       </c>
       <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 60295-2022 artfynd.xlsx", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 31213-2023 artfynd.xlsx", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 60295-2022 karta.png", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 31213-2023 karta.png", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 60295-2022 georefererad karta.tif", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 31213-2023 georefererad karta.tif", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 60295-2022 FSC-klagomål.docx", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 31213-2023 FSC-klagomål.docx", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 60295-2022 FSC-klagomål mail.docx", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 31213-2023 FSC-klagomål mail.docx", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 60295-2022 tillsynsbegäran.docx", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 31213-2023 tillsynsbegäran.docx", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 60295-2022 tillsynsbegäran mail.docx", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 31213-2023 tillsynsbegäran mail.docx", "A 31213-2023")</f>
         <v/>
       </c>
     </row>
@@ -1030,7 +1030,7 @@
         <v>44756</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 61558-2023</t>
+          <t>A 13766-2023</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1128,14 +1128,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45265</v>
+        <v>45007</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1147,16 +1147,11 @@
           <t>YSTAD</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I7" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -1168,7 +1163,7 @@
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1177,10 +1172,10 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1193,42 +1188,42 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 61558-2023 artfynd.xlsx", "A 61558-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 13766-2023 artfynd.xlsx", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 61558-2023 karta.png", "A 61558-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 13766-2023 karta.png", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 61558-2023 georefererad karta.tif", "A 61558-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 13766-2023 georefererad karta.tif", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 61558-2023 FSC-klagomål.docx", "A 61558-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 13766-2023 FSC-klagomål.docx", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 61558-2023 FSC-klagomål mail.docx", "A 61558-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 13766-2023 FSC-klagomål mail.docx", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 61558-2023 tillsynsbegäran.docx", "A 61558-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 13766-2023 tillsynsbegäran.docx", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 61558-2023 tillsynsbegäran mail.docx", "A 61558-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 13766-2023 tillsynsbegäran mail.docx", "A 13766-2023")</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 34341-2024</t>
+          <t>A 61558-2023</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1242,10 +1237,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45525</v>
+        <v>45265</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1259,11 +1254,11 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Övriga statliga verk och myndigheter</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>14.4</v>
+        <v>1.5</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1272,13 +1267,13 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1290,7 +1285,7 @@
         <v>1</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1299,39 +1294,39 @@
         <v>1</v>
       </c>
       <c r="U8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>Desmeknopp</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 34341-2024 artfynd.xlsx", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 61558-2023 artfynd.xlsx", "A 61558-2023")</f>
         <v/>
       </c>
       <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 34341-2024 karta.png", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 61558-2023 karta.png", "A 61558-2023")</f>
         <v/>
       </c>
       <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 34341-2024 georefererad karta.tif", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 61558-2023 georefererad karta.tif", "A 61558-2023")</f>
         <v/>
       </c>
       <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 34341-2024 FSC-klagomål.docx", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 61558-2023 FSC-klagomål.docx", "A 61558-2023")</f>
         <v/>
       </c>
       <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 34341-2024 FSC-klagomål mail.docx", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 61558-2023 FSC-klagomål mail.docx", "A 61558-2023")</f>
         <v/>
       </c>
       <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 34341-2024 tillsynsbegäran.docx", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 61558-2023 tillsynsbegäran.docx", "A 61558-2023")</f>
         <v/>
       </c>
       <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 34341-2024 tillsynsbegäran mail.docx", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 61558-2023 tillsynsbegäran mail.docx", "A 61558-2023")</f>
         <v/>
       </c>
     </row>
@@ -1355,7 +1350,7 @@
         <v>45939</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1460,7 +1455,7 @@
         <v>45939</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1548,7 +1543,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 13766-2023</t>
+          <t>A 60891-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1558,14 +1553,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45007</v>
+        <v>45644</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1578,7 +1573,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0.9</v>
+        <v>16.1</v>
       </c>
       <c r="J11" t="n">
         <v>1</v>
@@ -1618,42 +1613,42 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Lövgroda</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 13766-2023 artfynd.xlsx", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 60891-2024 artfynd.xlsx", "A 60891-2024")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 13766-2023 karta.png", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 60891-2024 karta.png", "A 60891-2024")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 13766-2023 georefererad karta.tif", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 60891-2024 georefererad karta.tif", "A 60891-2024")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 13766-2023 FSC-klagomål.docx", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 60891-2024 FSC-klagomål.docx", "A 60891-2024")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 13766-2023 FSC-klagomål mail.docx", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 60891-2024 FSC-klagomål mail.docx", "A 60891-2024")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 13766-2023 tillsynsbegäran.docx", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 60891-2024 tillsynsbegäran.docx", "A 60891-2024")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 13766-2023 tillsynsbegäran mail.docx", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 60891-2024 tillsynsbegäran mail.docx", "A 60891-2024")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 60891-2024</t>
+          <t>A 34341-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1667,10 +1662,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45644</v>
+        <v>45525</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1682,17 +1677,22 @@
           <t>YSTAD</t>
         </is>
       </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I12" t="n">
-        <v>16.1</v>
+        <v>14.4</v>
       </c>
       <c r="J12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -1707,7 +1707,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -1719,39 +1719,39 @@
         <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Lövgroda</t>
+          <t>Desmeknopp</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 60891-2024 artfynd.xlsx", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 34341-2024 artfynd.xlsx", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 60891-2024 karta.png", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 34341-2024 karta.png", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 60891-2024 georefererad karta.tif", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 34341-2024 georefererad karta.tif", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 60891-2024 FSC-klagomål.docx", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 34341-2024 FSC-klagomål.docx", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 60891-2024 FSC-klagomål mail.docx", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 34341-2024 FSC-klagomål mail.docx", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 60891-2024 tillsynsbegäran.docx", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 34341-2024 tillsynsbegäran.docx", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 60891-2024 tillsynsbegäran mail.docx", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 34341-2024 tillsynsbegäran mail.docx", "A 34341-2024")</f>
         <v/>
       </c>
     </row>
@@ -1775,7 +1775,7 @@
         <v>44617</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 40417-2022</t>
+          <t>A 32596-2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1845,10 +1845,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44823</v>
+        <v>45513</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1904,7 +1904,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 34302-2024</t>
+          <t>A 40417-2022</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1918,10 +1918,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45524</v>
+        <v>44823</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1977,7 +1977,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 32596-2024</t>
+          <t>A 49536-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1991,10 +1991,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45513</v>
+        <v>45939</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>2.6</v>
+        <v>1.5</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2050,7 +2050,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 60803-2023</t>
+          <t>A 18090-2022</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2060,14 +2060,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45260</v>
+        <v>44684</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2080,7 +2080,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1.6</v>
+        <v>4.9</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2123,7 +2123,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 38631-2023</t>
+          <t>A 60803-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2137,10 +2137,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45162</v>
+        <v>45260</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2196,7 +2196,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 18090-2022</t>
+          <t>A 27578-2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2206,14 +2206,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44684</v>
+        <v>46190</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>4.9</v>
+        <v>6.6</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2269,7 +2269,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 49536-2025</t>
+          <t>A 38631-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2283,10 +2283,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45939</v>
+        <v>45162</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2299,7 +2299,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2359,7 +2359,7 @@
         <v>45069</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2420,7 +2420,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 27578-2026</t>
+          <t>A 34302-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2434,10 +2434,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46190</v>
+        <v>45524</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2450,7 +2450,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>6.6</v>
+        <v>1.9</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>

--- a/Översikt YSTAD.xlsx
+++ b/Översikt YSTAD.xlsx
@@ -584,7 +584,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A 3253-2025</t>
+          <t>A 49546-2025</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>45679</v>
+        <v>45939</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -613,19 +613,14 @@
           <t>YSTAD</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I2" t="n">
-        <v>2.5</v>
+        <v>4.4</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -634,7 +629,7 @@
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -643,59 +638,59 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S2" t="n">
         <v>2</v>
       </c>
       <c r="T2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
-          <t>Lönnlav
-Strävlosta</t>
+          <t>Skogsalm
+Igelkottsröksvamp</t>
         </is>
       </c>
       <c r="W2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 3253-2025 artfynd.xlsx", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 49546-2025 artfynd.xlsx", "A 49546-2025")</f>
         <v/>
       </c>
       <c r="X2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 3253-2025 karta.png", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 49546-2025 karta.png", "A 49546-2025")</f>
         <v/>
       </c>
       <c r="Y2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 3253-2025 georefererad karta.tif", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 49546-2025 georefererad karta.tif", "A 49546-2025")</f>
         <v/>
       </c>
       <c r="AA2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 3253-2025 FSC-klagomål.docx", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 49546-2025 FSC-klagomål.docx", "A 49546-2025")</f>
         <v/>
       </c>
       <c r="AB2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 3253-2025 FSC-klagomål mail.docx", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 49546-2025 FSC-klagomål mail.docx", "A 49546-2025")</f>
         <v/>
       </c>
       <c r="AC2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 3253-2025 tillsynsbegäran.docx", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 49546-2025 tillsynsbegäran.docx", "A 49546-2025")</f>
         <v/>
       </c>
       <c r="AD2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 3253-2025 tillsynsbegäran mail.docx", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 49546-2025 tillsynsbegäran mail.docx", "A 49546-2025")</f>
         <v/>
       </c>
     </row>
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 49546-2025</t>
+          <t>A 31213-2023</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -709,10 +704,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>45939</v>
+        <v>45113</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -725,22 +720,22 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>4.4</v>
+        <v>6.5</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -752,49 +747,49 @@
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
         <v>2</v>
       </c>
       <c r="T3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
-          <t>Skogsalm
-Igelkottsröksvamp</t>
+          <t>Skogsveronika
+Skärmstarr</t>
         </is>
       </c>
       <c r="W3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 49546-2025 artfynd.xlsx", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 31213-2023 artfynd.xlsx", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="X3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 49546-2025 karta.png", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 31213-2023 karta.png", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="Y3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 49546-2025 georefererad karta.tif", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 31213-2023 georefererad karta.tif", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="AA3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 49546-2025 FSC-klagomål.docx", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 31213-2023 FSC-klagomål.docx", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="AB3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 49546-2025 FSC-klagomål mail.docx", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 31213-2023 FSC-klagomål mail.docx", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="AC3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 49546-2025 tillsynsbegäran.docx", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 31213-2023 tillsynsbegäran.docx", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="AD3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 49546-2025 tillsynsbegäran mail.docx", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 31213-2023 tillsynsbegäran mail.docx", "A 31213-2023")</f>
         <v/>
       </c>
     </row>
@@ -818,7 +813,7 @@
         <v>44903</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -907,7 +902,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 31213-2023</t>
+          <t>A 3253-2025</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -921,10 +916,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>45113</v>
+        <v>45679</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -936,17 +931,22 @@
           <t>YSTAD</t>
         </is>
       </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I5" t="n">
-        <v>6.5</v>
+        <v>2.5</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -961,7 +961,7 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -973,40 +973,40 @@
         <v>3</v>
       </c>
       <c r="U5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>Skogsveronika
-Skärmstarr</t>
+          <t>Lönnlav
+Strävlosta</t>
         </is>
       </c>
       <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 31213-2023 artfynd.xlsx", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 3253-2025 artfynd.xlsx", "A 3253-2025")</f>
         <v/>
       </c>
       <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 31213-2023 karta.png", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 3253-2025 karta.png", "A 3253-2025")</f>
         <v/>
       </c>
       <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 31213-2023 georefererad karta.tif", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 3253-2025 georefererad karta.tif", "A 3253-2025")</f>
         <v/>
       </c>
       <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 31213-2023 FSC-klagomål.docx", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 3253-2025 FSC-klagomål.docx", "A 3253-2025")</f>
         <v/>
       </c>
       <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 31213-2023 FSC-klagomål mail.docx", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 3253-2025 FSC-klagomål mail.docx", "A 3253-2025")</f>
         <v/>
       </c>
       <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 31213-2023 tillsynsbegäran.docx", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 3253-2025 tillsynsbegäran.docx", "A 3253-2025")</f>
         <v/>
       </c>
       <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 31213-2023 tillsynsbegäran mail.docx", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 3253-2025 tillsynsbegäran mail.docx", "A 3253-2025")</f>
         <v/>
       </c>
     </row>
@@ -1030,7 +1030,7 @@
         <v>44756</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 13766-2023</t>
+          <t>A 61558-2023</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1128,14 +1128,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45007</v>
+        <v>45265</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1147,11 +1147,16 @@
           <t>YSTAD</t>
         </is>
       </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I7" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -1163,7 +1168,7 @@
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1172,10 +1177,10 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1188,42 +1193,42 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 13766-2023 artfynd.xlsx", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 61558-2023 artfynd.xlsx", "A 61558-2023")</f>
         <v/>
       </c>
       <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 13766-2023 karta.png", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 61558-2023 karta.png", "A 61558-2023")</f>
         <v/>
       </c>
       <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 13766-2023 georefererad karta.tif", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 61558-2023 georefererad karta.tif", "A 61558-2023")</f>
         <v/>
       </c>
       <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 13766-2023 FSC-klagomål.docx", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 61558-2023 FSC-klagomål.docx", "A 61558-2023")</f>
         <v/>
       </c>
       <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 13766-2023 FSC-klagomål mail.docx", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 61558-2023 FSC-klagomål mail.docx", "A 61558-2023")</f>
         <v/>
       </c>
       <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 13766-2023 tillsynsbegäran.docx", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 61558-2023 tillsynsbegäran.docx", "A 61558-2023")</f>
         <v/>
       </c>
       <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 13766-2023 tillsynsbegäran mail.docx", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 61558-2023 tillsynsbegäran mail.docx", "A 61558-2023")</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 61558-2023</t>
+          <t>A 49549-2025</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1237,10 +1242,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45265</v>
+        <v>45939</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1252,19 +1257,14 @@
           <t>YSTAD</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I8" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -1273,7 +1273,7 @@
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1282,10 +1282,10 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1294,39 +1294,39 @@
         <v>1</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Noshornsoxe</t>
         </is>
       </c>
       <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 61558-2023 artfynd.xlsx", "A 61558-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 49549-2025 artfynd.xlsx", "A 49549-2025")</f>
         <v/>
       </c>
       <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 61558-2023 karta.png", "A 61558-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 49549-2025 karta.png", "A 49549-2025")</f>
         <v/>
       </c>
       <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 61558-2023 georefererad karta.tif", "A 61558-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 49549-2025 georefererad karta.tif", "A 49549-2025")</f>
         <v/>
       </c>
       <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 61558-2023 FSC-klagomål.docx", "A 61558-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 49549-2025 FSC-klagomål.docx", "A 49549-2025")</f>
         <v/>
       </c>
       <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 61558-2023 FSC-klagomål mail.docx", "A 61558-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 49549-2025 FSC-klagomål mail.docx", "A 49549-2025")</f>
         <v/>
       </c>
       <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 61558-2023 tillsynsbegäran.docx", "A 61558-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 49549-2025 tillsynsbegäran.docx", "A 49549-2025")</f>
         <v/>
       </c>
       <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 61558-2023 tillsynsbegäran mail.docx", "A 61558-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 49549-2025 tillsynsbegäran mail.docx", "A 49549-2025")</f>
         <v/>
       </c>
     </row>
@@ -1350,7 +1350,7 @@
         <v>45939</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 49549-2025</t>
+          <t>A 34341-2024</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1452,10 +1452,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45939</v>
+        <v>45525</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1467,17 +1467,22 @@
           <t>YSTAD</t>
         </is>
       </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I10" t="n">
-        <v>0.5</v>
+        <v>14.4</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -1492,7 +1497,7 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -1508,42 +1513,42 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>Noshornsoxe</t>
+          <t>Desmeknopp</t>
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 49549-2025 artfynd.xlsx", "A 49549-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 34341-2024 artfynd.xlsx", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 49549-2025 karta.png", "A 49549-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 34341-2024 karta.png", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 49549-2025 georefererad karta.tif", "A 49549-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 34341-2024 georefererad karta.tif", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 49549-2025 FSC-klagomål.docx", "A 49549-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 34341-2024 FSC-klagomål.docx", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 49549-2025 FSC-klagomål mail.docx", "A 49549-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 34341-2024 FSC-klagomål mail.docx", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 49549-2025 tillsynsbegäran.docx", "A 49549-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 34341-2024 tillsynsbegäran.docx", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 49549-2025 tillsynsbegäran mail.docx", "A 49549-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 34341-2024 tillsynsbegäran mail.docx", "A 34341-2024")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 60891-2024</t>
+          <t>A 13766-2023</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1553,14 +1558,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45644</v>
+        <v>45007</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1573,7 +1578,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>16.1</v>
+        <v>0.9</v>
       </c>
       <c r="J11" t="n">
         <v>1</v>
@@ -1613,42 +1618,42 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Lövgroda</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 60891-2024 artfynd.xlsx", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 13766-2023 artfynd.xlsx", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 60891-2024 karta.png", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 13766-2023 karta.png", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 60891-2024 georefererad karta.tif", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 13766-2023 georefererad karta.tif", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 60891-2024 FSC-klagomål.docx", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 13766-2023 FSC-klagomål.docx", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 60891-2024 FSC-klagomål mail.docx", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 13766-2023 FSC-klagomål mail.docx", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 60891-2024 tillsynsbegäran.docx", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 13766-2023 tillsynsbegäran.docx", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 60891-2024 tillsynsbegäran mail.docx", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 13766-2023 tillsynsbegäran mail.docx", "A 13766-2023")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 34341-2024</t>
+          <t>A 60891-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1662,10 +1667,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45525</v>
+        <v>45644</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1677,22 +1682,17 @@
           <t>YSTAD</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I12" t="n">
-        <v>14.4</v>
+        <v>16.1</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -1707,7 +1707,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -1719,39 +1719,39 @@
         <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Desmeknopp</t>
+          <t>Lövgroda</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 34341-2024 artfynd.xlsx", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 60891-2024 artfynd.xlsx", "A 60891-2024")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 34341-2024 karta.png", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 60891-2024 karta.png", "A 60891-2024")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 34341-2024 georefererad karta.tif", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 60891-2024 georefererad karta.tif", "A 60891-2024")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 34341-2024 FSC-klagomål.docx", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 60891-2024 FSC-klagomål.docx", "A 60891-2024")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 34341-2024 FSC-klagomål mail.docx", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 60891-2024 FSC-klagomål mail.docx", "A 60891-2024")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 34341-2024 tillsynsbegäran.docx", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 60891-2024 tillsynsbegäran.docx", "A 60891-2024")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 34341-2024 tillsynsbegäran mail.docx", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 60891-2024 tillsynsbegäran mail.docx", "A 60891-2024")</f>
         <v/>
       </c>
     </row>
@@ -1775,7 +1775,7 @@
         <v>44617</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 32596-2024</t>
+          <t>A 40417-2022</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1845,10 +1845,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45513</v>
+        <v>44823</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1904,7 +1904,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 40417-2022</t>
+          <t>A 34302-2024</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1918,10 +1918,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44823</v>
+        <v>45524</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1977,7 +1977,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 49536-2025</t>
+          <t>A 60803-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1991,10 +1991,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45939</v>
+        <v>45260</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2050,7 +2050,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 18090-2022</t>
+          <t>A 49536-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2060,14 +2060,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44684</v>
+        <v>45939</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2080,7 +2080,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>4.9</v>
+        <v>1.5</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2123,7 +2123,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 60803-2023</t>
+          <t>A 38631-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2137,10 +2137,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45260</v>
+        <v>45162</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1.6</v>
+        <v>0.8</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2196,7 +2196,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 27578-2026</t>
+          <t>A 18090-2022</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2206,14 +2206,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46190</v>
+        <v>44684</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>6.6</v>
+        <v>4.9</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2269,7 +2269,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 38631-2023</t>
+          <t>A 22195-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2283,10 +2283,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45162</v>
+        <v>45069</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2298,8 +2298,13 @@
           <t>YSTAD</t>
         </is>
       </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I20" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2342,7 +2347,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 22195-2023</t>
+          <t>A 27578-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2356,10 +2361,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45069</v>
+        <v>46190</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2371,13 +2376,8 @@
           <t>YSTAD</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I21" t="n">
-        <v>1.1</v>
+        <v>6.6</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2420,7 +2420,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 34302-2024</t>
+          <t>A 32596-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2434,10 +2434,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45524</v>
+        <v>45513</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2450,7 +2450,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.9</v>
+        <v>2.6</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>

--- a/Översikt YSTAD.xlsx
+++ b/Översikt YSTAD.xlsx
@@ -584,7 +584,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A 49546-2025</t>
+          <t>A 3253-2025</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>45939</v>
+        <v>45679</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -613,14 +613,19 @@
           <t>YSTAD</t>
         </is>
       </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I2" t="n">
-        <v>4.4</v>
+        <v>2.5</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -629,7 +634,7 @@
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -638,59 +643,59 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
         <v>2</v>
       </c>
       <c r="T2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
-          <t>Skogsalm
-Igelkottsröksvamp</t>
+          <t>Lönnlav
+Strävlosta</t>
         </is>
       </c>
       <c r="W2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 49546-2025 artfynd.xlsx", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 3253-2025 artfynd.xlsx", "A 3253-2025")</f>
         <v/>
       </c>
       <c r="X2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 49546-2025 karta.png", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 3253-2025 karta.png", "A 3253-2025")</f>
         <v/>
       </c>
       <c r="Y2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 49546-2025 georefererad karta.tif", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 3253-2025 georefererad karta.tif", "A 3253-2025")</f>
         <v/>
       </c>
       <c r="AA2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 49546-2025 FSC-klagomål.docx", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 3253-2025 FSC-klagomål.docx", "A 3253-2025")</f>
         <v/>
       </c>
       <c r="AB2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 49546-2025 FSC-klagomål mail.docx", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 3253-2025 FSC-klagomål mail.docx", "A 3253-2025")</f>
         <v/>
       </c>
       <c r="AC2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 49546-2025 tillsynsbegäran.docx", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 3253-2025 tillsynsbegäran.docx", "A 3253-2025")</f>
         <v/>
       </c>
       <c r="AD2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 49546-2025 tillsynsbegäran mail.docx", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 3253-2025 tillsynsbegäran mail.docx", "A 3253-2025")</f>
         <v/>
       </c>
     </row>
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 31213-2023</t>
+          <t>A 49546-2025</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -704,10 +709,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>45113</v>
+        <v>45939</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -720,22 +725,22 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>6.5</v>
+        <v>4.4</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -747,49 +752,49 @@
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S3" t="n">
         <v>2</v>
       </c>
       <c r="T3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
-          <t>Skogsveronika
-Skärmstarr</t>
+          <t>Skogsalm
+Igelkottsröksvamp</t>
         </is>
       </c>
       <c r="W3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 31213-2023 artfynd.xlsx", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 49546-2025 artfynd.xlsx", "A 49546-2025")</f>
         <v/>
       </c>
       <c r="X3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 31213-2023 karta.png", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 49546-2025 karta.png", "A 49546-2025")</f>
         <v/>
       </c>
       <c r="Y3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 31213-2023 georefererad karta.tif", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 49546-2025 georefererad karta.tif", "A 49546-2025")</f>
         <v/>
       </c>
       <c r="AA3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 31213-2023 FSC-klagomål.docx", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 49546-2025 FSC-klagomål.docx", "A 49546-2025")</f>
         <v/>
       </c>
       <c r="AB3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 31213-2023 FSC-klagomål mail.docx", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 49546-2025 FSC-klagomål mail.docx", "A 49546-2025")</f>
         <v/>
       </c>
       <c r="AC3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 31213-2023 tillsynsbegäran.docx", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 49546-2025 tillsynsbegäran.docx", "A 49546-2025")</f>
         <v/>
       </c>
       <c r="AD3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 31213-2023 tillsynsbegäran mail.docx", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 49546-2025 tillsynsbegäran mail.docx", "A 49546-2025")</f>
         <v/>
       </c>
     </row>
@@ -813,7 +818,7 @@
         <v>44903</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -902,7 +907,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 3253-2025</t>
+          <t>A 31213-2023</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -916,10 +921,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>45679</v>
+        <v>45113</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -931,22 +936,17 @@
           <t>YSTAD</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I5" t="n">
-        <v>2.5</v>
+        <v>6.5</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -961,7 +961,7 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -973,40 +973,40 @@
         <v>3</v>
       </c>
       <c r="U5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>Lönnlav
-Strävlosta</t>
+          <t>Skogsveronika
+Skärmstarr</t>
         </is>
       </c>
       <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 3253-2025 artfynd.xlsx", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 31213-2023 artfynd.xlsx", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 3253-2025 karta.png", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 31213-2023 karta.png", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 3253-2025 georefererad karta.tif", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 31213-2023 georefererad karta.tif", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 3253-2025 FSC-klagomål.docx", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 31213-2023 FSC-klagomål.docx", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 3253-2025 FSC-klagomål mail.docx", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 31213-2023 FSC-klagomål mail.docx", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 3253-2025 tillsynsbegäran.docx", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 31213-2023 tillsynsbegäran.docx", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 3253-2025 tillsynsbegäran mail.docx", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 31213-2023 tillsynsbegäran mail.docx", "A 31213-2023")</f>
         <v/>
       </c>
     </row>
@@ -1030,7 +1030,7 @@
         <v>44756</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 61558-2023</t>
+          <t>A 13766-2023</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1128,14 +1128,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45265</v>
+        <v>45007</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1147,16 +1147,11 @@
           <t>YSTAD</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I7" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -1168,7 +1163,7 @@
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1177,10 +1172,10 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1193,42 +1188,42 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 61558-2023 artfynd.xlsx", "A 61558-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 13766-2023 artfynd.xlsx", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 61558-2023 karta.png", "A 61558-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 13766-2023 karta.png", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 61558-2023 georefererad karta.tif", "A 61558-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 13766-2023 georefererad karta.tif", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 61558-2023 FSC-klagomål.docx", "A 61558-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 13766-2023 FSC-klagomål.docx", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 61558-2023 FSC-klagomål mail.docx", "A 61558-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 13766-2023 FSC-klagomål mail.docx", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 61558-2023 tillsynsbegäran.docx", "A 61558-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 13766-2023 tillsynsbegäran.docx", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 61558-2023 tillsynsbegäran mail.docx", "A 61558-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 13766-2023 tillsynsbegäran mail.docx", "A 13766-2023")</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 49549-2025</t>
+          <t>A 61558-2023</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1242,10 +1237,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45939</v>
+        <v>45265</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1257,14 +1252,19 @@
           <t>YSTAD</t>
         </is>
       </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I8" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -1273,7 +1273,7 @@
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1282,10 +1282,10 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1294,39 +1294,39 @@
         <v>1</v>
       </c>
       <c r="U8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>Noshornsoxe</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 49549-2025 artfynd.xlsx", "A 49549-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 61558-2023 artfynd.xlsx", "A 61558-2023")</f>
         <v/>
       </c>
       <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 49549-2025 karta.png", "A 49549-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 61558-2023 karta.png", "A 61558-2023")</f>
         <v/>
       </c>
       <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 49549-2025 georefererad karta.tif", "A 49549-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 61558-2023 georefererad karta.tif", "A 61558-2023")</f>
         <v/>
       </c>
       <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 49549-2025 FSC-klagomål.docx", "A 49549-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 61558-2023 FSC-klagomål.docx", "A 61558-2023")</f>
         <v/>
       </c>
       <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 49549-2025 FSC-klagomål mail.docx", "A 49549-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 61558-2023 FSC-klagomål mail.docx", "A 61558-2023")</f>
         <v/>
       </c>
       <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 49549-2025 tillsynsbegäran.docx", "A 49549-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 61558-2023 tillsynsbegäran.docx", "A 61558-2023")</f>
         <v/>
       </c>
       <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 49549-2025 tillsynsbegäran mail.docx", "A 49549-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 61558-2023 tillsynsbegäran mail.docx", "A 61558-2023")</f>
         <v/>
       </c>
     </row>
@@ -1350,7 +1350,7 @@
         <v>45939</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 34341-2024</t>
+          <t>A 49549-2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1452,10 +1452,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45525</v>
+        <v>45939</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1467,22 +1467,17 @@
           <t>YSTAD</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I10" t="n">
-        <v>14.4</v>
+        <v>0.5</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -1497,7 +1492,7 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -1513,42 +1508,42 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>Desmeknopp</t>
+          <t>Noshornsoxe</t>
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 34341-2024 artfynd.xlsx", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 49549-2025 artfynd.xlsx", "A 49549-2025")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 34341-2024 karta.png", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 49549-2025 karta.png", "A 49549-2025")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 34341-2024 georefererad karta.tif", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 49549-2025 georefererad karta.tif", "A 49549-2025")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 34341-2024 FSC-klagomål.docx", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 49549-2025 FSC-klagomål.docx", "A 49549-2025")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 34341-2024 FSC-klagomål mail.docx", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 49549-2025 FSC-klagomål mail.docx", "A 49549-2025")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 34341-2024 tillsynsbegäran.docx", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 49549-2025 tillsynsbegäran.docx", "A 49549-2025")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 34341-2024 tillsynsbegäran mail.docx", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 49549-2025 tillsynsbegäran mail.docx", "A 49549-2025")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 13766-2023</t>
+          <t>A 60891-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1558,14 +1553,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45007</v>
+        <v>45644</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1578,7 +1573,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0.9</v>
+        <v>16.1</v>
       </c>
       <c r="J11" t="n">
         <v>1</v>
@@ -1618,42 +1613,42 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Lövgroda</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 13766-2023 artfynd.xlsx", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 60891-2024 artfynd.xlsx", "A 60891-2024")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 13766-2023 karta.png", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 60891-2024 karta.png", "A 60891-2024")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 13766-2023 georefererad karta.tif", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 60891-2024 georefererad karta.tif", "A 60891-2024")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 13766-2023 FSC-klagomål.docx", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 60891-2024 FSC-klagomål.docx", "A 60891-2024")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 13766-2023 FSC-klagomål mail.docx", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 60891-2024 FSC-klagomål mail.docx", "A 60891-2024")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 13766-2023 tillsynsbegäran.docx", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 60891-2024 tillsynsbegäran.docx", "A 60891-2024")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 13766-2023 tillsynsbegäran mail.docx", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 60891-2024 tillsynsbegäran mail.docx", "A 60891-2024")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 60891-2024</t>
+          <t>A 34341-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1667,10 +1662,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45644</v>
+        <v>45525</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1682,17 +1677,22 @@
           <t>YSTAD</t>
         </is>
       </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I12" t="n">
-        <v>16.1</v>
+        <v>14.4</v>
       </c>
       <c r="J12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -1707,7 +1707,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -1719,39 +1719,39 @@
         <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Lövgroda</t>
+          <t>Desmeknopp</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 60891-2024 artfynd.xlsx", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 34341-2024 artfynd.xlsx", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 60891-2024 karta.png", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 34341-2024 karta.png", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 60891-2024 georefererad karta.tif", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 34341-2024 georefererad karta.tif", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 60891-2024 FSC-klagomål.docx", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 34341-2024 FSC-klagomål.docx", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 60891-2024 FSC-klagomål mail.docx", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 34341-2024 FSC-klagomål mail.docx", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 60891-2024 tillsynsbegäran.docx", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 34341-2024 tillsynsbegäran.docx", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 60891-2024 tillsynsbegäran mail.docx", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 34341-2024 tillsynsbegäran mail.docx", "A 34341-2024")</f>
         <v/>
       </c>
     </row>
@@ -1775,7 +1775,7 @@
         <v>44617</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 40417-2022</t>
+          <t>A 32596-2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1845,10 +1845,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44823</v>
+        <v>45513</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1904,7 +1904,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 34302-2024</t>
+          <t>A 40417-2022</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1918,10 +1918,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45524</v>
+        <v>44823</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1977,7 +1977,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 60803-2023</t>
+          <t>A 18090-2022</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1987,14 +1987,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45260</v>
+        <v>44684</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.6</v>
+        <v>4.9</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2050,7 +2050,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 49536-2025</t>
+          <t>A 60803-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2064,10 +2064,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45939</v>
+        <v>45260</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2080,7 +2080,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2140,7 +2140,7 @@
         <v>45162</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2196,7 +2196,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 18090-2022</t>
+          <t>A 49536-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2206,14 +2206,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44684</v>
+        <v>45939</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>4.9</v>
+        <v>1.5</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2286,7 +2286,7 @@
         <v>45069</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2347,7 +2347,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 27578-2026</t>
+          <t>A 34302-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2361,10 +2361,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46190</v>
+        <v>45524</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>6.6</v>
+        <v>1.9</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2420,7 +2420,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 32596-2024</t>
+          <t>A 27578-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2434,10 +2434,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45513</v>
+        <v>46190</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2450,7 +2450,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>2.6</v>
+        <v>6.6</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>

--- a/Översikt YSTAD.xlsx
+++ b/Översikt YSTAD.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE22"/>
+  <dimension ref="A1:AE23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -584,7 +584,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A 3253-2025</t>
+          <t>A 31213-2023</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>45679</v>
+        <v>45113</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -613,22 +613,17 @@
           <t>YSTAD</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I2" t="n">
-        <v>2.5</v>
+        <v>6.5</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
@@ -643,7 +638,7 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -655,40 +650,40 @@
         <v>3</v>
       </c>
       <c r="U2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
-          <t>Lönnlav
-Strävlosta</t>
+          <t>Skogsveronika
+Skärmstarr</t>
         </is>
       </c>
       <c r="W2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 3253-2025 artfynd.xlsx", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 31213-2023 artfynd.xlsx", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="X2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 3253-2025 karta.png", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 31213-2023 karta.png", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="Y2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 3253-2025 georefererad karta.tif", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 31213-2023 georefererad karta.tif", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="AA2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 3253-2025 FSC-klagomål.docx", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 31213-2023 FSC-klagomål.docx", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="AB2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 3253-2025 FSC-klagomål mail.docx", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 31213-2023 FSC-klagomål mail.docx", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="AC2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 3253-2025 tillsynsbegäran.docx", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 31213-2023 tillsynsbegäran.docx", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="AD2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 3253-2025 tillsynsbegäran mail.docx", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 31213-2023 tillsynsbegäran mail.docx", "A 31213-2023")</f>
         <v/>
       </c>
     </row>
@@ -712,7 +707,7 @@
         <v>45939</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -801,7 +796,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 60295-2022</t>
+          <t>A 3253-2025</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -811,14 +806,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>44903</v>
+        <v>45679</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -830,14 +825,19 @@
           <t>YSTAD</t>
         </is>
       </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I4" t="n">
-        <v>1.1</v>
+        <v>2.5</v>
       </c>
       <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
         <v>2</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -864,50 +864,50 @@
         <v>2</v>
       </c>
       <c r="T4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="U4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>Klockgroda
-Ätlig groda</t>
+          <t>Lönnlav
+Strävlosta</t>
         </is>
       </c>
       <c r="W4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 60295-2022 artfynd.xlsx", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 3253-2025 artfynd.xlsx", "A 3253-2025")</f>
         <v/>
       </c>
       <c r="X4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 60295-2022 karta.png", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 3253-2025 karta.png", "A 3253-2025")</f>
         <v/>
       </c>
       <c r="Y4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 60295-2022 georefererad karta.tif", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 3253-2025 georefererad karta.tif", "A 3253-2025")</f>
         <v/>
       </c>
       <c r="AA4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 60295-2022 FSC-klagomål.docx", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 3253-2025 FSC-klagomål.docx", "A 3253-2025")</f>
         <v/>
       </c>
       <c r="AB4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 60295-2022 FSC-klagomål mail.docx", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 3253-2025 FSC-klagomål mail.docx", "A 3253-2025")</f>
         <v/>
       </c>
       <c r="AC4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 60295-2022 tillsynsbegäran.docx", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 3253-2025 tillsynsbegäran.docx", "A 3253-2025")</f>
         <v/>
       </c>
       <c r="AD4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 60295-2022 tillsynsbegäran mail.docx", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 3253-2025 tillsynsbegäran mail.docx", "A 3253-2025")</f>
         <v/>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 31213-2023</t>
+          <t>A 60295-2022</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -917,14 +917,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>45113</v>
+        <v>44903</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -937,16 +937,16 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>6.5</v>
+        <v>1.1</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -961,7 +961,7 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -970,43 +970,43 @@
         <v>2</v>
       </c>
       <c r="T5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="U5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>Skogsveronika
-Skärmstarr</t>
+          <t>Klockgroda
+Ätlig groda</t>
         </is>
       </c>
       <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 31213-2023 artfynd.xlsx", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 60295-2022 artfynd.xlsx", "A 60295-2022")</f>
         <v/>
       </c>
       <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 31213-2023 karta.png", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 60295-2022 karta.png", "A 60295-2022")</f>
         <v/>
       </c>
       <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 31213-2023 georefererad karta.tif", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 60295-2022 georefererad karta.tif", "A 60295-2022")</f>
         <v/>
       </c>
       <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 31213-2023 FSC-klagomål.docx", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 60295-2022 FSC-klagomål.docx", "A 60295-2022")</f>
         <v/>
       </c>
       <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 31213-2023 FSC-klagomål mail.docx", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 60295-2022 FSC-klagomål mail.docx", "A 60295-2022")</f>
         <v/>
       </c>
       <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 31213-2023 tillsynsbegäran.docx", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 60295-2022 tillsynsbegäran.docx", "A 60295-2022")</f>
         <v/>
       </c>
       <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 31213-2023 tillsynsbegäran mail.docx", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 60295-2022 tillsynsbegäran mail.docx", "A 60295-2022")</f>
         <v/>
       </c>
     </row>
@@ -1030,7 +1030,7 @@
         <v>44756</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 13766-2023</t>
+          <t>A 34341-2024</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1128,14 +1128,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45007</v>
+        <v>45525</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1147,17 +1147,22 @@
           <t>YSTAD</t>
         </is>
       </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I7" t="n">
-        <v>0.9</v>
+        <v>14.4</v>
       </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -1172,7 +1177,7 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1184,39 +1189,39 @@
         <v>1</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Desmeknopp</t>
         </is>
       </c>
       <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 13766-2023 artfynd.xlsx", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 34341-2024 artfynd.xlsx", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 13766-2023 karta.png", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 34341-2024 karta.png", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 13766-2023 georefererad karta.tif", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 34341-2024 georefererad karta.tif", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 13766-2023 FSC-klagomål.docx", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 34341-2024 FSC-klagomål.docx", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 13766-2023 FSC-klagomål mail.docx", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 34341-2024 FSC-klagomål mail.docx", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 13766-2023 tillsynsbegäran.docx", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 34341-2024 tillsynsbegäran.docx", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 13766-2023 tillsynsbegäran mail.docx", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 34341-2024 tillsynsbegäran mail.docx", "A 34341-2024")</f>
         <v/>
       </c>
     </row>
@@ -1240,7 +1245,7 @@
         <v>45265</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1333,7 +1338,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 49543-2025</t>
+          <t>A 49549-2025</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1350,7 +1355,7 @@
         <v>45939</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1363,16 +1368,16 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -1387,7 +1392,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -1396,49 +1401,49 @@
         <v>1</v>
       </c>
       <c r="T9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>Svartöra</t>
+          <t>Noshornsoxe</t>
         </is>
       </c>
       <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 49543-2025 artfynd.xlsx", "A 49543-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 49549-2025 artfynd.xlsx", "A 49549-2025")</f>
         <v/>
       </c>
       <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 49543-2025 karta.png", "A 49543-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 49549-2025 karta.png", "A 49549-2025")</f>
         <v/>
       </c>
       <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 49543-2025 georefererad karta.tif", "A 49543-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 49549-2025 georefererad karta.tif", "A 49549-2025")</f>
         <v/>
       </c>
       <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 49543-2025 FSC-klagomål.docx", "A 49543-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 49549-2025 FSC-klagomål.docx", "A 49549-2025")</f>
         <v/>
       </c>
       <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 49543-2025 FSC-klagomål mail.docx", "A 49543-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 49549-2025 FSC-klagomål mail.docx", "A 49549-2025")</f>
         <v/>
       </c>
       <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 49543-2025 tillsynsbegäran.docx", "A 49543-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 49549-2025 tillsynsbegäran.docx", "A 49549-2025")</f>
         <v/>
       </c>
       <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 49543-2025 tillsynsbegäran mail.docx", "A 49543-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 49549-2025 tillsynsbegäran mail.docx", "A 49549-2025")</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 49549-2025</t>
+          <t>A 49543-2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1455,7 +1460,7 @@
         <v>45939</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1468,16 +1473,16 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -1492,7 +1497,7 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -1501,49 +1506,49 @@
         <v>1</v>
       </c>
       <c r="T10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>Noshornsoxe</t>
+          <t>Svartöra</t>
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 49549-2025 artfynd.xlsx", "A 49549-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 49543-2025 artfynd.xlsx", "A 49543-2025")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 49549-2025 karta.png", "A 49549-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 49543-2025 karta.png", "A 49543-2025")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 49549-2025 georefererad karta.tif", "A 49549-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 49543-2025 georefererad karta.tif", "A 49543-2025")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 49549-2025 FSC-klagomål.docx", "A 49549-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 49543-2025 FSC-klagomål.docx", "A 49543-2025")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 49549-2025 FSC-klagomål mail.docx", "A 49549-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 49543-2025 FSC-klagomål mail.docx", "A 49543-2025")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 49549-2025 tillsynsbegäran.docx", "A 49549-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 49543-2025 tillsynsbegäran.docx", "A 49543-2025")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 49549-2025 tillsynsbegäran mail.docx", "A 49549-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 49543-2025 tillsynsbegäran mail.docx", "A 49543-2025")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 60891-2024</t>
+          <t>A 13766-2023</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1553,14 +1558,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45644</v>
+        <v>45007</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1573,7 +1578,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>16.1</v>
+        <v>0.9</v>
       </c>
       <c r="J11" t="n">
         <v>1</v>
@@ -1613,42 +1618,42 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Lövgroda</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 60891-2024 artfynd.xlsx", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 13766-2023 artfynd.xlsx", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 60891-2024 karta.png", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 13766-2023 karta.png", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 60891-2024 georefererad karta.tif", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 13766-2023 georefererad karta.tif", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 60891-2024 FSC-klagomål.docx", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 13766-2023 FSC-klagomål.docx", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 60891-2024 FSC-klagomål mail.docx", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 13766-2023 FSC-klagomål mail.docx", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 60891-2024 tillsynsbegäran.docx", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 13766-2023 tillsynsbegäran.docx", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 60891-2024 tillsynsbegäran mail.docx", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 13766-2023 tillsynsbegäran mail.docx", "A 13766-2023")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 34341-2024</t>
+          <t>A 60891-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1662,10 +1667,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45525</v>
+        <v>45644</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1677,22 +1682,17 @@
           <t>YSTAD</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I12" t="n">
-        <v>14.4</v>
+        <v>16.1</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -1707,7 +1707,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -1719,39 +1719,39 @@
         <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Desmeknopp</t>
+          <t>Lövgroda</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 34341-2024 artfynd.xlsx", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 60891-2024 artfynd.xlsx", "A 60891-2024")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 34341-2024 karta.png", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 60891-2024 karta.png", "A 60891-2024")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 34341-2024 georefererad karta.tif", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 60891-2024 georefererad karta.tif", "A 60891-2024")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 34341-2024 FSC-klagomål.docx", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 60891-2024 FSC-klagomål.docx", "A 60891-2024")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 34341-2024 FSC-klagomål mail.docx", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 60891-2024 FSC-klagomål mail.docx", "A 60891-2024")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 34341-2024 tillsynsbegäran.docx", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 60891-2024 tillsynsbegäran.docx", "A 60891-2024")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 34341-2024 tillsynsbegäran mail.docx", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 60891-2024 tillsynsbegäran mail.docx", "A 60891-2024")</f>
         <v/>
       </c>
     </row>
@@ -1775,7 +1775,7 @@
         <v>44617</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 32596-2024</t>
+          <t>A 40417-2022</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1845,10 +1845,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45513</v>
+        <v>44823</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1904,7 +1904,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 40417-2022</t>
+          <t>A 34302-2024</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1918,10 +1918,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44823</v>
+        <v>45524</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1977,7 +1977,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 18090-2022</t>
+          <t>A 32596-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1987,14 +1987,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44684</v>
+        <v>45513</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>4.9</v>
+        <v>2.6</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2067,7 +2067,7 @@
         <v>45260</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2123,7 +2123,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 38631-2023</t>
+          <t>A 49536-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2137,10 +2137,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45162</v>
+        <v>45939</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2196,7 +2196,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 49536-2025</t>
+          <t>A 38631-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2210,10 +2210,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45939</v>
+        <v>45162</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2269,7 +2269,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 22195-2023</t>
+          <t>A 18090-2022</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2279,14 +2279,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45069</v>
+        <v>44684</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2298,13 +2298,8 @@
           <t>YSTAD</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I20" t="n">
-        <v>1.1</v>
+        <v>4.9</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2347,7 +2342,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 34302-2024</t>
+          <t>A 38413-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2361,10 +2356,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45524</v>
+        <v>46282</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2377,7 +2372,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.9</v>
+        <v>0.6</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2417,7 +2412,7 @@
       </c>
       <c r="V21" s="2" t="inlineStr"/>
     </row>
-    <row r="22">
+    <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
           <t>A 27578-2026</t>
@@ -2437,7 +2432,7 @@
         <v>46190</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2489,6 +2484,84 @@
         <v>0</v>
       </c>
       <c r="V22" s="2" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>A 22195-2023</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D23" s="1" t="n">
+        <v>45069</v>
+      </c>
+      <c r="E23" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>YSTAD</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt YSTAD.xlsx
+++ b/Översikt YSTAD.xlsx
@@ -584,7 +584,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A 31213-2023</t>
+          <t>A 3253-2025</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>45113</v>
+        <v>45679</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -613,17 +613,22 @@
           <t>YSTAD</t>
         </is>
       </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I2" t="n">
-        <v>6.5</v>
+        <v>2.5</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
@@ -638,7 +643,7 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -650,47 +655,47 @@
         <v>3</v>
       </c>
       <c r="U2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
-          <t>Skogsveronika
-Skärmstarr</t>
+          <t>Lönnlav
+Strävlosta</t>
         </is>
       </c>
       <c r="W2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 31213-2023 artfynd.xlsx", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 3253-2025 artfynd.xlsx", "A 3253-2025")</f>
         <v/>
       </c>
       <c r="X2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 31213-2023 karta.png", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 3253-2025 karta.png", "A 3253-2025")</f>
         <v/>
       </c>
       <c r="Y2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 31213-2023 georefererad karta.tif", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 3253-2025 georefererad karta.tif", "A 3253-2025")</f>
         <v/>
       </c>
       <c r="AA2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 31213-2023 FSC-klagomål.docx", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 3253-2025 FSC-klagomål.docx", "A 3253-2025")</f>
         <v/>
       </c>
       <c r="AB2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 31213-2023 FSC-klagomål mail.docx", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 3253-2025 FSC-klagomål mail.docx", "A 3253-2025")</f>
         <v/>
       </c>
       <c r="AC2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 31213-2023 tillsynsbegäran.docx", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 3253-2025 tillsynsbegäran.docx", "A 3253-2025")</f>
         <v/>
       </c>
       <c r="AD2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 31213-2023 tillsynsbegäran mail.docx", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 3253-2025 tillsynsbegäran mail.docx", "A 3253-2025")</f>
         <v/>
       </c>
     </row>
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 49546-2025</t>
+          <t>A 60295-2022</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -700,14 +705,14 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>45939</v>
+        <v>44903</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -720,13 +725,13 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>4.4</v>
+        <v>1.1</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -735,7 +740,7 @@
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -744,59 +749,59 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
         <v>2</v>
       </c>
       <c r="T3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
-          <t>Skogsalm
-Igelkottsröksvamp</t>
+          <t>Klockgroda
+Ätlig groda</t>
         </is>
       </c>
       <c r="W3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 49546-2025 artfynd.xlsx", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 60295-2022 artfynd.xlsx", "A 60295-2022")</f>
         <v/>
       </c>
       <c r="X3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 49546-2025 karta.png", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 60295-2022 karta.png", "A 60295-2022")</f>
         <v/>
       </c>
       <c r="Y3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 49546-2025 georefererad karta.tif", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 60295-2022 georefererad karta.tif", "A 60295-2022")</f>
         <v/>
       </c>
       <c r="AA3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 49546-2025 FSC-klagomål.docx", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 60295-2022 FSC-klagomål.docx", "A 60295-2022")</f>
         <v/>
       </c>
       <c r="AB3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 49546-2025 FSC-klagomål mail.docx", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 60295-2022 FSC-klagomål mail.docx", "A 60295-2022")</f>
         <v/>
       </c>
       <c r="AC3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 49546-2025 tillsynsbegäran.docx", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 60295-2022 tillsynsbegäran.docx", "A 60295-2022")</f>
         <v/>
       </c>
       <c r="AD3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 49546-2025 tillsynsbegäran mail.docx", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 60295-2022 tillsynsbegäran mail.docx", "A 60295-2022")</f>
         <v/>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 3253-2025</t>
+          <t>A 31213-2023</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -810,10 +815,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45679</v>
+        <v>45113</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -825,22 +830,17 @@
           <t>YSTAD</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I4" t="n">
-        <v>2.5</v>
+        <v>6.5</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -855,7 +855,7 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -867,47 +867,47 @@
         <v>3</v>
       </c>
       <c r="U4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>Lönnlav
-Strävlosta</t>
+          <t>Skogsveronika
+Skärmstarr</t>
         </is>
       </c>
       <c r="W4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 3253-2025 artfynd.xlsx", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 31213-2023 artfynd.xlsx", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="X4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 3253-2025 karta.png", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 31213-2023 karta.png", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="Y4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 3253-2025 georefererad karta.tif", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 31213-2023 georefererad karta.tif", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="AA4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 3253-2025 FSC-klagomål.docx", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 31213-2023 FSC-klagomål.docx", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="AB4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 3253-2025 FSC-klagomål mail.docx", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 31213-2023 FSC-klagomål mail.docx", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="AC4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 3253-2025 tillsynsbegäran.docx", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 31213-2023 tillsynsbegäran.docx", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="AD4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 3253-2025 tillsynsbegäran mail.docx", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 31213-2023 tillsynsbegäran mail.docx", "A 31213-2023")</f>
         <v/>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 60295-2022</t>
+          <t>A 49546-2025</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -917,14 +917,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>44903</v>
+        <v>45939</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -937,13 +937,13 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>1.1</v>
+        <v>4.4</v>
       </c>
       <c r="J5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -952,7 +952,7 @@
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -961,52 +961,52 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S5" t="n">
         <v>2</v>
       </c>
       <c r="T5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="U5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>Klockgroda
-Ätlig groda</t>
+          <t>Skogsalm
+Igelkottsröksvamp</t>
         </is>
       </c>
       <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 60295-2022 artfynd.xlsx", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 49546-2025 artfynd.xlsx", "A 49546-2025")</f>
         <v/>
       </c>
       <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 60295-2022 karta.png", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 49546-2025 karta.png", "A 49546-2025")</f>
         <v/>
       </c>
       <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 60295-2022 georefererad karta.tif", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 49546-2025 georefererad karta.tif", "A 49546-2025")</f>
         <v/>
       </c>
       <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 60295-2022 FSC-klagomål.docx", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 49546-2025 FSC-klagomål.docx", "A 49546-2025")</f>
         <v/>
       </c>
       <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 60295-2022 FSC-klagomål mail.docx", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 49546-2025 FSC-klagomål mail.docx", "A 49546-2025")</f>
         <v/>
       </c>
       <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 60295-2022 tillsynsbegäran.docx", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 49546-2025 tillsynsbegäran.docx", "A 49546-2025")</f>
         <v/>
       </c>
       <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 60295-2022 tillsynsbegäran mail.docx", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 49546-2025 tillsynsbegäran mail.docx", "A 49546-2025")</f>
         <v/>
       </c>
     </row>
@@ -1030,7 +1030,7 @@
         <v>44756</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 34341-2024</t>
+          <t>A 13766-2023</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1128,14 +1128,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45525</v>
+        <v>45007</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1147,22 +1147,17 @@
           <t>YSTAD</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I7" t="n">
-        <v>14.4</v>
+        <v>0.9</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -1177,7 +1172,7 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1189,39 +1184,39 @@
         <v>1</v>
       </c>
       <c r="U7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>Desmeknopp</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 34341-2024 artfynd.xlsx", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 13766-2023 artfynd.xlsx", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 34341-2024 karta.png", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 13766-2023 karta.png", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 34341-2024 georefererad karta.tif", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 13766-2023 georefererad karta.tif", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 34341-2024 FSC-klagomål.docx", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 13766-2023 FSC-klagomål.docx", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 34341-2024 FSC-klagomål mail.docx", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 13766-2023 FSC-klagomål mail.docx", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 34341-2024 tillsynsbegäran.docx", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 13766-2023 tillsynsbegäran.docx", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 34341-2024 tillsynsbegäran mail.docx", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 13766-2023 tillsynsbegäran mail.docx", "A 13766-2023")</f>
         <v/>
       </c>
     </row>
@@ -1245,7 +1240,7 @@
         <v>45265</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1338,7 +1333,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 49549-2025</t>
+          <t>A 49543-2025</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1355,7 +1350,7 @@
         <v>45939</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1368,16 +1363,16 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -1392,7 +1387,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -1401,49 +1396,49 @@
         <v>1</v>
       </c>
       <c r="T9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>Noshornsoxe</t>
+          <t>Svartöra</t>
         </is>
       </c>
       <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 49549-2025 artfynd.xlsx", "A 49549-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 49543-2025 artfynd.xlsx", "A 49543-2025")</f>
         <v/>
       </c>
       <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 49549-2025 karta.png", "A 49549-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 49543-2025 karta.png", "A 49543-2025")</f>
         <v/>
       </c>
       <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 49549-2025 georefererad karta.tif", "A 49549-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 49543-2025 georefererad karta.tif", "A 49543-2025")</f>
         <v/>
       </c>
       <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 49549-2025 FSC-klagomål.docx", "A 49549-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 49543-2025 FSC-klagomål.docx", "A 49543-2025")</f>
         <v/>
       </c>
       <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 49549-2025 FSC-klagomål mail.docx", "A 49549-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 49543-2025 FSC-klagomål mail.docx", "A 49543-2025")</f>
         <v/>
       </c>
       <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 49549-2025 tillsynsbegäran.docx", "A 49549-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 49543-2025 tillsynsbegäran.docx", "A 49543-2025")</f>
         <v/>
       </c>
       <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 49549-2025 tillsynsbegäran mail.docx", "A 49549-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 49543-2025 tillsynsbegäran mail.docx", "A 49543-2025")</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 49543-2025</t>
+          <t>A 60891-2024</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1457,10 +1452,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45939</v>
+        <v>45644</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1473,16 +1468,16 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1.4</v>
+        <v>16.1</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -1497,7 +1492,7 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -1506,49 +1501,49 @@
         <v>1</v>
       </c>
       <c r="T10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U10" t="n">
         <v>0</v>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>Svartöra</t>
+          <t>Lövgroda</t>
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 49543-2025 artfynd.xlsx", "A 49543-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 60891-2024 artfynd.xlsx", "A 60891-2024")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 49543-2025 karta.png", "A 49543-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 60891-2024 karta.png", "A 60891-2024")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 49543-2025 georefererad karta.tif", "A 49543-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 60891-2024 georefererad karta.tif", "A 60891-2024")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 49543-2025 FSC-klagomål.docx", "A 49543-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 60891-2024 FSC-klagomål.docx", "A 60891-2024")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 49543-2025 FSC-klagomål mail.docx", "A 49543-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 60891-2024 FSC-klagomål mail.docx", "A 60891-2024")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 49543-2025 tillsynsbegäran.docx", "A 49543-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 60891-2024 tillsynsbegäran.docx", "A 60891-2024")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 49543-2025 tillsynsbegäran mail.docx", "A 49543-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 60891-2024 tillsynsbegäran mail.docx", "A 60891-2024")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 13766-2023</t>
+          <t>A 49549-2025</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1558,14 +1553,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45007</v>
+        <v>45939</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1578,13 +1573,13 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -1614,46 +1609,46 @@
         <v>1</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Noshornsoxe</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 13766-2023 artfynd.xlsx", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 49549-2025 artfynd.xlsx", "A 49549-2025")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 13766-2023 karta.png", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 49549-2025 karta.png", "A 49549-2025")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 13766-2023 georefererad karta.tif", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 49549-2025 georefererad karta.tif", "A 49549-2025")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 13766-2023 FSC-klagomål.docx", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 49549-2025 FSC-klagomål.docx", "A 49549-2025")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 13766-2023 FSC-klagomål mail.docx", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 49549-2025 FSC-klagomål mail.docx", "A 49549-2025")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 13766-2023 tillsynsbegäran.docx", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 49549-2025 tillsynsbegäran.docx", "A 49549-2025")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 13766-2023 tillsynsbegäran mail.docx", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 49549-2025 tillsynsbegäran mail.docx", "A 49549-2025")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 60891-2024</t>
+          <t>A 34341-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1667,10 +1662,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45644</v>
+        <v>45525</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1682,17 +1677,22 @@
           <t>YSTAD</t>
         </is>
       </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I12" t="n">
-        <v>16.1</v>
+        <v>14.4</v>
       </c>
       <c r="J12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -1707,7 +1707,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -1719,39 +1719,39 @@
         <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Lövgroda</t>
+          <t>Desmeknopp</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 60891-2024 artfynd.xlsx", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 34341-2024 artfynd.xlsx", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 60891-2024 karta.png", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 34341-2024 karta.png", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 60891-2024 georefererad karta.tif", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 34341-2024 georefererad karta.tif", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 60891-2024 FSC-klagomål.docx", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 34341-2024 FSC-klagomål.docx", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 60891-2024 FSC-klagomål mail.docx", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 34341-2024 FSC-klagomål mail.docx", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 60891-2024 tillsynsbegäran.docx", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 34341-2024 tillsynsbegäran.docx", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 60891-2024 tillsynsbegäran mail.docx", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 34341-2024 tillsynsbegäran mail.docx", "A 34341-2024")</f>
         <v/>
       </c>
     </row>
@@ -1775,7 +1775,7 @@
         <v>44617</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         <v>44823</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1904,7 +1904,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 34302-2024</t>
+          <t>A 18090-2022</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1914,14 +1914,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45524</v>
+        <v>44684</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.9</v>
+        <v>4.9</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1977,7 +1977,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 32596-2024</t>
+          <t>A 60803-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1991,10 +1991,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45513</v>
+        <v>45260</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>2.6</v>
+        <v>1.6</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2050,7 +2050,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 60803-2023</t>
+          <t>A 49536-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2064,10 +2064,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45260</v>
+        <v>45939</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2080,7 +2080,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2123,7 +2123,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 49536-2025</t>
+          <t>A 38631-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2137,10 +2137,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45939</v>
+        <v>45162</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2196,7 +2196,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 38631-2023</t>
+          <t>A 22195-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2210,10 +2210,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45162</v>
+        <v>45069</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2225,8 +2225,13 @@
           <t>YSTAD</t>
         </is>
       </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I19" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2269,7 +2274,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 18090-2022</t>
+          <t>A 34302-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2279,14 +2284,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44684</v>
+        <v>45524</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2299,7 +2304,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>4.9</v>
+        <v>1.9</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2342,7 +2347,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 38413-2026</t>
+          <t>A 27578-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2356,10 +2361,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46282</v>
+        <v>46190</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2372,7 +2377,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.6</v>
+        <v>6.6</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2415,7 +2420,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 27578-2026</t>
+          <t>A 38413-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2429,10 +2434,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46190</v>
+        <v>46282</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2445,7 +2450,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>6.6</v>
+        <v>0.6</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2488,7 +2493,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 22195-2023</t>
+          <t>A 32596-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2502,10 +2507,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45069</v>
+        <v>45513</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2517,13 +2522,8 @@
           <t>YSTAD</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I23" t="n">
-        <v>1.1</v>
+        <v>2.6</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>

--- a/Översikt YSTAD.xlsx
+++ b/Översikt YSTAD.xlsx
@@ -601,7 +601,7 @@
         <v>45679</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -712,7 +712,7 @@
         <v>44903</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -818,7 +818,7 @@
         <v>45113</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -924,7 +924,7 @@
         <v>45939</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>44756</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1135,7 +1135,7 @@
         <v>45007</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>45265</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
         <v>45939</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         <v>45644</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
         <v>45939</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1665,7 +1665,7 @@
         <v>45525</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1775,7 +1775,7 @@
         <v>44617</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         <v>44823</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
         <v>44684</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1994,7 +1994,7 @@
         <v>45260</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2067,7 +2067,7 @@
         <v>45939</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2140,7 +2140,7 @@
         <v>45162</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>45069</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2291,7 +2291,7 @@
         <v>45524</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         <v>46190</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
         <v>46282</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2510,7 +2510,7 @@
         <v>45513</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>

--- a/Översikt YSTAD.xlsx
+++ b/Översikt YSTAD.xlsx
@@ -601,7 +601,7 @@
         <v>45679</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -695,7 +695,7 @@
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 60295-2022</t>
+          <t>A 49546-2025</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -705,14 +705,14 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>44903</v>
+        <v>45939</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -725,13 +725,13 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>1.1</v>
+        <v>4.4</v>
       </c>
       <c r="J3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -740,7 +740,7 @@
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -749,59 +749,59 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S3" t="n">
         <v>2</v>
       </c>
       <c r="T3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="U3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
-          <t>Klockgroda
-Ätlig groda</t>
+          <t>Skogsalm
+Igelkottsröksvamp</t>
         </is>
       </c>
       <c r="W3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 60295-2022 artfynd.xlsx", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 49546-2025 artfynd.xlsx", "A 49546-2025")</f>
         <v/>
       </c>
       <c r="X3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 60295-2022 karta.png", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 49546-2025 karta.png", "A 49546-2025")</f>
         <v/>
       </c>
       <c r="Y3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 60295-2022 georefererad karta.tif", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 49546-2025 georefererad karta.tif", "A 49546-2025")</f>
         <v/>
       </c>
       <c r="AA3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 60295-2022 FSC-klagomål.docx", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 49546-2025 FSC-klagomål.docx", "A 49546-2025")</f>
         <v/>
       </c>
       <c r="AB3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 60295-2022 FSC-klagomål mail.docx", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 49546-2025 FSC-klagomål mail.docx", "A 49546-2025")</f>
         <v/>
       </c>
       <c r="AC3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 60295-2022 tillsynsbegäran.docx", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 49546-2025 tillsynsbegäran.docx", "A 49546-2025")</f>
         <v/>
       </c>
       <c r="AD3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 60295-2022 tillsynsbegäran mail.docx", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 49546-2025 tillsynsbegäran mail.docx", "A 49546-2025")</f>
         <v/>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 31213-2023</t>
+          <t>A 60295-2022</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -811,14 +811,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45113</v>
+        <v>44903</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -831,16 +831,16 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>6.5</v>
+        <v>1.1</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -855,7 +855,7 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -864,50 +864,50 @@
         <v>2</v>
       </c>
       <c r="T4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="U4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>Skogsveronika
-Skärmstarr</t>
+          <t>Klockgroda
+Ätlig groda</t>
         </is>
       </c>
       <c r="W4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 31213-2023 artfynd.xlsx", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 60295-2022 artfynd.xlsx", "A 60295-2022")</f>
         <v/>
       </c>
       <c r="X4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 31213-2023 karta.png", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 60295-2022 karta.png", "A 60295-2022")</f>
         <v/>
       </c>
       <c r="Y4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 31213-2023 georefererad karta.tif", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 60295-2022 georefererad karta.tif", "A 60295-2022")</f>
         <v/>
       </c>
       <c r="AA4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 31213-2023 FSC-klagomål.docx", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 60295-2022 FSC-klagomål.docx", "A 60295-2022")</f>
         <v/>
       </c>
       <c r="AB4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 31213-2023 FSC-klagomål mail.docx", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 60295-2022 FSC-klagomål mail.docx", "A 60295-2022")</f>
         <v/>
       </c>
       <c r="AC4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 31213-2023 tillsynsbegäran.docx", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 60295-2022 tillsynsbegäran.docx", "A 60295-2022")</f>
         <v/>
       </c>
       <c r="AD4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 31213-2023 tillsynsbegäran mail.docx", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 60295-2022 tillsynsbegäran mail.docx", "A 60295-2022")</f>
         <v/>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 49546-2025</t>
+          <t>A 31213-2023</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -921,10 +921,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>45939</v>
+        <v>45113</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -937,22 +937,22 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>4.4</v>
+        <v>6.5</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -964,49 +964,49 @@
         <v>1</v>
       </c>
       <c r="R5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
         <v>2</v>
       </c>
       <c r="T5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>Skogsalm
-Igelkottsröksvamp</t>
+          <t>Skogsveronika
+Skärmstarr</t>
         </is>
       </c>
       <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 49546-2025 artfynd.xlsx", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 31213-2023 artfynd.xlsx", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 49546-2025 karta.png", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 31213-2023 karta.png", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 49546-2025 georefererad karta.tif", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 31213-2023 georefererad karta.tif", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 49546-2025 FSC-klagomål.docx", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 31213-2023 FSC-klagomål.docx", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 49546-2025 FSC-klagomål mail.docx", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 31213-2023 FSC-klagomål mail.docx", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 49546-2025 tillsynsbegäran.docx", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 31213-2023 tillsynsbegäran.docx", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 49546-2025 tillsynsbegäran mail.docx", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 31213-2023 tillsynsbegäran mail.docx", "A 31213-2023")</f>
         <v/>
       </c>
     </row>
@@ -1030,7 +1030,7 @@
         <v>44756</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1135,7 +1135,7 @@
         <v>45007</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>45265</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
         <v>45939</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         <v>45644</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
         <v>45939</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1665,7 +1665,7 @@
         <v>45525</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1775,7 +1775,7 @@
         <v>44617</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         <v>44823</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1904,7 +1904,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 18090-2022</t>
+          <t>A 49536-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1914,14 +1914,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44684</v>
+        <v>45939</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>4.9</v>
+        <v>1.5</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1977,7 +1977,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 60803-2023</t>
+          <t>A 18090-2022</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1987,14 +1987,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45260</v>
+        <v>44684</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.6</v>
+        <v>4.9</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2050,7 +2050,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 49536-2025</t>
+          <t>A 60803-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2064,10 +2064,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45939</v>
+        <v>45260</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2080,7 +2080,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2140,7 +2140,7 @@
         <v>45162</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>45069</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2274,7 +2274,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 34302-2024</t>
+          <t>A 38413-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2288,10 +2288,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45524</v>
+        <v>46282</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.9</v>
+        <v>0.6</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2347,7 +2347,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 27578-2026</t>
+          <t>A 34302-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2361,10 +2361,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46190</v>
+        <v>45524</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>6.6</v>
+        <v>1.9</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2420,7 +2420,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 38413-2026</t>
+          <t>A 27578-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2434,10 +2434,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46282</v>
+        <v>46190</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2450,7 +2450,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.6</v>
+        <v>6.6</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2510,7 +2510,7 @@
         <v>45513</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>

--- a/Översikt YSTAD.xlsx
+++ b/Översikt YSTAD.xlsx
@@ -601,7 +601,7 @@
         <v>45679</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -695,7 +695,7 @@
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 49546-2025</t>
+          <t>A 31213-2023</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -709,10 +709,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>45939</v>
+        <v>45113</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -725,22 +725,22 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>4.4</v>
+        <v>6.5</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -752,49 +752,49 @@
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
         <v>2</v>
       </c>
       <c r="T3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
-          <t>Skogsalm
-Igelkottsröksvamp</t>
+          <t>Skogsveronika
+Skärmstarr</t>
         </is>
       </c>
       <c r="W3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 49546-2025 artfynd.xlsx", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 31213-2023 artfynd.xlsx", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="X3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 49546-2025 karta.png", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 31213-2023 karta.png", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="Y3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 49546-2025 georefererad karta.tif", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 31213-2023 georefererad karta.tif", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="AA3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 49546-2025 FSC-klagomål.docx", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 31213-2023 FSC-klagomål.docx", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="AB3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 49546-2025 FSC-klagomål mail.docx", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 31213-2023 FSC-klagomål mail.docx", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="AC3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 49546-2025 tillsynsbegäran.docx", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 31213-2023 tillsynsbegäran.docx", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="AD3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 49546-2025 tillsynsbegäran mail.docx", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 31213-2023 tillsynsbegäran mail.docx", "A 31213-2023")</f>
         <v/>
       </c>
     </row>
@@ -818,7 +818,7 @@
         <v>44903</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 31213-2023</t>
+          <t>A 49546-2025</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -921,10 +921,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>45113</v>
+        <v>45939</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -937,22 +937,22 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>6.5</v>
+        <v>4.4</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -964,49 +964,49 @@
         <v>1</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S5" t="n">
         <v>2</v>
       </c>
       <c r="T5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>Skogsveronika
-Skärmstarr</t>
+          <t>Skogsalm
+Igelkottsröksvamp</t>
         </is>
       </c>
       <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 31213-2023 artfynd.xlsx", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 49546-2025 artfynd.xlsx", "A 49546-2025")</f>
         <v/>
       </c>
       <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 31213-2023 karta.png", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 49546-2025 karta.png", "A 49546-2025")</f>
         <v/>
       </c>
       <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 31213-2023 georefererad karta.tif", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 49546-2025 georefererad karta.tif", "A 49546-2025")</f>
         <v/>
       </c>
       <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 31213-2023 FSC-klagomål.docx", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 49546-2025 FSC-klagomål.docx", "A 49546-2025")</f>
         <v/>
       </c>
       <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 31213-2023 FSC-klagomål mail.docx", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 49546-2025 FSC-klagomål mail.docx", "A 49546-2025")</f>
         <v/>
       </c>
       <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 31213-2023 tillsynsbegäran.docx", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 49546-2025 tillsynsbegäran.docx", "A 49546-2025")</f>
         <v/>
       </c>
       <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 31213-2023 tillsynsbegäran mail.docx", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 49546-2025 tillsynsbegäran mail.docx", "A 49546-2025")</f>
         <v/>
       </c>
     </row>
@@ -1030,7 +1030,7 @@
         <v>44756</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 13766-2023</t>
+          <t>A 61558-2023</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1128,14 +1128,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45007</v>
+        <v>45265</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1147,11 +1147,16 @@
           <t>YSTAD</t>
         </is>
       </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I7" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -1163,7 +1168,7 @@
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1172,10 +1177,10 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1188,42 +1193,42 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 13766-2023 artfynd.xlsx", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 61558-2023 artfynd.xlsx", "A 61558-2023")</f>
         <v/>
       </c>
       <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 13766-2023 karta.png", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 61558-2023 karta.png", "A 61558-2023")</f>
         <v/>
       </c>
       <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 13766-2023 georefererad karta.tif", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 61558-2023 georefererad karta.tif", "A 61558-2023")</f>
         <v/>
       </c>
       <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 13766-2023 FSC-klagomål.docx", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 61558-2023 FSC-klagomål.docx", "A 61558-2023")</f>
         <v/>
       </c>
       <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 13766-2023 FSC-klagomål mail.docx", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 61558-2023 FSC-klagomål mail.docx", "A 61558-2023")</f>
         <v/>
       </c>
       <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 13766-2023 tillsynsbegäran.docx", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 61558-2023 tillsynsbegäran.docx", "A 61558-2023")</f>
         <v/>
       </c>
       <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 13766-2023 tillsynsbegäran mail.docx", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 61558-2023 tillsynsbegäran mail.docx", "A 61558-2023")</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 61558-2023</t>
+          <t>A 13766-2023</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1233,14 +1238,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45265</v>
+        <v>45007</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1252,16 +1257,11 @@
           <t>YSTAD</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I8" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -1273,7 +1273,7 @@
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1282,10 +1282,10 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1298,42 +1298,42 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 61558-2023 artfynd.xlsx", "A 61558-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 13766-2023 artfynd.xlsx", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 61558-2023 karta.png", "A 61558-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 13766-2023 karta.png", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 61558-2023 georefererad karta.tif", "A 61558-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 13766-2023 georefererad karta.tif", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 61558-2023 FSC-klagomål.docx", "A 61558-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 13766-2023 FSC-klagomål.docx", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 61558-2023 FSC-klagomål mail.docx", "A 61558-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 13766-2023 FSC-klagomål mail.docx", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 61558-2023 tillsynsbegäran.docx", "A 61558-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 13766-2023 tillsynsbegäran.docx", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 61558-2023 tillsynsbegäran mail.docx", "A 61558-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 13766-2023 tillsynsbegäran mail.docx", "A 13766-2023")</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 49543-2025</t>
+          <t>A 60891-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1347,10 +1347,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45939</v>
+        <v>45644</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1363,16 +1363,16 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1.4</v>
+        <v>16.1</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -1387,7 +1387,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -1396,49 +1396,49 @@
         <v>1</v>
       </c>
       <c r="T9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>Svartöra</t>
+          <t>Lövgroda</t>
         </is>
       </c>
       <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 49543-2025 artfynd.xlsx", "A 49543-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 60891-2024 artfynd.xlsx", "A 60891-2024")</f>
         <v/>
       </c>
       <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 49543-2025 karta.png", "A 49543-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 60891-2024 karta.png", "A 60891-2024")</f>
         <v/>
       </c>
       <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 49543-2025 georefererad karta.tif", "A 49543-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 60891-2024 georefererad karta.tif", "A 60891-2024")</f>
         <v/>
       </c>
       <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 49543-2025 FSC-klagomål.docx", "A 49543-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 60891-2024 FSC-klagomål.docx", "A 60891-2024")</f>
         <v/>
       </c>
       <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 49543-2025 FSC-klagomål mail.docx", "A 49543-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 60891-2024 FSC-klagomål mail.docx", "A 60891-2024")</f>
         <v/>
       </c>
       <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 49543-2025 tillsynsbegäran.docx", "A 49543-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 60891-2024 tillsynsbegäran.docx", "A 60891-2024")</f>
         <v/>
       </c>
       <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 49543-2025 tillsynsbegäran mail.docx", "A 49543-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 60891-2024 tillsynsbegäran mail.docx", "A 60891-2024")</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 60891-2024</t>
+          <t>A 49543-2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1452,10 +1452,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45644</v>
+        <v>45939</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1468,16 +1468,16 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>16.1</v>
+        <v>1.4</v>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -1492,7 +1492,7 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -1501,49 +1501,49 @@
         <v>1</v>
       </c>
       <c r="T10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U10" t="n">
         <v>0</v>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>Lövgroda</t>
+          <t>Svartöra</t>
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 60891-2024 artfynd.xlsx", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 49543-2025 artfynd.xlsx", "A 49543-2025")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 60891-2024 karta.png", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 49543-2025 karta.png", "A 49543-2025")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 60891-2024 georefererad karta.tif", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 49543-2025 georefererad karta.tif", "A 49543-2025")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 60891-2024 FSC-klagomål.docx", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 49543-2025 FSC-klagomål.docx", "A 49543-2025")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 60891-2024 FSC-klagomål mail.docx", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 49543-2025 FSC-klagomål mail.docx", "A 49543-2025")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 60891-2024 tillsynsbegäran.docx", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 49543-2025 tillsynsbegäran.docx", "A 49543-2025")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 60891-2024 tillsynsbegäran mail.docx", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 49543-2025 tillsynsbegäran mail.docx", "A 49543-2025")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 49549-2025</t>
+          <t>A 34341-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1557,10 +1557,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45939</v>
+        <v>45525</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1572,17 +1572,22 @@
           <t>YSTAD</t>
         </is>
       </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I11" t="n">
-        <v>0.5</v>
+        <v>14.4</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -1597,7 +1602,7 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -1613,42 +1618,42 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Noshornsoxe</t>
+          <t>Desmeknopp</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 49549-2025 artfynd.xlsx", "A 49549-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 34341-2024 artfynd.xlsx", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 49549-2025 karta.png", "A 49549-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 34341-2024 karta.png", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 49549-2025 georefererad karta.tif", "A 49549-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 34341-2024 georefererad karta.tif", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 49549-2025 FSC-klagomål.docx", "A 49549-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 34341-2024 FSC-klagomål.docx", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 49549-2025 FSC-klagomål mail.docx", "A 49549-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 34341-2024 FSC-klagomål mail.docx", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 49549-2025 tillsynsbegäran.docx", "A 49549-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 34341-2024 tillsynsbegäran.docx", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 49549-2025 tillsynsbegäran mail.docx", "A 49549-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 34341-2024 tillsynsbegäran mail.docx", "A 34341-2024")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 34341-2024</t>
+          <t>A 49549-2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1662,10 +1667,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45525</v>
+        <v>45939</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1677,22 +1682,17 @@
           <t>YSTAD</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I12" t="n">
-        <v>14.4</v>
+        <v>0.5</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -1707,7 +1707,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -1723,35 +1723,35 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Desmeknopp</t>
+          <t>Noshornsoxe</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 34341-2024 artfynd.xlsx", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 49549-2025 artfynd.xlsx", "A 49549-2025")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 34341-2024 karta.png", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 49549-2025 karta.png", "A 49549-2025")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 34341-2024 georefererad karta.tif", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 49549-2025 georefererad karta.tif", "A 49549-2025")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 34341-2024 FSC-klagomål.docx", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 49549-2025 FSC-klagomål.docx", "A 49549-2025")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 34341-2024 FSC-klagomål mail.docx", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 49549-2025 FSC-klagomål mail.docx", "A 49549-2025")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 34341-2024 tillsynsbegäran.docx", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 49549-2025 tillsynsbegäran.docx", "A 49549-2025")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 34341-2024 tillsynsbegäran mail.docx", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 49549-2025 tillsynsbegäran mail.docx", "A 49549-2025")</f>
         <v/>
       </c>
     </row>
@@ -1775,7 +1775,7 @@
         <v>44617</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         <v>44823</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1904,7 +1904,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 49536-2025</t>
+          <t>A 34302-2024</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1918,10 +1918,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45939</v>
+        <v>45524</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1977,7 +1977,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 18090-2022</t>
+          <t>A 60803-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1987,14 +1987,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44684</v>
+        <v>45260</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>4.9</v>
+        <v>1.6</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2050,7 +2050,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 60803-2023</t>
+          <t>A 38631-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2064,10 +2064,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45260</v>
+        <v>45162</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2080,7 +2080,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1.6</v>
+        <v>0.8</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2123,7 +2123,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 38631-2023</t>
+          <t>A 18090-2022</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2133,14 +2133,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45162</v>
+        <v>44684</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.8</v>
+        <v>4.9</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2196,7 +2196,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 22195-2023</t>
+          <t>A 27578-2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2210,10 +2210,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45069</v>
+        <v>46190</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2225,13 +2225,8 @@
           <t>YSTAD</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I19" t="n">
-        <v>1.1</v>
+        <v>6.6</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2274,7 +2269,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 38413-2026</t>
+          <t>A 32596-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2288,10 +2283,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46282</v>
+        <v>45513</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2304,7 +2299,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.6</v>
+        <v>2.6</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2347,7 +2342,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 34302-2024</t>
+          <t>A 22195-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2361,10 +2356,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45524</v>
+        <v>45069</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2376,8 +2371,13 @@
           <t>YSTAD</t>
         </is>
       </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I21" t="n">
-        <v>1.9</v>
+        <v>1.1</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2420,7 +2420,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 27578-2026</t>
+          <t>A 49536-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2434,10 +2434,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46190</v>
+        <v>45939</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2450,7 +2450,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>6.6</v>
+        <v>1.5</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2493,7 +2493,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 32596-2024</t>
+          <t>A 38413-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2507,10 +2507,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45513</v>
+        <v>46282</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2523,7 +2523,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>2.6</v>
+        <v>0.6</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>

--- a/Översikt YSTAD.xlsx
+++ b/Översikt YSTAD.xlsx
@@ -601,7 +601,7 @@
         <v>45679</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -695,7 +695,7 @@
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 31213-2023</t>
+          <t>A 49546-2025</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -709,10 +709,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>45113</v>
+        <v>45939</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -725,22 +725,22 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>6.5</v>
+        <v>4.4</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -752,49 +752,49 @@
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S3" t="n">
         <v>2</v>
       </c>
       <c r="T3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
-          <t>Skogsveronika
-Skärmstarr</t>
+          <t>Skogsalm
+Igelkottsröksvamp</t>
         </is>
       </c>
       <c r="W3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 31213-2023 artfynd.xlsx", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 49546-2025 artfynd.xlsx", "A 49546-2025")</f>
         <v/>
       </c>
       <c r="X3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 31213-2023 karta.png", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 49546-2025 karta.png", "A 49546-2025")</f>
         <v/>
       </c>
       <c r="Y3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 31213-2023 georefererad karta.tif", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 49546-2025 georefererad karta.tif", "A 49546-2025")</f>
         <v/>
       </c>
       <c r="AA3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 31213-2023 FSC-klagomål.docx", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 49546-2025 FSC-klagomål.docx", "A 49546-2025")</f>
         <v/>
       </c>
       <c r="AB3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 31213-2023 FSC-klagomål mail.docx", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 49546-2025 FSC-klagomål mail.docx", "A 49546-2025")</f>
         <v/>
       </c>
       <c r="AC3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 31213-2023 tillsynsbegäran.docx", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 49546-2025 tillsynsbegäran.docx", "A 49546-2025")</f>
         <v/>
       </c>
       <c r="AD3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 31213-2023 tillsynsbegäran mail.docx", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 49546-2025 tillsynsbegäran mail.docx", "A 49546-2025")</f>
         <v/>
       </c>
     </row>
@@ -818,7 +818,7 @@
         <v>44903</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 49546-2025</t>
+          <t>A 31213-2023</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -921,10 +921,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>45939</v>
+        <v>45113</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -937,22 +937,22 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>4.4</v>
+        <v>6.5</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -964,49 +964,49 @@
         <v>1</v>
       </c>
       <c r="R5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
         <v>2</v>
       </c>
       <c r="T5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>Skogsalm
-Igelkottsröksvamp</t>
+          <t>Skogsveronika
+Skärmstarr</t>
         </is>
       </c>
       <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 49546-2025 artfynd.xlsx", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 31213-2023 artfynd.xlsx", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 49546-2025 karta.png", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 31213-2023 karta.png", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 49546-2025 georefererad karta.tif", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 31213-2023 georefererad karta.tif", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 49546-2025 FSC-klagomål.docx", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 31213-2023 FSC-klagomål.docx", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 49546-2025 FSC-klagomål mail.docx", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 31213-2023 FSC-klagomål mail.docx", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 49546-2025 tillsynsbegäran.docx", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 31213-2023 tillsynsbegäran.docx", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 49546-2025 tillsynsbegäran mail.docx", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 31213-2023 tillsynsbegäran mail.docx", "A 31213-2023")</f>
         <v/>
       </c>
     </row>
@@ -1030,7 +1030,7 @@
         <v>44756</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 61558-2023</t>
+          <t>A 13766-2023</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1128,14 +1128,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45265</v>
+        <v>45007</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1147,16 +1147,11 @@
           <t>YSTAD</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I7" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -1168,7 +1163,7 @@
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1177,10 +1172,10 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1193,42 +1188,42 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 61558-2023 artfynd.xlsx", "A 61558-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 13766-2023 artfynd.xlsx", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 61558-2023 karta.png", "A 61558-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 13766-2023 karta.png", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 61558-2023 georefererad karta.tif", "A 61558-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 13766-2023 georefererad karta.tif", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 61558-2023 FSC-klagomål.docx", "A 61558-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 13766-2023 FSC-klagomål.docx", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 61558-2023 FSC-klagomål mail.docx", "A 61558-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 13766-2023 FSC-klagomål mail.docx", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 61558-2023 tillsynsbegäran.docx", "A 61558-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 13766-2023 tillsynsbegäran.docx", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 61558-2023 tillsynsbegäran mail.docx", "A 61558-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 13766-2023 tillsynsbegäran mail.docx", "A 13766-2023")</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 13766-2023</t>
+          <t>A 61558-2023</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1238,14 +1233,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45007</v>
+        <v>45265</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1257,11 +1252,16 @@
           <t>YSTAD</t>
         </is>
       </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I8" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -1273,7 +1273,7 @@
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1282,10 +1282,10 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1298,42 +1298,42 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 13766-2023 artfynd.xlsx", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 61558-2023 artfynd.xlsx", "A 61558-2023")</f>
         <v/>
       </c>
       <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 13766-2023 karta.png", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 61558-2023 karta.png", "A 61558-2023")</f>
         <v/>
       </c>
       <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 13766-2023 georefererad karta.tif", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 61558-2023 georefererad karta.tif", "A 61558-2023")</f>
         <v/>
       </c>
       <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 13766-2023 FSC-klagomål.docx", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 61558-2023 FSC-klagomål.docx", "A 61558-2023")</f>
         <v/>
       </c>
       <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 13766-2023 FSC-klagomål mail.docx", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 61558-2023 FSC-klagomål mail.docx", "A 61558-2023")</f>
         <v/>
       </c>
       <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 13766-2023 tillsynsbegäran.docx", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 61558-2023 tillsynsbegäran.docx", "A 61558-2023")</f>
         <v/>
       </c>
       <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 13766-2023 tillsynsbegäran mail.docx", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 61558-2023 tillsynsbegäran mail.docx", "A 61558-2023")</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 60891-2024</t>
+          <t>A 49543-2025</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1347,10 +1347,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45644</v>
+        <v>45939</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1363,16 +1363,16 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>16.1</v>
+        <v>1.4</v>
       </c>
       <c r="J9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -1387,7 +1387,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -1396,49 +1396,49 @@
         <v>1</v>
       </c>
       <c r="T9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>Lövgroda</t>
+          <t>Svartöra</t>
         </is>
       </c>
       <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 60891-2024 artfynd.xlsx", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 49543-2025 artfynd.xlsx", "A 49543-2025")</f>
         <v/>
       </c>
       <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 60891-2024 karta.png", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 49543-2025 karta.png", "A 49543-2025")</f>
         <v/>
       </c>
       <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 60891-2024 georefererad karta.tif", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 49543-2025 georefererad karta.tif", "A 49543-2025")</f>
         <v/>
       </c>
       <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 60891-2024 FSC-klagomål.docx", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 49543-2025 FSC-klagomål.docx", "A 49543-2025")</f>
         <v/>
       </c>
       <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 60891-2024 FSC-klagomål mail.docx", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 49543-2025 FSC-klagomål mail.docx", "A 49543-2025")</f>
         <v/>
       </c>
       <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 60891-2024 tillsynsbegäran.docx", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 49543-2025 tillsynsbegäran.docx", "A 49543-2025")</f>
         <v/>
       </c>
       <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 60891-2024 tillsynsbegäran mail.docx", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 49543-2025 tillsynsbegäran mail.docx", "A 49543-2025")</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 49543-2025</t>
+          <t>A 60891-2024</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1452,10 +1452,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45939</v>
+        <v>45644</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1468,16 +1468,16 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1.4</v>
+        <v>16.1</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -1492,7 +1492,7 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -1501,49 +1501,49 @@
         <v>1</v>
       </c>
       <c r="T10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U10" t="n">
         <v>0</v>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>Svartöra</t>
+          <t>Lövgroda</t>
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 49543-2025 artfynd.xlsx", "A 49543-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 60891-2024 artfynd.xlsx", "A 60891-2024")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 49543-2025 karta.png", "A 49543-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 60891-2024 karta.png", "A 60891-2024")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 49543-2025 georefererad karta.tif", "A 49543-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 60891-2024 georefererad karta.tif", "A 60891-2024")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 49543-2025 FSC-klagomål.docx", "A 49543-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 60891-2024 FSC-klagomål.docx", "A 60891-2024")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 49543-2025 FSC-klagomål mail.docx", "A 49543-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 60891-2024 FSC-klagomål mail.docx", "A 60891-2024")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 49543-2025 tillsynsbegäran.docx", "A 49543-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 60891-2024 tillsynsbegäran.docx", "A 60891-2024")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 49543-2025 tillsynsbegäran mail.docx", "A 49543-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 60891-2024 tillsynsbegäran mail.docx", "A 60891-2024")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 34341-2024</t>
+          <t>A 49549-2025</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1557,10 +1557,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45525</v>
+        <v>45939</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1572,22 +1572,17 @@
           <t>YSTAD</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I11" t="n">
-        <v>14.4</v>
+        <v>0.5</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -1602,7 +1597,7 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -1618,42 +1613,42 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Desmeknopp</t>
+          <t>Noshornsoxe</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 34341-2024 artfynd.xlsx", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 49549-2025 artfynd.xlsx", "A 49549-2025")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 34341-2024 karta.png", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 49549-2025 karta.png", "A 49549-2025")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 34341-2024 georefererad karta.tif", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 49549-2025 georefererad karta.tif", "A 49549-2025")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 34341-2024 FSC-klagomål.docx", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 49549-2025 FSC-klagomål.docx", "A 49549-2025")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 34341-2024 FSC-klagomål mail.docx", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 49549-2025 FSC-klagomål mail.docx", "A 49549-2025")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 34341-2024 tillsynsbegäran.docx", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 49549-2025 tillsynsbegäran.docx", "A 49549-2025")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 34341-2024 tillsynsbegäran mail.docx", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 49549-2025 tillsynsbegäran mail.docx", "A 49549-2025")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 49549-2025</t>
+          <t>A 34341-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1667,10 +1662,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45939</v>
+        <v>45525</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1682,17 +1677,22 @@
           <t>YSTAD</t>
         </is>
       </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I12" t="n">
-        <v>0.5</v>
+        <v>14.4</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -1707,7 +1707,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -1723,35 +1723,35 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Noshornsoxe</t>
+          <t>Desmeknopp</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 49549-2025 artfynd.xlsx", "A 49549-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 34341-2024 artfynd.xlsx", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 49549-2025 karta.png", "A 49549-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 34341-2024 karta.png", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 49549-2025 georefererad karta.tif", "A 49549-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 34341-2024 georefererad karta.tif", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 49549-2025 FSC-klagomål.docx", "A 49549-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 34341-2024 FSC-klagomål.docx", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 49549-2025 FSC-klagomål mail.docx", "A 49549-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 34341-2024 FSC-klagomål mail.docx", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 49549-2025 tillsynsbegäran.docx", "A 49549-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 34341-2024 tillsynsbegäran.docx", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 49549-2025 tillsynsbegäran mail.docx", "A 49549-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 34341-2024 tillsynsbegäran mail.docx", "A 34341-2024")</f>
         <v/>
       </c>
     </row>
@@ -1775,7 +1775,7 @@
         <v>44617</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         <v>44823</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1904,7 +1904,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 34302-2024</t>
+          <t>A 18090-2022</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1914,14 +1914,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45524</v>
+        <v>44684</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.9</v>
+        <v>4.9</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1994,7 +1994,7 @@
         <v>45260</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2050,7 +2050,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 38631-2023</t>
+          <t>A 49536-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2064,10 +2064,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45162</v>
+        <v>45939</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2080,7 +2080,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2123,7 +2123,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 18090-2022</t>
+          <t>A 38631-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2133,14 +2133,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44684</v>
+        <v>45162</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>4.9</v>
+        <v>0.8</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2196,7 +2196,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 27578-2026</t>
+          <t>A 22195-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2210,10 +2210,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46190</v>
+        <v>45069</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2225,8 +2225,13 @@
           <t>YSTAD</t>
         </is>
       </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I19" t="n">
-        <v>6.6</v>
+        <v>1.1</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2269,7 +2274,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 32596-2024</t>
+          <t>A 34302-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2283,10 +2288,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45513</v>
+        <v>45524</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2299,7 +2304,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>2.6</v>
+        <v>1.9</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2342,7 +2347,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 22195-2023</t>
+          <t>A 38413-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2356,10 +2361,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45069</v>
+        <v>46282</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2371,13 +2376,8 @@
           <t>YSTAD</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I21" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2420,7 +2420,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 49536-2025</t>
+          <t>A 27578-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2434,10 +2434,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45939</v>
+        <v>46190</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2450,7 +2450,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.5</v>
+        <v>6.6</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2493,7 +2493,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 38413-2026</t>
+          <t>A 32596-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2507,10 +2507,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46282</v>
+        <v>45513</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2523,7 +2523,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.6</v>
+        <v>2.6</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>

--- a/Översikt YSTAD.xlsx
+++ b/Översikt YSTAD.xlsx
@@ -584,7 +584,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A 3253-2025</t>
+          <t>A 31213-2023</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>45679</v>
+        <v>45113</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -613,22 +613,17 @@
           <t>YSTAD</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I2" t="n">
-        <v>2.5</v>
+        <v>6.5</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
@@ -643,7 +638,7 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -655,40 +650,40 @@
         <v>3</v>
       </c>
       <c r="U2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
-          <t>Lönnlav
-Strävlosta</t>
+          <t>Skogsveronika
+Skärmstarr</t>
         </is>
       </c>
       <c r="W2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 3253-2025 artfynd.xlsx", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 31213-2023 artfynd.xlsx", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="X2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 3253-2025 karta.png", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 31213-2023 karta.png", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="Y2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 3253-2025 georefererad karta.tif", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 31213-2023 georefererad karta.tif", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="AA2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 3253-2025 FSC-klagomål.docx", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 31213-2023 FSC-klagomål.docx", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="AB2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 3253-2025 FSC-klagomål mail.docx", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 31213-2023 FSC-klagomål mail.docx", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="AC2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 3253-2025 tillsynsbegäran.docx", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 31213-2023 tillsynsbegäran.docx", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="AD2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 3253-2025 tillsynsbegäran mail.docx", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 31213-2023 tillsynsbegäran mail.docx", "A 31213-2023")</f>
         <v/>
       </c>
     </row>
@@ -712,7 +707,7 @@
         <v>45939</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -801,7 +796,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 60295-2022</t>
+          <t>A 3253-2025</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -811,14 +806,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>44903</v>
+        <v>45679</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -830,14 +825,19 @@
           <t>YSTAD</t>
         </is>
       </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I4" t="n">
-        <v>1.1</v>
+        <v>2.5</v>
       </c>
       <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
         <v>2</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -864,50 +864,50 @@
         <v>2</v>
       </c>
       <c r="T4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="U4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>Klockgroda
-Ätlig groda</t>
+          <t>Lönnlav
+Strävlosta</t>
         </is>
       </c>
       <c r="W4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 60295-2022 artfynd.xlsx", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 3253-2025 artfynd.xlsx", "A 3253-2025")</f>
         <v/>
       </c>
       <c r="X4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 60295-2022 karta.png", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 3253-2025 karta.png", "A 3253-2025")</f>
         <v/>
       </c>
       <c r="Y4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 60295-2022 georefererad karta.tif", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 3253-2025 georefererad karta.tif", "A 3253-2025")</f>
         <v/>
       </c>
       <c r="AA4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 60295-2022 FSC-klagomål.docx", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 3253-2025 FSC-klagomål.docx", "A 3253-2025")</f>
         <v/>
       </c>
       <c r="AB4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 60295-2022 FSC-klagomål mail.docx", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 3253-2025 FSC-klagomål mail.docx", "A 3253-2025")</f>
         <v/>
       </c>
       <c r="AC4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 60295-2022 tillsynsbegäran.docx", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 3253-2025 tillsynsbegäran.docx", "A 3253-2025")</f>
         <v/>
       </c>
       <c r="AD4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 60295-2022 tillsynsbegäran mail.docx", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 3253-2025 tillsynsbegäran mail.docx", "A 3253-2025")</f>
         <v/>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 31213-2023</t>
+          <t>A 60295-2022</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -917,14 +917,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>45113</v>
+        <v>44903</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -937,16 +937,16 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>6.5</v>
+        <v>1.1</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -961,7 +961,7 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -970,43 +970,43 @@
         <v>2</v>
       </c>
       <c r="T5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="U5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>Skogsveronika
-Skärmstarr</t>
+          <t>Klockgroda
+Ätlig groda</t>
         </is>
       </c>
       <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 31213-2023 artfynd.xlsx", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 60295-2022 artfynd.xlsx", "A 60295-2022")</f>
         <v/>
       </c>
       <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 31213-2023 karta.png", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 60295-2022 karta.png", "A 60295-2022")</f>
         <v/>
       </c>
       <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 31213-2023 georefererad karta.tif", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 60295-2022 georefererad karta.tif", "A 60295-2022")</f>
         <v/>
       </c>
       <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 31213-2023 FSC-klagomål.docx", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 60295-2022 FSC-klagomål.docx", "A 60295-2022")</f>
         <v/>
       </c>
       <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 31213-2023 FSC-klagomål mail.docx", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 60295-2022 FSC-klagomål mail.docx", "A 60295-2022")</f>
         <v/>
       </c>
       <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 31213-2023 tillsynsbegäran.docx", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 60295-2022 tillsynsbegäran.docx", "A 60295-2022")</f>
         <v/>
       </c>
       <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 31213-2023 tillsynsbegäran mail.docx", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 60295-2022 tillsynsbegäran mail.docx", "A 60295-2022")</f>
         <v/>
       </c>
     </row>
@@ -1030,7 +1030,7 @@
         <v>44756</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 13766-2023</t>
+          <t>A 61558-2023</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1128,14 +1128,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45007</v>
+        <v>45265</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1147,11 +1147,16 @@
           <t>YSTAD</t>
         </is>
       </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I7" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -1163,7 +1168,7 @@
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1172,10 +1177,10 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1188,42 +1193,42 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 13766-2023 artfynd.xlsx", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 61558-2023 artfynd.xlsx", "A 61558-2023")</f>
         <v/>
       </c>
       <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 13766-2023 karta.png", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 61558-2023 karta.png", "A 61558-2023")</f>
         <v/>
       </c>
       <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 13766-2023 georefererad karta.tif", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 61558-2023 georefererad karta.tif", "A 61558-2023")</f>
         <v/>
       </c>
       <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 13766-2023 FSC-klagomål.docx", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 61558-2023 FSC-klagomål.docx", "A 61558-2023")</f>
         <v/>
       </c>
       <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 13766-2023 FSC-klagomål mail.docx", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 61558-2023 FSC-klagomål mail.docx", "A 61558-2023")</f>
         <v/>
       </c>
       <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 13766-2023 tillsynsbegäran.docx", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 61558-2023 tillsynsbegäran.docx", "A 61558-2023")</f>
         <v/>
       </c>
       <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 13766-2023 tillsynsbegäran mail.docx", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 61558-2023 tillsynsbegäran mail.docx", "A 61558-2023")</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 61558-2023</t>
+          <t>A 49543-2025</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1237,10 +1242,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45265</v>
+        <v>45939</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1252,13 +1257,8 @@
           <t>YSTAD</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I8" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1285,55 +1285,55 @@
         <v>1</v>
       </c>
       <c r="R8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
       </c>
       <c r="T8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U8" t="n">
         <v>0</v>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Svartöra</t>
         </is>
       </c>
       <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 61558-2023 artfynd.xlsx", "A 61558-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 49543-2025 artfynd.xlsx", "A 49543-2025")</f>
         <v/>
       </c>
       <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 61558-2023 karta.png", "A 61558-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 49543-2025 karta.png", "A 49543-2025")</f>
         <v/>
       </c>
       <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 61558-2023 georefererad karta.tif", "A 61558-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 49543-2025 georefererad karta.tif", "A 49543-2025")</f>
         <v/>
       </c>
       <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 61558-2023 FSC-klagomål.docx", "A 61558-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 49543-2025 FSC-klagomål.docx", "A 49543-2025")</f>
         <v/>
       </c>
       <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 61558-2023 FSC-klagomål mail.docx", "A 61558-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 49543-2025 FSC-klagomål mail.docx", "A 49543-2025")</f>
         <v/>
       </c>
       <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 61558-2023 tillsynsbegäran.docx", "A 61558-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 49543-2025 tillsynsbegäran.docx", "A 49543-2025")</f>
         <v/>
       </c>
       <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 61558-2023 tillsynsbegäran mail.docx", "A 61558-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 49543-2025 tillsynsbegäran mail.docx", "A 49543-2025")</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 49543-2025</t>
+          <t>A 34341-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1347,10 +1347,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45939</v>
+        <v>45525</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1362,8 +1362,13 @@
           <t>YSTAD</t>
         </is>
       </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I9" t="n">
-        <v>1.4</v>
+        <v>14.4</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1396,49 +1401,49 @@
         <v>1</v>
       </c>
       <c r="T9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>Svartöra</t>
+          <t>Desmeknopp</t>
         </is>
       </c>
       <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 49543-2025 artfynd.xlsx", "A 49543-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 34341-2024 artfynd.xlsx", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 49543-2025 karta.png", "A 49543-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 34341-2024 karta.png", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 49543-2025 georefererad karta.tif", "A 49543-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 34341-2024 georefererad karta.tif", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 49543-2025 FSC-klagomål.docx", "A 49543-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 34341-2024 FSC-klagomål.docx", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 49543-2025 FSC-klagomål mail.docx", "A 49543-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 34341-2024 FSC-klagomål mail.docx", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 49543-2025 tillsynsbegäran.docx", "A 49543-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 34341-2024 tillsynsbegäran.docx", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 49543-2025 tillsynsbegäran mail.docx", "A 49543-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 34341-2024 tillsynsbegäran mail.docx", "A 34341-2024")</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 60891-2024</t>
+          <t>A 49549-2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1452,10 +1457,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45644</v>
+        <v>45939</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1468,13 +1473,13 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>16.1</v>
+        <v>0.5</v>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -1504,46 +1509,46 @@
         <v>1</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>Lövgroda</t>
+          <t>Noshornsoxe</t>
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 60891-2024 artfynd.xlsx", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 49549-2025 artfynd.xlsx", "A 49549-2025")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 60891-2024 karta.png", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 49549-2025 karta.png", "A 49549-2025")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 60891-2024 georefererad karta.tif", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 49549-2025 georefererad karta.tif", "A 49549-2025")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 60891-2024 FSC-klagomål.docx", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 49549-2025 FSC-klagomål.docx", "A 49549-2025")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 60891-2024 FSC-klagomål mail.docx", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 49549-2025 FSC-klagomål mail.docx", "A 49549-2025")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 60891-2024 tillsynsbegäran.docx", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 49549-2025 tillsynsbegäran.docx", "A 49549-2025")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 60891-2024 tillsynsbegäran mail.docx", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 49549-2025 tillsynsbegäran mail.docx", "A 49549-2025")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 49549-2025</t>
+          <t>A 13766-2023</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1553,14 +1558,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45939</v>
+        <v>45007</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1573,13 +1578,13 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -1609,46 +1614,46 @@
         <v>1</v>
       </c>
       <c r="U11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Noshornsoxe</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 49549-2025 artfynd.xlsx", "A 49549-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 13766-2023 artfynd.xlsx", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 49549-2025 karta.png", "A 49549-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 13766-2023 karta.png", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 49549-2025 georefererad karta.tif", "A 49549-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 13766-2023 georefererad karta.tif", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 49549-2025 FSC-klagomål.docx", "A 49549-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 13766-2023 FSC-klagomål.docx", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 49549-2025 FSC-klagomål mail.docx", "A 49549-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 13766-2023 FSC-klagomål mail.docx", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 49549-2025 tillsynsbegäran.docx", "A 49549-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 13766-2023 tillsynsbegäran.docx", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 49549-2025 tillsynsbegäran mail.docx", "A 49549-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 13766-2023 tillsynsbegäran mail.docx", "A 13766-2023")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 34341-2024</t>
+          <t>A 60891-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1662,10 +1667,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45525</v>
+        <v>45644</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1677,22 +1682,17 @@
           <t>YSTAD</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I12" t="n">
-        <v>14.4</v>
+        <v>16.1</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -1707,7 +1707,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -1719,39 +1719,39 @@
         <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Desmeknopp</t>
+          <t>Lövgroda</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 34341-2024 artfynd.xlsx", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 60891-2024 artfynd.xlsx", "A 60891-2024")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 34341-2024 karta.png", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 60891-2024 karta.png", "A 60891-2024")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 34341-2024 georefererad karta.tif", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 60891-2024 georefererad karta.tif", "A 60891-2024")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 34341-2024 FSC-klagomål.docx", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 60891-2024 FSC-klagomål.docx", "A 60891-2024")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 34341-2024 FSC-klagomål mail.docx", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 60891-2024 FSC-klagomål mail.docx", "A 60891-2024")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 34341-2024 tillsynsbegäran.docx", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 60891-2024 tillsynsbegäran.docx", "A 60891-2024")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 34341-2024 tillsynsbegäran mail.docx", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 60891-2024 tillsynsbegäran mail.docx", "A 60891-2024")</f>
         <v/>
       </c>
     </row>
@@ -1775,7 +1775,7 @@
         <v>44617</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         <v>44823</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1904,7 +1904,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 18090-2022</t>
+          <t>A 34302-2024</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1914,14 +1914,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44684</v>
+        <v>45524</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>4.9</v>
+        <v>1.9</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1994,7 +1994,7 @@
         <v>45260</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2050,7 +2050,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 49536-2025</t>
+          <t>A 32596-2024</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2064,10 +2064,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45939</v>
+        <v>45513</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2080,7 +2080,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1.5</v>
+        <v>2.6</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2123,7 +2123,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 38631-2023</t>
+          <t>A 49536-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2137,10 +2137,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45162</v>
+        <v>45939</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2196,7 +2196,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 22195-2023</t>
+          <t>A 38631-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2210,10 +2210,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45069</v>
+        <v>45162</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2225,13 +2225,8 @@
           <t>YSTAD</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I19" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2274,7 +2269,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 34302-2024</t>
+          <t>A 18090-2022</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2284,14 +2279,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45524</v>
+        <v>44684</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2304,7 +2299,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.9</v>
+        <v>4.9</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2364,7 +2359,7 @@
         <v>46282</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2437,7 +2432,7 @@
         <v>46190</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2493,7 +2488,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 32596-2024</t>
+          <t>A 22195-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2507,10 +2502,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45513</v>
+        <v>45069</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2522,8 +2517,13 @@
           <t>YSTAD</t>
         </is>
       </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I23" t="n">
-        <v>2.6</v>
+        <v>1.1</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>

--- a/Översikt YSTAD.xlsx
+++ b/Översikt YSTAD.xlsx
@@ -601,7 +601,7 @@
         <v>45113</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -707,7 +707,7 @@
         <v>45939</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -813,7 +813,7 @@
         <v>45679</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -924,7 +924,7 @@
         <v>44903</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>44756</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1135,7 +1135,7 @@
         <v>45265</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1245,7 +1245,7 @@
         <v>45939</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
         <v>45525</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>45939</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1565,7 +1565,7 @@
         <v>45007</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1670,7 +1670,7 @@
         <v>45644</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1775,7 +1775,7 @@
         <v>44617</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         <v>44823</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
         <v>45524</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1994,7 +1994,7 @@
         <v>45260</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2067,7 +2067,7 @@
         <v>45513</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2140,7 +2140,7 @@
         <v>45939</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>45162</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2286,7 +2286,7 @@
         <v>44684</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
         <v>46282</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2432,7 +2432,7 @@
         <v>46190</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2505,7 +2505,7 @@
         <v>45069</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>

--- a/Översikt YSTAD.xlsx
+++ b/Översikt YSTAD.xlsx
@@ -601,7 +601,7 @@
         <v>45113</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -707,7 +707,7 @@
         <v>45939</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -813,7 +813,7 @@
         <v>45679</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -924,7 +924,7 @@
         <v>44903</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>44756</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1135,7 +1135,7 @@
         <v>45265</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1245,7 +1245,7 @@
         <v>45939</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
         <v>45525</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>45939</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1565,7 +1565,7 @@
         <v>45007</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1670,7 +1670,7 @@
         <v>45644</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1775,7 +1775,7 @@
         <v>44617</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         <v>44823</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
         <v>45524</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1994,7 +1994,7 @@
         <v>45260</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2067,7 +2067,7 @@
         <v>45513</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2140,7 +2140,7 @@
         <v>45939</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>45162</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2286,7 +2286,7 @@
         <v>44684</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
         <v>46282</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2432,7 +2432,7 @@
         <v>46190</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2505,7 +2505,7 @@
         <v>45069</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>

--- a/Översikt YSTAD.xlsx
+++ b/Översikt YSTAD.xlsx
@@ -584,7 +584,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A 31213-2023</t>
+          <t>A 3253-2025</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>45113</v>
+        <v>45679</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -613,17 +613,22 @@
           <t>YSTAD</t>
         </is>
       </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I2" t="n">
-        <v>6.5</v>
+        <v>2.5</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
@@ -638,7 +643,7 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -650,40 +655,40 @@
         <v>3</v>
       </c>
       <c r="U2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
-          <t>Skogsveronika
-Skärmstarr</t>
+          <t>Lönnlav
+Strävlosta</t>
         </is>
       </c>
       <c r="W2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 31213-2023 artfynd.xlsx", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 3253-2025 artfynd.xlsx", "A 3253-2025")</f>
         <v/>
       </c>
       <c r="X2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 31213-2023 karta.png", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 3253-2025 karta.png", "A 3253-2025")</f>
         <v/>
       </c>
       <c r="Y2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 31213-2023 georefererad karta.tif", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 3253-2025 georefererad karta.tif", "A 3253-2025")</f>
         <v/>
       </c>
       <c r="AA2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 31213-2023 FSC-klagomål.docx", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 3253-2025 FSC-klagomål.docx", "A 3253-2025")</f>
         <v/>
       </c>
       <c r="AB2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 31213-2023 FSC-klagomål mail.docx", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 3253-2025 FSC-klagomål mail.docx", "A 3253-2025")</f>
         <v/>
       </c>
       <c r="AC2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 31213-2023 tillsynsbegäran.docx", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 3253-2025 tillsynsbegäran.docx", "A 3253-2025")</f>
         <v/>
       </c>
       <c r="AD2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 31213-2023 tillsynsbegäran mail.docx", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 3253-2025 tillsynsbegäran mail.docx", "A 3253-2025")</f>
         <v/>
       </c>
     </row>
@@ -707,7 +712,7 @@
         <v>45939</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -796,7 +801,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 3253-2025</t>
+          <t>A 60295-2022</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -806,14 +811,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45679</v>
+        <v>44903</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -825,19 +830,14 @@
           <t>YSTAD</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I4" t="n">
-        <v>2.5</v>
+        <v>1.1</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -864,50 +864,50 @@
         <v>2</v>
       </c>
       <c r="T4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="U4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>Lönnlav
-Strävlosta</t>
+          <t>Klockgroda
+Ätlig groda</t>
         </is>
       </c>
       <c r="W4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 3253-2025 artfynd.xlsx", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 60295-2022 artfynd.xlsx", "A 60295-2022")</f>
         <v/>
       </c>
       <c r="X4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 3253-2025 karta.png", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 60295-2022 karta.png", "A 60295-2022")</f>
         <v/>
       </c>
       <c r="Y4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 3253-2025 georefererad karta.tif", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 60295-2022 georefererad karta.tif", "A 60295-2022")</f>
         <v/>
       </c>
       <c r="AA4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 3253-2025 FSC-klagomål.docx", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 60295-2022 FSC-klagomål.docx", "A 60295-2022")</f>
         <v/>
       </c>
       <c r="AB4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 3253-2025 FSC-klagomål mail.docx", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 60295-2022 FSC-klagomål mail.docx", "A 60295-2022")</f>
         <v/>
       </c>
       <c r="AC4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 3253-2025 tillsynsbegäran.docx", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 60295-2022 tillsynsbegäran.docx", "A 60295-2022")</f>
         <v/>
       </c>
       <c r="AD4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 3253-2025 tillsynsbegäran mail.docx", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 60295-2022 tillsynsbegäran mail.docx", "A 60295-2022")</f>
         <v/>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 60295-2022</t>
+          <t>A 31213-2023</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -917,14 +917,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>44903</v>
+        <v>45113</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -937,16 +937,16 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>1.1</v>
+        <v>6.5</v>
       </c>
       <c r="J5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -961,7 +961,7 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -970,43 +970,43 @@
         <v>2</v>
       </c>
       <c r="T5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="U5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>Klockgroda
-Ätlig groda</t>
+          <t>Skogsveronika
+Skärmstarr</t>
         </is>
       </c>
       <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 60295-2022 artfynd.xlsx", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 31213-2023 artfynd.xlsx", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 60295-2022 karta.png", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 31213-2023 karta.png", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 60295-2022 georefererad karta.tif", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 31213-2023 georefererad karta.tif", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 60295-2022 FSC-klagomål.docx", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 31213-2023 FSC-klagomål.docx", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 60295-2022 FSC-klagomål mail.docx", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 31213-2023 FSC-klagomål mail.docx", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 60295-2022 tillsynsbegäran.docx", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 31213-2023 tillsynsbegäran.docx", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 60295-2022 tillsynsbegäran mail.docx", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 31213-2023 tillsynsbegäran mail.docx", "A 31213-2023")</f>
         <v/>
       </c>
     </row>
@@ -1030,7 +1030,7 @@
         <v>44756</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1135,7 +1135,7 @@
         <v>45265</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 49543-2025</t>
+          <t>A 13766-2023</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1238,14 +1238,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45939</v>
+        <v>45007</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1258,16 +1258,16 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -1282,7 +1282,7 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -1291,49 +1291,49 @@
         <v>1</v>
       </c>
       <c r="T8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U8" t="n">
         <v>0</v>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>Svartöra</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 49543-2025 artfynd.xlsx", "A 49543-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 13766-2023 artfynd.xlsx", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 49543-2025 karta.png", "A 49543-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 13766-2023 karta.png", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 49543-2025 georefererad karta.tif", "A 49543-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 13766-2023 georefererad karta.tif", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 49543-2025 FSC-klagomål.docx", "A 49543-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 13766-2023 FSC-klagomål.docx", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 49543-2025 FSC-klagomål mail.docx", "A 49543-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 13766-2023 FSC-klagomål mail.docx", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 49543-2025 tillsynsbegäran.docx", "A 49543-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 13766-2023 tillsynsbegäran.docx", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 49543-2025 tillsynsbegäran mail.docx", "A 49543-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 13766-2023 tillsynsbegäran mail.docx", "A 13766-2023")</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 34341-2024</t>
+          <t>A 49543-2025</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1347,10 +1347,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45525</v>
+        <v>45939</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1362,13 +1362,8 @@
           <t>YSTAD</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I9" t="n">
-        <v>14.4</v>
+        <v>1.4</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1401,42 +1396,42 @@
         <v>1</v>
       </c>
       <c r="T9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>Desmeknopp</t>
+          <t>Svartöra</t>
         </is>
       </c>
       <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 34341-2024 artfynd.xlsx", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 49543-2025 artfynd.xlsx", "A 49543-2025")</f>
         <v/>
       </c>
       <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 34341-2024 karta.png", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 49543-2025 karta.png", "A 49543-2025")</f>
         <v/>
       </c>
       <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 34341-2024 georefererad karta.tif", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 49543-2025 georefererad karta.tif", "A 49543-2025")</f>
         <v/>
       </c>
       <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 34341-2024 FSC-klagomål.docx", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 49543-2025 FSC-klagomål.docx", "A 49543-2025")</f>
         <v/>
       </c>
       <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 34341-2024 FSC-klagomål mail.docx", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 49543-2025 FSC-klagomål mail.docx", "A 49543-2025")</f>
         <v/>
       </c>
       <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 34341-2024 tillsynsbegäran.docx", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 49543-2025 tillsynsbegäran.docx", "A 49543-2025")</f>
         <v/>
       </c>
       <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 34341-2024 tillsynsbegäran mail.docx", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 49543-2025 tillsynsbegäran mail.docx", "A 49543-2025")</f>
         <v/>
       </c>
     </row>
@@ -1460,7 +1455,7 @@
         <v>45939</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1548,7 +1543,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 13766-2023</t>
+          <t>A 60891-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1558,14 +1553,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45007</v>
+        <v>45644</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1578,7 +1573,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0.9</v>
+        <v>16.1</v>
       </c>
       <c r="J11" t="n">
         <v>1</v>
@@ -1618,42 +1613,42 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Lövgroda</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 13766-2023 artfynd.xlsx", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 60891-2024 artfynd.xlsx", "A 60891-2024")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 13766-2023 karta.png", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 60891-2024 karta.png", "A 60891-2024")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 13766-2023 georefererad karta.tif", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 60891-2024 georefererad karta.tif", "A 60891-2024")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 13766-2023 FSC-klagomål.docx", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 60891-2024 FSC-klagomål.docx", "A 60891-2024")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 13766-2023 FSC-klagomål mail.docx", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 60891-2024 FSC-klagomål mail.docx", "A 60891-2024")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 13766-2023 tillsynsbegäran.docx", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 60891-2024 tillsynsbegäran.docx", "A 60891-2024")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 13766-2023 tillsynsbegäran mail.docx", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 60891-2024 tillsynsbegäran mail.docx", "A 60891-2024")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 60891-2024</t>
+          <t>A 34341-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1667,10 +1662,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45644</v>
+        <v>45525</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1682,17 +1677,22 @@
           <t>YSTAD</t>
         </is>
       </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I12" t="n">
-        <v>16.1</v>
+        <v>14.4</v>
       </c>
       <c r="J12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -1707,7 +1707,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -1719,39 +1719,39 @@
         <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Lövgroda</t>
+          <t>Desmeknopp</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 60891-2024 artfynd.xlsx", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 34341-2024 artfynd.xlsx", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 60891-2024 karta.png", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 34341-2024 karta.png", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 60891-2024 georefererad karta.tif", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 34341-2024 georefererad karta.tif", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 60891-2024 FSC-klagomål.docx", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 34341-2024 FSC-klagomål.docx", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 60891-2024 FSC-klagomål mail.docx", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 34341-2024 FSC-klagomål mail.docx", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 60891-2024 tillsynsbegäran.docx", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 34341-2024 tillsynsbegäran.docx", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 60891-2024 tillsynsbegäran mail.docx", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 34341-2024 tillsynsbegäran mail.docx", "A 34341-2024")</f>
         <v/>
       </c>
     </row>
@@ -1775,7 +1775,7 @@
         <v>44617</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 40417-2022</t>
+          <t>A 32596-2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1845,10 +1845,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44823</v>
+        <v>45513</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1904,7 +1904,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 34302-2024</t>
+          <t>A 40417-2022</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1918,10 +1918,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45524</v>
+        <v>44823</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1977,7 +1977,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 60803-2023</t>
+          <t>A 18090-2022</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1987,14 +1987,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45260</v>
+        <v>44684</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.6</v>
+        <v>4.9</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2050,7 +2050,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 32596-2024</t>
+          <t>A 60803-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2064,10 +2064,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45513</v>
+        <v>45260</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2080,7 +2080,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>2.6</v>
+        <v>1.6</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2123,7 +2123,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 49536-2025</t>
+          <t>A 38631-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2137,10 +2137,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45939</v>
+        <v>45162</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2196,7 +2196,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 38631-2023</t>
+          <t>A 49536-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2210,10 +2210,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45162</v>
+        <v>45939</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2269,7 +2269,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 18090-2022</t>
+          <t>A 22195-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2279,14 +2279,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44684</v>
+        <v>45069</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2298,8 +2298,13 @@
           <t>YSTAD</t>
         </is>
       </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I20" t="n">
-        <v>4.9</v>
+        <v>1.1</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2342,7 +2347,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 38413-2026</t>
+          <t>A 34302-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2356,10 +2361,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46282</v>
+        <v>45524</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2372,7 +2377,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.6</v>
+        <v>1.9</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2415,7 +2420,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 27578-2026</t>
+          <t>A 38413-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2429,10 +2434,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46190</v>
+        <v>46282</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2445,7 +2450,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>6.6</v>
+        <v>0.6</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2488,7 +2493,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 22195-2023</t>
+          <t>A 27578-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2502,10 +2507,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45069</v>
+        <v>46190</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2517,13 +2522,8 @@
           <t>YSTAD</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I23" t="n">
-        <v>1.1</v>
+        <v>6.6</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>

--- a/Översikt YSTAD.xlsx
+++ b/Översikt YSTAD.xlsx
@@ -584,7 +584,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A 3253-2025</t>
+          <t>A 31213-2023</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>45679</v>
+        <v>45113</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -613,22 +613,17 @@
           <t>YSTAD</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I2" t="n">
-        <v>2.5</v>
+        <v>6.5</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
@@ -643,7 +638,7 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -655,47 +650,47 @@
         <v>3</v>
       </c>
       <c r="U2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
-          <t>Lönnlav
-Strävlosta</t>
+          <t>Skogsveronika
+Skärmstarr</t>
         </is>
       </c>
       <c r="W2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 3253-2025 artfynd.xlsx", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 31213-2023 artfynd.xlsx", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="X2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 3253-2025 karta.png", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 31213-2023 karta.png", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="Y2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 3253-2025 georefererad karta.tif", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 31213-2023 georefererad karta.tif", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="AA2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 3253-2025 FSC-klagomål.docx", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 31213-2023 FSC-klagomål.docx", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="AB2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 3253-2025 FSC-klagomål mail.docx", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 31213-2023 FSC-klagomål mail.docx", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="AC2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 3253-2025 tillsynsbegäran.docx", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 31213-2023 tillsynsbegäran.docx", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="AD2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 3253-2025 tillsynsbegäran mail.docx", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 31213-2023 tillsynsbegäran mail.docx", "A 31213-2023")</f>
         <v/>
       </c>
     </row>
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 49546-2025</t>
+          <t>A 3253-2025</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -709,10 +704,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>45939</v>
+        <v>45679</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -724,14 +719,19 @@
           <t>YSTAD</t>
         </is>
       </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I3" t="n">
-        <v>4.4</v>
+        <v>2.5</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -740,7 +740,7 @@
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -749,59 +749,59 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
         <v>2</v>
       </c>
       <c r="T3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
-          <t>Skogsalm
-Igelkottsröksvamp</t>
+          <t>Lönnlav
+Strävlosta</t>
         </is>
       </c>
       <c r="W3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 49546-2025 artfynd.xlsx", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 3253-2025 artfynd.xlsx", "A 3253-2025")</f>
         <v/>
       </c>
       <c r="X3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 49546-2025 karta.png", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 3253-2025 karta.png", "A 3253-2025")</f>
         <v/>
       </c>
       <c r="Y3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 49546-2025 georefererad karta.tif", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 3253-2025 georefererad karta.tif", "A 3253-2025")</f>
         <v/>
       </c>
       <c r="AA3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 49546-2025 FSC-klagomål.docx", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 3253-2025 FSC-klagomål.docx", "A 3253-2025")</f>
         <v/>
       </c>
       <c r="AB3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 49546-2025 FSC-klagomål mail.docx", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 3253-2025 FSC-klagomål mail.docx", "A 3253-2025")</f>
         <v/>
       </c>
       <c r="AC3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 49546-2025 tillsynsbegäran.docx", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 3253-2025 tillsynsbegäran.docx", "A 3253-2025")</f>
         <v/>
       </c>
       <c r="AD3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 49546-2025 tillsynsbegäran mail.docx", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 3253-2025 tillsynsbegäran mail.docx", "A 3253-2025")</f>
         <v/>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 60295-2022</t>
+          <t>A 49546-2025</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -811,14 +811,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>44903</v>
+        <v>45939</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -831,13 +831,13 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>1.1</v>
+        <v>4.4</v>
       </c>
       <c r="J4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -846,7 +846,7 @@
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -855,59 +855,59 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S4" t="n">
         <v>2</v>
       </c>
       <c r="T4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="U4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>Klockgroda
-Ätlig groda</t>
+          <t>Skogsalm
+Igelkottsröksvamp</t>
         </is>
       </c>
       <c r="W4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 60295-2022 artfynd.xlsx", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 49546-2025 artfynd.xlsx", "A 49546-2025")</f>
         <v/>
       </c>
       <c r="X4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 60295-2022 karta.png", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 49546-2025 karta.png", "A 49546-2025")</f>
         <v/>
       </c>
       <c r="Y4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 60295-2022 georefererad karta.tif", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 49546-2025 georefererad karta.tif", "A 49546-2025")</f>
         <v/>
       </c>
       <c r="AA4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 60295-2022 FSC-klagomål.docx", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 49546-2025 FSC-klagomål.docx", "A 49546-2025")</f>
         <v/>
       </c>
       <c r="AB4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 60295-2022 FSC-klagomål mail.docx", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 49546-2025 FSC-klagomål mail.docx", "A 49546-2025")</f>
         <v/>
       </c>
       <c r="AC4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 60295-2022 tillsynsbegäran.docx", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 49546-2025 tillsynsbegäran.docx", "A 49546-2025")</f>
         <v/>
       </c>
       <c r="AD4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 60295-2022 tillsynsbegäran mail.docx", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 49546-2025 tillsynsbegäran mail.docx", "A 49546-2025")</f>
         <v/>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 31213-2023</t>
+          <t>A 60295-2022</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -917,14 +917,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>45113</v>
+        <v>44903</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -937,16 +937,16 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>6.5</v>
+        <v>1.1</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -961,7 +961,7 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -970,43 +970,43 @@
         <v>2</v>
       </c>
       <c r="T5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="U5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>Skogsveronika
-Skärmstarr</t>
+          <t>Klockgroda
+Ätlig groda</t>
         </is>
       </c>
       <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 31213-2023 artfynd.xlsx", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 60295-2022 artfynd.xlsx", "A 60295-2022")</f>
         <v/>
       </c>
       <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 31213-2023 karta.png", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 60295-2022 karta.png", "A 60295-2022")</f>
         <v/>
       </c>
       <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 31213-2023 georefererad karta.tif", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 60295-2022 georefererad karta.tif", "A 60295-2022")</f>
         <v/>
       </c>
       <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 31213-2023 FSC-klagomål.docx", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 60295-2022 FSC-klagomål.docx", "A 60295-2022")</f>
         <v/>
       </c>
       <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 31213-2023 FSC-klagomål mail.docx", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 60295-2022 FSC-klagomål mail.docx", "A 60295-2022")</f>
         <v/>
       </c>
       <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 31213-2023 tillsynsbegäran.docx", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 60295-2022 tillsynsbegäran.docx", "A 60295-2022")</f>
         <v/>
       </c>
       <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 31213-2023 tillsynsbegäran mail.docx", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 60295-2022 tillsynsbegäran mail.docx", "A 60295-2022")</f>
         <v/>
       </c>
     </row>
@@ -1030,7 +1030,7 @@
         <v>44756</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1135,7 +1135,7 @@
         <v>45265</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 13766-2023</t>
+          <t>A 49543-2025</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1238,14 +1238,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45007</v>
+        <v>45939</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1258,16 +1258,16 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -1282,7 +1282,7 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -1291,49 +1291,49 @@
         <v>1</v>
       </c>
       <c r="T8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U8" t="n">
         <v>0</v>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Svartöra</t>
         </is>
       </c>
       <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 13766-2023 artfynd.xlsx", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 49543-2025 artfynd.xlsx", "A 49543-2025")</f>
         <v/>
       </c>
       <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 13766-2023 karta.png", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 49543-2025 karta.png", "A 49543-2025")</f>
         <v/>
       </c>
       <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 13766-2023 georefererad karta.tif", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 49543-2025 georefererad karta.tif", "A 49543-2025")</f>
         <v/>
       </c>
       <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 13766-2023 FSC-klagomål.docx", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 49543-2025 FSC-klagomål.docx", "A 49543-2025")</f>
         <v/>
       </c>
       <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 13766-2023 FSC-klagomål mail.docx", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 49543-2025 FSC-klagomål mail.docx", "A 49543-2025")</f>
         <v/>
       </c>
       <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 13766-2023 tillsynsbegäran.docx", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 49543-2025 tillsynsbegäran.docx", "A 49543-2025")</f>
         <v/>
       </c>
       <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 13766-2023 tillsynsbegäran mail.docx", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 49543-2025 tillsynsbegäran mail.docx", "A 49543-2025")</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 49543-2025</t>
+          <t>A 34341-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1347,10 +1347,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45939</v>
+        <v>45525</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1362,8 +1362,13 @@
           <t>YSTAD</t>
         </is>
       </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I9" t="n">
-        <v>1.4</v>
+        <v>14.4</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1396,42 +1401,42 @@
         <v>1</v>
       </c>
       <c r="T9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>Svartöra</t>
+          <t>Desmeknopp</t>
         </is>
       </c>
       <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 49543-2025 artfynd.xlsx", "A 49543-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 34341-2024 artfynd.xlsx", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 49543-2025 karta.png", "A 49543-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 34341-2024 karta.png", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 49543-2025 georefererad karta.tif", "A 49543-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 34341-2024 georefererad karta.tif", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 49543-2025 FSC-klagomål.docx", "A 49543-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 34341-2024 FSC-klagomål.docx", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 49543-2025 FSC-klagomål mail.docx", "A 49543-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 34341-2024 FSC-klagomål mail.docx", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 49543-2025 tillsynsbegäran.docx", "A 49543-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 34341-2024 tillsynsbegäran.docx", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 49543-2025 tillsynsbegäran mail.docx", "A 49543-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 34341-2024 tillsynsbegäran mail.docx", "A 34341-2024")</f>
         <v/>
       </c>
     </row>
@@ -1455,7 +1460,7 @@
         <v>45939</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1543,7 +1548,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 60891-2024</t>
+          <t>A 13766-2023</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1553,14 +1558,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45644</v>
+        <v>45007</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1573,7 +1578,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>16.1</v>
+        <v>0.9</v>
       </c>
       <c r="J11" t="n">
         <v>1</v>
@@ -1613,42 +1618,42 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Lövgroda</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 60891-2024 artfynd.xlsx", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 13766-2023 artfynd.xlsx", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 60891-2024 karta.png", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 13766-2023 karta.png", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 60891-2024 georefererad karta.tif", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 13766-2023 georefererad karta.tif", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 60891-2024 FSC-klagomål.docx", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 13766-2023 FSC-klagomål.docx", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 60891-2024 FSC-klagomål mail.docx", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 13766-2023 FSC-klagomål mail.docx", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 60891-2024 tillsynsbegäran.docx", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 13766-2023 tillsynsbegäran.docx", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 60891-2024 tillsynsbegäran mail.docx", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 13766-2023 tillsynsbegäran mail.docx", "A 13766-2023")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 34341-2024</t>
+          <t>A 60891-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1662,10 +1667,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45525</v>
+        <v>45644</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1677,22 +1682,17 @@
           <t>YSTAD</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I12" t="n">
-        <v>14.4</v>
+        <v>16.1</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -1707,7 +1707,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -1719,39 +1719,39 @@
         <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Desmeknopp</t>
+          <t>Lövgroda</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 34341-2024 artfynd.xlsx", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 60891-2024 artfynd.xlsx", "A 60891-2024")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 34341-2024 karta.png", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 60891-2024 karta.png", "A 60891-2024")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 34341-2024 georefererad karta.tif", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 60891-2024 georefererad karta.tif", "A 60891-2024")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 34341-2024 FSC-klagomål.docx", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 60891-2024 FSC-klagomål.docx", "A 60891-2024")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 34341-2024 FSC-klagomål mail.docx", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 60891-2024 FSC-klagomål mail.docx", "A 60891-2024")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 34341-2024 tillsynsbegäran.docx", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 60891-2024 tillsynsbegäran.docx", "A 60891-2024")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 34341-2024 tillsynsbegäran mail.docx", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 60891-2024 tillsynsbegäran mail.docx", "A 60891-2024")</f>
         <v/>
       </c>
     </row>
@@ -1775,7 +1775,7 @@
         <v>44617</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 32596-2024</t>
+          <t>A 40417-2022</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1845,10 +1845,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45513</v>
+        <v>44823</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1904,7 +1904,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 40417-2022</t>
+          <t>A 34302-2024</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1918,10 +1918,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44823</v>
+        <v>45524</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1977,7 +1977,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 18090-2022</t>
+          <t>A 32596-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1987,14 +1987,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44684</v>
+        <v>45513</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>4.9</v>
+        <v>2.6</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2067,7 +2067,7 @@
         <v>45260</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2140,7 +2140,7 @@
         <v>45162</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2196,7 +2196,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 49536-2025</t>
+          <t>A 18090-2022</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2206,14 +2206,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45939</v>
+        <v>44684</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1.5</v>
+        <v>4.9</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2269,7 +2269,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 22195-2023</t>
+          <t>A 49536-2025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2283,10 +2283,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45069</v>
+        <v>45939</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2298,13 +2298,8 @@
           <t>YSTAD</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I20" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2347,7 +2342,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 34302-2024</t>
+          <t>A 22195-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2361,10 +2356,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45524</v>
+        <v>45069</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2376,8 +2371,13 @@
           <t>YSTAD</t>
         </is>
       </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I21" t="n">
-        <v>1.9</v>
+        <v>1.1</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2437,7 +2437,7 @@
         <v>46282</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2510,7 +2510,7 @@
         <v>46190</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>

--- a/Översikt YSTAD.xlsx
+++ b/Översikt YSTAD.xlsx
@@ -584,7 +584,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A 31213-2023</t>
+          <t>A 60295-2022</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -594,14 +594,14 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>45113</v>
+        <v>44903</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -614,16 +614,16 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>6.5</v>
+        <v>1.1</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
@@ -638,7 +638,7 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -647,50 +647,50 @@
         <v>2</v>
       </c>
       <c r="T2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="U2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
-          <t>Skogsveronika
-Skärmstarr</t>
+          <t>Klockgroda
+Ätlig groda</t>
         </is>
       </c>
       <c r="W2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 31213-2023 artfynd.xlsx", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 60295-2022 artfynd.xlsx", "A 60295-2022")</f>
         <v/>
       </c>
       <c r="X2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 31213-2023 karta.png", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 60295-2022 karta.png", "A 60295-2022")</f>
         <v/>
       </c>
       <c r="Y2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 31213-2023 georefererad karta.tif", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 60295-2022 georefererad karta.tif", "A 60295-2022")</f>
         <v/>
       </c>
       <c r="AA2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 31213-2023 FSC-klagomål.docx", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 60295-2022 FSC-klagomål.docx", "A 60295-2022")</f>
         <v/>
       </c>
       <c r="AB2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 31213-2023 FSC-klagomål mail.docx", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 60295-2022 FSC-klagomål mail.docx", "A 60295-2022")</f>
         <v/>
       </c>
       <c r="AC2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 31213-2023 tillsynsbegäran.docx", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 60295-2022 tillsynsbegäran.docx", "A 60295-2022")</f>
         <v/>
       </c>
       <c r="AD2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 31213-2023 tillsynsbegäran mail.docx", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 60295-2022 tillsynsbegäran mail.docx", "A 60295-2022")</f>
         <v/>
       </c>
     </row>
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 3253-2025</t>
+          <t>A 31213-2023</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -704,10 +704,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>45679</v>
+        <v>45113</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -719,22 +719,17 @@
           <t>YSTAD</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I3" t="n">
-        <v>2.5</v>
+        <v>6.5</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
@@ -749,7 +744,7 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -761,47 +756,47 @@
         <v>3</v>
       </c>
       <c r="U3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
-          <t>Lönnlav
-Strävlosta</t>
+          <t>Skogsveronika
+Skärmstarr</t>
         </is>
       </c>
       <c r="W3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 3253-2025 artfynd.xlsx", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 31213-2023 artfynd.xlsx", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="X3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 3253-2025 karta.png", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 31213-2023 karta.png", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="Y3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 3253-2025 georefererad karta.tif", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 31213-2023 georefererad karta.tif", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="AA3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 3253-2025 FSC-klagomål.docx", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 31213-2023 FSC-klagomål.docx", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="AB3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 3253-2025 FSC-klagomål mail.docx", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 31213-2023 FSC-klagomål mail.docx", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="AC3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 3253-2025 tillsynsbegäran.docx", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 31213-2023 tillsynsbegäran.docx", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="AD3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 3253-2025 tillsynsbegäran mail.docx", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 31213-2023 tillsynsbegäran mail.docx", "A 31213-2023")</f>
         <v/>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 49546-2025</t>
+          <t>A 3253-2025</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -815,10 +810,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45939</v>
+        <v>45679</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -830,14 +825,19 @@
           <t>YSTAD</t>
         </is>
       </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I4" t="n">
-        <v>4.4</v>
+        <v>2.5</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -846,7 +846,7 @@
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -855,59 +855,59 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>2</v>
       </c>
       <c r="T4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>Skogsalm
-Igelkottsröksvamp</t>
+          <t>Lönnlav
+Strävlosta</t>
         </is>
       </c>
       <c r="W4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 49546-2025 artfynd.xlsx", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 3253-2025 artfynd.xlsx", "A 3253-2025")</f>
         <v/>
       </c>
       <c r="X4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 49546-2025 karta.png", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 3253-2025 karta.png", "A 3253-2025")</f>
         <v/>
       </c>
       <c r="Y4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 49546-2025 georefererad karta.tif", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 3253-2025 georefererad karta.tif", "A 3253-2025")</f>
         <v/>
       </c>
       <c r="AA4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 49546-2025 FSC-klagomål.docx", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 3253-2025 FSC-klagomål.docx", "A 3253-2025")</f>
         <v/>
       </c>
       <c r="AB4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 49546-2025 FSC-klagomål mail.docx", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 3253-2025 FSC-klagomål mail.docx", "A 3253-2025")</f>
         <v/>
       </c>
       <c r="AC4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 49546-2025 tillsynsbegäran.docx", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 3253-2025 tillsynsbegäran.docx", "A 3253-2025")</f>
         <v/>
       </c>
       <c r="AD4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 49546-2025 tillsynsbegäran mail.docx", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 3253-2025 tillsynsbegäran mail.docx", "A 3253-2025")</f>
         <v/>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 60295-2022</t>
+          <t>A 49546-2025</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -917,14 +917,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>44903</v>
+        <v>45939</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -937,13 +937,13 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>1.1</v>
+        <v>4.4</v>
       </c>
       <c r="J5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -952,7 +952,7 @@
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -961,52 +961,52 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S5" t="n">
         <v>2</v>
       </c>
       <c r="T5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="U5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>Klockgroda
-Ätlig groda</t>
+          <t>Skogsalm
+Igelkottsröksvamp</t>
         </is>
       </c>
       <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 60295-2022 artfynd.xlsx", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 49546-2025 artfynd.xlsx", "A 49546-2025")</f>
         <v/>
       </c>
       <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 60295-2022 karta.png", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 49546-2025 karta.png", "A 49546-2025")</f>
         <v/>
       </c>
       <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 60295-2022 georefererad karta.tif", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 49546-2025 georefererad karta.tif", "A 49546-2025")</f>
         <v/>
       </c>
       <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 60295-2022 FSC-klagomål.docx", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 49546-2025 FSC-klagomål.docx", "A 49546-2025")</f>
         <v/>
       </c>
       <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 60295-2022 FSC-klagomål mail.docx", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 49546-2025 FSC-klagomål mail.docx", "A 49546-2025")</f>
         <v/>
       </c>
       <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 60295-2022 tillsynsbegäran.docx", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 49546-2025 tillsynsbegäran.docx", "A 49546-2025")</f>
         <v/>
       </c>
       <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 60295-2022 tillsynsbegäran mail.docx", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 49546-2025 tillsynsbegäran mail.docx", "A 49546-2025")</f>
         <v/>
       </c>
     </row>
@@ -1030,7 +1030,7 @@
         <v>44756</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 61558-2023</t>
+          <t>A 13766-2023</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1128,14 +1128,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45265</v>
+        <v>45007</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1147,16 +1147,11 @@
           <t>YSTAD</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I7" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -1168,7 +1163,7 @@
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1177,10 +1172,10 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1193,42 +1188,42 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 61558-2023 artfynd.xlsx", "A 61558-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 13766-2023 artfynd.xlsx", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 61558-2023 karta.png", "A 61558-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 13766-2023 karta.png", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 61558-2023 georefererad karta.tif", "A 61558-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 13766-2023 georefererad karta.tif", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 61558-2023 FSC-klagomål.docx", "A 61558-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 13766-2023 FSC-klagomål.docx", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 61558-2023 FSC-klagomål mail.docx", "A 61558-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 13766-2023 FSC-klagomål mail.docx", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 61558-2023 tillsynsbegäran.docx", "A 61558-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 13766-2023 tillsynsbegäran.docx", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 61558-2023 tillsynsbegäran mail.docx", "A 61558-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 13766-2023 tillsynsbegäran mail.docx", "A 13766-2023")</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 49543-2025</t>
+          <t>A 60891-2024</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1242,10 +1237,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45939</v>
+        <v>45644</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1258,16 +1253,16 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1.4</v>
+        <v>16.1</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -1282,7 +1277,7 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -1291,42 +1286,42 @@
         <v>1</v>
       </c>
       <c r="T8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U8" t="n">
         <v>0</v>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>Svartöra</t>
+          <t>Lövgroda</t>
         </is>
       </c>
       <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 49543-2025 artfynd.xlsx", "A 49543-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 60891-2024 artfynd.xlsx", "A 60891-2024")</f>
         <v/>
       </c>
       <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 49543-2025 karta.png", "A 49543-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 60891-2024 karta.png", "A 60891-2024")</f>
         <v/>
       </c>
       <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 49543-2025 georefererad karta.tif", "A 49543-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 60891-2024 georefererad karta.tif", "A 60891-2024")</f>
         <v/>
       </c>
       <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 49543-2025 FSC-klagomål.docx", "A 49543-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 60891-2024 FSC-klagomål.docx", "A 60891-2024")</f>
         <v/>
       </c>
       <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 49543-2025 FSC-klagomål mail.docx", "A 49543-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 60891-2024 FSC-klagomål mail.docx", "A 60891-2024")</f>
         <v/>
       </c>
       <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 49543-2025 tillsynsbegäran.docx", "A 49543-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 60891-2024 tillsynsbegäran.docx", "A 60891-2024")</f>
         <v/>
       </c>
       <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 49543-2025 tillsynsbegäran mail.docx", "A 49543-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 60891-2024 tillsynsbegäran mail.docx", "A 60891-2024")</f>
         <v/>
       </c>
     </row>
@@ -1350,7 +1345,7 @@
         <v>45525</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1443,7 +1438,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 49549-2025</t>
+          <t>A 49543-2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1460,7 +1455,7 @@
         <v>45939</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1473,16 +1468,16 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -1497,7 +1492,7 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -1506,49 +1501,49 @@
         <v>1</v>
       </c>
       <c r="T10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>Noshornsoxe</t>
+          <t>Svartöra</t>
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 49549-2025 artfynd.xlsx", "A 49549-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 49543-2025 artfynd.xlsx", "A 49543-2025")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 49549-2025 karta.png", "A 49549-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 49543-2025 karta.png", "A 49543-2025")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 49549-2025 georefererad karta.tif", "A 49549-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 49543-2025 georefererad karta.tif", "A 49543-2025")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 49549-2025 FSC-klagomål.docx", "A 49549-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 49543-2025 FSC-klagomål.docx", "A 49543-2025")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 49549-2025 FSC-klagomål mail.docx", "A 49549-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 49543-2025 FSC-klagomål mail.docx", "A 49543-2025")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 49549-2025 tillsynsbegäran.docx", "A 49549-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 49543-2025 tillsynsbegäran.docx", "A 49543-2025")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 49549-2025 tillsynsbegäran mail.docx", "A 49549-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 49543-2025 tillsynsbegäran mail.docx", "A 49543-2025")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 13766-2023</t>
+          <t>A 61558-2023</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1558,14 +1553,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45007</v>
+        <v>45265</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1577,11 +1572,16 @@
           <t>YSTAD</t>
         </is>
       </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I11" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="J11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -1593,7 +1593,7 @@
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1602,10 +1602,10 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1618,42 +1618,42 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 13766-2023 artfynd.xlsx", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 61558-2023 artfynd.xlsx", "A 61558-2023")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 13766-2023 karta.png", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 61558-2023 karta.png", "A 61558-2023")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 13766-2023 georefererad karta.tif", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 61558-2023 georefererad karta.tif", "A 61558-2023")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 13766-2023 FSC-klagomål.docx", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 61558-2023 FSC-klagomål.docx", "A 61558-2023")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 13766-2023 FSC-klagomål mail.docx", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 61558-2023 FSC-klagomål mail.docx", "A 61558-2023")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 13766-2023 tillsynsbegäran.docx", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 61558-2023 tillsynsbegäran.docx", "A 61558-2023")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 13766-2023 tillsynsbegäran mail.docx", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 61558-2023 tillsynsbegäran mail.docx", "A 61558-2023")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 60891-2024</t>
+          <t>A 49549-2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1667,10 +1667,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45644</v>
+        <v>45939</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1683,13 +1683,13 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>16.1</v>
+        <v>0.5</v>
       </c>
       <c r="J12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -1719,39 +1719,39 @@
         <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Lövgroda</t>
+          <t>Noshornsoxe</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 60891-2024 artfynd.xlsx", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 49549-2025 artfynd.xlsx", "A 49549-2025")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 60891-2024 karta.png", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 49549-2025 karta.png", "A 49549-2025")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 60891-2024 georefererad karta.tif", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 49549-2025 georefererad karta.tif", "A 49549-2025")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 60891-2024 FSC-klagomål.docx", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 49549-2025 FSC-klagomål.docx", "A 49549-2025")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 60891-2024 FSC-klagomål mail.docx", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 49549-2025 FSC-klagomål mail.docx", "A 49549-2025")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 60891-2024 tillsynsbegäran.docx", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 49549-2025 tillsynsbegäran.docx", "A 49549-2025")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 60891-2024 tillsynsbegäran mail.docx", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 49549-2025 tillsynsbegäran mail.docx", "A 49549-2025")</f>
         <v/>
       </c>
     </row>
@@ -1775,7 +1775,7 @@
         <v>44617</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 40417-2022</t>
+          <t>A 60803-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1845,10 +1845,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44823</v>
+        <v>45260</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>2.3</v>
+        <v>1.6</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1904,7 +1904,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 34302-2024</t>
+          <t>A 38631-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1918,10 +1918,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45524</v>
+        <v>45162</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.9</v>
+        <v>0.8</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1977,7 +1977,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 32596-2024</t>
+          <t>A 34302-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1991,10 +1991,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45513</v>
+        <v>45524</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>2.6</v>
+        <v>1.9</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2050,7 +2050,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 60803-2023</t>
+          <t>A 40417-2022</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2064,10 +2064,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45260</v>
+        <v>44823</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2080,7 +2080,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1.6</v>
+        <v>2.3</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2123,7 +2123,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 38631-2023</t>
+          <t>A 22195-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2137,10 +2137,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45162</v>
+        <v>45069</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2152,8 +2152,13 @@
           <t>YSTAD</t>
         </is>
       </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I18" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2213,7 +2218,7 @@
         <v>44684</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2269,7 +2274,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 49536-2025</t>
+          <t>A 32596-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2283,10 +2288,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45939</v>
+        <v>45513</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2299,7 +2304,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.5</v>
+        <v>2.6</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2342,7 +2347,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 22195-2023</t>
+          <t>A 49536-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2356,10 +2361,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45069</v>
+        <v>45939</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2371,13 +2376,8 @@
           <t>YSTAD</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I21" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2437,7 +2437,7 @@
         <v>46282</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2510,7 +2510,7 @@
         <v>46190</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>

--- a/Översikt YSTAD.xlsx
+++ b/Översikt YSTAD.xlsx
@@ -584,7 +584,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A 60295-2022</t>
+          <t>A 31213-2023</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -594,14 +594,14 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>44903</v>
+        <v>45113</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -614,16 +614,16 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>1.1</v>
+        <v>6.5</v>
       </c>
       <c r="J2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
@@ -638,7 +638,7 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -647,50 +647,50 @@
         <v>2</v>
       </c>
       <c r="T2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="U2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
-          <t>Klockgroda
-Ätlig groda</t>
+          <t>Skogsveronika
+Skärmstarr</t>
         </is>
       </c>
       <c r="W2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 60295-2022 artfynd.xlsx", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 31213-2023 artfynd.xlsx", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="X2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 60295-2022 karta.png", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 31213-2023 karta.png", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="Y2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 60295-2022 georefererad karta.tif", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 31213-2023 georefererad karta.tif", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="AA2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 60295-2022 FSC-klagomål.docx", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 31213-2023 FSC-klagomål.docx", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="AB2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 60295-2022 FSC-klagomål mail.docx", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 31213-2023 FSC-klagomål mail.docx", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="AC2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 60295-2022 tillsynsbegäran.docx", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 31213-2023 tillsynsbegäran.docx", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="AD2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 60295-2022 tillsynsbegäran mail.docx", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 31213-2023 tillsynsbegäran mail.docx", "A 31213-2023")</f>
         <v/>
       </c>
     </row>
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 31213-2023</t>
+          <t>A 49546-2025</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -704,10 +704,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>45113</v>
+        <v>45939</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -720,22 +720,22 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>6.5</v>
+        <v>4.4</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -747,49 +747,49 @@
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S3" t="n">
         <v>2</v>
       </c>
       <c r="T3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
-          <t>Skogsveronika
-Skärmstarr</t>
+          <t>Skogsalm
+Igelkottsröksvamp</t>
         </is>
       </c>
       <c r="W3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 31213-2023 artfynd.xlsx", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 49546-2025 artfynd.xlsx", "A 49546-2025")</f>
         <v/>
       </c>
       <c r="X3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 31213-2023 karta.png", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 49546-2025 karta.png", "A 49546-2025")</f>
         <v/>
       </c>
       <c r="Y3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 31213-2023 georefererad karta.tif", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 49546-2025 georefererad karta.tif", "A 49546-2025")</f>
         <v/>
       </c>
       <c r="AA3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 31213-2023 FSC-klagomål.docx", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 49546-2025 FSC-klagomål.docx", "A 49546-2025")</f>
         <v/>
       </c>
       <c r="AB3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 31213-2023 FSC-klagomål mail.docx", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 49546-2025 FSC-klagomål mail.docx", "A 49546-2025")</f>
         <v/>
       </c>
       <c r="AC3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 31213-2023 tillsynsbegäran.docx", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 49546-2025 tillsynsbegäran.docx", "A 49546-2025")</f>
         <v/>
       </c>
       <c r="AD3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 31213-2023 tillsynsbegäran mail.docx", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 49546-2025 tillsynsbegäran mail.docx", "A 49546-2025")</f>
         <v/>
       </c>
     </row>
@@ -813,7 +813,7 @@
         <v>45679</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 49546-2025</t>
+          <t>A 60295-2022</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -917,14 +917,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>45939</v>
+        <v>44903</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -937,13 +937,13 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>4.4</v>
+        <v>1.1</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -952,7 +952,7 @@
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -961,52 +961,52 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
         <v>2</v>
       </c>
       <c r="T5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>Skogsalm
-Igelkottsröksvamp</t>
+          <t>Klockgroda
+Ätlig groda</t>
         </is>
       </c>
       <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 49546-2025 artfynd.xlsx", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 60295-2022 artfynd.xlsx", "A 60295-2022")</f>
         <v/>
       </c>
       <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 49546-2025 karta.png", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 60295-2022 karta.png", "A 60295-2022")</f>
         <v/>
       </c>
       <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 49546-2025 georefererad karta.tif", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 60295-2022 georefererad karta.tif", "A 60295-2022")</f>
         <v/>
       </c>
       <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 49546-2025 FSC-klagomål.docx", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 60295-2022 FSC-klagomål.docx", "A 60295-2022")</f>
         <v/>
       </c>
       <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 49546-2025 FSC-klagomål mail.docx", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 60295-2022 FSC-klagomål mail.docx", "A 60295-2022")</f>
         <v/>
       </c>
       <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 49546-2025 tillsynsbegäran.docx", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 60295-2022 tillsynsbegäran.docx", "A 60295-2022")</f>
         <v/>
       </c>
       <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 49546-2025 tillsynsbegäran mail.docx", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 60295-2022 tillsynsbegäran mail.docx", "A 60295-2022")</f>
         <v/>
       </c>
     </row>
@@ -1030,7 +1030,7 @@
         <v>44756</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 13766-2023</t>
+          <t>A 61558-2023</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1128,14 +1128,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45007</v>
+        <v>45265</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1147,11 +1147,16 @@
           <t>YSTAD</t>
         </is>
       </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I7" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -1163,7 +1168,7 @@
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1172,10 +1177,10 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1188,42 +1193,42 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 13766-2023 artfynd.xlsx", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 61558-2023 artfynd.xlsx", "A 61558-2023")</f>
         <v/>
       </c>
       <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 13766-2023 karta.png", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 61558-2023 karta.png", "A 61558-2023")</f>
         <v/>
       </c>
       <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 13766-2023 georefererad karta.tif", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 61558-2023 georefererad karta.tif", "A 61558-2023")</f>
         <v/>
       </c>
       <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 13766-2023 FSC-klagomål.docx", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 61558-2023 FSC-klagomål.docx", "A 61558-2023")</f>
         <v/>
       </c>
       <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 13766-2023 FSC-klagomål mail.docx", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 61558-2023 FSC-klagomål mail.docx", "A 61558-2023")</f>
         <v/>
       </c>
       <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 13766-2023 tillsynsbegäran.docx", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 61558-2023 tillsynsbegäran.docx", "A 61558-2023")</f>
         <v/>
       </c>
       <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 13766-2023 tillsynsbegäran mail.docx", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 61558-2023 tillsynsbegäran mail.docx", "A 61558-2023")</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 60891-2024</t>
+          <t>A 49543-2025</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1237,10 +1242,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45644</v>
+        <v>45939</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1253,16 +1258,16 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>16.1</v>
+        <v>1.4</v>
       </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -1277,7 +1282,7 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -1286,42 +1291,42 @@
         <v>1</v>
       </c>
       <c r="T8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U8" t="n">
         <v>0</v>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>Lövgroda</t>
+          <t>Svartöra</t>
         </is>
       </c>
       <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 60891-2024 artfynd.xlsx", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 49543-2025 artfynd.xlsx", "A 49543-2025")</f>
         <v/>
       </c>
       <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 60891-2024 karta.png", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 49543-2025 karta.png", "A 49543-2025")</f>
         <v/>
       </c>
       <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 60891-2024 georefererad karta.tif", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 49543-2025 georefererad karta.tif", "A 49543-2025")</f>
         <v/>
       </c>
       <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 60891-2024 FSC-klagomål.docx", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 49543-2025 FSC-klagomål.docx", "A 49543-2025")</f>
         <v/>
       </c>
       <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 60891-2024 FSC-klagomål mail.docx", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 49543-2025 FSC-klagomål mail.docx", "A 49543-2025")</f>
         <v/>
       </c>
       <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 60891-2024 tillsynsbegäran.docx", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 49543-2025 tillsynsbegäran.docx", "A 49543-2025")</f>
         <v/>
       </c>
       <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 60891-2024 tillsynsbegäran mail.docx", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 49543-2025 tillsynsbegäran mail.docx", "A 49543-2025")</f>
         <v/>
       </c>
     </row>
@@ -1345,7 +1350,7 @@
         <v>45525</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1438,7 +1443,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 49543-2025</t>
+          <t>A 49549-2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1455,7 +1460,7 @@
         <v>45939</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1468,16 +1473,16 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -1492,7 +1497,7 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -1501,49 +1506,49 @@
         <v>1</v>
       </c>
       <c r="T10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>Svartöra</t>
+          <t>Noshornsoxe</t>
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 49543-2025 artfynd.xlsx", "A 49543-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 49549-2025 artfynd.xlsx", "A 49549-2025")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 49543-2025 karta.png", "A 49543-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 49549-2025 karta.png", "A 49549-2025")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 49543-2025 georefererad karta.tif", "A 49543-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 49549-2025 georefererad karta.tif", "A 49549-2025")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 49543-2025 FSC-klagomål.docx", "A 49543-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 49549-2025 FSC-klagomål.docx", "A 49549-2025")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 49543-2025 FSC-klagomål mail.docx", "A 49543-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 49549-2025 FSC-klagomål mail.docx", "A 49549-2025")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 49543-2025 tillsynsbegäran.docx", "A 49543-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 49549-2025 tillsynsbegäran.docx", "A 49549-2025")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 49543-2025 tillsynsbegäran mail.docx", "A 49543-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 49549-2025 tillsynsbegäran mail.docx", "A 49549-2025")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 61558-2023</t>
+          <t>A 13766-2023</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1553,14 +1558,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45265</v>
+        <v>45007</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1572,16 +1577,11 @@
           <t>YSTAD</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I11" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -1593,7 +1593,7 @@
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1602,10 +1602,10 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1618,42 +1618,42 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 61558-2023 artfynd.xlsx", "A 61558-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 13766-2023 artfynd.xlsx", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 61558-2023 karta.png", "A 61558-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 13766-2023 karta.png", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 61558-2023 georefererad karta.tif", "A 61558-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 13766-2023 georefererad karta.tif", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 61558-2023 FSC-klagomål.docx", "A 61558-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 13766-2023 FSC-klagomål.docx", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 61558-2023 FSC-klagomål mail.docx", "A 61558-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 13766-2023 FSC-klagomål mail.docx", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 61558-2023 tillsynsbegäran.docx", "A 61558-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 13766-2023 tillsynsbegäran.docx", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 61558-2023 tillsynsbegäran mail.docx", "A 61558-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 13766-2023 tillsynsbegäran mail.docx", "A 13766-2023")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 49549-2025</t>
+          <t>A 60891-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1667,10 +1667,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45939</v>
+        <v>45644</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1683,13 +1683,13 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.5</v>
+        <v>16.1</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -1719,39 +1719,39 @@
         <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Noshornsoxe</t>
+          <t>Lövgroda</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 49549-2025 artfynd.xlsx", "A 49549-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 60891-2024 artfynd.xlsx", "A 60891-2024")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 49549-2025 karta.png", "A 49549-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 60891-2024 karta.png", "A 60891-2024")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 49549-2025 georefererad karta.tif", "A 49549-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 60891-2024 georefererad karta.tif", "A 60891-2024")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 49549-2025 FSC-klagomål.docx", "A 49549-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 60891-2024 FSC-klagomål.docx", "A 60891-2024")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 49549-2025 FSC-klagomål mail.docx", "A 49549-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 60891-2024 FSC-klagomål mail.docx", "A 60891-2024")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 49549-2025 tillsynsbegäran.docx", "A 49549-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 60891-2024 tillsynsbegäran.docx", "A 60891-2024")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 49549-2025 tillsynsbegäran mail.docx", "A 49549-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 60891-2024 tillsynsbegäran mail.docx", "A 60891-2024")</f>
         <v/>
       </c>
     </row>
@@ -1775,7 +1775,7 @@
         <v>44617</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 60803-2023</t>
+          <t>A 40417-2022</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1845,10 +1845,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45260</v>
+        <v>44823</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1.6</v>
+        <v>2.3</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1904,7 +1904,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 38631-2023</t>
+          <t>A 34302-2024</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1918,10 +1918,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45162</v>
+        <v>45524</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.8</v>
+        <v>1.9</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1977,7 +1977,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 34302-2024</t>
+          <t>A 60803-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1991,10 +1991,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45524</v>
+        <v>45260</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2050,7 +2050,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 40417-2022</t>
+          <t>A 32596-2024</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2064,10 +2064,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44823</v>
+        <v>45513</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2080,7 +2080,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2123,7 +2123,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 22195-2023</t>
+          <t>A 49536-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2137,10 +2137,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45069</v>
+        <v>45939</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2152,13 +2152,8 @@
           <t>YSTAD</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I18" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2201,7 +2196,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 18090-2022</t>
+          <t>A 38631-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2211,14 +2206,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44684</v>
+        <v>45162</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2231,7 +2226,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>4.9</v>
+        <v>0.8</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2274,7 +2269,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 32596-2024</t>
+          <t>A 18090-2022</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2284,14 +2279,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45513</v>
+        <v>44684</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2304,7 +2299,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>2.6</v>
+        <v>4.9</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2347,7 +2342,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 49536-2025</t>
+          <t>A 38413-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2361,10 +2356,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45939</v>
+        <v>46282</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2377,7 +2372,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2420,7 +2415,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 38413-2026</t>
+          <t>A 27578-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2434,10 +2429,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46282</v>
+        <v>46190</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2450,7 +2445,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.6</v>
+        <v>6.6</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2493,7 +2488,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 27578-2026</t>
+          <t>A 22195-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2507,10 +2502,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46190</v>
+        <v>45069</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2522,8 +2517,13 @@
           <t>YSTAD</t>
         </is>
       </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I23" t="n">
-        <v>6.6</v>
+        <v>1.1</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>

--- a/Översikt YSTAD.xlsx
+++ b/Översikt YSTAD.xlsx
@@ -584,7 +584,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A 31213-2023</t>
+          <t>A 3253-2025</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>45113</v>
+        <v>45679</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -613,17 +613,22 @@
           <t>YSTAD</t>
         </is>
       </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I2" t="n">
-        <v>6.5</v>
+        <v>2.5</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
@@ -638,7 +643,7 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -650,40 +655,40 @@
         <v>3</v>
       </c>
       <c r="U2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
-          <t>Skogsveronika
-Skärmstarr</t>
+          <t>Lönnlav
+Strävlosta</t>
         </is>
       </c>
       <c r="W2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 31213-2023 artfynd.xlsx", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 3253-2025 artfynd.xlsx", "A 3253-2025")</f>
         <v/>
       </c>
       <c r="X2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 31213-2023 karta.png", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 3253-2025 karta.png", "A 3253-2025")</f>
         <v/>
       </c>
       <c r="Y2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 31213-2023 georefererad karta.tif", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 3253-2025 georefererad karta.tif", "A 3253-2025")</f>
         <v/>
       </c>
       <c r="AA2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 31213-2023 FSC-klagomål.docx", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 3253-2025 FSC-klagomål.docx", "A 3253-2025")</f>
         <v/>
       </c>
       <c r="AB2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 31213-2023 FSC-klagomål mail.docx", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 3253-2025 FSC-klagomål mail.docx", "A 3253-2025")</f>
         <v/>
       </c>
       <c r="AC2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 31213-2023 tillsynsbegäran.docx", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 3253-2025 tillsynsbegäran.docx", "A 3253-2025")</f>
         <v/>
       </c>
       <c r="AD2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 31213-2023 tillsynsbegäran mail.docx", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 3253-2025 tillsynsbegäran mail.docx", "A 3253-2025")</f>
         <v/>
       </c>
     </row>
@@ -707,7 +712,7 @@
         <v>45939</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -796,7 +801,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 3253-2025</t>
+          <t>A 60295-2022</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -806,14 +811,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45679</v>
+        <v>44903</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -825,19 +830,14 @@
           <t>YSTAD</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I4" t="n">
-        <v>2.5</v>
+        <v>1.1</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -864,50 +864,50 @@
         <v>2</v>
       </c>
       <c r="T4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="U4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>Lönnlav
-Strävlosta</t>
+          <t>Klockgroda
+Ätlig groda</t>
         </is>
       </c>
       <c r="W4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 3253-2025 artfynd.xlsx", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 60295-2022 artfynd.xlsx", "A 60295-2022")</f>
         <v/>
       </c>
       <c r="X4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 3253-2025 karta.png", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 60295-2022 karta.png", "A 60295-2022")</f>
         <v/>
       </c>
       <c r="Y4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 3253-2025 georefererad karta.tif", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 60295-2022 georefererad karta.tif", "A 60295-2022")</f>
         <v/>
       </c>
       <c r="AA4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 3253-2025 FSC-klagomål.docx", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 60295-2022 FSC-klagomål.docx", "A 60295-2022")</f>
         <v/>
       </c>
       <c r="AB4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 3253-2025 FSC-klagomål mail.docx", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 60295-2022 FSC-klagomål mail.docx", "A 60295-2022")</f>
         <v/>
       </c>
       <c r="AC4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 3253-2025 tillsynsbegäran.docx", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 60295-2022 tillsynsbegäran.docx", "A 60295-2022")</f>
         <v/>
       </c>
       <c r="AD4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 3253-2025 tillsynsbegäran mail.docx", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 60295-2022 tillsynsbegäran mail.docx", "A 60295-2022")</f>
         <v/>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 60295-2022</t>
+          <t>A 31213-2023</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -917,14 +917,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>44903</v>
+        <v>45113</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -937,16 +937,16 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>1.1</v>
+        <v>6.5</v>
       </c>
       <c r="J5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -961,7 +961,7 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -970,43 +970,43 @@
         <v>2</v>
       </c>
       <c r="T5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="U5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>Klockgroda
-Ätlig groda</t>
+          <t>Skogsveronika
+Skärmstarr</t>
         </is>
       </c>
       <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 60295-2022 artfynd.xlsx", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 31213-2023 artfynd.xlsx", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 60295-2022 karta.png", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 31213-2023 karta.png", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 60295-2022 georefererad karta.tif", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 31213-2023 georefererad karta.tif", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 60295-2022 FSC-klagomål.docx", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 31213-2023 FSC-klagomål.docx", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 60295-2022 FSC-klagomål mail.docx", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 31213-2023 FSC-klagomål mail.docx", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 60295-2022 tillsynsbegäran.docx", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 31213-2023 tillsynsbegäran.docx", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 60295-2022 tillsynsbegäran mail.docx", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 31213-2023 tillsynsbegäran mail.docx", "A 31213-2023")</f>
         <v/>
       </c>
     </row>
@@ -1030,7 +1030,7 @@
         <v>44756</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 61558-2023</t>
+          <t>A 13766-2023</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1128,14 +1128,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45265</v>
+        <v>45007</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1147,16 +1147,11 @@
           <t>YSTAD</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I7" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -1168,7 +1163,7 @@
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1177,10 +1172,10 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1193,42 +1188,42 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 61558-2023 artfynd.xlsx", "A 61558-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 13766-2023 artfynd.xlsx", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 61558-2023 karta.png", "A 61558-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 13766-2023 karta.png", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 61558-2023 georefererad karta.tif", "A 61558-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 13766-2023 georefererad karta.tif", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 61558-2023 FSC-klagomål.docx", "A 61558-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 13766-2023 FSC-klagomål.docx", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 61558-2023 FSC-klagomål mail.docx", "A 61558-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 13766-2023 FSC-klagomål mail.docx", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 61558-2023 tillsynsbegäran.docx", "A 61558-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 13766-2023 tillsynsbegäran.docx", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 61558-2023 tillsynsbegäran mail.docx", "A 61558-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 13766-2023 tillsynsbegäran mail.docx", "A 13766-2023")</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 49543-2025</t>
+          <t>A 61558-2023</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1242,10 +1237,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45939</v>
+        <v>45265</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1257,8 +1252,13 @@
           <t>YSTAD</t>
         </is>
       </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I8" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1285,55 +1285,55 @@
         <v>1</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
       </c>
       <c r="T8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U8" t="n">
         <v>0</v>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>Svartöra</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 49543-2025 artfynd.xlsx", "A 49543-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 61558-2023 artfynd.xlsx", "A 61558-2023")</f>
         <v/>
       </c>
       <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 49543-2025 karta.png", "A 49543-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 61558-2023 karta.png", "A 61558-2023")</f>
         <v/>
       </c>
       <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 49543-2025 georefererad karta.tif", "A 49543-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 61558-2023 georefererad karta.tif", "A 61558-2023")</f>
         <v/>
       </c>
       <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 49543-2025 FSC-klagomål.docx", "A 49543-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 61558-2023 FSC-klagomål.docx", "A 61558-2023")</f>
         <v/>
       </c>
       <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 49543-2025 FSC-klagomål mail.docx", "A 49543-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 61558-2023 FSC-klagomål mail.docx", "A 61558-2023")</f>
         <v/>
       </c>
       <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 49543-2025 tillsynsbegäran.docx", "A 49543-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 61558-2023 tillsynsbegäran.docx", "A 61558-2023")</f>
         <v/>
       </c>
       <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 49543-2025 tillsynsbegäran mail.docx", "A 49543-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 61558-2023 tillsynsbegäran mail.docx", "A 61558-2023")</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 34341-2024</t>
+          <t>A 49543-2025</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1347,10 +1347,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45525</v>
+        <v>45939</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1362,13 +1362,8 @@
           <t>YSTAD</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I9" t="n">
-        <v>14.4</v>
+        <v>1.4</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1401,42 +1396,42 @@
         <v>1</v>
       </c>
       <c r="T9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>Desmeknopp</t>
+          <t>Svartöra</t>
         </is>
       </c>
       <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 34341-2024 artfynd.xlsx", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 49543-2025 artfynd.xlsx", "A 49543-2025")</f>
         <v/>
       </c>
       <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 34341-2024 karta.png", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 49543-2025 karta.png", "A 49543-2025")</f>
         <v/>
       </c>
       <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 34341-2024 georefererad karta.tif", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 49543-2025 georefererad karta.tif", "A 49543-2025")</f>
         <v/>
       </c>
       <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 34341-2024 FSC-klagomål.docx", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 49543-2025 FSC-klagomål.docx", "A 49543-2025")</f>
         <v/>
       </c>
       <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 34341-2024 FSC-klagomål mail.docx", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 49543-2025 FSC-klagomål mail.docx", "A 49543-2025")</f>
         <v/>
       </c>
       <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 34341-2024 tillsynsbegäran.docx", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 49543-2025 tillsynsbegäran.docx", "A 49543-2025")</f>
         <v/>
       </c>
       <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 34341-2024 tillsynsbegäran mail.docx", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 49543-2025 tillsynsbegäran mail.docx", "A 49543-2025")</f>
         <v/>
       </c>
     </row>
@@ -1460,7 +1455,7 @@
         <v>45939</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1548,7 +1543,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 13766-2023</t>
+          <t>A 60891-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1558,14 +1553,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45007</v>
+        <v>45644</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1578,7 +1573,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0.9</v>
+        <v>16.1</v>
       </c>
       <c r="J11" t="n">
         <v>1</v>
@@ -1618,42 +1613,42 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Lövgroda</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 13766-2023 artfynd.xlsx", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 60891-2024 artfynd.xlsx", "A 60891-2024")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 13766-2023 karta.png", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 60891-2024 karta.png", "A 60891-2024")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 13766-2023 georefererad karta.tif", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 60891-2024 georefererad karta.tif", "A 60891-2024")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 13766-2023 FSC-klagomål.docx", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 60891-2024 FSC-klagomål.docx", "A 60891-2024")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 13766-2023 FSC-klagomål mail.docx", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 60891-2024 FSC-klagomål mail.docx", "A 60891-2024")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 13766-2023 tillsynsbegäran.docx", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 60891-2024 tillsynsbegäran.docx", "A 60891-2024")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 13766-2023 tillsynsbegäran mail.docx", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 60891-2024 tillsynsbegäran mail.docx", "A 60891-2024")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 60891-2024</t>
+          <t>A 34341-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1667,10 +1662,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45644</v>
+        <v>45525</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1682,17 +1677,22 @@
           <t>YSTAD</t>
         </is>
       </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I12" t="n">
-        <v>16.1</v>
+        <v>14.4</v>
       </c>
       <c r="J12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -1707,7 +1707,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -1719,39 +1719,39 @@
         <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Lövgroda</t>
+          <t>Desmeknopp</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 60891-2024 artfynd.xlsx", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 34341-2024 artfynd.xlsx", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 60891-2024 karta.png", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 34341-2024 karta.png", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 60891-2024 georefererad karta.tif", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 34341-2024 georefererad karta.tif", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 60891-2024 FSC-klagomål.docx", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 34341-2024 FSC-klagomål.docx", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 60891-2024 FSC-klagomål mail.docx", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 34341-2024 FSC-klagomål mail.docx", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 60891-2024 tillsynsbegäran.docx", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 34341-2024 tillsynsbegäran.docx", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 60891-2024 tillsynsbegäran mail.docx", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 34341-2024 tillsynsbegäran mail.docx", "A 34341-2024")</f>
         <v/>
       </c>
     </row>
@@ -1775,7 +1775,7 @@
         <v>44617</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         <v>44823</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1904,7 +1904,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 34302-2024</t>
+          <t>A 32596-2024</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1918,10 +1918,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45524</v>
+        <v>45513</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.9</v>
+        <v>2.6</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1977,7 +1977,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 60803-2023</t>
+          <t>A 18090-2022</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1987,14 +1987,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45260</v>
+        <v>44684</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.6</v>
+        <v>4.9</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2050,7 +2050,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 32596-2024</t>
+          <t>A 49536-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2064,10 +2064,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45513</v>
+        <v>45939</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2080,7 +2080,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>2.6</v>
+        <v>1.5</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2123,7 +2123,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 49536-2025</t>
+          <t>A 60803-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2137,10 +2137,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45939</v>
+        <v>45260</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2213,7 +2213,7 @@
         <v>45162</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2269,7 +2269,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 18090-2022</t>
+          <t>A 22195-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2279,14 +2279,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44684</v>
+        <v>45069</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2298,8 +2298,13 @@
           <t>YSTAD</t>
         </is>
       </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I20" t="n">
-        <v>4.9</v>
+        <v>1.1</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2359,7 +2364,7 @@
         <v>46282</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2432,7 +2437,7 @@
         <v>46190</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2488,7 +2493,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 22195-2023</t>
+          <t>A 34302-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2502,10 +2507,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45069</v>
+        <v>45524</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2517,13 +2522,8 @@
           <t>YSTAD</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I23" t="n">
-        <v>1.1</v>
+        <v>1.9</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>

--- a/Översikt YSTAD.xlsx
+++ b/Översikt YSTAD.xlsx
@@ -601,7 +601,7 @@
         <v>45679</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -712,7 +712,7 @@
         <v>45939</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -818,7 +818,7 @@
         <v>44903</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -924,7 +924,7 @@
         <v>45113</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>44756</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1135,7 +1135,7 @@
         <v>45007</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>45265</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
         <v>45939</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         <v>45939</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
         <v>45644</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1665,7 +1665,7 @@
         <v>45525</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1775,7 +1775,7 @@
         <v>44617</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         <v>44823</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
         <v>45513</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1994,7 +1994,7 @@
         <v>44684</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2067,7 +2067,7 @@
         <v>45939</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2140,7 +2140,7 @@
         <v>45260</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>45162</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2286,7 +2286,7 @@
         <v>45069</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         <v>46282</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
         <v>46190</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2510,7 +2510,7 @@
         <v>45524</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>

--- a/Översikt YSTAD.xlsx
+++ b/Översikt YSTAD.xlsx
@@ -601,7 +601,7 @@
         <v>45679</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -712,7 +712,7 @@
         <v>45939</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -818,7 +818,7 @@
         <v>44903</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -924,7 +924,7 @@
         <v>45113</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>44756</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1135,7 +1135,7 @@
         <v>45007</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>45265</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
         <v>45939</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         <v>45939</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
         <v>45644</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1665,7 +1665,7 @@
         <v>45525</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1775,7 +1775,7 @@
         <v>44617</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         <v>44823</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
         <v>45513</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1994,7 +1994,7 @@
         <v>44684</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2067,7 +2067,7 @@
         <v>45939</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2140,7 +2140,7 @@
         <v>45260</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>45162</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2286,7 +2286,7 @@
         <v>45069</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         <v>46282</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
         <v>46190</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2510,7 +2510,7 @@
         <v>45524</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>

--- a/Översikt YSTAD.xlsx
+++ b/Översikt YSTAD.xlsx
@@ -584,7 +584,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A 3253-2025</t>
+          <t>A 31213-2023</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>45679</v>
+        <v>45113</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -613,22 +613,17 @@
           <t>YSTAD</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I2" t="n">
-        <v>2.5</v>
+        <v>6.5</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
@@ -643,7 +638,7 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -655,47 +650,47 @@
         <v>3</v>
       </c>
       <c r="U2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
-          <t>Lönnlav
-Strävlosta</t>
+          <t>Skogsveronika
+Skärmstarr</t>
         </is>
       </c>
       <c r="W2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 3253-2025 artfynd.xlsx", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 31213-2023 artfynd.xlsx", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="X2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 3253-2025 karta.png", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 31213-2023 karta.png", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="Y2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 3253-2025 georefererad karta.tif", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 31213-2023 georefererad karta.tif", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="AA2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 3253-2025 FSC-klagomål.docx", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 31213-2023 FSC-klagomål.docx", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="AB2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 3253-2025 FSC-klagomål mail.docx", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 31213-2023 FSC-klagomål mail.docx", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="AC2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 3253-2025 tillsynsbegäran.docx", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 31213-2023 tillsynsbegäran.docx", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="AD2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 3253-2025 tillsynsbegäran mail.docx", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 31213-2023 tillsynsbegäran mail.docx", "A 31213-2023")</f>
         <v/>
       </c>
     </row>
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 49546-2025</t>
+          <t>A 3253-2025</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -709,10 +704,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>45939</v>
+        <v>45679</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -724,14 +719,19 @@
           <t>YSTAD</t>
         </is>
       </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I3" t="n">
-        <v>4.4</v>
+        <v>2.5</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -740,7 +740,7 @@
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -749,59 +749,59 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
         <v>2</v>
       </c>
       <c r="T3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
-          <t>Skogsalm
-Igelkottsröksvamp</t>
+          <t>Lönnlav
+Strävlosta</t>
         </is>
       </c>
       <c r="W3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 49546-2025 artfynd.xlsx", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 3253-2025 artfynd.xlsx", "A 3253-2025")</f>
         <v/>
       </c>
       <c r="X3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 49546-2025 karta.png", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 3253-2025 karta.png", "A 3253-2025")</f>
         <v/>
       </c>
       <c r="Y3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 49546-2025 georefererad karta.tif", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 3253-2025 georefererad karta.tif", "A 3253-2025")</f>
         <v/>
       </c>
       <c r="AA3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 49546-2025 FSC-klagomål.docx", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 3253-2025 FSC-klagomål.docx", "A 3253-2025")</f>
         <v/>
       </c>
       <c r="AB3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 49546-2025 FSC-klagomål mail.docx", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 3253-2025 FSC-klagomål mail.docx", "A 3253-2025")</f>
         <v/>
       </c>
       <c r="AC3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 49546-2025 tillsynsbegäran.docx", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 3253-2025 tillsynsbegäran.docx", "A 3253-2025")</f>
         <v/>
       </c>
       <c r="AD3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 49546-2025 tillsynsbegäran mail.docx", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 3253-2025 tillsynsbegäran mail.docx", "A 3253-2025")</f>
         <v/>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 60295-2022</t>
+          <t>A 49546-2025</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -811,14 +811,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>44903</v>
+        <v>45939</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -831,13 +831,13 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>1.1</v>
+        <v>4.4</v>
       </c>
       <c r="J4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -846,7 +846,7 @@
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -855,59 +855,59 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S4" t="n">
         <v>2</v>
       </c>
       <c r="T4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="U4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>Klockgroda
-Ätlig groda</t>
+          <t>Skogsalm
+Igelkottsröksvamp</t>
         </is>
       </c>
       <c r="W4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 60295-2022 artfynd.xlsx", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 49546-2025 artfynd.xlsx", "A 49546-2025")</f>
         <v/>
       </c>
       <c r="X4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 60295-2022 karta.png", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 49546-2025 karta.png", "A 49546-2025")</f>
         <v/>
       </c>
       <c r="Y4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 60295-2022 georefererad karta.tif", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 49546-2025 georefererad karta.tif", "A 49546-2025")</f>
         <v/>
       </c>
       <c r="AA4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 60295-2022 FSC-klagomål.docx", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 49546-2025 FSC-klagomål.docx", "A 49546-2025")</f>
         <v/>
       </c>
       <c r="AB4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 60295-2022 FSC-klagomål mail.docx", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 49546-2025 FSC-klagomål mail.docx", "A 49546-2025")</f>
         <v/>
       </c>
       <c r="AC4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 60295-2022 tillsynsbegäran.docx", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 49546-2025 tillsynsbegäran.docx", "A 49546-2025")</f>
         <v/>
       </c>
       <c r="AD4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 60295-2022 tillsynsbegäran mail.docx", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 49546-2025 tillsynsbegäran mail.docx", "A 49546-2025")</f>
         <v/>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 31213-2023</t>
+          <t>A 60295-2022</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -917,14 +917,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>45113</v>
+        <v>44903</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -937,16 +937,16 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>6.5</v>
+        <v>1.1</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -961,7 +961,7 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -970,43 +970,43 @@
         <v>2</v>
       </c>
       <c r="T5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="U5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>Skogsveronika
-Skärmstarr</t>
+          <t>Klockgroda
+Ätlig groda</t>
         </is>
       </c>
       <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 31213-2023 artfynd.xlsx", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 60295-2022 artfynd.xlsx", "A 60295-2022")</f>
         <v/>
       </c>
       <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 31213-2023 karta.png", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 60295-2022 karta.png", "A 60295-2022")</f>
         <v/>
       </c>
       <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 31213-2023 georefererad karta.tif", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 60295-2022 georefererad karta.tif", "A 60295-2022")</f>
         <v/>
       </c>
       <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 31213-2023 FSC-klagomål.docx", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 60295-2022 FSC-klagomål.docx", "A 60295-2022")</f>
         <v/>
       </c>
       <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 31213-2023 FSC-klagomål mail.docx", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 60295-2022 FSC-klagomål mail.docx", "A 60295-2022")</f>
         <v/>
       </c>
       <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 31213-2023 tillsynsbegäran.docx", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 60295-2022 tillsynsbegäran.docx", "A 60295-2022")</f>
         <v/>
       </c>
       <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 31213-2023 tillsynsbegäran mail.docx", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 60295-2022 tillsynsbegäran mail.docx", "A 60295-2022")</f>
         <v/>
       </c>
     </row>
@@ -1030,7 +1030,7 @@
         <v>44756</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 13766-2023</t>
+          <t>A 61558-2023</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1128,14 +1128,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45007</v>
+        <v>45265</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1147,11 +1147,16 @@
           <t>YSTAD</t>
         </is>
       </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I7" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -1163,7 +1168,7 @@
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1172,10 +1177,10 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1188,42 +1193,42 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 13766-2023 artfynd.xlsx", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 61558-2023 artfynd.xlsx", "A 61558-2023")</f>
         <v/>
       </c>
       <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 13766-2023 karta.png", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 61558-2023 karta.png", "A 61558-2023")</f>
         <v/>
       </c>
       <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 13766-2023 georefererad karta.tif", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 61558-2023 georefererad karta.tif", "A 61558-2023")</f>
         <v/>
       </c>
       <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 13766-2023 FSC-klagomål.docx", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 61558-2023 FSC-klagomål.docx", "A 61558-2023")</f>
         <v/>
       </c>
       <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 13766-2023 FSC-klagomål mail.docx", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 61558-2023 FSC-klagomål mail.docx", "A 61558-2023")</f>
         <v/>
       </c>
       <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 13766-2023 tillsynsbegäran.docx", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 61558-2023 tillsynsbegäran.docx", "A 61558-2023")</f>
         <v/>
       </c>
       <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 13766-2023 tillsynsbegäran mail.docx", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 61558-2023 tillsynsbegäran mail.docx", "A 61558-2023")</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 61558-2023</t>
+          <t>A 34341-2024</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1237,10 +1242,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45265</v>
+        <v>45525</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1254,11 +1259,11 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Övriga statliga verk och myndigheter</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1.5</v>
+        <v>14.4</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1267,13 +1272,13 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1285,7 +1290,7 @@
         <v>1</v>
       </c>
       <c r="R8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1294,39 +1299,39 @@
         <v>1</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Desmeknopp</t>
         </is>
       </c>
       <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 61558-2023 artfynd.xlsx", "A 61558-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 34341-2024 artfynd.xlsx", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 61558-2023 karta.png", "A 61558-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 34341-2024 karta.png", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 61558-2023 georefererad karta.tif", "A 61558-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 34341-2024 georefererad karta.tif", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 61558-2023 FSC-klagomål.docx", "A 61558-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 34341-2024 FSC-klagomål.docx", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 61558-2023 FSC-klagomål mail.docx", "A 61558-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 34341-2024 FSC-klagomål mail.docx", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 61558-2023 tillsynsbegäran.docx", "A 61558-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 34341-2024 tillsynsbegäran.docx", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 61558-2023 tillsynsbegäran mail.docx", "A 61558-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 34341-2024 tillsynsbegäran mail.docx", "A 34341-2024")</f>
         <v/>
       </c>
     </row>
@@ -1350,7 +1355,7 @@
         <v>45939</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1455,7 +1460,7 @@
         <v>45939</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1543,7 +1548,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 60891-2024</t>
+          <t>A 13766-2023</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1553,14 +1558,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45644</v>
+        <v>45007</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1573,7 +1578,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>16.1</v>
+        <v>0.9</v>
       </c>
       <c r="J11" t="n">
         <v>1</v>
@@ -1613,42 +1618,42 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Lövgroda</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 60891-2024 artfynd.xlsx", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 13766-2023 artfynd.xlsx", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 60891-2024 karta.png", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 13766-2023 karta.png", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 60891-2024 georefererad karta.tif", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 13766-2023 georefererad karta.tif", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 60891-2024 FSC-klagomål.docx", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 13766-2023 FSC-klagomål.docx", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 60891-2024 FSC-klagomål mail.docx", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 13766-2023 FSC-klagomål mail.docx", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 60891-2024 tillsynsbegäran.docx", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 13766-2023 tillsynsbegäran.docx", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 60891-2024 tillsynsbegäran mail.docx", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 13766-2023 tillsynsbegäran mail.docx", "A 13766-2023")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 34341-2024</t>
+          <t>A 60891-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1662,10 +1667,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45525</v>
+        <v>45644</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1677,22 +1682,17 @@
           <t>YSTAD</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I12" t="n">
-        <v>14.4</v>
+        <v>16.1</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -1707,7 +1707,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -1719,39 +1719,39 @@
         <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Desmeknopp</t>
+          <t>Lövgroda</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 34341-2024 artfynd.xlsx", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 60891-2024 artfynd.xlsx", "A 60891-2024")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 34341-2024 karta.png", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 60891-2024 karta.png", "A 60891-2024")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 34341-2024 georefererad karta.tif", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 60891-2024 georefererad karta.tif", "A 60891-2024")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 34341-2024 FSC-klagomål.docx", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 60891-2024 FSC-klagomål.docx", "A 60891-2024")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 34341-2024 FSC-klagomål mail.docx", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 60891-2024 FSC-klagomål mail.docx", "A 60891-2024")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 34341-2024 tillsynsbegäran.docx", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 60891-2024 tillsynsbegäran.docx", "A 60891-2024")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 34341-2024 tillsynsbegäran mail.docx", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 60891-2024 tillsynsbegäran mail.docx", "A 60891-2024")</f>
         <v/>
       </c>
     </row>
@@ -1775,7 +1775,7 @@
         <v>44617</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         <v>44823</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1904,7 +1904,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 32596-2024</t>
+          <t>A 34302-2024</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1918,10 +1918,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45513</v>
+        <v>45524</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>2.6</v>
+        <v>1.9</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1977,7 +1977,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 18090-2022</t>
+          <t>A 32596-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1987,14 +1987,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44684</v>
+        <v>45513</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>4.9</v>
+        <v>2.6</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2050,7 +2050,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 49536-2025</t>
+          <t>A 60803-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2064,10 +2064,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45939</v>
+        <v>45260</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2080,7 +2080,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2123,7 +2123,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 60803-2023</t>
+          <t>A 49536-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2137,10 +2137,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45260</v>
+        <v>45939</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2213,7 +2213,7 @@
         <v>45162</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2269,7 +2269,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 22195-2023</t>
+          <t>A 18090-2022</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2279,14 +2279,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45069</v>
+        <v>44684</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2298,13 +2298,8 @@
           <t>YSTAD</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I20" t="n">
-        <v>1.1</v>
+        <v>4.9</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2364,7 +2359,7 @@
         <v>46282</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2437,7 +2432,7 @@
         <v>46190</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2493,7 +2488,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 34302-2024</t>
+          <t>A 22195-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2507,10 +2502,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45524</v>
+        <v>45069</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2522,8 +2517,13 @@
           <t>YSTAD</t>
         </is>
       </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I23" t="n">
-        <v>1.9</v>
+        <v>1.1</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>

--- a/Översikt YSTAD.xlsx
+++ b/Översikt YSTAD.xlsx
@@ -584,7 +584,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A 31213-2023</t>
+          <t>A 3253-2025</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>45113</v>
+        <v>45679</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -613,17 +613,22 @@
           <t>YSTAD</t>
         </is>
       </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I2" t="n">
-        <v>6.5</v>
+        <v>2.5</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
@@ -638,7 +643,7 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -650,47 +655,47 @@
         <v>3</v>
       </c>
       <c r="U2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
-          <t>Skogsveronika
-Skärmstarr</t>
+          <t>Lönnlav
+Strävlosta</t>
         </is>
       </c>
       <c r="W2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 31213-2023 artfynd.xlsx", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 3253-2025 artfynd.xlsx", "A 3253-2025")</f>
         <v/>
       </c>
       <c r="X2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 31213-2023 karta.png", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 3253-2025 karta.png", "A 3253-2025")</f>
         <v/>
       </c>
       <c r="Y2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 31213-2023 georefererad karta.tif", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 3253-2025 georefererad karta.tif", "A 3253-2025")</f>
         <v/>
       </c>
       <c r="AA2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 31213-2023 FSC-klagomål.docx", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 3253-2025 FSC-klagomål.docx", "A 3253-2025")</f>
         <v/>
       </c>
       <c r="AB2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 31213-2023 FSC-klagomål mail.docx", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 3253-2025 FSC-klagomål mail.docx", "A 3253-2025")</f>
         <v/>
       </c>
       <c r="AC2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 31213-2023 tillsynsbegäran.docx", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 3253-2025 tillsynsbegäran.docx", "A 3253-2025")</f>
         <v/>
       </c>
       <c r="AD2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 31213-2023 tillsynsbegäran mail.docx", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 3253-2025 tillsynsbegäran mail.docx", "A 3253-2025")</f>
         <v/>
       </c>
     </row>
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 3253-2025</t>
+          <t>A 49546-2025</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -704,10 +709,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>45679</v>
+        <v>45939</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -719,19 +724,14 @@
           <t>YSTAD</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I3" t="n">
-        <v>2.5</v>
+        <v>4.4</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -740,7 +740,7 @@
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -749,59 +749,59 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S3" t="n">
         <v>2</v>
       </c>
       <c r="T3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
-          <t>Lönnlav
-Strävlosta</t>
+          <t>Skogsalm
+Igelkottsröksvamp</t>
         </is>
       </c>
       <c r="W3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 3253-2025 artfynd.xlsx", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 49546-2025 artfynd.xlsx", "A 49546-2025")</f>
         <v/>
       </c>
       <c r="X3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 3253-2025 karta.png", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 49546-2025 karta.png", "A 49546-2025")</f>
         <v/>
       </c>
       <c r="Y3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 3253-2025 georefererad karta.tif", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 49546-2025 georefererad karta.tif", "A 49546-2025")</f>
         <v/>
       </c>
       <c r="AA3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 3253-2025 FSC-klagomål.docx", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 49546-2025 FSC-klagomål.docx", "A 49546-2025")</f>
         <v/>
       </c>
       <c r="AB3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 3253-2025 FSC-klagomål mail.docx", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 49546-2025 FSC-klagomål mail.docx", "A 49546-2025")</f>
         <v/>
       </c>
       <c r="AC3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 3253-2025 tillsynsbegäran.docx", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 49546-2025 tillsynsbegäran.docx", "A 49546-2025")</f>
         <v/>
       </c>
       <c r="AD3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 3253-2025 tillsynsbegäran mail.docx", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 49546-2025 tillsynsbegäran mail.docx", "A 49546-2025")</f>
         <v/>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 49546-2025</t>
+          <t>A 60295-2022</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -811,14 +811,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45939</v>
+        <v>44903</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -831,13 +831,13 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>4.4</v>
+        <v>1.1</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -846,7 +846,7 @@
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -855,59 +855,59 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>2</v>
       </c>
       <c r="T4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>Skogsalm
-Igelkottsröksvamp</t>
+          <t>Klockgroda
+Ätlig groda</t>
         </is>
       </c>
       <c r="W4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 49546-2025 artfynd.xlsx", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 60295-2022 artfynd.xlsx", "A 60295-2022")</f>
         <v/>
       </c>
       <c r="X4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 49546-2025 karta.png", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 60295-2022 karta.png", "A 60295-2022")</f>
         <v/>
       </c>
       <c r="Y4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 49546-2025 georefererad karta.tif", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 60295-2022 georefererad karta.tif", "A 60295-2022")</f>
         <v/>
       </c>
       <c r="AA4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 49546-2025 FSC-klagomål.docx", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 60295-2022 FSC-klagomål.docx", "A 60295-2022")</f>
         <v/>
       </c>
       <c r="AB4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 49546-2025 FSC-klagomål mail.docx", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 60295-2022 FSC-klagomål mail.docx", "A 60295-2022")</f>
         <v/>
       </c>
       <c r="AC4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 49546-2025 tillsynsbegäran.docx", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 60295-2022 tillsynsbegäran.docx", "A 60295-2022")</f>
         <v/>
       </c>
       <c r="AD4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 49546-2025 tillsynsbegäran mail.docx", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 60295-2022 tillsynsbegäran mail.docx", "A 60295-2022")</f>
         <v/>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 60295-2022</t>
+          <t>A 31213-2023</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -917,14 +917,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>44903</v>
+        <v>45113</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -937,16 +937,16 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>1.1</v>
+        <v>6.5</v>
       </c>
       <c r="J5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -961,7 +961,7 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -970,43 +970,43 @@
         <v>2</v>
       </c>
       <c r="T5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="U5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>Klockgroda
-Ätlig groda</t>
+          <t>Skogsveronika
+Skärmstarr</t>
         </is>
       </c>
       <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 60295-2022 artfynd.xlsx", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 31213-2023 artfynd.xlsx", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 60295-2022 karta.png", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 31213-2023 karta.png", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 60295-2022 georefererad karta.tif", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 31213-2023 georefererad karta.tif", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 60295-2022 FSC-klagomål.docx", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 31213-2023 FSC-klagomål.docx", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 60295-2022 FSC-klagomål mail.docx", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 31213-2023 FSC-klagomål mail.docx", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 60295-2022 tillsynsbegäran.docx", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 31213-2023 tillsynsbegäran.docx", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 60295-2022 tillsynsbegäran mail.docx", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 31213-2023 tillsynsbegäran mail.docx", "A 31213-2023")</f>
         <v/>
       </c>
     </row>
@@ -1030,7 +1030,7 @@
         <v>44756</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 61558-2023</t>
+          <t>A 13766-2023</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1128,14 +1128,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45265</v>
+        <v>45007</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1147,16 +1147,11 @@
           <t>YSTAD</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I7" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -1168,7 +1163,7 @@
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1177,10 +1172,10 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1193,42 +1188,42 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 61558-2023 artfynd.xlsx", "A 61558-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 13766-2023 artfynd.xlsx", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 61558-2023 karta.png", "A 61558-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 13766-2023 karta.png", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 61558-2023 georefererad karta.tif", "A 61558-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 13766-2023 georefererad karta.tif", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 61558-2023 FSC-klagomål.docx", "A 61558-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 13766-2023 FSC-klagomål.docx", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 61558-2023 FSC-klagomål mail.docx", "A 61558-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 13766-2023 FSC-klagomål mail.docx", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 61558-2023 tillsynsbegäran.docx", "A 61558-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 13766-2023 tillsynsbegäran.docx", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 61558-2023 tillsynsbegäran mail.docx", "A 61558-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 13766-2023 tillsynsbegäran mail.docx", "A 13766-2023")</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 34341-2024</t>
+          <t>A 61558-2023</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1242,10 +1237,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45525</v>
+        <v>45265</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1259,11 +1254,11 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Övriga statliga verk och myndigheter</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>14.4</v>
+        <v>1.5</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1272,13 +1267,13 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1290,7 +1285,7 @@
         <v>1</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1299,39 +1294,39 @@
         <v>1</v>
       </c>
       <c r="U8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>Desmeknopp</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 34341-2024 artfynd.xlsx", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 61558-2023 artfynd.xlsx", "A 61558-2023")</f>
         <v/>
       </c>
       <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 34341-2024 karta.png", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 61558-2023 karta.png", "A 61558-2023")</f>
         <v/>
       </c>
       <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 34341-2024 georefererad karta.tif", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 61558-2023 georefererad karta.tif", "A 61558-2023")</f>
         <v/>
       </c>
       <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 34341-2024 FSC-klagomål.docx", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 61558-2023 FSC-klagomål.docx", "A 61558-2023")</f>
         <v/>
       </c>
       <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 34341-2024 FSC-klagomål mail.docx", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 61558-2023 FSC-klagomål mail.docx", "A 61558-2023")</f>
         <v/>
       </c>
       <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 34341-2024 tillsynsbegäran.docx", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 61558-2023 tillsynsbegäran.docx", "A 61558-2023")</f>
         <v/>
       </c>
       <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 34341-2024 tillsynsbegäran mail.docx", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 61558-2023 tillsynsbegäran mail.docx", "A 61558-2023")</f>
         <v/>
       </c>
     </row>
@@ -1355,7 +1350,7 @@
         <v>45939</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1460,7 +1455,7 @@
         <v>45939</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1548,7 +1543,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 13766-2023</t>
+          <t>A 60891-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1558,14 +1553,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45007</v>
+        <v>45644</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1578,7 +1573,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0.9</v>
+        <v>16.1</v>
       </c>
       <c r="J11" t="n">
         <v>1</v>
@@ -1618,42 +1613,42 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Lövgroda</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 13766-2023 artfynd.xlsx", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 60891-2024 artfynd.xlsx", "A 60891-2024")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 13766-2023 karta.png", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 60891-2024 karta.png", "A 60891-2024")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 13766-2023 georefererad karta.tif", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 60891-2024 georefererad karta.tif", "A 60891-2024")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 13766-2023 FSC-klagomål.docx", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 60891-2024 FSC-klagomål.docx", "A 60891-2024")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 13766-2023 FSC-klagomål mail.docx", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 60891-2024 FSC-klagomål mail.docx", "A 60891-2024")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 13766-2023 tillsynsbegäran.docx", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 60891-2024 tillsynsbegäran.docx", "A 60891-2024")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 13766-2023 tillsynsbegäran mail.docx", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 60891-2024 tillsynsbegäran mail.docx", "A 60891-2024")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 60891-2024</t>
+          <t>A 34341-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1667,10 +1662,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45644</v>
+        <v>45525</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1682,17 +1677,22 @@
           <t>YSTAD</t>
         </is>
       </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I12" t="n">
-        <v>16.1</v>
+        <v>14.4</v>
       </c>
       <c r="J12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -1707,7 +1707,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -1719,39 +1719,39 @@
         <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Lövgroda</t>
+          <t>Desmeknopp</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 60891-2024 artfynd.xlsx", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 34341-2024 artfynd.xlsx", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 60891-2024 karta.png", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 34341-2024 karta.png", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 60891-2024 georefererad karta.tif", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 34341-2024 georefererad karta.tif", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 60891-2024 FSC-klagomål.docx", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 34341-2024 FSC-klagomål.docx", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 60891-2024 FSC-klagomål mail.docx", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 34341-2024 FSC-klagomål mail.docx", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 60891-2024 tillsynsbegäran.docx", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 34341-2024 tillsynsbegäran.docx", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 60891-2024 tillsynsbegäran mail.docx", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 34341-2024 tillsynsbegäran mail.docx", "A 34341-2024")</f>
         <v/>
       </c>
     </row>
@@ -1775,7 +1775,7 @@
         <v>44617</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 40417-2022</t>
+          <t>A 32596-2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1845,10 +1845,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44823</v>
+        <v>45513</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1904,7 +1904,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 34302-2024</t>
+          <t>A 40417-2022</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1918,10 +1918,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45524</v>
+        <v>44823</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1977,7 +1977,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 32596-2024</t>
+          <t>A 49536-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1991,10 +1991,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45513</v>
+        <v>45939</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>2.6</v>
+        <v>1.5</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2050,7 +2050,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 60803-2023</t>
+          <t>A 18090-2022</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2060,14 +2060,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45260</v>
+        <v>44684</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2080,7 +2080,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1.6</v>
+        <v>4.9</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2123,7 +2123,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 49536-2025</t>
+          <t>A 60803-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2137,10 +2137,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45939</v>
+        <v>45260</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2213,7 +2213,7 @@
         <v>45162</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2269,7 +2269,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 18090-2022</t>
+          <t>A 38413-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2279,14 +2279,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44684</v>
+        <v>46282</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2299,7 +2299,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>4.9</v>
+        <v>0.6</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2342,7 +2342,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 38413-2026</t>
+          <t>A 27578-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2356,10 +2356,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46282</v>
+        <v>46190</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2372,7 +2372,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.6</v>
+        <v>6.6</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2415,7 +2415,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 27578-2026</t>
+          <t>A 22195-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2429,10 +2429,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46190</v>
+        <v>45069</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2444,8 +2444,13 @@
           <t>YSTAD</t>
         </is>
       </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I22" t="n">
-        <v>6.6</v>
+        <v>1.1</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2488,7 +2493,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 22195-2023</t>
+          <t>A 34302-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2502,10 +2507,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45069</v>
+        <v>45524</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2517,13 +2522,8 @@
           <t>YSTAD</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I23" t="n">
-        <v>1.1</v>
+        <v>1.9</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>

--- a/Översikt YSTAD.xlsx
+++ b/Översikt YSTAD.xlsx
@@ -601,7 +601,7 @@
         <v>45679</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -695,7 +695,7 @@
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 49546-2025</t>
+          <t>A 31213-2023</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -709,10 +709,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>45939</v>
+        <v>45113</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -725,22 +725,22 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>4.4</v>
+        <v>6.5</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -752,49 +752,49 @@
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
         <v>2</v>
       </c>
       <c r="T3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
-          <t>Skogsalm
-Igelkottsröksvamp</t>
+          <t>Skogsveronika
+Skärmstarr</t>
         </is>
       </c>
       <c r="W3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 49546-2025 artfynd.xlsx", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 31213-2023 artfynd.xlsx", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="X3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 49546-2025 karta.png", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 31213-2023 karta.png", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="Y3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 49546-2025 georefererad karta.tif", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 31213-2023 georefererad karta.tif", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="AA3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 49546-2025 FSC-klagomål.docx", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 31213-2023 FSC-klagomål.docx", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="AB3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 49546-2025 FSC-klagomål mail.docx", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 31213-2023 FSC-klagomål mail.docx", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="AC3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 49546-2025 tillsynsbegäran.docx", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 31213-2023 tillsynsbegäran.docx", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="AD3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 49546-2025 tillsynsbegäran mail.docx", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 31213-2023 tillsynsbegäran mail.docx", "A 31213-2023")</f>
         <v/>
       </c>
     </row>
@@ -818,7 +818,7 @@
         <v>44903</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 31213-2023</t>
+          <t>A 49546-2025</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -921,10 +921,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>45113</v>
+        <v>45939</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -937,22 +937,22 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>6.5</v>
+        <v>4.4</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -964,49 +964,49 @@
         <v>1</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S5" t="n">
         <v>2</v>
       </c>
       <c r="T5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>Skogsveronika
-Skärmstarr</t>
+          <t>Skogsalm
+Igelkottsröksvamp</t>
         </is>
       </c>
       <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 31213-2023 artfynd.xlsx", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 49546-2025 artfynd.xlsx", "A 49546-2025")</f>
         <v/>
       </c>
       <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 31213-2023 karta.png", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 49546-2025 karta.png", "A 49546-2025")</f>
         <v/>
       </c>
       <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 31213-2023 georefererad karta.tif", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 49546-2025 georefererad karta.tif", "A 49546-2025")</f>
         <v/>
       </c>
       <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 31213-2023 FSC-klagomål.docx", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 49546-2025 FSC-klagomål.docx", "A 49546-2025")</f>
         <v/>
       </c>
       <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 31213-2023 FSC-klagomål mail.docx", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 49546-2025 FSC-klagomål mail.docx", "A 49546-2025")</f>
         <v/>
       </c>
       <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 31213-2023 tillsynsbegäran.docx", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 49546-2025 tillsynsbegäran.docx", "A 49546-2025")</f>
         <v/>
       </c>
       <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 31213-2023 tillsynsbegäran mail.docx", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 49546-2025 tillsynsbegäran mail.docx", "A 49546-2025")</f>
         <v/>
       </c>
     </row>
@@ -1030,7 +1030,7 @@
         <v>44756</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 13766-2023</t>
+          <t>A 61558-2023</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1128,14 +1128,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45007</v>
+        <v>45265</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1147,11 +1147,16 @@
           <t>YSTAD</t>
         </is>
       </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I7" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -1163,7 +1168,7 @@
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1172,10 +1177,10 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1188,42 +1193,42 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 13766-2023 artfynd.xlsx", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 61558-2023 artfynd.xlsx", "A 61558-2023")</f>
         <v/>
       </c>
       <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 13766-2023 karta.png", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 61558-2023 karta.png", "A 61558-2023")</f>
         <v/>
       </c>
       <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 13766-2023 georefererad karta.tif", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 61558-2023 georefererad karta.tif", "A 61558-2023")</f>
         <v/>
       </c>
       <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 13766-2023 FSC-klagomål.docx", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 61558-2023 FSC-klagomål.docx", "A 61558-2023")</f>
         <v/>
       </c>
       <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 13766-2023 FSC-klagomål mail.docx", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 61558-2023 FSC-klagomål mail.docx", "A 61558-2023")</f>
         <v/>
       </c>
       <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 13766-2023 tillsynsbegäran.docx", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 61558-2023 tillsynsbegäran.docx", "A 61558-2023")</f>
         <v/>
       </c>
       <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 13766-2023 tillsynsbegäran mail.docx", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 61558-2023 tillsynsbegäran mail.docx", "A 61558-2023")</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 61558-2023</t>
+          <t>A 13766-2023</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1233,14 +1238,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45265</v>
+        <v>45007</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1252,16 +1257,11 @@
           <t>YSTAD</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I8" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -1273,7 +1273,7 @@
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1282,10 +1282,10 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1298,35 +1298,35 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 61558-2023 artfynd.xlsx", "A 61558-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 13766-2023 artfynd.xlsx", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 61558-2023 karta.png", "A 61558-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 13766-2023 karta.png", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 61558-2023 georefererad karta.tif", "A 61558-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 13766-2023 georefererad karta.tif", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 61558-2023 FSC-klagomål.docx", "A 61558-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 13766-2023 FSC-klagomål.docx", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 61558-2023 FSC-klagomål mail.docx", "A 61558-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 13766-2023 FSC-klagomål mail.docx", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 61558-2023 tillsynsbegäran.docx", "A 61558-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 13766-2023 tillsynsbegäran.docx", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 61558-2023 tillsynsbegäran mail.docx", "A 61558-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 13766-2023 tillsynsbegäran mail.docx", "A 13766-2023")</f>
         <v/>
       </c>
     </row>
@@ -1350,7 +1350,7 @@
         <v>45939</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 49549-2025</t>
+          <t>A 60891-2024</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1452,10 +1452,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45939</v>
+        <v>45644</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1468,13 +1468,13 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>0.5</v>
+        <v>16.1</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -1504,46 +1504,46 @@
         <v>1</v>
       </c>
       <c r="U10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>Noshornsoxe</t>
+          <t>Lövgroda</t>
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 49549-2025 artfynd.xlsx", "A 49549-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 60891-2024 artfynd.xlsx", "A 60891-2024")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 49549-2025 karta.png", "A 49549-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 60891-2024 karta.png", "A 60891-2024")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 49549-2025 georefererad karta.tif", "A 49549-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 60891-2024 georefererad karta.tif", "A 60891-2024")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 49549-2025 FSC-klagomål.docx", "A 49549-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 60891-2024 FSC-klagomål.docx", "A 60891-2024")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 49549-2025 FSC-klagomål mail.docx", "A 49549-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 60891-2024 FSC-klagomål mail.docx", "A 60891-2024")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 49549-2025 tillsynsbegäran.docx", "A 49549-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 60891-2024 tillsynsbegäran.docx", "A 60891-2024")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 49549-2025 tillsynsbegäran mail.docx", "A 49549-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 60891-2024 tillsynsbegäran mail.docx", "A 60891-2024")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 60891-2024</t>
+          <t>A 34341-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1557,10 +1557,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45644</v>
+        <v>45525</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1572,17 +1572,22 @@
           <t>YSTAD</t>
         </is>
       </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I11" t="n">
-        <v>16.1</v>
+        <v>14.4</v>
       </c>
       <c r="J11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -1597,7 +1602,7 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -1609,46 +1614,46 @@
         <v>1</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Lövgroda</t>
+          <t>Desmeknopp</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 60891-2024 artfynd.xlsx", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 34341-2024 artfynd.xlsx", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 60891-2024 karta.png", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 34341-2024 karta.png", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 60891-2024 georefererad karta.tif", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 34341-2024 georefererad karta.tif", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 60891-2024 FSC-klagomål.docx", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 34341-2024 FSC-klagomål.docx", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 60891-2024 FSC-klagomål mail.docx", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 34341-2024 FSC-klagomål mail.docx", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 60891-2024 tillsynsbegäran.docx", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 34341-2024 tillsynsbegäran.docx", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 60891-2024 tillsynsbegäran mail.docx", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 34341-2024 tillsynsbegäran mail.docx", "A 34341-2024")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 34341-2024</t>
+          <t>A 49549-2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1662,10 +1667,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45525</v>
+        <v>45939</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1677,22 +1682,17 @@
           <t>YSTAD</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I12" t="n">
-        <v>14.4</v>
+        <v>0.5</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -1707,7 +1707,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -1723,35 +1723,35 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Desmeknopp</t>
+          <t>Noshornsoxe</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 34341-2024 artfynd.xlsx", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 49549-2025 artfynd.xlsx", "A 49549-2025")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 34341-2024 karta.png", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 49549-2025 karta.png", "A 49549-2025")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 34341-2024 georefererad karta.tif", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 49549-2025 georefererad karta.tif", "A 49549-2025")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 34341-2024 FSC-klagomål.docx", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 49549-2025 FSC-klagomål.docx", "A 49549-2025")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 34341-2024 FSC-klagomål mail.docx", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 49549-2025 FSC-klagomål mail.docx", "A 49549-2025")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 34341-2024 tillsynsbegäran.docx", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 49549-2025 tillsynsbegäran.docx", "A 49549-2025")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 34341-2024 tillsynsbegäran mail.docx", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 49549-2025 tillsynsbegäran mail.docx", "A 49549-2025")</f>
         <v/>
       </c>
     </row>
@@ -1775,7 +1775,7 @@
         <v>44617</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 32596-2024</t>
+          <t>A 40417-2022</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1845,10 +1845,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45513</v>
+        <v>44823</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1904,7 +1904,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 40417-2022</t>
+          <t>A 34302-2024</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1918,10 +1918,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44823</v>
+        <v>45524</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1977,7 +1977,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 49536-2025</t>
+          <t>A 32596-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1991,10 +1991,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45939</v>
+        <v>45513</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.5</v>
+        <v>2.6</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2050,7 +2050,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 18090-2022</t>
+          <t>A 38631-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2060,14 +2060,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44684</v>
+        <v>45162</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2080,7 +2080,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>4.9</v>
+        <v>0.8</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2123,7 +2123,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 60803-2023</t>
+          <t>A 18090-2022</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2133,14 +2133,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45260</v>
+        <v>44684</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1.6</v>
+        <v>4.9</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2196,7 +2196,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 38631-2023</t>
+          <t>A 60803-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2210,10 +2210,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45162</v>
+        <v>45260</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2269,7 +2269,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 38413-2026</t>
+          <t>A 49536-2025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2283,10 +2283,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46282</v>
+        <v>45939</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2299,7 +2299,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2342,7 +2342,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 27578-2026</t>
+          <t>A 22195-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2356,10 +2356,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46190</v>
+        <v>45069</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2371,8 +2371,13 @@
           <t>YSTAD</t>
         </is>
       </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I21" t="n">
-        <v>6.6</v>
+        <v>1.1</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2415,7 +2420,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 22195-2023</t>
+          <t>A 38413-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2429,10 +2434,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45069</v>
+        <v>46282</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2444,13 +2449,8 @@
           <t>YSTAD</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I22" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2493,7 +2493,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 34302-2024</t>
+          <t>A 27578-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2507,10 +2507,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45524</v>
+        <v>46190</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2523,7 +2523,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.9</v>
+        <v>6.6</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>

--- a/Översikt YSTAD.xlsx
+++ b/Översikt YSTAD.xlsx
@@ -601,7 +601,7 @@
         <v>45679</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -695,7 +695,7 @@
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 31213-2023</t>
+          <t>A 49546-2025</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -709,10 +709,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>45113</v>
+        <v>45939</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -725,22 +725,22 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>6.5</v>
+        <v>4.4</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -752,49 +752,49 @@
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S3" t="n">
         <v>2</v>
       </c>
       <c r="T3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
-          <t>Skogsveronika
-Skärmstarr</t>
+          <t>Skogsalm
+Igelkottsröksvamp</t>
         </is>
       </c>
       <c r="W3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 31213-2023 artfynd.xlsx", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 49546-2025 artfynd.xlsx", "A 49546-2025")</f>
         <v/>
       </c>
       <c r="X3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 31213-2023 karta.png", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 49546-2025 karta.png", "A 49546-2025")</f>
         <v/>
       </c>
       <c r="Y3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 31213-2023 georefererad karta.tif", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 49546-2025 georefererad karta.tif", "A 49546-2025")</f>
         <v/>
       </c>
       <c r="AA3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 31213-2023 FSC-klagomål.docx", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 49546-2025 FSC-klagomål.docx", "A 49546-2025")</f>
         <v/>
       </c>
       <c r="AB3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 31213-2023 FSC-klagomål mail.docx", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 49546-2025 FSC-klagomål mail.docx", "A 49546-2025")</f>
         <v/>
       </c>
       <c r="AC3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 31213-2023 tillsynsbegäran.docx", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 49546-2025 tillsynsbegäran.docx", "A 49546-2025")</f>
         <v/>
       </c>
       <c r="AD3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 31213-2023 tillsynsbegäran mail.docx", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 49546-2025 tillsynsbegäran mail.docx", "A 49546-2025")</f>
         <v/>
       </c>
     </row>
@@ -818,7 +818,7 @@
         <v>44903</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 49546-2025</t>
+          <t>A 31213-2023</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -921,10 +921,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>45939</v>
+        <v>45113</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -937,22 +937,22 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>4.4</v>
+        <v>6.5</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -964,49 +964,49 @@
         <v>1</v>
       </c>
       <c r="R5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
         <v>2</v>
       </c>
       <c r="T5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>Skogsalm
-Igelkottsröksvamp</t>
+          <t>Skogsveronika
+Skärmstarr</t>
         </is>
       </c>
       <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 49546-2025 artfynd.xlsx", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 31213-2023 artfynd.xlsx", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 49546-2025 karta.png", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 31213-2023 karta.png", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 49546-2025 georefererad karta.tif", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 31213-2023 georefererad karta.tif", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 49546-2025 FSC-klagomål.docx", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 31213-2023 FSC-klagomål.docx", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 49546-2025 FSC-klagomål mail.docx", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 31213-2023 FSC-klagomål mail.docx", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 49546-2025 tillsynsbegäran.docx", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 31213-2023 tillsynsbegäran.docx", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 49546-2025 tillsynsbegäran mail.docx", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 31213-2023 tillsynsbegäran mail.docx", "A 31213-2023")</f>
         <v/>
       </c>
     </row>
@@ -1030,7 +1030,7 @@
         <v>44756</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 61558-2023</t>
+          <t>A 13766-2023</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1128,14 +1128,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45265</v>
+        <v>45007</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1147,16 +1147,11 @@
           <t>YSTAD</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I7" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -1168,7 +1163,7 @@
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1177,10 +1172,10 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1193,42 +1188,42 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 61558-2023 artfynd.xlsx", "A 61558-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 13766-2023 artfynd.xlsx", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 61558-2023 karta.png", "A 61558-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 13766-2023 karta.png", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 61558-2023 georefererad karta.tif", "A 61558-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 13766-2023 georefererad karta.tif", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 61558-2023 FSC-klagomål.docx", "A 61558-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 13766-2023 FSC-klagomål.docx", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 61558-2023 FSC-klagomål mail.docx", "A 61558-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 13766-2023 FSC-klagomål mail.docx", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 61558-2023 tillsynsbegäran.docx", "A 61558-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 13766-2023 tillsynsbegäran.docx", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 61558-2023 tillsynsbegäran mail.docx", "A 61558-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 13766-2023 tillsynsbegäran mail.docx", "A 13766-2023")</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 13766-2023</t>
+          <t>A 61558-2023</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1238,14 +1233,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45007</v>
+        <v>45265</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1257,11 +1252,16 @@
           <t>YSTAD</t>
         </is>
       </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I8" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -1273,7 +1273,7 @@
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1282,10 +1282,10 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1298,35 +1298,35 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 13766-2023 artfynd.xlsx", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 61558-2023 artfynd.xlsx", "A 61558-2023")</f>
         <v/>
       </c>
       <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 13766-2023 karta.png", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 61558-2023 karta.png", "A 61558-2023")</f>
         <v/>
       </c>
       <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 13766-2023 georefererad karta.tif", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 61558-2023 georefererad karta.tif", "A 61558-2023")</f>
         <v/>
       </c>
       <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 13766-2023 FSC-klagomål.docx", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 61558-2023 FSC-klagomål.docx", "A 61558-2023")</f>
         <v/>
       </c>
       <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 13766-2023 FSC-klagomål mail.docx", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 61558-2023 FSC-klagomål mail.docx", "A 61558-2023")</f>
         <v/>
       </c>
       <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 13766-2023 tillsynsbegäran.docx", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 61558-2023 tillsynsbegäran.docx", "A 61558-2023")</f>
         <v/>
       </c>
       <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 13766-2023 tillsynsbegäran mail.docx", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 61558-2023 tillsynsbegäran mail.docx", "A 61558-2023")</f>
         <v/>
       </c>
     </row>
@@ -1350,7 +1350,7 @@
         <v>45939</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 60891-2024</t>
+          <t>A 49549-2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1452,10 +1452,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45644</v>
+        <v>45939</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1468,13 +1468,13 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>16.1</v>
+        <v>0.5</v>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -1504,46 +1504,46 @@
         <v>1</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>Lövgroda</t>
+          <t>Noshornsoxe</t>
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 60891-2024 artfynd.xlsx", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 49549-2025 artfynd.xlsx", "A 49549-2025")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 60891-2024 karta.png", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 49549-2025 karta.png", "A 49549-2025")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 60891-2024 georefererad karta.tif", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 49549-2025 georefererad karta.tif", "A 49549-2025")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 60891-2024 FSC-klagomål.docx", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 49549-2025 FSC-klagomål.docx", "A 49549-2025")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 60891-2024 FSC-klagomål mail.docx", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 49549-2025 FSC-klagomål mail.docx", "A 49549-2025")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 60891-2024 tillsynsbegäran.docx", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 49549-2025 tillsynsbegäran.docx", "A 49549-2025")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 60891-2024 tillsynsbegäran mail.docx", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 49549-2025 tillsynsbegäran mail.docx", "A 49549-2025")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 34341-2024</t>
+          <t>A 60891-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1557,10 +1557,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45525</v>
+        <v>45644</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1572,22 +1572,17 @@
           <t>YSTAD</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I11" t="n">
-        <v>14.4</v>
+        <v>16.1</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -1602,7 +1597,7 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -1614,46 +1609,46 @@
         <v>1</v>
       </c>
       <c r="U11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Desmeknopp</t>
+          <t>Lövgroda</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 34341-2024 artfynd.xlsx", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 60891-2024 artfynd.xlsx", "A 60891-2024")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 34341-2024 karta.png", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 60891-2024 karta.png", "A 60891-2024")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 34341-2024 georefererad karta.tif", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 60891-2024 georefererad karta.tif", "A 60891-2024")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 34341-2024 FSC-klagomål.docx", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 60891-2024 FSC-klagomål.docx", "A 60891-2024")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 34341-2024 FSC-klagomål mail.docx", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 60891-2024 FSC-klagomål mail.docx", "A 60891-2024")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 34341-2024 tillsynsbegäran.docx", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 60891-2024 tillsynsbegäran.docx", "A 60891-2024")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 34341-2024 tillsynsbegäran mail.docx", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 60891-2024 tillsynsbegäran mail.docx", "A 60891-2024")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 49549-2025</t>
+          <t>A 34341-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1667,10 +1662,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45939</v>
+        <v>45525</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1682,17 +1677,22 @@
           <t>YSTAD</t>
         </is>
       </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I12" t="n">
-        <v>0.5</v>
+        <v>14.4</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -1707,7 +1707,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -1723,35 +1723,35 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Noshornsoxe</t>
+          <t>Desmeknopp</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 49549-2025 artfynd.xlsx", "A 49549-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 34341-2024 artfynd.xlsx", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 49549-2025 karta.png", "A 49549-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 34341-2024 karta.png", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 49549-2025 georefererad karta.tif", "A 49549-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 34341-2024 georefererad karta.tif", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 49549-2025 FSC-klagomål.docx", "A 49549-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 34341-2024 FSC-klagomål.docx", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 49549-2025 FSC-klagomål mail.docx", "A 49549-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 34341-2024 FSC-klagomål mail.docx", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 49549-2025 tillsynsbegäran.docx", "A 49549-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 34341-2024 tillsynsbegäran.docx", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 49549-2025 tillsynsbegäran mail.docx", "A 49549-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 34341-2024 tillsynsbegäran mail.docx", "A 34341-2024")</f>
         <v/>
       </c>
     </row>
@@ -1775,7 +1775,7 @@
         <v>44617</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 40417-2022</t>
+          <t>A 32596-2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1845,10 +1845,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44823</v>
+        <v>45513</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1904,7 +1904,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 34302-2024</t>
+          <t>A 40417-2022</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1918,10 +1918,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45524</v>
+        <v>44823</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1977,7 +1977,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 32596-2024</t>
+          <t>A 18090-2022</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1987,14 +1987,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45513</v>
+        <v>44684</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>2.6</v>
+        <v>4.9</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2050,7 +2050,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 38631-2023</t>
+          <t>A 60803-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2064,10 +2064,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45162</v>
+        <v>45260</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2080,7 +2080,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2123,7 +2123,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 18090-2022</t>
+          <t>A 38631-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2133,14 +2133,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44684</v>
+        <v>45162</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>4.9</v>
+        <v>0.8</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2196,7 +2196,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 60803-2023</t>
+          <t>A 49536-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2210,10 +2210,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45260</v>
+        <v>45939</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2269,7 +2269,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 49536-2025</t>
+          <t>A 22195-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2283,10 +2283,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45939</v>
+        <v>45069</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2298,8 +2298,13 @@
           <t>YSTAD</t>
         </is>
       </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I20" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2342,7 +2347,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 22195-2023</t>
+          <t>A 34302-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2356,10 +2361,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45069</v>
+        <v>45524</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2371,13 +2376,8 @@
           <t>YSTAD</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I21" t="n">
-        <v>1.1</v>
+        <v>1.9</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2437,7 +2437,7 @@
         <v>46282</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2510,7 +2510,7 @@
         <v>46190</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>

--- a/Översikt YSTAD.xlsx
+++ b/Översikt YSTAD.xlsx
@@ -584,7 +584,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A 3253-2025</t>
+          <t>A 31213-2023</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>45679</v>
+        <v>45113</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -613,22 +613,17 @@
           <t>YSTAD</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I2" t="n">
-        <v>2.5</v>
+        <v>6.5</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
@@ -643,7 +638,7 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -655,47 +650,47 @@
         <v>3</v>
       </c>
       <c r="U2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
-          <t>Lönnlav
-Strävlosta</t>
+          <t>Skogsveronika
+Skärmstarr</t>
         </is>
       </c>
       <c r="W2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 3253-2025 artfynd.xlsx", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 31213-2023 artfynd.xlsx", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="X2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 3253-2025 karta.png", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 31213-2023 karta.png", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="Y2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 3253-2025 georefererad karta.tif", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 31213-2023 georefererad karta.tif", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="AA2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 3253-2025 FSC-klagomål.docx", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 31213-2023 FSC-klagomål.docx", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="AB2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 3253-2025 FSC-klagomål mail.docx", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 31213-2023 FSC-klagomål mail.docx", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="AC2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 3253-2025 tillsynsbegäran.docx", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 31213-2023 tillsynsbegäran.docx", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="AD2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 3253-2025 tillsynsbegäran mail.docx", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 31213-2023 tillsynsbegäran mail.docx", "A 31213-2023")</f>
         <v/>
       </c>
     </row>
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 49546-2025</t>
+          <t>A 3253-2025</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -709,10 +704,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>45939</v>
+        <v>45679</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -724,14 +719,19 @@
           <t>YSTAD</t>
         </is>
       </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I3" t="n">
-        <v>4.4</v>
+        <v>2.5</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -740,7 +740,7 @@
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -749,59 +749,59 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
         <v>2</v>
       </c>
       <c r="T3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
-          <t>Skogsalm
-Igelkottsröksvamp</t>
+          <t>Lönnlav
+Strävlosta</t>
         </is>
       </c>
       <c r="W3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 49546-2025 artfynd.xlsx", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 3253-2025 artfynd.xlsx", "A 3253-2025")</f>
         <v/>
       </c>
       <c r="X3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 49546-2025 karta.png", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 3253-2025 karta.png", "A 3253-2025")</f>
         <v/>
       </c>
       <c r="Y3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 49546-2025 georefererad karta.tif", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 3253-2025 georefererad karta.tif", "A 3253-2025")</f>
         <v/>
       </c>
       <c r="AA3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 49546-2025 FSC-klagomål.docx", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 3253-2025 FSC-klagomål.docx", "A 3253-2025")</f>
         <v/>
       </c>
       <c r="AB3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 49546-2025 FSC-klagomål mail.docx", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 3253-2025 FSC-klagomål mail.docx", "A 3253-2025")</f>
         <v/>
       </c>
       <c r="AC3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 49546-2025 tillsynsbegäran.docx", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 3253-2025 tillsynsbegäran.docx", "A 3253-2025")</f>
         <v/>
       </c>
       <c r="AD3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 49546-2025 tillsynsbegäran mail.docx", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 3253-2025 tillsynsbegäran mail.docx", "A 3253-2025")</f>
         <v/>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 60295-2022</t>
+          <t>A 49546-2025</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -811,14 +811,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>44903</v>
+        <v>45939</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -831,13 +831,13 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>1.1</v>
+        <v>4.4</v>
       </c>
       <c r="J4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -846,7 +846,7 @@
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -855,59 +855,59 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S4" t="n">
         <v>2</v>
       </c>
       <c r="T4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="U4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>Klockgroda
-Ätlig groda</t>
+          <t>Skogsalm
+Igelkottsröksvamp</t>
         </is>
       </c>
       <c r="W4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 60295-2022 artfynd.xlsx", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 49546-2025 artfynd.xlsx", "A 49546-2025")</f>
         <v/>
       </c>
       <c r="X4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 60295-2022 karta.png", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 49546-2025 karta.png", "A 49546-2025")</f>
         <v/>
       </c>
       <c r="Y4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 60295-2022 georefererad karta.tif", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 49546-2025 georefererad karta.tif", "A 49546-2025")</f>
         <v/>
       </c>
       <c r="AA4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 60295-2022 FSC-klagomål.docx", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 49546-2025 FSC-klagomål.docx", "A 49546-2025")</f>
         <v/>
       </c>
       <c r="AB4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 60295-2022 FSC-klagomål mail.docx", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 49546-2025 FSC-klagomål mail.docx", "A 49546-2025")</f>
         <v/>
       </c>
       <c r="AC4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 60295-2022 tillsynsbegäran.docx", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 49546-2025 tillsynsbegäran.docx", "A 49546-2025")</f>
         <v/>
       </c>
       <c r="AD4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 60295-2022 tillsynsbegäran mail.docx", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 49546-2025 tillsynsbegäran mail.docx", "A 49546-2025")</f>
         <v/>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 31213-2023</t>
+          <t>A 60295-2022</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -917,14 +917,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>45113</v>
+        <v>44903</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -937,16 +937,16 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>6.5</v>
+        <v>1.1</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -961,7 +961,7 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -970,43 +970,43 @@
         <v>2</v>
       </c>
       <c r="T5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="U5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>Skogsveronika
-Skärmstarr</t>
+          <t>Klockgroda
+Ätlig groda</t>
         </is>
       </c>
       <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 31213-2023 artfynd.xlsx", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 60295-2022 artfynd.xlsx", "A 60295-2022")</f>
         <v/>
       </c>
       <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 31213-2023 karta.png", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 60295-2022 karta.png", "A 60295-2022")</f>
         <v/>
       </c>
       <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 31213-2023 georefererad karta.tif", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 60295-2022 georefererad karta.tif", "A 60295-2022")</f>
         <v/>
       </c>
       <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 31213-2023 FSC-klagomål.docx", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 60295-2022 FSC-klagomål.docx", "A 60295-2022")</f>
         <v/>
       </c>
       <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 31213-2023 FSC-klagomål mail.docx", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 60295-2022 FSC-klagomål mail.docx", "A 60295-2022")</f>
         <v/>
       </c>
       <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 31213-2023 tillsynsbegäran.docx", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 60295-2022 tillsynsbegäran.docx", "A 60295-2022")</f>
         <v/>
       </c>
       <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 31213-2023 tillsynsbegäran mail.docx", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 60295-2022 tillsynsbegäran mail.docx", "A 60295-2022")</f>
         <v/>
       </c>
     </row>
@@ -1030,7 +1030,7 @@
         <v>44756</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 13766-2023</t>
+          <t>A 61558-2023</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1128,14 +1128,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45007</v>
+        <v>45265</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1147,11 +1147,16 @@
           <t>YSTAD</t>
         </is>
       </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I7" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -1163,7 +1168,7 @@
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1172,10 +1177,10 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1188,42 +1193,42 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 13766-2023 artfynd.xlsx", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 61558-2023 artfynd.xlsx", "A 61558-2023")</f>
         <v/>
       </c>
       <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 13766-2023 karta.png", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 61558-2023 karta.png", "A 61558-2023")</f>
         <v/>
       </c>
       <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 13766-2023 georefererad karta.tif", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 61558-2023 georefererad karta.tif", "A 61558-2023")</f>
         <v/>
       </c>
       <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 13766-2023 FSC-klagomål.docx", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 61558-2023 FSC-klagomål.docx", "A 61558-2023")</f>
         <v/>
       </c>
       <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 13766-2023 FSC-klagomål mail.docx", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 61558-2023 FSC-klagomål mail.docx", "A 61558-2023")</f>
         <v/>
       </c>
       <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 13766-2023 tillsynsbegäran.docx", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 61558-2023 tillsynsbegäran.docx", "A 61558-2023")</f>
         <v/>
       </c>
       <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 13766-2023 tillsynsbegäran mail.docx", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 61558-2023 tillsynsbegäran mail.docx", "A 61558-2023")</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 61558-2023</t>
+          <t>A 13766-2023</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1233,14 +1238,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45265</v>
+        <v>45007</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1252,16 +1257,11 @@
           <t>YSTAD</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I8" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -1273,7 +1273,7 @@
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1282,10 +1282,10 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1298,42 +1298,42 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 61558-2023 artfynd.xlsx", "A 61558-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 13766-2023 artfynd.xlsx", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 61558-2023 karta.png", "A 61558-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 13766-2023 karta.png", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 61558-2023 georefererad karta.tif", "A 61558-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 13766-2023 georefererad karta.tif", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 61558-2023 FSC-klagomål.docx", "A 61558-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 13766-2023 FSC-klagomål.docx", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 61558-2023 FSC-klagomål mail.docx", "A 61558-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 13766-2023 FSC-klagomål mail.docx", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 61558-2023 tillsynsbegäran.docx", "A 61558-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 13766-2023 tillsynsbegäran.docx", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 61558-2023 tillsynsbegäran mail.docx", "A 61558-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 13766-2023 tillsynsbegäran mail.docx", "A 13766-2023")</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 49543-2025</t>
+          <t>A 60891-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1347,10 +1347,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45939</v>
+        <v>45644</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1363,16 +1363,16 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1.4</v>
+        <v>16.1</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -1387,7 +1387,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -1396,49 +1396,49 @@
         <v>1</v>
       </c>
       <c r="T9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>Svartöra</t>
+          <t>Lövgroda</t>
         </is>
       </c>
       <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 49543-2025 artfynd.xlsx", "A 49543-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 60891-2024 artfynd.xlsx", "A 60891-2024")</f>
         <v/>
       </c>
       <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 49543-2025 karta.png", "A 49543-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 60891-2024 karta.png", "A 60891-2024")</f>
         <v/>
       </c>
       <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 49543-2025 georefererad karta.tif", "A 49543-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 60891-2024 georefererad karta.tif", "A 60891-2024")</f>
         <v/>
       </c>
       <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 49543-2025 FSC-klagomål.docx", "A 49543-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 60891-2024 FSC-klagomål.docx", "A 60891-2024")</f>
         <v/>
       </c>
       <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 49543-2025 FSC-klagomål mail.docx", "A 49543-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 60891-2024 FSC-klagomål mail.docx", "A 60891-2024")</f>
         <v/>
       </c>
       <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 49543-2025 tillsynsbegäran.docx", "A 49543-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 60891-2024 tillsynsbegäran.docx", "A 60891-2024")</f>
         <v/>
       </c>
       <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 49543-2025 tillsynsbegäran mail.docx", "A 49543-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 60891-2024 tillsynsbegäran mail.docx", "A 60891-2024")</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 49549-2025</t>
+          <t>A 34341-2024</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1452,10 +1452,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45939</v>
+        <v>45525</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1467,17 +1467,22 @@
           <t>YSTAD</t>
         </is>
       </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I10" t="n">
-        <v>0.5</v>
+        <v>14.4</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -1492,7 +1497,7 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -1508,42 +1513,42 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>Noshornsoxe</t>
+          <t>Desmeknopp</t>
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 49549-2025 artfynd.xlsx", "A 49549-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 34341-2024 artfynd.xlsx", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 49549-2025 karta.png", "A 49549-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 34341-2024 karta.png", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 49549-2025 georefererad karta.tif", "A 49549-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 34341-2024 georefererad karta.tif", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 49549-2025 FSC-klagomål.docx", "A 49549-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 34341-2024 FSC-klagomål.docx", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 49549-2025 FSC-klagomål mail.docx", "A 49549-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 34341-2024 FSC-klagomål mail.docx", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 49549-2025 tillsynsbegäran.docx", "A 49549-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 34341-2024 tillsynsbegäran.docx", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 49549-2025 tillsynsbegäran mail.docx", "A 49549-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 34341-2024 tillsynsbegäran mail.docx", "A 34341-2024")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 60891-2024</t>
+          <t>A 49543-2025</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1557,10 +1562,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45644</v>
+        <v>45939</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1573,16 +1578,16 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>16.1</v>
+        <v>1.4</v>
       </c>
       <c r="J11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -1597,7 +1602,7 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -1606,49 +1611,49 @@
         <v>1</v>
       </c>
       <c r="T11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U11" t="n">
         <v>0</v>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Lövgroda</t>
+          <t>Svartöra</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 60891-2024 artfynd.xlsx", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 49543-2025 artfynd.xlsx", "A 49543-2025")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 60891-2024 karta.png", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 49543-2025 karta.png", "A 49543-2025")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 60891-2024 georefererad karta.tif", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 49543-2025 georefererad karta.tif", "A 49543-2025")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 60891-2024 FSC-klagomål.docx", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 49543-2025 FSC-klagomål.docx", "A 49543-2025")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 60891-2024 FSC-klagomål mail.docx", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 49543-2025 FSC-klagomål mail.docx", "A 49543-2025")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 60891-2024 tillsynsbegäran.docx", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 49543-2025 tillsynsbegäran.docx", "A 49543-2025")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 60891-2024 tillsynsbegäran mail.docx", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 49543-2025 tillsynsbegäran mail.docx", "A 49543-2025")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 34341-2024</t>
+          <t>A 49549-2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1662,10 +1667,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45525</v>
+        <v>45939</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1677,22 +1682,17 @@
           <t>YSTAD</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I12" t="n">
-        <v>14.4</v>
+        <v>0.5</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -1707,7 +1707,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -1723,35 +1723,35 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Desmeknopp</t>
+          <t>Noshornsoxe</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 34341-2024 artfynd.xlsx", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 49549-2025 artfynd.xlsx", "A 49549-2025")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 34341-2024 karta.png", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 49549-2025 karta.png", "A 49549-2025")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 34341-2024 georefererad karta.tif", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 49549-2025 georefererad karta.tif", "A 49549-2025")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 34341-2024 FSC-klagomål.docx", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 49549-2025 FSC-klagomål.docx", "A 49549-2025")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 34341-2024 FSC-klagomål mail.docx", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 49549-2025 FSC-klagomål mail.docx", "A 49549-2025")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 34341-2024 tillsynsbegäran.docx", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 49549-2025 tillsynsbegäran.docx", "A 49549-2025")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 34341-2024 tillsynsbegäran mail.docx", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 49549-2025 tillsynsbegäran mail.docx", "A 49549-2025")</f>
         <v/>
       </c>
     </row>
@@ -1775,7 +1775,7 @@
         <v>44617</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 32596-2024</t>
+          <t>A 22195-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1845,10 +1845,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45513</v>
+        <v>45069</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1860,8 +1860,13 @@
           <t>YSTAD</t>
         </is>
       </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I14" t="n">
-        <v>2.6</v>
+        <v>1.1</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1921,7 +1926,7 @@
         <v>44823</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1977,7 +1982,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 18090-2022</t>
+          <t>A 34302-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1987,14 +1992,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44684</v>
+        <v>45524</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2007,7 +2012,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>4.9</v>
+        <v>1.9</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2050,7 +2055,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 60803-2023</t>
+          <t>A 38631-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2064,10 +2069,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45260</v>
+        <v>45162</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2080,7 +2085,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1.6</v>
+        <v>0.8</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2123,7 +2128,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 38631-2023</t>
+          <t>A 60803-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2137,10 +2142,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45162</v>
+        <v>45260</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2153,7 +2158,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2196,7 +2201,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 49536-2025</t>
+          <t>A 18090-2022</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2206,14 +2211,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45939</v>
+        <v>44684</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2226,7 +2231,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1.5</v>
+        <v>4.9</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2269,7 +2274,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 22195-2023</t>
+          <t>A 32596-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2283,10 +2288,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45069</v>
+        <v>45513</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2298,13 +2303,8 @@
           <t>YSTAD</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I20" t="n">
-        <v>1.1</v>
+        <v>2.6</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2347,7 +2347,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 34302-2024</t>
+          <t>A 49536-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2361,10 +2361,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45524</v>
+        <v>45939</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2437,7 +2437,7 @@
         <v>46282</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2510,7 +2510,7 @@
         <v>46190</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>

--- a/Översikt YSTAD.xlsx
+++ b/Översikt YSTAD.xlsx
@@ -601,7 +601,7 @@
         <v>45113</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -707,7 +707,7 @@
         <v>45679</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -818,7 +818,7 @@
         <v>45939</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -924,7 +924,7 @@
         <v>44903</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>44756</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1135,7 +1135,7 @@
         <v>45265</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1245,7 +1245,7 @@
         <v>45007</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
         <v>45644</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         <v>45525</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1565,7 +1565,7 @@
         <v>45939</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1670,7 +1670,7 @@
         <v>45939</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1775,7 +1775,7 @@
         <v>44617</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         <v>45069</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
         <v>44823</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1999,7 +1999,7 @@
         <v>45524</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
         <v>45162</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         <v>45260</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2218,7 +2218,7 @@
         <v>44684</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2291,7 +2291,7 @@
         <v>45513</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         <v>45939</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
         <v>46282</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2510,7 +2510,7 @@
         <v>46190</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>

--- a/Översikt YSTAD.xlsx
+++ b/Översikt YSTAD.xlsx
@@ -601,7 +601,7 @@
         <v>45113</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -707,7 +707,7 @@
         <v>45679</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -818,7 +818,7 @@
         <v>45939</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -924,7 +924,7 @@
         <v>44903</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>44756</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1135,7 +1135,7 @@
         <v>45265</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1245,7 +1245,7 @@
         <v>45007</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
         <v>45644</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         <v>45525</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1565,7 +1565,7 @@
         <v>45939</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1670,7 +1670,7 @@
         <v>45939</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1775,7 +1775,7 @@
         <v>44617</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         <v>45069</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
         <v>44823</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1999,7 +1999,7 @@
         <v>45524</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
         <v>45162</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         <v>45260</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2218,7 +2218,7 @@
         <v>44684</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2291,7 +2291,7 @@
         <v>45513</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         <v>45939</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
         <v>46282</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2510,7 +2510,7 @@
         <v>46190</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>

--- a/Översikt YSTAD.xlsx
+++ b/Översikt YSTAD.xlsx
@@ -584,7 +584,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A 31213-2023</t>
+          <t>A 49546-2025</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>45113</v>
+        <v>45939</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -614,22 +614,22 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>6.5</v>
+        <v>4.4</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -641,49 +641,49 @@
         <v>1</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S2" t="n">
         <v>2</v>
       </c>
       <c r="T2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
-          <t>Skogsveronika
-Skärmstarr</t>
+          <t>Skogsalm
+Igelkottsröksvamp</t>
         </is>
       </c>
       <c r="W2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 31213-2023 artfynd.xlsx", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 49546-2025 artfynd.xlsx", "A 49546-2025")</f>
         <v/>
       </c>
       <c r="X2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 31213-2023 karta.png", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 49546-2025 karta.png", "A 49546-2025")</f>
         <v/>
       </c>
       <c r="Y2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 31213-2023 georefererad karta.tif", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 49546-2025 georefererad karta.tif", "A 49546-2025")</f>
         <v/>
       </c>
       <c r="AA2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 31213-2023 FSC-klagomål.docx", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 49546-2025 FSC-klagomål.docx", "A 49546-2025")</f>
         <v/>
       </c>
       <c r="AB2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 31213-2023 FSC-klagomål mail.docx", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 49546-2025 FSC-klagomål mail.docx", "A 49546-2025")</f>
         <v/>
       </c>
       <c r="AC2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 31213-2023 tillsynsbegäran.docx", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 49546-2025 tillsynsbegäran.docx", "A 49546-2025")</f>
         <v/>
       </c>
       <c r="AD2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 31213-2023 tillsynsbegäran mail.docx", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 49546-2025 tillsynsbegäran mail.docx", "A 49546-2025")</f>
         <v/>
       </c>
     </row>
@@ -707,7 +707,7 @@
         <v>45679</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -801,7 +801,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 49546-2025</t>
+          <t>A 60295-2022</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -811,14 +811,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45939</v>
+        <v>44903</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -831,13 +831,13 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>4.4</v>
+        <v>1.1</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -846,7 +846,7 @@
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -855,59 +855,59 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>2</v>
       </c>
       <c r="T4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>Skogsalm
-Igelkottsröksvamp</t>
+          <t>Klockgroda
+Ätlig groda</t>
         </is>
       </c>
       <c r="W4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 49546-2025 artfynd.xlsx", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 60295-2022 artfynd.xlsx", "A 60295-2022")</f>
         <v/>
       </c>
       <c r="X4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 49546-2025 karta.png", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 60295-2022 karta.png", "A 60295-2022")</f>
         <v/>
       </c>
       <c r="Y4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 49546-2025 georefererad karta.tif", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 60295-2022 georefererad karta.tif", "A 60295-2022")</f>
         <v/>
       </c>
       <c r="AA4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 49546-2025 FSC-klagomål.docx", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 60295-2022 FSC-klagomål.docx", "A 60295-2022")</f>
         <v/>
       </c>
       <c r="AB4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 49546-2025 FSC-klagomål mail.docx", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 60295-2022 FSC-klagomål mail.docx", "A 60295-2022")</f>
         <v/>
       </c>
       <c r="AC4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 49546-2025 tillsynsbegäran.docx", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 60295-2022 tillsynsbegäran.docx", "A 60295-2022")</f>
         <v/>
       </c>
       <c r="AD4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 49546-2025 tillsynsbegäran mail.docx", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 60295-2022 tillsynsbegäran mail.docx", "A 60295-2022")</f>
         <v/>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 60295-2022</t>
+          <t>A 31213-2023</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -917,14 +917,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>44903</v>
+        <v>45113</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -937,16 +937,16 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>1.1</v>
+        <v>6.5</v>
       </c>
       <c r="J5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -961,7 +961,7 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -970,43 +970,43 @@
         <v>2</v>
       </c>
       <c r="T5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="U5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>Klockgroda
-Ätlig groda</t>
+          <t>Skogsveronika
+Skärmstarr</t>
         </is>
       </c>
       <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 60295-2022 artfynd.xlsx", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 31213-2023 artfynd.xlsx", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 60295-2022 karta.png", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 31213-2023 karta.png", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 60295-2022 georefererad karta.tif", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 31213-2023 georefererad karta.tif", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 60295-2022 FSC-klagomål.docx", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 31213-2023 FSC-klagomål.docx", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 60295-2022 FSC-klagomål mail.docx", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 31213-2023 FSC-klagomål mail.docx", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 60295-2022 tillsynsbegäran.docx", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 31213-2023 tillsynsbegäran.docx", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 60295-2022 tillsynsbegäran mail.docx", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 31213-2023 tillsynsbegäran mail.docx", "A 31213-2023")</f>
         <v/>
       </c>
     </row>
@@ -1030,7 +1030,7 @@
         <v>44756</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1135,7 +1135,7 @@
         <v>45265</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 13766-2023</t>
+          <t>A 49543-2025</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1238,14 +1238,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45007</v>
+        <v>45939</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1258,16 +1258,16 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -1282,7 +1282,7 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -1291,49 +1291,49 @@
         <v>1</v>
       </c>
       <c r="T8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U8" t="n">
         <v>0</v>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Svartöra</t>
         </is>
       </c>
       <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 13766-2023 artfynd.xlsx", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 49543-2025 artfynd.xlsx", "A 49543-2025")</f>
         <v/>
       </c>
       <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 13766-2023 karta.png", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 49543-2025 karta.png", "A 49543-2025")</f>
         <v/>
       </c>
       <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 13766-2023 georefererad karta.tif", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 49543-2025 georefererad karta.tif", "A 49543-2025")</f>
         <v/>
       </c>
       <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 13766-2023 FSC-klagomål.docx", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 49543-2025 FSC-klagomål.docx", "A 49543-2025")</f>
         <v/>
       </c>
       <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 13766-2023 FSC-klagomål mail.docx", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 49543-2025 FSC-klagomål mail.docx", "A 49543-2025")</f>
         <v/>
       </c>
       <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 13766-2023 tillsynsbegäran.docx", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 49543-2025 tillsynsbegäran.docx", "A 49543-2025")</f>
         <v/>
       </c>
       <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 13766-2023 tillsynsbegäran mail.docx", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 49543-2025 tillsynsbegäran mail.docx", "A 49543-2025")</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 60891-2024</t>
+          <t>A 13766-2023</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1343,14 +1343,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45644</v>
+        <v>45007</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1363,7 +1363,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>16.1</v>
+        <v>0.9</v>
       </c>
       <c r="J9" t="n">
         <v>1</v>
@@ -1403,42 +1403,42 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>Lövgroda</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 60891-2024 artfynd.xlsx", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 13766-2023 artfynd.xlsx", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 60891-2024 karta.png", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 13766-2023 karta.png", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 60891-2024 georefererad karta.tif", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 13766-2023 georefererad karta.tif", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 60891-2024 FSC-klagomål.docx", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 13766-2023 FSC-klagomål.docx", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 60891-2024 FSC-klagomål mail.docx", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 13766-2023 FSC-klagomål mail.docx", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 60891-2024 tillsynsbegäran.docx", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 13766-2023 tillsynsbegäran.docx", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 60891-2024 tillsynsbegäran mail.docx", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 13766-2023 tillsynsbegäran mail.docx", "A 13766-2023")</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 34341-2024</t>
+          <t>A 49549-2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1452,10 +1452,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45525</v>
+        <v>45939</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1467,22 +1467,17 @@
           <t>YSTAD</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I10" t="n">
-        <v>14.4</v>
+        <v>0.5</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -1497,7 +1492,7 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -1513,42 +1508,42 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>Desmeknopp</t>
+          <t>Noshornsoxe</t>
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 34341-2024 artfynd.xlsx", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 49549-2025 artfynd.xlsx", "A 49549-2025")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 34341-2024 karta.png", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 49549-2025 karta.png", "A 49549-2025")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 34341-2024 georefererad karta.tif", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 49549-2025 georefererad karta.tif", "A 49549-2025")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 34341-2024 FSC-klagomål.docx", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 49549-2025 FSC-klagomål.docx", "A 49549-2025")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 34341-2024 FSC-klagomål mail.docx", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 49549-2025 FSC-klagomål mail.docx", "A 49549-2025")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 34341-2024 tillsynsbegäran.docx", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 49549-2025 tillsynsbegäran.docx", "A 49549-2025")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 34341-2024 tillsynsbegäran mail.docx", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 49549-2025 tillsynsbegäran mail.docx", "A 49549-2025")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 49543-2025</t>
+          <t>A 60891-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1562,10 +1557,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45939</v>
+        <v>45644</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1578,16 +1573,16 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>1.4</v>
+        <v>16.1</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -1602,7 +1597,7 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -1611,49 +1606,49 @@
         <v>1</v>
       </c>
       <c r="T11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U11" t="n">
         <v>0</v>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Svartöra</t>
+          <t>Lövgroda</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 49543-2025 artfynd.xlsx", "A 49543-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 60891-2024 artfynd.xlsx", "A 60891-2024")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 49543-2025 karta.png", "A 49543-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 60891-2024 karta.png", "A 60891-2024")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 49543-2025 georefererad karta.tif", "A 49543-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 60891-2024 georefererad karta.tif", "A 60891-2024")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 49543-2025 FSC-klagomål.docx", "A 49543-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 60891-2024 FSC-klagomål.docx", "A 60891-2024")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 49543-2025 FSC-klagomål mail.docx", "A 49543-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 60891-2024 FSC-klagomål mail.docx", "A 60891-2024")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 49543-2025 tillsynsbegäran.docx", "A 49543-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 60891-2024 tillsynsbegäran.docx", "A 60891-2024")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 49543-2025 tillsynsbegäran mail.docx", "A 49543-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 60891-2024 tillsynsbegäran mail.docx", "A 60891-2024")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 49549-2025</t>
+          <t>A 34341-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1667,10 +1662,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45939</v>
+        <v>45525</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1682,17 +1677,22 @@
           <t>YSTAD</t>
         </is>
       </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I12" t="n">
-        <v>0.5</v>
+        <v>14.4</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -1707,7 +1707,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -1723,35 +1723,35 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Noshornsoxe</t>
+          <t>Desmeknopp</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 49549-2025 artfynd.xlsx", "A 49549-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 34341-2024 artfynd.xlsx", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 49549-2025 karta.png", "A 49549-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 34341-2024 karta.png", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 49549-2025 georefererad karta.tif", "A 49549-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 34341-2024 georefererad karta.tif", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 49549-2025 FSC-klagomål.docx", "A 49549-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 34341-2024 FSC-klagomål.docx", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 49549-2025 FSC-klagomål mail.docx", "A 49549-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 34341-2024 FSC-klagomål mail.docx", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 49549-2025 tillsynsbegäran.docx", "A 49549-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 34341-2024 tillsynsbegäran.docx", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 49549-2025 tillsynsbegäran mail.docx", "A 49549-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 34341-2024 tillsynsbegäran mail.docx", "A 34341-2024")</f>
         <v/>
       </c>
     </row>
@@ -1775,7 +1775,7 @@
         <v>44617</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 22195-2023</t>
+          <t>A 49536-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1845,10 +1845,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45069</v>
+        <v>45939</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1860,13 +1860,8 @@
           <t>YSTAD</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I14" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1909,7 +1904,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 40417-2022</t>
+          <t>A 34302-2024</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1923,10 +1918,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44823</v>
+        <v>45524</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1939,7 +1934,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1982,7 +1977,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 34302-2024</t>
+          <t>A 32596-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1996,10 +1991,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45524</v>
+        <v>45513</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2012,7 +2007,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.9</v>
+        <v>2.6</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2055,7 +2050,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 38631-2023</t>
+          <t>A 38413-2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2069,10 +2064,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45162</v>
+        <v>46282</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2085,7 +2080,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2128,7 +2123,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 60803-2023</t>
+          <t>A 27578-2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2142,10 +2137,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45260</v>
+        <v>46190</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2158,7 +2153,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1.6</v>
+        <v>6.6</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2201,7 +2196,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 18090-2022</t>
+          <t>A 40417-2022</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2211,14 +2206,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44684</v>
+        <v>44823</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2231,7 +2226,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>4.9</v>
+        <v>2.3</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2274,7 +2269,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 32596-2024</t>
+          <t>A 18090-2022</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2284,14 +2279,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45513</v>
+        <v>44684</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2304,7 +2299,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>2.6</v>
+        <v>4.9</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2347,7 +2342,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 49536-2025</t>
+          <t>A 60803-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2361,10 +2356,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45939</v>
+        <v>45260</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2377,7 +2372,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2420,7 +2415,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 38413-2026</t>
+          <t>A 38631-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2434,10 +2429,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46282</v>
+        <v>45162</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2450,7 +2445,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2493,7 +2488,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 27578-2026</t>
+          <t>A 22195-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2507,10 +2502,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46190</v>
+        <v>45069</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2522,8 +2517,13 @@
           <t>YSTAD</t>
         </is>
       </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I23" t="n">
-        <v>6.6</v>
+        <v>1.1</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>

--- a/Översikt YSTAD.xlsx
+++ b/Översikt YSTAD.xlsx
@@ -584,7 +584,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A 49546-2025</t>
+          <t>A 31213-2023</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>45939</v>
+        <v>45113</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -614,22 +614,22 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>4.4</v>
+        <v>6.5</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -641,49 +641,49 @@
         <v>1</v>
       </c>
       <c r="R2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
         <v>2</v>
       </c>
       <c r="T2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
-          <t>Skogsalm
-Igelkottsröksvamp</t>
+          <t>Skogsveronika
+Skärmstarr</t>
         </is>
       </c>
       <c r="W2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 49546-2025 artfynd.xlsx", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 31213-2023 artfynd.xlsx", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="X2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 49546-2025 karta.png", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 31213-2023 karta.png", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="Y2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 49546-2025 georefererad karta.tif", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 31213-2023 georefererad karta.tif", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="AA2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 49546-2025 FSC-klagomål.docx", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 31213-2023 FSC-klagomål.docx", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="AB2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 49546-2025 FSC-klagomål mail.docx", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 31213-2023 FSC-klagomål mail.docx", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="AC2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 49546-2025 tillsynsbegäran.docx", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 31213-2023 tillsynsbegäran.docx", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="AD2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 49546-2025 tillsynsbegäran mail.docx", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 31213-2023 tillsynsbegäran mail.docx", "A 31213-2023")</f>
         <v/>
       </c>
     </row>
@@ -707,7 +707,7 @@
         <v>45679</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -801,7 +801,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 60295-2022</t>
+          <t>A 49546-2025</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -811,14 +811,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>44903</v>
+        <v>45939</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -831,13 +831,13 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>1.1</v>
+        <v>4.4</v>
       </c>
       <c r="J4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -846,7 +846,7 @@
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -855,59 +855,59 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S4" t="n">
         <v>2</v>
       </c>
       <c r="T4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="U4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>Klockgroda
-Ätlig groda</t>
+          <t>Skogsalm
+Igelkottsröksvamp</t>
         </is>
       </c>
       <c r="W4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 60295-2022 artfynd.xlsx", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 49546-2025 artfynd.xlsx", "A 49546-2025")</f>
         <v/>
       </c>
       <c r="X4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 60295-2022 karta.png", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 49546-2025 karta.png", "A 49546-2025")</f>
         <v/>
       </c>
       <c r="Y4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 60295-2022 georefererad karta.tif", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 49546-2025 georefererad karta.tif", "A 49546-2025")</f>
         <v/>
       </c>
       <c r="AA4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 60295-2022 FSC-klagomål.docx", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 49546-2025 FSC-klagomål.docx", "A 49546-2025")</f>
         <v/>
       </c>
       <c r="AB4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 60295-2022 FSC-klagomål mail.docx", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 49546-2025 FSC-klagomål mail.docx", "A 49546-2025")</f>
         <v/>
       </c>
       <c r="AC4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 60295-2022 tillsynsbegäran.docx", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 49546-2025 tillsynsbegäran.docx", "A 49546-2025")</f>
         <v/>
       </c>
       <c r="AD4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 60295-2022 tillsynsbegäran mail.docx", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 49546-2025 tillsynsbegäran mail.docx", "A 49546-2025")</f>
         <v/>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 31213-2023</t>
+          <t>A 60295-2022</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -917,14 +917,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>45113</v>
+        <v>44903</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -937,16 +937,16 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>6.5</v>
+        <v>1.1</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -961,7 +961,7 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -970,43 +970,43 @@
         <v>2</v>
       </c>
       <c r="T5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="U5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>Skogsveronika
-Skärmstarr</t>
+          <t>Klockgroda
+Ätlig groda</t>
         </is>
       </c>
       <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 31213-2023 artfynd.xlsx", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 60295-2022 artfynd.xlsx", "A 60295-2022")</f>
         <v/>
       </c>
       <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 31213-2023 karta.png", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 60295-2022 karta.png", "A 60295-2022")</f>
         <v/>
       </c>
       <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 31213-2023 georefererad karta.tif", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 60295-2022 georefererad karta.tif", "A 60295-2022")</f>
         <v/>
       </c>
       <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 31213-2023 FSC-klagomål.docx", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 60295-2022 FSC-klagomål.docx", "A 60295-2022")</f>
         <v/>
       </c>
       <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 31213-2023 FSC-klagomål mail.docx", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 60295-2022 FSC-klagomål mail.docx", "A 60295-2022")</f>
         <v/>
       </c>
       <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 31213-2023 tillsynsbegäran.docx", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 60295-2022 tillsynsbegäran.docx", "A 60295-2022")</f>
         <v/>
       </c>
       <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 31213-2023 tillsynsbegäran mail.docx", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 60295-2022 tillsynsbegäran mail.docx", "A 60295-2022")</f>
         <v/>
       </c>
     </row>
@@ -1030,7 +1030,7 @@
         <v>44756</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1135,7 +1135,7 @@
         <v>45265</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1245,7 +1245,7 @@
         <v>45939</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1333,7 +1333,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 13766-2023</t>
+          <t>A 34341-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1343,14 +1343,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45007</v>
+        <v>45525</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1362,17 +1362,22 @@
           <t>YSTAD</t>
         </is>
       </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I9" t="n">
-        <v>0.9</v>
+        <v>14.4</v>
       </c>
       <c r="J9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -1387,7 +1392,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -1399,39 +1404,39 @@
         <v>1</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Desmeknopp</t>
         </is>
       </c>
       <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 13766-2023 artfynd.xlsx", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 34341-2024 artfynd.xlsx", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 13766-2023 karta.png", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 34341-2024 karta.png", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 13766-2023 georefererad karta.tif", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 34341-2024 georefererad karta.tif", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 13766-2023 FSC-klagomål.docx", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 34341-2024 FSC-klagomål.docx", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 13766-2023 FSC-klagomål mail.docx", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 34341-2024 FSC-klagomål mail.docx", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 13766-2023 tillsynsbegäran.docx", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 34341-2024 tillsynsbegäran.docx", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 13766-2023 tillsynsbegäran mail.docx", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 34341-2024 tillsynsbegäran mail.docx", "A 34341-2024")</f>
         <v/>
       </c>
     </row>
@@ -1455,7 +1460,7 @@
         <v>45939</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1543,7 +1548,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 60891-2024</t>
+          <t>A 13766-2023</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1553,14 +1558,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45644</v>
+        <v>45007</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1573,7 +1578,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>16.1</v>
+        <v>0.9</v>
       </c>
       <c r="J11" t="n">
         <v>1</v>
@@ -1613,42 +1618,42 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Lövgroda</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 60891-2024 artfynd.xlsx", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 13766-2023 artfynd.xlsx", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 60891-2024 karta.png", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 13766-2023 karta.png", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 60891-2024 georefererad karta.tif", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 13766-2023 georefererad karta.tif", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 60891-2024 FSC-klagomål.docx", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 13766-2023 FSC-klagomål.docx", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 60891-2024 FSC-klagomål mail.docx", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 13766-2023 FSC-klagomål mail.docx", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 60891-2024 tillsynsbegäran.docx", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 13766-2023 tillsynsbegäran.docx", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 60891-2024 tillsynsbegäran mail.docx", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 13766-2023 tillsynsbegäran mail.docx", "A 13766-2023")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 34341-2024</t>
+          <t>A 60891-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1662,10 +1667,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45525</v>
+        <v>45644</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1677,22 +1682,17 @@
           <t>YSTAD</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I12" t="n">
-        <v>14.4</v>
+        <v>16.1</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -1707,7 +1707,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -1719,39 +1719,39 @@
         <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Desmeknopp</t>
+          <t>Lövgroda</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 34341-2024 artfynd.xlsx", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 60891-2024 artfynd.xlsx", "A 60891-2024")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 34341-2024 karta.png", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 60891-2024 karta.png", "A 60891-2024")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 34341-2024 georefererad karta.tif", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 60891-2024 georefererad karta.tif", "A 60891-2024")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 34341-2024 FSC-klagomål.docx", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 60891-2024 FSC-klagomål.docx", "A 60891-2024")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 34341-2024 FSC-klagomål mail.docx", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 60891-2024 FSC-klagomål mail.docx", "A 60891-2024")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 34341-2024 tillsynsbegäran.docx", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 60891-2024 tillsynsbegäran.docx", "A 60891-2024")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 34341-2024 tillsynsbegäran mail.docx", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 60891-2024 tillsynsbegäran mail.docx", "A 60891-2024")</f>
         <v/>
       </c>
     </row>
@@ -1775,7 +1775,7 @@
         <v>44617</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 49536-2025</t>
+          <t>A 40417-2022</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1845,10 +1845,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45939</v>
+        <v>44823</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1921,7 +1921,7 @@
         <v>45524</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1994,7 +1994,7 @@
         <v>45513</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2050,7 +2050,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 38413-2026</t>
+          <t>A 60803-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2064,10 +2064,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46282</v>
+        <v>45260</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2080,7 +2080,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2123,7 +2123,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 27578-2026</t>
+          <t>A 38631-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2137,10 +2137,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46190</v>
+        <v>45162</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>6.6</v>
+        <v>0.8</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2196,7 +2196,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 40417-2022</t>
+          <t>A 18090-2022</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2206,14 +2206,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44823</v>
+        <v>44684</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>2.3</v>
+        <v>4.9</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2269,7 +2269,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 18090-2022</t>
+          <t>A 49536-2025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2279,14 +2279,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44684</v>
+        <v>45939</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2299,7 +2299,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>4.9</v>
+        <v>1.5</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2342,7 +2342,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 60803-2023</t>
+          <t>A 38413-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2356,10 +2356,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45260</v>
+        <v>46282</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2372,7 +2372,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2415,7 +2415,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 38631-2023</t>
+          <t>A 22195-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2429,10 +2429,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45162</v>
+        <v>45069</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2444,8 +2444,13 @@
           <t>YSTAD</t>
         </is>
       </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I22" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2488,7 +2493,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 22195-2023</t>
+          <t>A 27578-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2502,10 +2507,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45069</v>
+        <v>46190</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2517,13 +2522,8 @@
           <t>YSTAD</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I23" t="n">
-        <v>1.1</v>
+        <v>6.6</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>

--- a/Översikt YSTAD.xlsx
+++ b/Översikt YSTAD.xlsx
@@ -584,7 +584,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A 31213-2023</t>
+          <t>A 3253-2025</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>45113</v>
+        <v>45679</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -613,17 +613,22 @@
           <t>YSTAD</t>
         </is>
       </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I2" t="n">
-        <v>6.5</v>
+        <v>2.5</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
@@ -638,7 +643,7 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -650,47 +655,47 @@
         <v>3</v>
       </c>
       <c r="U2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
-          <t>Skogsveronika
-Skärmstarr</t>
+          <t>Lönnlav
+Strävlosta</t>
         </is>
       </c>
       <c r="W2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 31213-2023 artfynd.xlsx", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 3253-2025 artfynd.xlsx", "A 3253-2025")</f>
         <v/>
       </c>
       <c r="X2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 31213-2023 karta.png", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 3253-2025 karta.png", "A 3253-2025")</f>
         <v/>
       </c>
       <c r="Y2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 31213-2023 georefererad karta.tif", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 3253-2025 georefererad karta.tif", "A 3253-2025")</f>
         <v/>
       </c>
       <c r="AA2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 31213-2023 FSC-klagomål.docx", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 3253-2025 FSC-klagomål.docx", "A 3253-2025")</f>
         <v/>
       </c>
       <c r="AB2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 31213-2023 FSC-klagomål mail.docx", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 3253-2025 FSC-klagomål mail.docx", "A 3253-2025")</f>
         <v/>
       </c>
       <c r="AC2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 31213-2023 tillsynsbegäran.docx", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 3253-2025 tillsynsbegäran.docx", "A 3253-2025")</f>
         <v/>
       </c>
       <c r="AD2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 31213-2023 tillsynsbegäran mail.docx", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 3253-2025 tillsynsbegäran mail.docx", "A 3253-2025")</f>
         <v/>
       </c>
     </row>
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 3253-2025</t>
+          <t>A 49546-2025</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -704,10 +709,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>45679</v>
+        <v>45939</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -719,19 +724,14 @@
           <t>YSTAD</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I3" t="n">
-        <v>2.5</v>
+        <v>4.4</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -740,7 +740,7 @@
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -749,59 +749,59 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S3" t="n">
         <v>2</v>
       </c>
       <c r="T3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
-          <t>Lönnlav
-Strävlosta</t>
+          <t>Skogsalm
+Igelkottsröksvamp</t>
         </is>
       </c>
       <c r="W3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 3253-2025 artfynd.xlsx", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 49546-2025 artfynd.xlsx", "A 49546-2025")</f>
         <v/>
       </c>
       <c r="X3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 3253-2025 karta.png", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 49546-2025 karta.png", "A 49546-2025")</f>
         <v/>
       </c>
       <c r="Y3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 3253-2025 georefererad karta.tif", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 49546-2025 georefererad karta.tif", "A 49546-2025")</f>
         <v/>
       </c>
       <c r="AA3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 3253-2025 FSC-klagomål.docx", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 49546-2025 FSC-klagomål.docx", "A 49546-2025")</f>
         <v/>
       </c>
       <c r="AB3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 3253-2025 FSC-klagomål mail.docx", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 49546-2025 FSC-klagomål mail.docx", "A 49546-2025")</f>
         <v/>
       </c>
       <c r="AC3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 3253-2025 tillsynsbegäran.docx", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 49546-2025 tillsynsbegäran.docx", "A 49546-2025")</f>
         <v/>
       </c>
       <c r="AD3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 3253-2025 tillsynsbegäran mail.docx", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 49546-2025 tillsynsbegäran mail.docx", "A 49546-2025")</f>
         <v/>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 49546-2025</t>
+          <t>A 60295-2022</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -811,14 +811,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45939</v>
+        <v>44903</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -831,13 +831,13 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>4.4</v>
+        <v>1.1</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -846,7 +846,7 @@
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -855,59 +855,59 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>2</v>
       </c>
       <c r="T4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>Skogsalm
-Igelkottsröksvamp</t>
+          <t>Klockgroda
+Ätlig groda</t>
         </is>
       </c>
       <c r="W4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 49546-2025 artfynd.xlsx", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 60295-2022 artfynd.xlsx", "A 60295-2022")</f>
         <v/>
       </c>
       <c r="X4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 49546-2025 karta.png", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 60295-2022 karta.png", "A 60295-2022")</f>
         <v/>
       </c>
       <c r="Y4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 49546-2025 georefererad karta.tif", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 60295-2022 georefererad karta.tif", "A 60295-2022")</f>
         <v/>
       </c>
       <c r="AA4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 49546-2025 FSC-klagomål.docx", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 60295-2022 FSC-klagomål.docx", "A 60295-2022")</f>
         <v/>
       </c>
       <c r="AB4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 49546-2025 FSC-klagomål mail.docx", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 60295-2022 FSC-klagomål mail.docx", "A 60295-2022")</f>
         <v/>
       </c>
       <c r="AC4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 49546-2025 tillsynsbegäran.docx", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 60295-2022 tillsynsbegäran.docx", "A 60295-2022")</f>
         <v/>
       </c>
       <c r="AD4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 49546-2025 tillsynsbegäran mail.docx", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 60295-2022 tillsynsbegäran mail.docx", "A 60295-2022")</f>
         <v/>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 60295-2022</t>
+          <t>A 31213-2023</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -917,14 +917,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>44903</v>
+        <v>45113</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -937,16 +937,16 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>1.1</v>
+        <v>6.5</v>
       </c>
       <c r="J5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -961,7 +961,7 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -970,43 +970,43 @@
         <v>2</v>
       </c>
       <c r="T5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="U5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>Klockgroda
-Ätlig groda</t>
+          <t>Skogsveronika
+Skärmstarr</t>
         </is>
       </c>
       <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 60295-2022 artfynd.xlsx", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 31213-2023 artfynd.xlsx", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 60295-2022 karta.png", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 31213-2023 karta.png", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 60295-2022 georefererad karta.tif", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 31213-2023 georefererad karta.tif", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 60295-2022 FSC-klagomål.docx", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 31213-2023 FSC-klagomål.docx", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 60295-2022 FSC-klagomål mail.docx", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 31213-2023 FSC-klagomål mail.docx", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 60295-2022 tillsynsbegäran.docx", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 31213-2023 tillsynsbegäran.docx", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 60295-2022 tillsynsbegäran mail.docx", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 31213-2023 tillsynsbegäran mail.docx", "A 31213-2023")</f>
         <v/>
       </c>
     </row>
@@ -1030,7 +1030,7 @@
         <v>44756</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1135,7 +1135,7 @@
         <v>45265</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 49543-2025</t>
+          <t>A 60891-2024</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1242,10 +1242,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45939</v>
+        <v>45644</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1258,16 +1258,16 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1.4</v>
+        <v>16.1</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -1282,7 +1282,7 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -1291,49 +1291,49 @@
         <v>1</v>
       </c>
       <c r="T8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U8" t="n">
         <v>0</v>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>Svartöra</t>
+          <t>Lövgroda</t>
         </is>
       </c>
       <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 49543-2025 artfynd.xlsx", "A 49543-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 60891-2024 artfynd.xlsx", "A 60891-2024")</f>
         <v/>
       </c>
       <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 49543-2025 karta.png", "A 49543-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 60891-2024 karta.png", "A 60891-2024")</f>
         <v/>
       </c>
       <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 49543-2025 georefererad karta.tif", "A 49543-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 60891-2024 georefererad karta.tif", "A 60891-2024")</f>
         <v/>
       </c>
       <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 49543-2025 FSC-klagomål.docx", "A 49543-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 60891-2024 FSC-klagomål.docx", "A 60891-2024")</f>
         <v/>
       </c>
       <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 49543-2025 FSC-klagomål mail.docx", "A 49543-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 60891-2024 FSC-klagomål mail.docx", "A 60891-2024")</f>
         <v/>
       </c>
       <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 49543-2025 tillsynsbegäran.docx", "A 49543-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 60891-2024 tillsynsbegäran.docx", "A 60891-2024")</f>
         <v/>
       </c>
       <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 49543-2025 tillsynsbegäran mail.docx", "A 49543-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 60891-2024 tillsynsbegäran mail.docx", "A 60891-2024")</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 34341-2024</t>
+          <t>A 13766-2023</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1343,14 +1343,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45525</v>
+        <v>45007</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1362,22 +1362,17 @@
           <t>YSTAD</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I9" t="n">
-        <v>14.4</v>
+        <v>0.9</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -1392,7 +1387,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -1404,46 +1399,46 @@
         <v>1</v>
       </c>
       <c r="U9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>Desmeknopp</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 34341-2024 artfynd.xlsx", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 13766-2023 artfynd.xlsx", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 34341-2024 karta.png", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 13766-2023 karta.png", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 34341-2024 georefererad karta.tif", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 13766-2023 georefererad karta.tif", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 34341-2024 FSC-klagomål.docx", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 13766-2023 FSC-klagomål.docx", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 34341-2024 FSC-klagomål mail.docx", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 13766-2023 FSC-klagomål mail.docx", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 34341-2024 tillsynsbegäran.docx", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 13766-2023 tillsynsbegäran.docx", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 34341-2024 tillsynsbegäran mail.docx", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 13766-2023 tillsynsbegäran mail.docx", "A 13766-2023")</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 49549-2025</t>
+          <t>A 49543-2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1460,7 +1455,7 @@
         <v>45939</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1473,16 +1468,16 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -1497,7 +1492,7 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -1506,49 +1501,49 @@
         <v>1</v>
       </c>
       <c r="T10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>Noshornsoxe</t>
+          <t>Svartöra</t>
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 49549-2025 artfynd.xlsx", "A 49549-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 49543-2025 artfynd.xlsx", "A 49543-2025")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 49549-2025 karta.png", "A 49549-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 49543-2025 karta.png", "A 49543-2025")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 49549-2025 georefererad karta.tif", "A 49549-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 49543-2025 georefererad karta.tif", "A 49543-2025")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 49549-2025 FSC-klagomål.docx", "A 49549-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 49543-2025 FSC-klagomål.docx", "A 49543-2025")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 49549-2025 FSC-klagomål mail.docx", "A 49549-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 49543-2025 FSC-klagomål mail.docx", "A 49543-2025")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 49549-2025 tillsynsbegäran.docx", "A 49549-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 49543-2025 tillsynsbegäran.docx", "A 49543-2025")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 49549-2025 tillsynsbegäran mail.docx", "A 49549-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 49543-2025 tillsynsbegäran mail.docx", "A 49543-2025")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 13766-2023</t>
+          <t>A 49549-2025</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1558,14 +1553,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45007</v>
+        <v>45939</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1578,13 +1573,13 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -1614,46 +1609,46 @@
         <v>1</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Noshornsoxe</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 13766-2023 artfynd.xlsx", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 49549-2025 artfynd.xlsx", "A 49549-2025")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 13766-2023 karta.png", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 49549-2025 karta.png", "A 49549-2025")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 13766-2023 georefererad karta.tif", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 49549-2025 georefererad karta.tif", "A 49549-2025")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 13766-2023 FSC-klagomål.docx", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 49549-2025 FSC-klagomål.docx", "A 49549-2025")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 13766-2023 FSC-klagomål mail.docx", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 49549-2025 FSC-klagomål mail.docx", "A 49549-2025")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 13766-2023 tillsynsbegäran.docx", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 49549-2025 tillsynsbegäran.docx", "A 49549-2025")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 13766-2023 tillsynsbegäran mail.docx", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 49549-2025 tillsynsbegäran mail.docx", "A 49549-2025")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 60891-2024</t>
+          <t>A 34341-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1667,10 +1662,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45644</v>
+        <v>45525</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1682,17 +1677,22 @@
           <t>YSTAD</t>
         </is>
       </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I12" t="n">
-        <v>16.1</v>
+        <v>14.4</v>
       </c>
       <c r="J12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -1707,7 +1707,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -1719,39 +1719,39 @@
         <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Lövgroda</t>
+          <t>Desmeknopp</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 60891-2024 artfynd.xlsx", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 34341-2024 artfynd.xlsx", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 60891-2024 karta.png", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 34341-2024 karta.png", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 60891-2024 georefererad karta.tif", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 34341-2024 georefererad karta.tif", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 60891-2024 FSC-klagomål.docx", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 34341-2024 FSC-klagomål.docx", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 60891-2024 FSC-klagomål mail.docx", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 34341-2024 FSC-klagomål mail.docx", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 60891-2024 tillsynsbegäran.docx", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 34341-2024 tillsynsbegäran.docx", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 60891-2024 tillsynsbegäran mail.docx", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 34341-2024 tillsynsbegäran mail.docx", "A 34341-2024")</f>
         <v/>
       </c>
     </row>
@@ -1775,7 +1775,7 @@
         <v>44617</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 40417-2022</t>
+          <t>A 32596-2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1845,10 +1845,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44823</v>
+        <v>45513</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1904,7 +1904,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 34302-2024</t>
+          <t>A 18090-2022</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1914,14 +1914,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45524</v>
+        <v>44684</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.9</v>
+        <v>4.9</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1977,7 +1977,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 32596-2024</t>
+          <t>A 40417-2022</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1991,10 +1991,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45513</v>
+        <v>44823</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2067,7 +2067,7 @@
         <v>45260</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2123,7 +2123,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 38631-2023</t>
+          <t>A 49536-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2137,10 +2137,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45162</v>
+        <v>45939</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2196,7 +2196,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 18090-2022</t>
+          <t>A 38631-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2206,14 +2206,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44684</v>
+        <v>45162</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>4.9</v>
+        <v>0.8</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2269,7 +2269,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 49536-2025</t>
+          <t>A 22195-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2283,10 +2283,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45939</v>
+        <v>45069</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2298,8 +2298,13 @@
           <t>YSTAD</t>
         </is>
       </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I20" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2359,7 +2364,7 @@
         <v>46282</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2415,7 +2420,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 22195-2023</t>
+          <t>A 34302-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2429,10 +2434,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45069</v>
+        <v>45524</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2444,13 +2449,8 @@
           <t>YSTAD</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I22" t="n">
-        <v>1.1</v>
+        <v>1.9</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2510,7 +2510,7 @@
         <v>46190</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>

--- a/Översikt YSTAD.xlsx
+++ b/Översikt YSTAD.xlsx
@@ -584,7 +584,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A 3253-2025</t>
+          <t>A 49546-2025</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>45679</v>
+        <v>45939</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -613,19 +613,14 @@
           <t>YSTAD</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I2" t="n">
-        <v>2.5</v>
+        <v>4.4</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -634,7 +629,7 @@
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -643,59 +638,59 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S2" t="n">
         <v>2</v>
       </c>
       <c r="T2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
-          <t>Lönnlav
-Strävlosta</t>
+          <t>Skogsalm
+Igelkottsröksvamp</t>
         </is>
       </c>
       <c r="W2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 3253-2025 artfynd.xlsx", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 49546-2025 artfynd.xlsx", "A 49546-2025")</f>
         <v/>
       </c>
       <c r="X2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 3253-2025 karta.png", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 49546-2025 karta.png", "A 49546-2025")</f>
         <v/>
       </c>
       <c r="Y2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 3253-2025 georefererad karta.tif", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 49546-2025 georefererad karta.tif", "A 49546-2025")</f>
         <v/>
       </c>
       <c r="AA2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 3253-2025 FSC-klagomål.docx", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 49546-2025 FSC-klagomål.docx", "A 49546-2025")</f>
         <v/>
       </c>
       <c r="AB2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 3253-2025 FSC-klagomål mail.docx", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 49546-2025 FSC-klagomål mail.docx", "A 49546-2025")</f>
         <v/>
       </c>
       <c r="AC2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 3253-2025 tillsynsbegäran.docx", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 49546-2025 tillsynsbegäran.docx", "A 49546-2025")</f>
         <v/>
       </c>
       <c r="AD2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 3253-2025 tillsynsbegäran mail.docx", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 49546-2025 tillsynsbegäran mail.docx", "A 49546-2025")</f>
         <v/>
       </c>
     </row>
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 49546-2025</t>
+          <t>A 31213-2023</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -709,10 +704,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>45939</v>
+        <v>45113</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -725,22 +720,22 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>4.4</v>
+        <v>6.5</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -752,56 +747,56 @@
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
         <v>2</v>
       </c>
       <c r="T3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
-          <t>Skogsalm
-Igelkottsröksvamp</t>
+          <t>Skogsveronika
+Skärmstarr</t>
         </is>
       </c>
       <c r="W3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 49546-2025 artfynd.xlsx", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 31213-2023 artfynd.xlsx", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="X3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 49546-2025 karta.png", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 31213-2023 karta.png", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="Y3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 49546-2025 georefererad karta.tif", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 31213-2023 georefererad karta.tif", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="AA3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 49546-2025 FSC-klagomål.docx", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 31213-2023 FSC-klagomål.docx", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="AB3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 49546-2025 FSC-klagomål mail.docx", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 31213-2023 FSC-klagomål mail.docx", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="AC3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 49546-2025 tillsynsbegäran.docx", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 31213-2023 tillsynsbegäran.docx", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="AD3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 49546-2025 tillsynsbegäran mail.docx", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 31213-2023 tillsynsbegäran mail.docx", "A 31213-2023")</f>
         <v/>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 60295-2022</t>
+          <t>A 3253-2025</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -811,14 +806,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>44903</v>
+        <v>45679</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -830,14 +825,19 @@
           <t>YSTAD</t>
         </is>
       </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I4" t="n">
-        <v>1.1</v>
+        <v>2.5</v>
       </c>
       <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
         <v>2</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -864,50 +864,50 @@
         <v>2</v>
       </c>
       <c r="T4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="U4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>Klockgroda
-Ätlig groda</t>
+          <t>Lönnlav
+Strävlosta</t>
         </is>
       </c>
       <c r="W4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 60295-2022 artfynd.xlsx", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 3253-2025 artfynd.xlsx", "A 3253-2025")</f>
         <v/>
       </c>
       <c r="X4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 60295-2022 karta.png", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 3253-2025 karta.png", "A 3253-2025")</f>
         <v/>
       </c>
       <c r="Y4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 60295-2022 georefererad karta.tif", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 3253-2025 georefererad karta.tif", "A 3253-2025")</f>
         <v/>
       </c>
       <c r="AA4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 60295-2022 FSC-klagomål.docx", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 3253-2025 FSC-klagomål.docx", "A 3253-2025")</f>
         <v/>
       </c>
       <c r="AB4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 60295-2022 FSC-klagomål mail.docx", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 3253-2025 FSC-klagomål mail.docx", "A 3253-2025")</f>
         <v/>
       </c>
       <c r="AC4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 60295-2022 tillsynsbegäran.docx", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 3253-2025 tillsynsbegäran.docx", "A 3253-2025")</f>
         <v/>
       </c>
       <c r="AD4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 60295-2022 tillsynsbegäran mail.docx", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 3253-2025 tillsynsbegäran mail.docx", "A 3253-2025")</f>
         <v/>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 31213-2023</t>
+          <t>A 60295-2022</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -917,14 +917,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>45113</v>
+        <v>44903</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -937,16 +937,16 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>6.5</v>
+        <v>1.1</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -961,7 +961,7 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -970,43 +970,43 @@
         <v>2</v>
       </c>
       <c r="T5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="U5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>Skogsveronika
-Skärmstarr</t>
+          <t>Klockgroda
+Ätlig groda</t>
         </is>
       </c>
       <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 31213-2023 artfynd.xlsx", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 60295-2022 artfynd.xlsx", "A 60295-2022")</f>
         <v/>
       </c>
       <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 31213-2023 karta.png", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 60295-2022 karta.png", "A 60295-2022")</f>
         <v/>
       </c>
       <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 31213-2023 georefererad karta.tif", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 60295-2022 georefererad karta.tif", "A 60295-2022")</f>
         <v/>
       </c>
       <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 31213-2023 FSC-klagomål.docx", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 60295-2022 FSC-klagomål.docx", "A 60295-2022")</f>
         <v/>
       </c>
       <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 31213-2023 FSC-klagomål mail.docx", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 60295-2022 FSC-klagomål mail.docx", "A 60295-2022")</f>
         <v/>
       </c>
       <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 31213-2023 tillsynsbegäran.docx", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 60295-2022 tillsynsbegäran.docx", "A 60295-2022")</f>
         <v/>
       </c>
       <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 31213-2023 tillsynsbegäran mail.docx", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 60295-2022 tillsynsbegäran mail.docx", "A 60295-2022")</f>
         <v/>
       </c>
     </row>
@@ -1030,7 +1030,7 @@
         <v>44756</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1135,7 +1135,7 @@
         <v>45265</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 60891-2024</t>
+          <t>A 13766-2023</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1238,14 +1238,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45644</v>
+        <v>45007</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>16.1</v>
+        <v>0.9</v>
       </c>
       <c r="J8" t="n">
         <v>1</v>
@@ -1298,42 +1298,42 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>Lövgroda</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 60891-2024 artfynd.xlsx", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 13766-2023 artfynd.xlsx", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 60891-2024 karta.png", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 13766-2023 karta.png", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 60891-2024 georefererad karta.tif", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 13766-2023 georefererad karta.tif", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 60891-2024 FSC-klagomål.docx", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 13766-2023 FSC-klagomål.docx", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 60891-2024 FSC-klagomål mail.docx", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 13766-2023 FSC-klagomål mail.docx", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 60891-2024 tillsynsbegäran.docx", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 13766-2023 tillsynsbegäran.docx", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 60891-2024 tillsynsbegäran mail.docx", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 13766-2023 tillsynsbegäran mail.docx", "A 13766-2023")</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 13766-2023</t>
+          <t>A 49549-2025</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1343,14 +1343,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45007</v>
+        <v>45939</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1363,13 +1363,13 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -1399,46 +1399,46 @@
         <v>1</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Noshornsoxe</t>
         </is>
       </c>
       <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 13766-2023 artfynd.xlsx", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 49549-2025 artfynd.xlsx", "A 49549-2025")</f>
         <v/>
       </c>
       <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 13766-2023 karta.png", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 49549-2025 karta.png", "A 49549-2025")</f>
         <v/>
       </c>
       <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 13766-2023 georefererad karta.tif", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 49549-2025 georefererad karta.tif", "A 49549-2025")</f>
         <v/>
       </c>
       <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 13766-2023 FSC-klagomål.docx", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 49549-2025 FSC-klagomål.docx", "A 49549-2025")</f>
         <v/>
       </c>
       <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 13766-2023 FSC-klagomål mail.docx", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 49549-2025 FSC-klagomål mail.docx", "A 49549-2025")</f>
         <v/>
       </c>
       <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 13766-2023 tillsynsbegäran.docx", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 49549-2025 tillsynsbegäran.docx", "A 49549-2025")</f>
         <v/>
       </c>
       <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 13766-2023 tillsynsbegäran mail.docx", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 49549-2025 tillsynsbegäran mail.docx", "A 49549-2025")</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 49543-2025</t>
+          <t>A 60891-2024</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1452,10 +1452,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45939</v>
+        <v>45644</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1468,16 +1468,16 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1.4</v>
+        <v>16.1</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -1492,7 +1492,7 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -1501,49 +1501,49 @@
         <v>1</v>
       </c>
       <c r="T10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U10" t="n">
         <v>0</v>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>Svartöra</t>
+          <t>Lövgroda</t>
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 49543-2025 artfynd.xlsx", "A 49543-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 60891-2024 artfynd.xlsx", "A 60891-2024")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 49543-2025 karta.png", "A 49543-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 60891-2024 karta.png", "A 60891-2024")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 49543-2025 georefererad karta.tif", "A 49543-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 60891-2024 georefererad karta.tif", "A 60891-2024")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 49543-2025 FSC-klagomål.docx", "A 49543-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 60891-2024 FSC-klagomål.docx", "A 60891-2024")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 49543-2025 FSC-klagomål mail.docx", "A 49543-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 60891-2024 FSC-klagomål mail.docx", "A 60891-2024")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 49543-2025 tillsynsbegäran.docx", "A 49543-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 60891-2024 tillsynsbegäran.docx", "A 60891-2024")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 49543-2025 tillsynsbegäran mail.docx", "A 49543-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 60891-2024 tillsynsbegäran mail.docx", "A 60891-2024")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 49549-2025</t>
+          <t>A 34341-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1557,10 +1557,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45939</v>
+        <v>45525</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1572,17 +1572,22 @@
           <t>YSTAD</t>
         </is>
       </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I11" t="n">
-        <v>0.5</v>
+        <v>14.4</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -1597,7 +1602,7 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -1613,42 +1618,42 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Noshornsoxe</t>
+          <t>Desmeknopp</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 49549-2025 artfynd.xlsx", "A 49549-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 34341-2024 artfynd.xlsx", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 49549-2025 karta.png", "A 49549-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 34341-2024 karta.png", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 49549-2025 georefererad karta.tif", "A 49549-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 34341-2024 georefererad karta.tif", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 49549-2025 FSC-klagomål.docx", "A 49549-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 34341-2024 FSC-klagomål.docx", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 49549-2025 FSC-klagomål mail.docx", "A 49549-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 34341-2024 FSC-klagomål mail.docx", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 49549-2025 tillsynsbegäran.docx", "A 49549-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 34341-2024 tillsynsbegäran.docx", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 49549-2025 tillsynsbegäran mail.docx", "A 49549-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 34341-2024 tillsynsbegäran mail.docx", "A 34341-2024")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 34341-2024</t>
+          <t>A 49543-2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1662,10 +1667,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45525</v>
+        <v>45939</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1677,13 +1682,8 @@
           <t>YSTAD</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I12" t="n">
-        <v>14.4</v>
+        <v>1.4</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1716,42 +1716,42 @@
         <v>1</v>
       </c>
       <c r="T12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Desmeknopp</t>
+          <t>Svartöra</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 34341-2024 artfynd.xlsx", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 49543-2025 artfynd.xlsx", "A 49543-2025")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 34341-2024 karta.png", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 49543-2025 karta.png", "A 49543-2025")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 34341-2024 georefererad karta.tif", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 49543-2025 georefererad karta.tif", "A 49543-2025")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 34341-2024 FSC-klagomål.docx", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 49543-2025 FSC-klagomål.docx", "A 49543-2025")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 34341-2024 FSC-klagomål mail.docx", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 49543-2025 FSC-klagomål mail.docx", "A 49543-2025")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 34341-2024 tillsynsbegäran.docx", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 49543-2025 tillsynsbegäran.docx", "A 49543-2025")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 34341-2024 tillsynsbegäran mail.docx", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 49543-2025 tillsynsbegäran mail.docx", "A 49543-2025")</f>
         <v/>
       </c>
     </row>
@@ -1775,7 +1775,7 @@
         <v>44617</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         <v>45513</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1904,7 +1904,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 18090-2022</t>
+          <t>A 40417-2022</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1914,14 +1914,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44684</v>
+        <v>44823</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>4.9</v>
+        <v>2.3</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1977,7 +1977,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 40417-2022</t>
+          <t>A 34302-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1991,10 +1991,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44823</v>
+        <v>45524</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2067,7 +2067,7 @@
         <v>45260</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2123,7 +2123,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 49536-2025</t>
+          <t>A 38631-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2137,10 +2137,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45939</v>
+        <v>45162</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2196,7 +2196,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 38631-2023</t>
+          <t>A 18090-2022</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2206,14 +2206,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45162</v>
+        <v>44684</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.8</v>
+        <v>4.9</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2269,7 +2269,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 22195-2023</t>
+          <t>A 49536-2025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2283,10 +2283,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45069</v>
+        <v>45939</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2298,13 +2298,8 @@
           <t>YSTAD</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I20" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2347,7 +2342,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 38413-2026</t>
+          <t>A 22195-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2361,10 +2356,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46282</v>
+        <v>45069</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2376,8 +2371,13 @@
           <t>YSTAD</t>
         </is>
       </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I21" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2420,7 +2420,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 34302-2024</t>
+          <t>A 38413-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2434,10 +2434,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45524</v>
+        <v>46282</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2450,7 +2450,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.9</v>
+        <v>0.6</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2510,7 +2510,7 @@
         <v>46190</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>

--- a/Översikt YSTAD.xlsx
+++ b/Översikt YSTAD.xlsx
@@ -584,7 +584,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A 49546-2025</t>
+          <t>A 3253-2025</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>45939</v>
+        <v>45679</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -613,14 +613,19 @@
           <t>YSTAD</t>
         </is>
       </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I2" t="n">
-        <v>4.4</v>
+        <v>2.5</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -629,7 +634,7 @@
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -638,59 +643,59 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
         <v>2</v>
       </c>
       <c r="T2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
-          <t>Skogsalm
-Igelkottsröksvamp</t>
+          <t>Lönnlav
+Strävlosta</t>
         </is>
       </c>
       <c r="W2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 49546-2025 artfynd.xlsx", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 3253-2025 artfynd.xlsx", "A 3253-2025")</f>
         <v/>
       </c>
       <c r="X2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 49546-2025 karta.png", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 3253-2025 karta.png", "A 3253-2025")</f>
         <v/>
       </c>
       <c r="Y2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 49546-2025 georefererad karta.tif", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 3253-2025 georefererad karta.tif", "A 3253-2025")</f>
         <v/>
       </c>
       <c r="AA2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 49546-2025 FSC-klagomål.docx", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 3253-2025 FSC-klagomål.docx", "A 3253-2025")</f>
         <v/>
       </c>
       <c r="AB2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 49546-2025 FSC-klagomål mail.docx", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 3253-2025 FSC-klagomål mail.docx", "A 3253-2025")</f>
         <v/>
       </c>
       <c r="AC2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 49546-2025 tillsynsbegäran.docx", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 3253-2025 tillsynsbegäran.docx", "A 3253-2025")</f>
         <v/>
       </c>
       <c r="AD2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 49546-2025 tillsynsbegäran mail.docx", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 3253-2025 tillsynsbegäran mail.docx", "A 3253-2025")</f>
         <v/>
       </c>
     </row>
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 31213-2023</t>
+          <t>A 49546-2025</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -704,10 +709,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>45113</v>
+        <v>45939</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -720,22 +725,22 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>6.5</v>
+        <v>4.4</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -747,56 +752,56 @@
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S3" t="n">
         <v>2</v>
       </c>
       <c r="T3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
-          <t>Skogsveronika
-Skärmstarr</t>
+          <t>Skogsalm
+Igelkottsröksvamp</t>
         </is>
       </c>
       <c r="W3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 31213-2023 artfynd.xlsx", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 49546-2025 artfynd.xlsx", "A 49546-2025")</f>
         <v/>
       </c>
       <c r="X3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 31213-2023 karta.png", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 49546-2025 karta.png", "A 49546-2025")</f>
         <v/>
       </c>
       <c r="Y3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 31213-2023 georefererad karta.tif", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 49546-2025 georefererad karta.tif", "A 49546-2025")</f>
         <v/>
       </c>
       <c r="AA3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 31213-2023 FSC-klagomål.docx", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 49546-2025 FSC-klagomål.docx", "A 49546-2025")</f>
         <v/>
       </c>
       <c r="AB3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 31213-2023 FSC-klagomål mail.docx", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 49546-2025 FSC-klagomål mail.docx", "A 49546-2025")</f>
         <v/>
       </c>
       <c r="AC3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 31213-2023 tillsynsbegäran.docx", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 49546-2025 tillsynsbegäran.docx", "A 49546-2025")</f>
         <v/>
       </c>
       <c r="AD3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 31213-2023 tillsynsbegäran mail.docx", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 49546-2025 tillsynsbegäran mail.docx", "A 49546-2025")</f>
         <v/>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 3253-2025</t>
+          <t>A 60295-2022</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -806,14 +811,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45679</v>
+        <v>44903</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -825,19 +830,14 @@
           <t>YSTAD</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I4" t="n">
-        <v>2.5</v>
+        <v>1.1</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -864,50 +864,50 @@
         <v>2</v>
       </c>
       <c r="T4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="U4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>Lönnlav
-Strävlosta</t>
+          <t>Klockgroda
+Ätlig groda</t>
         </is>
       </c>
       <c r="W4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 3253-2025 artfynd.xlsx", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 60295-2022 artfynd.xlsx", "A 60295-2022")</f>
         <v/>
       </c>
       <c r="X4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 3253-2025 karta.png", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 60295-2022 karta.png", "A 60295-2022")</f>
         <v/>
       </c>
       <c r="Y4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 3253-2025 georefererad karta.tif", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 60295-2022 georefererad karta.tif", "A 60295-2022")</f>
         <v/>
       </c>
       <c r="AA4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 3253-2025 FSC-klagomål.docx", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 60295-2022 FSC-klagomål.docx", "A 60295-2022")</f>
         <v/>
       </c>
       <c r="AB4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 3253-2025 FSC-klagomål mail.docx", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 60295-2022 FSC-klagomål mail.docx", "A 60295-2022")</f>
         <v/>
       </c>
       <c r="AC4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 3253-2025 tillsynsbegäran.docx", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 60295-2022 tillsynsbegäran.docx", "A 60295-2022")</f>
         <v/>
       </c>
       <c r="AD4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 3253-2025 tillsynsbegäran mail.docx", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 60295-2022 tillsynsbegäran mail.docx", "A 60295-2022")</f>
         <v/>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 60295-2022</t>
+          <t>A 31213-2023</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -917,14 +917,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>44903</v>
+        <v>45113</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -937,16 +937,16 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>1.1</v>
+        <v>6.5</v>
       </c>
       <c r="J5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -961,7 +961,7 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -970,43 +970,43 @@
         <v>2</v>
       </c>
       <c r="T5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="U5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>Klockgroda
-Ätlig groda</t>
+          <t>Skogsveronika
+Skärmstarr</t>
         </is>
       </c>
       <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 60295-2022 artfynd.xlsx", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 31213-2023 artfynd.xlsx", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 60295-2022 karta.png", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 31213-2023 karta.png", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 60295-2022 georefererad karta.tif", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 31213-2023 georefererad karta.tif", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 60295-2022 FSC-klagomål.docx", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 31213-2023 FSC-klagomål.docx", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 60295-2022 FSC-klagomål mail.docx", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 31213-2023 FSC-klagomål mail.docx", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 60295-2022 tillsynsbegäran.docx", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 31213-2023 tillsynsbegäran.docx", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 60295-2022 tillsynsbegäran mail.docx", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 31213-2023 tillsynsbegäran mail.docx", "A 31213-2023")</f>
         <v/>
       </c>
     </row>
@@ -1030,7 +1030,7 @@
         <v>44756</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 61558-2023</t>
+          <t>A 13766-2023</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1128,14 +1128,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45265</v>
+        <v>45007</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1147,16 +1147,11 @@
           <t>YSTAD</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I7" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -1168,7 +1163,7 @@
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1177,10 +1172,10 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1193,42 +1188,42 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 61558-2023 artfynd.xlsx", "A 61558-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 13766-2023 artfynd.xlsx", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 61558-2023 karta.png", "A 61558-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 13766-2023 karta.png", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 61558-2023 georefererad karta.tif", "A 61558-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 13766-2023 georefererad karta.tif", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 61558-2023 FSC-klagomål.docx", "A 61558-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 13766-2023 FSC-klagomål.docx", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 61558-2023 FSC-klagomål mail.docx", "A 61558-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 13766-2023 FSC-klagomål mail.docx", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 61558-2023 tillsynsbegäran.docx", "A 61558-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 13766-2023 tillsynsbegäran.docx", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 61558-2023 tillsynsbegäran mail.docx", "A 61558-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 13766-2023 tillsynsbegäran mail.docx", "A 13766-2023")</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 13766-2023</t>
+          <t>A 61558-2023</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1238,14 +1233,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45007</v>
+        <v>45265</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1257,11 +1252,16 @@
           <t>YSTAD</t>
         </is>
       </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I8" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -1273,7 +1273,7 @@
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1282,10 +1282,10 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1298,42 +1298,42 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 13766-2023 artfynd.xlsx", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 61558-2023 artfynd.xlsx", "A 61558-2023")</f>
         <v/>
       </c>
       <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 13766-2023 karta.png", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 61558-2023 karta.png", "A 61558-2023")</f>
         <v/>
       </c>
       <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 13766-2023 georefererad karta.tif", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 61558-2023 georefererad karta.tif", "A 61558-2023")</f>
         <v/>
       </c>
       <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 13766-2023 FSC-klagomål.docx", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 61558-2023 FSC-klagomål.docx", "A 61558-2023")</f>
         <v/>
       </c>
       <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 13766-2023 FSC-klagomål mail.docx", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 61558-2023 FSC-klagomål mail.docx", "A 61558-2023")</f>
         <v/>
       </c>
       <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 13766-2023 tillsynsbegäran.docx", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 61558-2023 tillsynsbegäran.docx", "A 61558-2023")</f>
         <v/>
       </c>
       <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 13766-2023 tillsynsbegäran mail.docx", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 61558-2023 tillsynsbegäran mail.docx", "A 61558-2023")</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 49549-2025</t>
+          <t>A 49543-2025</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1350,7 +1350,7 @@
         <v>45939</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1363,16 +1363,16 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -1387,7 +1387,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -1396,42 +1396,42 @@
         <v>1</v>
       </c>
       <c r="T9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>Noshornsoxe</t>
+          <t>Svartöra</t>
         </is>
       </c>
       <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 49549-2025 artfynd.xlsx", "A 49549-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 49543-2025 artfynd.xlsx", "A 49543-2025")</f>
         <v/>
       </c>
       <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 49549-2025 karta.png", "A 49549-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 49543-2025 karta.png", "A 49543-2025")</f>
         <v/>
       </c>
       <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 49549-2025 georefererad karta.tif", "A 49549-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 49543-2025 georefererad karta.tif", "A 49543-2025")</f>
         <v/>
       </c>
       <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 49549-2025 FSC-klagomål.docx", "A 49549-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 49543-2025 FSC-klagomål.docx", "A 49543-2025")</f>
         <v/>
       </c>
       <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 49549-2025 FSC-klagomål mail.docx", "A 49549-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 49543-2025 FSC-klagomål mail.docx", "A 49543-2025")</f>
         <v/>
       </c>
       <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 49549-2025 tillsynsbegäran.docx", "A 49549-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 49543-2025 tillsynsbegäran.docx", "A 49543-2025")</f>
         <v/>
       </c>
       <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 49549-2025 tillsynsbegäran mail.docx", "A 49549-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 49543-2025 tillsynsbegäran mail.docx", "A 49543-2025")</f>
         <v/>
       </c>
     </row>
@@ -1455,7 +1455,7 @@
         <v>45644</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1543,7 +1543,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 34341-2024</t>
+          <t>A 49549-2025</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1557,10 +1557,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45525</v>
+        <v>45939</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1572,22 +1572,17 @@
           <t>YSTAD</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I11" t="n">
-        <v>14.4</v>
+        <v>0.5</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -1602,7 +1597,7 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -1618,42 +1613,42 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Desmeknopp</t>
+          <t>Noshornsoxe</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 34341-2024 artfynd.xlsx", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 49549-2025 artfynd.xlsx", "A 49549-2025")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 34341-2024 karta.png", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 49549-2025 karta.png", "A 49549-2025")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 34341-2024 georefererad karta.tif", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 49549-2025 georefererad karta.tif", "A 49549-2025")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 34341-2024 FSC-klagomål.docx", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 49549-2025 FSC-klagomål.docx", "A 49549-2025")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 34341-2024 FSC-klagomål mail.docx", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 49549-2025 FSC-klagomål mail.docx", "A 49549-2025")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 34341-2024 tillsynsbegäran.docx", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 49549-2025 tillsynsbegäran.docx", "A 49549-2025")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 34341-2024 tillsynsbegäran mail.docx", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 49549-2025 tillsynsbegäran mail.docx", "A 49549-2025")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 49543-2025</t>
+          <t>A 34341-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1667,10 +1662,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45939</v>
+        <v>45525</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1682,8 +1677,13 @@
           <t>YSTAD</t>
         </is>
       </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I12" t="n">
-        <v>1.4</v>
+        <v>14.4</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1716,42 +1716,42 @@
         <v>1</v>
       </c>
       <c r="T12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Svartöra</t>
+          <t>Desmeknopp</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 49543-2025 artfynd.xlsx", "A 49543-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 34341-2024 artfynd.xlsx", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 49543-2025 karta.png", "A 49543-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 34341-2024 karta.png", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 49543-2025 georefererad karta.tif", "A 49543-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 34341-2024 georefererad karta.tif", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 49543-2025 FSC-klagomål.docx", "A 49543-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 34341-2024 FSC-klagomål.docx", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 49543-2025 FSC-klagomål mail.docx", "A 49543-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 34341-2024 FSC-klagomål mail.docx", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 49543-2025 tillsynsbegäran.docx", "A 49543-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 34341-2024 tillsynsbegäran.docx", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 49543-2025 tillsynsbegäran mail.docx", "A 49543-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 34341-2024 tillsynsbegäran mail.docx", "A 34341-2024")</f>
         <v/>
       </c>
     </row>
@@ -1775,7 +1775,7 @@
         <v>44617</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 32596-2024</t>
+          <t>A 40417-2022</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1845,10 +1845,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45513</v>
+        <v>44823</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1904,7 +1904,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 40417-2022</t>
+          <t>A 18090-2022</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1914,14 +1914,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44823</v>
+        <v>44684</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>2.3</v>
+        <v>4.9</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1977,7 +1977,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 34302-2024</t>
+          <t>A 49536-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1991,10 +1991,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45524</v>
+        <v>45939</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2067,7 +2067,7 @@
         <v>45260</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2140,7 +2140,7 @@
         <v>45162</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2196,7 +2196,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 18090-2022</t>
+          <t>A 22195-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2206,14 +2206,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44684</v>
+        <v>45069</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2225,8 +2225,13 @@
           <t>YSTAD</t>
         </is>
       </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I19" t="n">
-        <v>4.9</v>
+        <v>1.1</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2269,7 +2274,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 49536-2025</t>
+          <t>A 38413-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2283,10 +2288,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45939</v>
+        <v>46282</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2299,7 +2304,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2342,7 +2347,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 22195-2023</t>
+          <t>A 34302-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2356,10 +2361,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45069</v>
+        <v>45524</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2371,13 +2376,8 @@
           <t>YSTAD</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I21" t="n">
-        <v>1.1</v>
+        <v>1.9</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2420,7 +2420,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 38413-2026</t>
+          <t>A 27578-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2434,10 +2434,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46282</v>
+        <v>46190</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2450,7 +2450,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.6</v>
+        <v>6.6</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2493,7 +2493,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 27578-2026</t>
+          <t>A 32596-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2507,10 +2507,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46190</v>
+        <v>45513</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2523,7 +2523,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>6.6</v>
+        <v>2.6</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>

--- a/Översikt YSTAD.xlsx
+++ b/Översikt YSTAD.xlsx
@@ -601,7 +601,7 @@
         <v>45679</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -712,7 +712,7 @@
         <v>45939</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -818,7 +818,7 @@
         <v>44903</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -924,7 +924,7 @@
         <v>45113</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>44756</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1135,7 +1135,7 @@
         <v>45007</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>45265</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
         <v>45939</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         <v>45644</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
         <v>45939</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1665,7 +1665,7 @@
         <v>45525</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1775,7 +1775,7 @@
         <v>44617</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         <v>44823</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
         <v>44684</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1994,7 +1994,7 @@
         <v>45939</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2067,7 +2067,7 @@
         <v>45260</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2140,7 +2140,7 @@
         <v>45162</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>45069</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2291,7 +2291,7 @@
         <v>46282</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         <v>45524</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
         <v>46190</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2510,7 +2510,7 @@
         <v>45513</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>

--- a/Översikt YSTAD.xlsx
+++ b/Översikt YSTAD.xlsx
@@ -601,7 +601,7 @@
         <v>45679</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -712,7 +712,7 @@
         <v>45939</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -818,7 +818,7 @@
         <v>44903</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -924,7 +924,7 @@
         <v>45113</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>44756</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1135,7 +1135,7 @@
         <v>45007</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>45265</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
         <v>45939</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         <v>45644</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
         <v>45939</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1665,7 +1665,7 @@
         <v>45525</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1775,7 +1775,7 @@
         <v>44617</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         <v>44823</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
         <v>44684</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1994,7 +1994,7 @@
         <v>45939</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2067,7 +2067,7 @@
         <v>45260</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2140,7 +2140,7 @@
         <v>45162</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>45069</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2291,7 +2291,7 @@
         <v>46282</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         <v>45524</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
         <v>46190</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2510,7 +2510,7 @@
         <v>45513</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>

--- a/Översikt YSTAD.xlsx
+++ b/Översikt YSTAD.xlsx
@@ -584,7 +584,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A 3253-2025</t>
+          <t>A 31213-2023</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>45679</v>
+        <v>45113</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -613,22 +613,17 @@
           <t>YSTAD</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I2" t="n">
-        <v>2.5</v>
+        <v>6.5</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
@@ -643,7 +638,7 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -655,47 +650,47 @@
         <v>3</v>
       </c>
       <c r="U2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
-          <t>Lönnlav
-Strävlosta</t>
+          <t>Skogsveronika
+Skärmstarr</t>
         </is>
       </c>
       <c r="W2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 3253-2025 artfynd.xlsx", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 31213-2023 artfynd.xlsx", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="X2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 3253-2025 karta.png", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 31213-2023 karta.png", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="Y2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 3253-2025 georefererad karta.tif", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 31213-2023 georefererad karta.tif", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="AA2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 3253-2025 FSC-klagomål.docx", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 31213-2023 FSC-klagomål.docx", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="AB2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 3253-2025 FSC-klagomål mail.docx", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 31213-2023 FSC-klagomål mail.docx", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="AC2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 3253-2025 tillsynsbegäran.docx", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 31213-2023 tillsynsbegäran.docx", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="AD2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 3253-2025 tillsynsbegäran mail.docx", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 31213-2023 tillsynsbegäran mail.docx", "A 31213-2023")</f>
         <v/>
       </c>
     </row>
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 49546-2025</t>
+          <t>A 3253-2025</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -709,10 +704,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>45939</v>
+        <v>45679</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -724,14 +719,19 @@
           <t>YSTAD</t>
         </is>
       </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I3" t="n">
-        <v>4.4</v>
+        <v>2.5</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -740,7 +740,7 @@
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -749,59 +749,59 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
         <v>2</v>
       </c>
       <c r="T3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
-          <t>Skogsalm
-Igelkottsröksvamp</t>
+          <t>Lönnlav
+Strävlosta</t>
         </is>
       </c>
       <c r="W3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 49546-2025 artfynd.xlsx", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 3253-2025 artfynd.xlsx", "A 3253-2025")</f>
         <v/>
       </c>
       <c r="X3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 49546-2025 karta.png", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 3253-2025 karta.png", "A 3253-2025")</f>
         <v/>
       </c>
       <c r="Y3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 49546-2025 georefererad karta.tif", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 3253-2025 georefererad karta.tif", "A 3253-2025")</f>
         <v/>
       </c>
       <c r="AA3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 49546-2025 FSC-klagomål.docx", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 3253-2025 FSC-klagomål.docx", "A 3253-2025")</f>
         <v/>
       </c>
       <c r="AB3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 49546-2025 FSC-klagomål mail.docx", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 3253-2025 FSC-klagomål mail.docx", "A 3253-2025")</f>
         <v/>
       </c>
       <c r="AC3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 49546-2025 tillsynsbegäran.docx", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 3253-2025 tillsynsbegäran.docx", "A 3253-2025")</f>
         <v/>
       </c>
       <c r="AD3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 49546-2025 tillsynsbegäran mail.docx", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 3253-2025 tillsynsbegäran mail.docx", "A 3253-2025")</f>
         <v/>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 60295-2022</t>
+          <t>A 49546-2025</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -811,14 +811,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>44903</v>
+        <v>45939</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -831,13 +831,13 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>1.1</v>
+        <v>4.4</v>
       </c>
       <c r="J4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -846,7 +846,7 @@
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -855,59 +855,59 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S4" t="n">
         <v>2</v>
       </c>
       <c r="T4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="U4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>Klockgroda
-Ätlig groda</t>
+          <t>Skogsalm
+Igelkottsröksvamp</t>
         </is>
       </c>
       <c r="W4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 60295-2022 artfynd.xlsx", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 49546-2025 artfynd.xlsx", "A 49546-2025")</f>
         <v/>
       </c>
       <c r="X4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 60295-2022 karta.png", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 49546-2025 karta.png", "A 49546-2025")</f>
         <v/>
       </c>
       <c r="Y4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 60295-2022 georefererad karta.tif", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 49546-2025 georefererad karta.tif", "A 49546-2025")</f>
         <v/>
       </c>
       <c r="AA4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 60295-2022 FSC-klagomål.docx", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 49546-2025 FSC-klagomål.docx", "A 49546-2025")</f>
         <v/>
       </c>
       <c r="AB4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 60295-2022 FSC-klagomål mail.docx", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 49546-2025 FSC-klagomål mail.docx", "A 49546-2025")</f>
         <v/>
       </c>
       <c r="AC4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 60295-2022 tillsynsbegäran.docx", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 49546-2025 tillsynsbegäran.docx", "A 49546-2025")</f>
         <v/>
       </c>
       <c r="AD4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 60295-2022 tillsynsbegäran mail.docx", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 49546-2025 tillsynsbegäran mail.docx", "A 49546-2025")</f>
         <v/>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 31213-2023</t>
+          <t>A 60295-2022</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -917,14 +917,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>45113</v>
+        <v>44903</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -937,16 +937,16 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>6.5</v>
+        <v>1.1</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -961,7 +961,7 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -970,43 +970,43 @@
         <v>2</v>
       </c>
       <c r="T5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="U5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>Skogsveronika
-Skärmstarr</t>
+          <t>Klockgroda
+Ätlig groda</t>
         </is>
       </c>
       <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 31213-2023 artfynd.xlsx", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 60295-2022 artfynd.xlsx", "A 60295-2022")</f>
         <v/>
       </c>
       <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 31213-2023 karta.png", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 60295-2022 karta.png", "A 60295-2022")</f>
         <v/>
       </c>
       <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 31213-2023 georefererad karta.tif", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 60295-2022 georefererad karta.tif", "A 60295-2022")</f>
         <v/>
       </c>
       <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 31213-2023 FSC-klagomål.docx", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 60295-2022 FSC-klagomål.docx", "A 60295-2022")</f>
         <v/>
       </c>
       <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 31213-2023 FSC-klagomål mail.docx", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 60295-2022 FSC-klagomål mail.docx", "A 60295-2022")</f>
         <v/>
       </c>
       <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 31213-2023 tillsynsbegäran.docx", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 60295-2022 tillsynsbegäran.docx", "A 60295-2022")</f>
         <v/>
       </c>
       <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 31213-2023 tillsynsbegäran mail.docx", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 60295-2022 tillsynsbegäran mail.docx", "A 60295-2022")</f>
         <v/>
       </c>
     </row>
@@ -1030,7 +1030,7 @@
         <v>44756</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 13766-2023</t>
+          <t>A 34341-2024</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1128,14 +1128,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45007</v>
+        <v>45525</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1147,17 +1147,22 @@
           <t>YSTAD</t>
         </is>
       </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I7" t="n">
-        <v>0.9</v>
+        <v>14.4</v>
       </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -1172,7 +1177,7 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1184,39 +1189,39 @@
         <v>1</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Desmeknopp</t>
         </is>
       </c>
       <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 13766-2023 artfynd.xlsx", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 34341-2024 artfynd.xlsx", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 13766-2023 karta.png", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 34341-2024 karta.png", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 13766-2023 georefererad karta.tif", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 34341-2024 georefererad karta.tif", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 13766-2023 FSC-klagomål.docx", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 34341-2024 FSC-klagomål.docx", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 13766-2023 FSC-klagomål mail.docx", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 34341-2024 FSC-klagomål mail.docx", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 13766-2023 tillsynsbegäran.docx", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 34341-2024 tillsynsbegäran.docx", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 13766-2023 tillsynsbegäran mail.docx", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 34341-2024 tillsynsbegäran mail.docx", "A 34341-2024")</f>
         <v/>
       </c>
     </row>
@@ -1240,7 +1245,7 @@
         <v>45265</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1350,7 +1355,7 @@
         <v>45939</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1438,7 +1443,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 60891-2024</t>
+          <t>A 13766-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1448,14 +1453,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45644</v>
+        <v>45007</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1468,7 +1473,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>16.1</v>
+        <v>0.9</v>
       </c>
       <c r="J10" t="n">
         <v>1</v>
@@ -1508,42 +1513,42 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>Lövgroda</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 60891-2024 artfynd.xlsx", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 13766-2023 artfynd.xlsx", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 60891-2024 karta.png", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 13766-2023 karta.png", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 60891-2024 georefererad karta.tif", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 13766-2023 georefererad karta.tif", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 60891-2024 FSC-klagomål.docx", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 13766-2023 FSC-klagomål.docx", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 60891-2024 FSC-klagomål mail.docx", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 13766-2023 FSC-klagomål mail.docx", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 60891-2024 tillsynsbegäran.docx", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 13766-2023 tillsynsbegäran.docx", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 60891-2024 tillsynsbegäran mail.docx", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 13766-2023 tillsynsbegäran mail.docx", "A 13766-2023")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 49549-2025</t>
+          <t>A 60891-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1557,10 +1562,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45939</v>
+        <v>45644</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1573,13 +1578,13 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0.5</v>
+        <v>16.1</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -1609,46 +1614,46 @@
         <v>1</v>
       </c>
       <c r="U11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Noshornsoxe</t>
+          <t>Lövgroda</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 49549-2025 artfynd.xlsx", "A 49549-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 60891-2024 artfynd.xlsx", "A 60891-2024")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 49549-2025 karta.png", "A 49549-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 60891-2024 karta.png", "A 60891-2024")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 49549-2025 georefererad karta.tif", "A 49549-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 60891-2024 georefererad karta.tif", "A 60891-2024")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 49549-2025 FSC-klagomål.docx", "A 49549-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 60891-2024 FSC-klagomål.docx", "A 60891-2024")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 49549-2025 FSC-klagomål mail.docx", "A 49549-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 60891-2024 FSC-klagomål mail.docx", "A 60891-2024")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 49549-2025 tillsynsbegäran.docx", "A 49549-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 60891-2024 tillsynsbegäran.docx", "A 60891-2024")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 49549-2025 tillsynsbegäran mail.docx", "A 49549-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 60891-2024 tillsynsbegäran mail.docx", "A 60891-2024")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 34341-2024</t>
+          <t>A 49549-2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1662,10 +1667,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45525</v>
+        <v>45939</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1677,22 +1682,17 @@
           <t>YSTAD</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I12" t="n">
-        <v>14.4</v>
+        <v>0.5</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -1707,7 +1707,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -1723,35 +1723,35 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Desmeknopp</t>
+          <t>Noshornsoxe</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 34341-2024 artfynd.xlsx", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 49549-2025 artfynd.xlsx", "A 49549-2025")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 34341-2024 karta.png", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 49549-2025 karta.png", "A 49549-2025")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 34341-2024 georefererad karta.tif", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 49549-2025 georefererad karta.tif", "A 49549-2025")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 34341-2024 FSC-klagomål.docx", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 49549-2025 FSC-klagomål.docx", "A 49549-2025")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 34341-2024 FSC-klagomål mail.docx", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 49549-2025 FSC-klagomål mail.docx", "A 49549-2025")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 34341-2024 tillsynsbegäran.docx", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 49549-2025 tillsynsbegäran.docx", "A 49549-2025")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 34341-2024 tillsynsbegäran mail.docx", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 49549-2025 tillsynsbegäran mail.docx", "A 49549-2025")</f>
         <v/>
       </c>
     </row>
@@ -1775,7 +1775,7 @@
         <v>44617</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         <v>44823</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1904,7 +1904,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 18090-2022</t>
+          <t>A 34302-2024</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1914,14 +1914,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44684</v>
+        <v>45524</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>4.9</v>
+        <v>1.9</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1977,7 +1977,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 49536-2025</t>
+          <t>A 60803-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1991,10 +1991,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45939</v>
+        <v>45260</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2050,7 +2050,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 60803-2023</t>
+          <t>A 49536-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2064,10 +2064,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45260</v>
+        <v>45939</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2080,7 +2080,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2140,7 +2140,7 @@
         <v>45162</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2196,7 +2196,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 22195-2023</t>
+          <t>A 18090-2022</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2206,14 +2206,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45069</v>
+        <v>44684</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2225,13 +2225,8 @@
           <t>YSTAD</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I19" t="n">
-        <v>1.1</v>
+        <v>4.9</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2291,7 +2286,7 @@
         <v>46282</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2347,7 +2342,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 34302-2024</t>
+          <t>A 22195-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2361,10 +2356,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45524</v>
+        <v>45069</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2376,8 +2371,13 @@
           <t>YSTAD</t>
         </is>
       </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I21" t="n">
-        <v>1.9</v>
+        <v>1.1</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2437,7 +2437,7 @@
         <v>46190</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2510,7 +2510,7 @@
         <v>45513</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>

--- a/Översikt YSTAD.xlsx
+++ b/Översikt YSTAD.xlsx
@@ -584,7 +584,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A 31213-2023</t>
+          <t>A 3253-2025</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>45113</v>
+        <v>45679</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -613,17 +613,22 @@
           <t>YSTAD</t>
         </is>
       </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I2" t="n">
-        <v>6.5</v>
+        <v>2.5</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
@@ -638,7 +643,7 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -650,47 +655,47 @@
         <v>3</v>
       </c>
       <c r="U2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
-          <t>Skogsveronika
-Skärmstarr</t>
+          <t>Lönnlav
+Strävlosta</t>
         </is>
       </c>
       <c r="W2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 31213-2023 artfynd.xlsx", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 3253-2025 artfynd.xlsx", "A 3253-2025")</f>
         <v/>
       </c>
       <c r="X2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 31213-2023 karta.png", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 3253-2025 karta.png", "A 3253-2025")</f>
         <v/>
       </c>
       <c r="Y2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 31213-2023 georefererad karta.tif", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 3253-2025 georefererad karta.tif", "A 3253-2025")</f>
         <v/>
       </c>
       <c r="AA2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 31213-2023 FSC-klagomål.docx", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 3253-2025 FSC-klagomål.docx", "A 3253-2025")</f>
         <v/>
       </c>
       <c r="AB2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 31213-2023 FSC-klagomål mail.docx", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 3253-2025 FSC-klagomål mail.docx", "A 3253-2025")</f>
         <v/>
       </c>
       <c r="AC2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 31213-2023 tillsynsbegäran.docx", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 3253-2025 tillsynsbegäran.docx", "A 3253-2025")</f>
         <v/>
       </c>
       <c r="AD2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 31213-2023 tillsynsbegäran mail.docx", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 3253-2025 tillsynsbegäran mail.docx", "A 3253-2025")</f>
         <v/>
       </c>
     </row>
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 3253-2025</t>
+          <t>A 49546-2025</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -704,10 +709,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>45679</v>
+        <v>45939</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -719,19 +724,14 @@
           <t>YSTAD</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I3" t="n">
-        <v>2.5</v>
+        <v>4.4</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -740,7 +740,7 @@
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -749,59 +749,59 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S3" t="n">
         <v>2</v>
       </c>
       <c r="T3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
-          <t>Lönnlav
-Strävlosta</t>
+          <t>Skogsalm
+Igelkottsröksvamp</t>
         </is>
       </c>
       <c r="W3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 3253-2025 artfynd.xlsx", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 49546-2025 artfynd.xlsx", "A 49546-2025")</f>
         <v/>
       </c>
       <c r="X3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 3253-2025 karta.png", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 49546-2025 karta.png", "A 49546-2025")</f>
         <v/>
       </c>
       <c r="Y3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 3253-2025 georefererad karta.tif", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 49546-2025 georefererad karta.tif", "A 49546-2025")</f>
         <v/>
       </c>
       <c r="AA3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 3253-2025 FSC-klagomål.docx", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 49546-2025 FSC-klagomål.docx", "A 49546-2025")</f>
         <v/>
       </c>
       <c r="AB3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 3253-2025 FSC-klagomål mail.docx", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 49546-2025 FSC-klagomål mail.docx", "A 49546-2025")</f>
         <v/>
       </c>
       <c r="AC3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 3253-2025 tillsynsbegäran.docx", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 49546-2025 tillsynsbegäran.docx", "A 49546-2025")</f>
         <v/>
       </c>
       <c r="AD3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 3253-2025 tillsynsbegäran mail.docx", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 49546-2025 tillsynsbegäran mail.docx", "A 49546-2025")</f>
         <v/>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 49546-2025</t>
+          <t>A 60295-2022</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -811,14 +811,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45939</v>
+        <v>44903</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -831,13 +831,13 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>4.4</v>
+        <v>1.1</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -846,7 +846,7 @@
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -855,59 +855,59 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>2</v>
       </c>
       <c r="T4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>Skogsalm
-Igelkottsröksvamp</t>
+          <t>Klockgroda
+Ätlig groda</t>
         </is>
       </c>
       <c r="W4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 49546-2025 artfynd.xlsx", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 60295-2022 artfynd.xlsx", "A 60295-2022")</f>
         <v/>
       </c>
       <c r="X4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 49546-2025 karta.png", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 60295-2022 karta.png", "A 60295-2022")</f>
         <v/>
       </c>
       <c r="Y4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 49546-2025 georefererad karta.tif", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 60295-2022 georefererad karta.tif", "A 60295-2022")</f>
         <v/>
       </c>
       <c r="AA4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 49546-2025 FSC-klagomål.docx", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 60295-2022 FSC-klagomål.docx", "A 60295-2022")</f>
         <v/>
       </c>
       <c r="AB4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 49546-2025 FSC-klagomål mail.docx", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 60295-2022 FSC-klagomål mail.docx", "A 60295-2022")</f>
         <v/>
       </c>
       <c r="AC4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 49546-2025 tillsynsbegäran.docx", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 60295-2022 tillsynsbegäran.docx", "A 60295-2022")</f>
         <v/>
       </c>
       <c r="AD4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 49546-2025 tillsynsbegäran mail.docx", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 60295-2022 tillsynsbegäran mail.docx", "A 60295-2022")</f>
         <v/>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 60295-2022</t>
+          <t>A 31213-2023</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -917,14 +917,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>44903</v>
+        <v>45113</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -937,16 +937,16 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>1.1</v>
+        <v>6.5</v>
       </c>
       <c r="J5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -961,7 +961,7 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -970,43 +970,43 @@
         <v>2</v>
       </c>
       <c r="T5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="U5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>Klockgroda
-Ätlig groda</t>
+          <t>Skogsveronika
+Skärmstarr</t>
         </is>
       </c>
       <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 60295-2022 artfynd.xlsx", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 31213-2023 artfynd.xlsx", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 60295-2022 karta.png", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 31213-2023 karta.png", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 60295-2022 georefererad karta.tif", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 31213-2023 georefererad karta.tif", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 60295-2022 FSC-klagomål.docx", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 31213-2023 FSC-klagomål.docx", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 60295-2022 FSC-klagomål mail.docx", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 31213-2023 FSC-klagomål mail.docx", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 60295-2022 tillsynsbegäran.docx", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 31213-2023 tillsynsbegäran.docx", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 60295-2022 tillsynsbegäran mail.docx", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 31213-2023 tillsynsbegäran mail.docx", "A 31213-2023")</f>
         <v/>
       </c>
     </row>
@@ -1030,7 +1030,7 @@
         <v>44756</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 34341-2024</t>
+          <t>A 61558-2023</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1132,10 +1132,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45525</v>
+        <v>45265</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1149,11 +1149,11 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Övriga statliga verk och myndigheter</t>
         </is>
       </c>
       <c r="I7" t="n">
-        <v>14.4</v>
+        <v>1.5</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1162,13 +1162,13 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1180,7 +1180,7 @@
         <v>1</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1189,46 +1189,46 @@
         <v>1</v>
       </c>
       <c r="U7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>Desmeknopp</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 34341-2024 artfynd.xlsx", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 61558-2023 artfynd.xlsx", "A 61558-2023")</f>
         <v/>
       </c>
       <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 34341-2024 karta.png", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 61558-2023 karta.png", "A 61558-2023")</f>
         <v/>
       </c>
       <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 34341-2024 georefererad karta.tif", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 61558-2023 georefererad karta.tif", "A 61558-2023")</f>
         <v/>
       </c>
       <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 34341-2024 FSC-klagomål.docx", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 61558-2023 FSC-klagomål.docx", "A 61558-2023")</f>
         <v/>
       </c>
       <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 34341-2024 FSC-klagomål mail.docx", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 61558-2023 FSC-klagomål mail.docx", "A 61558-2023")</f>
         <v/>
       </c>
       <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 34341-2024 tillsynsbegäran.docx", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 61558-2023 tillsynsbegäran.docx", "A 61558-2023")</f>
         <v/>
       </c>
       <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 34341-2024 tillsynsbegäran mail.docx", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 61558-2023 tillsynsbegäran mail.docx", "A 61558-2023")</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 61558-2023</t>
+          <t>A 13766-2023</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1238,14 +1238,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45265</v>
+        <v>45007</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1257,16 +1257,11 @@
           <t>YSTAD</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I8" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -1278,7 +1273,7 @@
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1287,10 +1282,10 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1303,35 +1298,35 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 61558-2023 artfynd.xlsx", "A 61558-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 13766-2023 artfynd.xlsx", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 61558-2023 karta.png", "A 61558-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 13766-2023 karta.png", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 61558-2023 georefererad karta.tif", "A 61558-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 13766-2023 georefererad karta.tif", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 61558-2023 FSC-klagomål.docx", "A 61558-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 13766-2023 FSC-klagomål.docx", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 61558-2023 FSC-klagomål mail.docx", "A 61558-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 13766-2023 FSC-klagomål mail.docx", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 61558-2023 tillsynsbegäran.docx", "A 61558-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 13766-2023 tillsynsbegäran.docx", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 61558-2023 tillsynsbegäran mail.docx", "A 61558-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 13766-2023 tillsynsbegäran mail.docx", "A 13766-2023")</f>
         <v/>
       </c>
     </row>
@@ -1355,7 +1350,7 @@
         <v>45939</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1443,7 +1438,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 13766-2023</t>
+          <t>A 49549-2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1453,14 +1448,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45007</v>
+        <v>45939</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1473,13 +1468,13 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -1509,39 +1504,39 @@
         <v>1</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Noshornsoxe</t>
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 13766-2023 artfynd.xlsx", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 49549-2025 artfynd.xlsx", "A 49549-2025")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 13766-2023 karta.png", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 49549-2025 karta.png", "A 49549-2025")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 13766-2023 georefererad karta.tif", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 49549-2025 georefererad karta.tif", "A 49549-2025")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 13766-2023 FSC-klagomål.docx", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 49549-2025 FSC-klagomål.docx", "A 49549-2025")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 13766-2023 FSC-klagomål mail.docx", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 49549-2025 FSC-klagomål mail.docx", "A 49549-2025")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 13766-2023 tillsynsbegäran.docx", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 49549-2025 tillsynsbegäran.docx", "A 49549-2025")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 13766-2023 tillsynsbegäran mail.docx", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 49549-2025 tillsynsbegäran mail.docx", "A 49549-2025")</f>
         <v/>
       </c>
     </row>
@@ -1565,7 +1560,7 @@
         <v>45644</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1653,7 +1648,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 49549-2025</t>
+          <t>A 34341-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1667,10 +1662,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45939</v>
+        <v>45525</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1682,17 +1677,22 @@
           <t>YSTAD</t>
         </is>
       </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I12" t="n">
-        <v>0.5</v>
+        <v>14.4</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -1707,7 +1707,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -1723,35 +1723,35 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Noshornsoxe</t>
+          <t>Desmeknopp</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 49549-2025 artfynd.xlsx", "A 49549-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 34341-2024 artfynd.xlsx", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 49549-2025 karta.png", "A 49549-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 34341-2024 karta.png", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 49549-2025 georefererad karta.tif", "A 49549-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 34341-2024 georefererad karta.tif", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 49549-2025 FSC-klagomål.docx", "A 49549-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 34341-2024 FSC-klagomål.docx", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 49549-2025 FSC-klagomål mail.docx", "A 49549-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 34341-2024 FSC-klagomål mail.docx", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 49549-2025 tillsynsbegäran.docx", "A 49549-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 34341-2024 tillsynsbegäran.docx", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 49549-2025 tillsynsbegäran mail.docx", "A 49549-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 34341-2024 tillsynsbegäran mail.docx", "A 34341-2024")</f>
         <v/>
       </c>
     </row>
@@ -1775,7 +1775,7 @@
         <v>44617</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 40417-2022</t>
+          <t>A 32596-2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1845,10 +1845,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44823</v>
+        <v>45513</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1904,7 +1904,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 34302-2024</t>
+          <t>A 40417-2022</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1918,10 +1918,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45524</v>
+        <v>44823</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1977,7 +1977,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 60803-2023</t>
+          <t>A 18090-2022</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1987,14 +1987,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45260</v>
+        <v>44684</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.6</v>
+        <v>4.9</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2067,7 +2067,7 @@
         <v>45939</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2123,7 +2123,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 38631-2023</t>
+          <t>A 60803-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2137,10 +2137,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45162</v>
+        <v>45260</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2196,7 +2196,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 18090-2022</t>
+          <t>A 38631-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2206,14 +2206,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44684</v>
+        <v>45162</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>4.9</v>
+        <v>0.8</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2286,7 +2286,7 @@
         <v>46282</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
         <v>45069</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
         <v>46190</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2493,7 +2493,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 32596-2024</t>
+          <t>A 34302-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2507,10 +2507,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45513</v>
+        <v>45524</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2523,7 +2523,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>2.6</v>
+        <v>1.9</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>

--- a/Översikt YSTAD.xlsx
+++ b/Översikt YSTAD.xlsx
@@ -584,7 +584,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A 3253-2025</t>
+          <t>A 31213-2023</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>45679</v>
+        <v>45113</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -613,22 +613,17 @@
           <t>YSTAD</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I2" t="n">
-        <v>2.5</v>
+        <v>6.5</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
@@ -643,7 +638,7 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -655,47 +650,47 @@
         <v>3</v>
       </c>
       <c r="U2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
-          <t>Lönnlav
-Strävlosta</t>
+          <t>Skogsveronika
+Skärmstarr</t>
         </is>
       </c>
       <c r="W2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 3253-2025 artfynd.xlsx", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 31213-2023 artfynd.xlsx", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="X2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 3253-2025 karta.png", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 31213-2023 karta.png", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="Y2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 3253-2025 georefererad karta.tif", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 31213-2023 georefererad karta.tif", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="AA2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 3253-2025 FSC-klagomål.docx", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 31213-2023 FSC-klagomål.docx", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="AB2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 3253-2025 FSC-klagomål mail.docx", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 31213-2023 FSC-klagomål mail.docx", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="AC2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 3253-2025 tillsynsbegäran.docx", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 31213-2023 tillsynsbegäran.docx", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="AD2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 3253-2025 tillsynsbegäran mail.docx", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 31213-2023 tillsynsbegäran mail.docx", "A 31213-2023")</f>
         <v/>
       </c>
     </row>
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 49546-2025</t>
+          <t>A 3253-2025</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -709,10 +704,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>45939</v>
+        <v>45679</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -724,14 +719,19 @@
           <t>YSTAD</t>
         </is>
       </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I3" t="n">
-        <v>4.4</v>
+        <v>2.5</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -740,7 +740,7 @@
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -749,59 +749,59 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
         <v>2</v>
       </c>
       <c r="T3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
-          <t>Skogsalm
-Igelkottsröksvamp</t>
+          <t>Lönnlav
+Strävlosta</t>
         </is>
       </c>
       <c r="W3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 49546-2025 artfynd.xlsx", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 3253-2025 artfynd.xlsx", "A 3253-2025")</f>
         <v/>
       </c>
       <c r="X3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 49546-2025 karta.png", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 3253-2025 karta.png", "A 3253-2025")</f>
         <v/>
       </c>
       <c r="Y3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 49546-2025 georefererad karta.tif", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 3253-2025 georefererad karta.tif", "A 3253-2025")</f>
         <v/>
       </c>
       <c r="AA3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 49546-2025 FSC-klagomål.docx", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 3253-2025 FSC-klagomål.docx", "A 3253-2025")</f>
         <v/>
       </c>
       <c r="AB3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 49546-2025 FSC-klagomål mail.docx", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 3253-2025 FSC-klagomål mail.docx", "A 3253-2025")</f>
         <v/>
       </c>
       <c r="AC3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 49546-2025 tillsynsbegäran.docx", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 3253-2025 tillsynsbegäran.docx", "A 3253-2025")</f>
         <v/>
       </c>
       <c r="AD3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 49546-2025 tillsynsbegäran mail.docx", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 3253-2025 tillsynsbegäran mail.docx", "A 3253-2025")</f>
         <v/>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 60295-2022</t>
+          <t>A 49546-2025</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -811,14 +811,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>44903</v>
+        <v>45939</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -831,13 +831,13 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>1.1</v>
+        <v>4.4</v>
       </c>
       <c r="J4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -846,7 +846,7 @@
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -855,59 +855,59 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S4" t="n">
         <v>2</v>
       </c>
       <c r="T4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="U4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>Klockgroda
-Ätlig groda</t>
+          <t>Skogsalm
+Igelkottsröksvamp</t>
         </is>
       </c>
       <c r="W4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 60295-2022 artfynd.xlsx", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 49546-2025 artfynd.xlsx", "A 49546-2025")</f>
         <v/>
       </c>
       <c r="X4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 60295-2022 karta.png", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 49546-2025 karta.png", "A 49546-2025")</f>
         <v/>
       </c>
       <c r="Y4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 60295-2022 georefererad karta.tif", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 49546-2025 georefererad karta.tif", "A 49546-2025")</f>
         <v/>
       </c>
       <c r="AA4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 60295-2022 FSC-klagomål.docx", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 49546-2025 FSC-klagomål.docx", "A 49546-2025")</f>
         <v/>
       </c>
       <c r="AB4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 60295-2022 FSC-klagomål mail.docx", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 49546-2025 FSC-klagomål mail.docx", "A 49546-2025")</f>
         <v/>
       </c>
       <c r="AC4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 60295-2022 tillsynsbegäran.docx", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 49546-2025 tillsynsbegäran.docx", "A 49546-2025")</f>
         <v/>
       </c>
       <c r="AD4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 60295-2022 tillsynsbegäran mail.docx", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 49546-2025 tillsynsbegäran mail.docx", "A 49546-2025")</f>
         <v/>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 31213-2023</t>
+          <t>A 60295-2022</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -917,14 +917,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>45113</v>
+        <v>44903</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -937,16 +937,16 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>6.5</v>
+        <v>1.1</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -961,7 +961,7 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -970,43 +970,43 @@
         <v>2</v>
       </c>
       <c r="T5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="U5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>Skogsveronika
-Skärmstarr</t>
+          <t>Klockgroda
+Ätlig groda</t>
         </is>
       </c>
       <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 31213-2023 artfynd.xlsx", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 60295-2022 artfynd.xlsx", "A 60295-2022")</f>
         <v/>
       </c>
       <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 31213-2023 karta.png", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 60295-2022 karta.png", "A 60295-2022")</f>
         <v/>
       </c>
       <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 31213-2023 georefererad karta.tif", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 60295-2022 georefererad karta.tif", "A 60295-2022")</f>
         <v/>
       </c>
       <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 31213-2023 FSC-klagomål.docx", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 60295-2022 FSC-klagomål.docx", "A 60295-2022")</f>
         <v/>
       </c>
       <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 31213-2023 FSC-klagomål mail.docx", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 60295-2022 FSC-klagomål mail.docx", "A 60295-2022")</f>
         <v/>
       </c>
       <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 31213-2023 tillsynsbegäran.docx", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 60295-2022 tillsynsbegäran.docx", "A 60295-2022")</f>
         <v/>
       </c>
       <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 31213-2023 tillsynsbegäran mail.docx", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 60295-2022 tillsynsbegäran mail.docx", "A 60295-2022")</f>
         <v/>
       </c>
     </row>
@@ -1030,7 +1030,7 @@
         <v>44756</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1135,7 +1135,7 @@
         <v>45265</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 13766-2023</t>
+          <t>A 49543-2025</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1238,14 +1238,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45007</v>
+        <v>45939</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1258,16 +1258,16 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -1282,7 +1282,7 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -1291,49 +1291,49 @@
         <v>1</v>
       </c>
       <c r="T8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U8" t="n">
         <v>0</v>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Svartöra</t>
         </is>
       </c>
       <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 13766-2023 artfynd.xlsx", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 49543-2025 artfynd.xlsx", "A 49543-2025")</f>
         <v/>
       </c>
       <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 13766-2023 karta.png", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 49543-2025 karta.png", "A 49543-2025")</f>
         <v/>
       </c>
       <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 13766-2023 georefererad karta.tif", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 49543-2025 georefererad karta.tif", "A 49543-2025")</f>
         <v/>
       </c>
       <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 13766-2023 FSC-klagomål.docx", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 49543-2025 FSC-klagomål.docx", "A 49543-2025")</f>
         <v/>
       </c>
       <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 13766-2023 FSC-klagomål mail.docx", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 49543-2025 FSC-klagomål mail.docx", "A 49543-2025")</f>
         <v/>
       </c>
       <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 13766-2023 tillsynsbegäran.docx", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 49543-2025 tillsynsbegäran.docx", "A 49543-2025")</f>
         <v/>
       </c>
       <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 13766-2023 tillsynsbegäran mail.docx", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 49543-2025 tillsynsbegäran mail.docx", "A 49543-2025")</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 49543-2025</t>
+          <t>A 34341-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1347,10 +1347,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45939</v>
+        <v>45525</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1362,8 +1362,13 @@
           <t>YSTAD</t>
         </is>
       </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I9" t="n">
-        <v>1.4</v>
+        <v>14.4</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1396,42 +1401,42 @@
         <v>1</v>
       </c>
       <c r="T9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>Svartöra</t>
+          <t>Desmeknopp</t>
         </is>
       </c>
       <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 49543-2025 artfynd.xlsx", "A 49543-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 34341-2024 artfynd.xlsx", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 49543-2025 karta.png", "A 49543-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 34341-2024 karta.png", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 49543-2025 georefererad karta.tif", "A 49543-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 34341-2024 georefererad karta.tif", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 49543-2025 FSC-klagomål.docx", "A 49543-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 34341-2024 FSC-klagomål.docx", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 49543-2025 FSC-klagomål mail.docx", "A 49543-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 34341-2024 FSC-klagomål mail.docx", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 49543-2025 tillsynsbegäran.docx", "A 49543-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 34341-2024 tillsynsbegäran.docx", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 49543-2025 tillsynsbegäran mail.docx", "A 49543-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 34341-2024 tillsynsbegäran mail.docx", "A 34341-2024")</f>
         <v/>
       </c>
     </row>
@@ -1455,7 +1460,7 @@
         <v>45939</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1543,7 +1548,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 60891-2024</t>
+          <t>A 13766-2023</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1553,14 +1558,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45644</v>
+        <v>45007</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1573,7 +1578,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>16.1</v>
+        <v>0.9</v>
       </c>
       <c r="J11" t="n">
         <v>1</v>
@@ -1613,42 +1618,42 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Lövgroda</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 60891-2024 artfynd.xlsx", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 13766-2023 artfynd.xlsx", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 60891-2024 karta.png", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 13766-2023 karta.png", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 60891-2024 georefererad karta.tif", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 13766-2023 georefererad karta.tif", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 60891-2024 FSC-klagomål.docx", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 13766-2023 FSC-klagomål.docx", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 60891-2024 FSC-klagomål mail.docx", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 13766-2023 FSC-klagomål mail.docx", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 60891-2024 tillsynsbegäran.docx", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 13766-2023 tillsynsbegäran.docx", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 60891-2024 tillsynsbegäran mail.docx", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 13766-2023 tillsynsbegäran mail.docx", "A 13766-2023")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 34341-2024</t>
+          <t>A 60891-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1662,10 +1667,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45525</v>
+        <v>45644</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1677,22 +1682,17 @@
           <t>YSTAD</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I12" t="n">
-        <v>14.4</v>
+        <v>16.1</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -1707,7 +1707,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -1719,39 +1719,39 @@
         <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Desmeknopp</t>
+          <t>Lövgroda</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 34341-2024 artfynd.xlsx", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 60891-2024 artfynd.xlsx", "A 60891-2024")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 34341-2024 karta.png", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 60891-2024 karta.png", "A 60891-2024")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 34341-2024 georefererad karta.tif", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 60891-2024 georefererad karta.tif", "A 60891-2024")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 34341-2024 FSC-klagomål.docx", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 60891-2024 FSC-klagomål.docx", "A 60891-2024")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 34341-2024 FSC-klagomål mail.docx", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 60891-2024 FSC-klagomål mail.docx", "A 60891-2024")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 34341-2024 tillsynsbegäran.docx", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 60891-2024 tillsynsbegäran.docx", "A 60891-2024")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 34341-2024 tillsynsbegäran mail.docx", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 60891-2024 tillsynsbegäran mail.docx", "A 60891-2024")</f>
         <v/>
       </c>
     </row>
@@ -1775,7 +1775,7 @@
         <v>44617</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 32596-2024</t>
+          <t>A 40417-2022</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1845,10 +1845,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45513</v>
+        <v>44823</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1904,7 +1904,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 40417-2022</t>
+          <t>A 34302-2024</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1918,10 +1918,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44823</v>
+        <v>45524</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1977,7 +1977,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 18090-2022</t>
+          <t>A 32596-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1987,14 +1987,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44684</v>
+        <v>45513</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>4.9</v>
+        <v>2.6</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2050,7 +2050,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 49536-2025</t>
+          <t>A 60803-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2064,10 +2064,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45939</v>
+        <v>45260</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2080,7 +2080,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2123,7 +2123,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 60803-2023</t>
+          <t>A 38631-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2137,10 +2137,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45260</v>
+        <v>45162</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1.6</v>
+        <v>0.8</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2196,7 +2196,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 38631-2023</t>
+          <t>A 18090-2022</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2206,14 +2206,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45162</v>
+        <v>44684</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.8</v>
+        <v>4.9</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2269,7 +2269,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 38413-2026</t>
+          <t>A 49536-2025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2283,10 +2283,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46282</v>
+        <v>45939</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2299,7 +2299,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2342,7 +2342,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 22195-2023</t>
+          <t>A 38413-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2356,10 +2356,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45069</v>
+        <v>46282</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2371,13 +2371,8 @@
           <t>YSTAD</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I21" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2420,7 +2415,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 27578-2026</t>
+          <t>A 22195-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2434,10 +2429,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46190</v>
+        <v>45069</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2449,8 +2444,13 @@
           <t>YSTAD</t>
         </is>
       </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I22" t="n">
-        <v>6.6</v>
+        <v>1.1</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2493,7 +2493,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 34302-2024</t>
+          <t>A 27578-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2507,10 +2507,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45524</v>
+        <v>46190</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2523,7 +2523,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.9</v>
+        <v>6.6</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>

--- a/Översikt YSTAD.xlsx
+++ b/Översikt YSTAD.xlsx
@@ -584,7 +584,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A 31213-2023</t>
+          <t>A 60295-2022</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -594,14 +594,14 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>45113</v>
+        <v>44903</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -614,16 +614,16 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>6.5</v>
+        <v>1.1</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
@@ -638,7 +638,7 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -647,50 +647,50 @@
         <v>2</v>
       </c>
       <c r="T2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="U2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
-          <t>Skogsveronika
-Skärmstarr</t>
+          <t>Klockgroda
+Ätlig groda</t>
         </is>
       </c>
       <c r="W2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 31213-2023 artfynd.xlsx", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 60295-2022 artfynd.xlsx", "A 60295-2022")</f>
         <v/>
       </c>
       <c r="X2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 31213-2023 karta.png", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 60295-2022 karta.png", "A 60295-2022")</f>
         <v/>
       </c>
       <c r="Y2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 31213-2023 georefererad karta.tif", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 60295-2022 georefererad karta.tif", "A 60295-2022")</f>
         <v/>
       </c>
       <c r="AA2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 31213-2023 FSC-klagomål.docx", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 60295-2022 FSC-klagomål.docx", "A 60295-2022")</f>
         <v/>
       </c>
       <c r="AB2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 31213-2023 FSC-klagomål mail.docx", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 60295-2022 FSC-klagomål mail.docx", "A 60295-2022")</f>
         <v/>
       </c>
       <c r="AC2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 31213-2023 tillsynsbegäran.docx", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 60295-2022 tillsynsbegäran.docx", "A 60295-2022")</f>
         <v/>
       </c>
       <c r="AD2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 31213-2023 tillsynsbegäran mail.docx", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 60295-2022 tillsynsbegäran mail.docx", "A 60295-2022")</f>
         <v/>
       </c>
     </row>
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 3253-2025</t>
+          <t>A 31213-2023</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -704,10 +704,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>45679</v>
+        <v>45113</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -719,22 +719,17 @@
           <t>YSTAD</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I3" t="n">
-        <v>2.5</v>
+        <v>6.5</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
@@ -749,7 +744,7 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -761,47 +756,47 @@
         <v>3</v>
       </c>
       <c r="U3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
-          <t>Lönnlav
-Strävlosta</t>
+          <t>Skogsveronika
+Skärmstarr</t>
         </is>
       </c>
       <c r="W3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 3253-2025 artfynd.xlsx", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 31213-2023 artfynd.xlsx", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="X3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 3253-2025 karta.png", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 31213-2023 karta.png", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="Y3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 3253-2025 georefererad karta.tif", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 31213-2023 georefererad karta.tif", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="AA3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 3253-2025 FSC-klagomål.docx", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 31213-2023 FSC-klagomål.docx", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="AB3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 3253-2025 FSC-klagomål mail.docx", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 31213-2023 FSC-klagomål mail.docx", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="AC3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 3253-2025 tillsynsbegäran.docx", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 31213-2023 tillsynsbegäran.docx", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="AD3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 3253-2025 tillsynsbegäran mail.docx", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 31213-2023 tillsynsbegäran mail.docx", "A 31213-2023")</f>
         <v/>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 49546-2025</t>
+          <t>A 3253-2025</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -815,10 +810,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45939</v>
+        <v>45679</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -830,14 +825,19 @@
           <t>YSTAD</t>
         </is>
       </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I4" t="n">
-        <v>4.4</v>
+        <v>2.5</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -846,7 +846,7 @@
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -855,59 +855,59 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>2</v>
       </c>
       <c r="T4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>Skogsalm
-Igelkottsröksvamp</t>
+          <t>Lönnlav
+Strävlosta</t>
         </is>
       </c>
       <c r="W4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 49546-2025 artfynd.xlsx", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 3253-2025 artfynd.xlsx", "A 3253-2025")</f>
         <v/>
       </c>
       <c r="X4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 49546-2025 karta.png", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 3253-2025 karta.png", "A 3253-2025")</f>
         <v/>
       </c>
       <c r="Y4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 49546-2025 georefererad karta.tif", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 3253-2025 georefererad karta.tif", "A 3253-2025")</f>
         <v/>
       </c>
       <c r="AA4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 49546-2025 FSC-klagomål.docx", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 3253-2025 FSC-klagomål.docx", "A 3253-2025")</f>
         <v/>
       </c>
       <c r="AB4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 49546-2025 FSC-klagomål mail.docx", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 3253-2025 FSC-klagomål mail.docx", "A 3253-2025")</f>
         <v/>
       </c>
       <c r="AC4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 49546-2025 tillsynsbegäran.docx", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 3253-2025 tillsynsbegäran.docx", "A 3253-2025")</f>
         <v/>
       </c>
       <c r="AD4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 49546-2025 tillsynsbegäran mail.docx", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 3253-2025 tillsynsbegäran mail.docx", "A 3253-2025")</f>
         <v/>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 60295-2022</t>
+          <t>A 49546-2025</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -917,14 +917,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>44903</v>
+        <v>45939</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -937,13 +937,13 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>1.1</v>
+        <v>4.4</v>
       </c>
       <c r="J5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -952,7 +952,7 @@
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -961,52 +961,52 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S5" t="n">
         <v>2</v>
       </c>
       <c r="T5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="U5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>Klockgroda
-Ätlig groda</t>
+          <t>Skogsalm
+Igelkottsröksvamp</t>
         </is>
       </c>
       <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 60295-2022 artfynd.xlsx", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 49546-2025 artfynd.xlsx", "A 49546-2025")</f>
         <v/>
       </c>
       <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 60295-2022 karta.png", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 49546-2025 karta.png", "A 49546-2025")</f>
         <v/>
       </c>
       <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 60295-2022 georefererad karta.tif", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 49546-2025 georefererad karta.tif", "A 49546-2025")</f>
         <v/>
       </c>
       <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 60295-2022 FSC-klagomål.docx", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 49546-2025 FSC-klagomål.docx", "A 49546-2025")</f>
         <v/>
       </c>
       <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 60295-2022 FSC-klagomål mail.docx", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 49546-2025 FSC-klagomål mail.docx", "A 49546-2025")</f>
         <v/>
       </c>
       <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 60295-2022 tillsynsbegäran.docx", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 49546-2025 tillsynsbegäran.docx", "A 49546-2025")</f>
         <v/>
       </c>
       <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 60295-2022 tillsynsbegäran mail.docx", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 49546-2025 tillsynsbegäran mail.docx", "A 49546-2025")</f>
         <v/>
       </c>
     </row>
@@ -1030,7 +1030,7 @@
         <v>44756</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1135,7 +1135,7 @@
         <v>45265</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 49543-2025</t>
+          <t>A 13766-2023</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1238,14 +1238,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45939</v>
+        <v>45007</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1258,16 +1258,16 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -1282,7 +1282,7 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -1291,49 +1291,49 @@
         <v>1</v>
       </c>
       <c r="T8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U8" t="n">
         <v>0</v>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>Svartöra</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 49543-2025 artfynd.xlsx", "A 49543-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 13766-2023 artfynd.xlsx", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 49543-2025 karta.png", "A 49543-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 13766-2023 karta.png", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 49543-2025 georefererad karta.tif", "A 49543-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 13766-2023 georefererad karta.tif", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 49543-2025 FSC-klagomål.docx", "A 49543-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 13766-2023 FSC-klagomål.docx", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 49543-2025 FSC-klagomål mail.docx", "A 49543-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 13766-2023 FSC-klagomål mail.docx", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 49543-2025 tillsynsbegäran.docx", "A 49543-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 13766-2023 tillsynsbegäran.docx", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 49543-2025 tillsynsbegäran mail.docx", "A 49543-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 13766-2023 tillsynsbegäran mail.docx", "A 13766-2023")</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 34341-2024</t>
+          <t>A 49543-2025</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1347,10 +1347,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45525</v>
+        <v>45939</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1362,13 +1362,8 @@
           <t>YSTAD</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I9" t="n">
-        <v>14.4</v>
+        <v>1.4</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1401,49 +1396,49 @@
         <v>1</v>
       </c>
       <c r="T9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>Desmeknopp</t>
+          <t>Svartöra</t>
         </is>
       </c>
       <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 34341-2024 artfynd.xlsx", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 49543-2025 artfynd.xlsx", "A 49543-2025")</f>
         <v/>
       </c>
       <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 34341-2024 karta.png", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 49543-2025 karta.png", "A 49543-2025")</f>
         <v/>
       </c>
       <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 34341-2024 georefererad karta.tif", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 49543-2025 georefererad karta.tif", "A 49543-2025")</f>
         <v/>
       </c>
       <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 34341-2024 FSC-klagomål.docx", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 49543-2025 FSC-klagomål.docx", "A 49543-2025")</f>
         <v/>
       </c>
       <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 34341-2024 FSC-klagomål mail.docx", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 49543-2025 FSC-klagomål mail.docx", "A 49543-2025")</f>
         <v/>
       </c>
       <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 34341-2024 tillsynsbegäran.docx", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 49543-2025 tillsynsbegäran.docx", "A 49543-2025")</f>
         <v/>
       </c>
       <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 34341-2024 tillsynsbegäran mail.docx", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 49543-2025 tillsynsbegäran mail.docx", "A 49543-2025")</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 49549-2025</t>
+          <t>A 34341-2024</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1457,10 +1452,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45939</v>
+        <v>45525</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1472,17 +1467,22 @@
           <t>YSTAD</t>
         </is>
       </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I10" t="n">
-        <v>0.5</v>
+        <v>14.4</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -1497,7 +1497,7 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -1513,42 +1513,42 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>Noshornsoxe</t>
+          <t>Desmeknopp</t>
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 49549-2025 artfynd.xlsx", "A 49549-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 34341-2024 artfynd.xlsx", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 49549-2025 karta.png", "A 49549-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 34341-2024 karta.png", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 49549-2025 georefererad karta.tif", "A 49549-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 34341-2024 georefererad karta.tif", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 49549-2025 FSC-klagomål.docx", "A 49549-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 34341-2024 FSC-klagomål.docx", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 49549-2025 FSC-klagomål mail.docx", "A 49549-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 34341-2024 FSC-klagomål mail.docx", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 49549-2025 tillsynsbegäran.docx", "A 49549-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 34341-2024 tillsynsbegäran.docx", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 49549-2025 tillsynsbegäran mail.docx", "A 49549-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 34341-2024 tillsynsbegäran mail.docx", "A 34341-2024")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 13766-2023</t>
+          <t>A 49549-2025</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1558,14 +1558,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45007</v>
+        <v>45939</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1578,13 +1578,13 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -1614,39 +1614,39 @@
         <v>1</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Noshornsoxe</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 13766-2023 artfynd.xlsx", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 49549-2025 artfynd.xlsx", "A 49549-2025")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 13766-2023 karta.png", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 49549-2025 karta.png", "A 49549-2025")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 13766-2023 georefererad karta.tif", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 49549-2025 georefererad karta.tif", "A 49549-2025")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 13766-2023 FSC-klagomål.docx", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 49549-2025 FSC-klagomål.docx", "A 49549-2025")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 13766-2023 FSC-klagomål mail.docx", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 49549-2025 FSC-klagomål mail.docx", "A 49549-2025")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 13766-2023 tillsynsbegäran.docx", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 49549-2025 tillsynsbegäran.docx", "A 49549-2025")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 13766-2023 tillsynsbegäran mail.docx", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 49549-2025 tillsynsbegäran mail.docx", "A 49549-2025")</f>
         <v/>
       </c>
     </row>
@@ -1670,7 +1670,7 @@
         <v>45644</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1775,7 +1775,7 @@
         <v>44617</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 40417-2022</t>
+          <t>A 38631-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1845,10 +1845,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44823</v>
+        <v>45162</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>2.3</v>
+        <v>0.8</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1904,7 +1904,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 34302-2024</t>
+          <t>A 32596-2024</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1918,10 +1918,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45524</v>
+        <v>45513</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.9</v>
+        <v>2.6</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1977,7 +1977,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 32596-2024</t>
+          <t>A 22195-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1991,10 +1991,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45513</v>
+        <v>45069</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2006,8 +2006,13 @@
           <t>YSTAD</t>
         </is>
       </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I16" t="n">
-        <v>2.6</v>
+        <v>1.1</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2050,7 +2055,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 60803-2023</t>
+          <t>A 34302-2024</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2064,10 +2069,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45260</v>
+        <v>45524</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2080,7 +2085,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2123,7 +2128,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 38631-2023</t>
+          <t>A 49536-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2137,10 +2142,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45162</v>
+        <v>45939</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2153,7 +2158,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2196,7 +2201,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 18090-2022</t>
+          <t>A 38413-2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2206,14 +2211,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44684</v>
+        <v>46282</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2226,7 +2231,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>4.9</v>
+        <v>0.6</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2269,7 +2274,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 49536-2025</t>
+          <t>A 40417-2022</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2283,10 +2288,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45939</v>
+        <v>44823</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2299,7 +2304,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2342,7 +2347,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 38413-2026</t>
+          <t>A 27578-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2356,10 +2361,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46282</v>
+        <v>46190</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2372,7 +2377,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.6</v>
+        <v>6.6</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2415,7 +2420,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 22195-2023</t>
+          <t>A 18090-2022</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2425,14 +2430,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45069</v>
+        <v>44684</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2444,13 +2449,8 @@
           <t>YSTAD</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I22" t="n">
-        <v>1.1</v>
+        <v>4.9</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2493,7 +2493,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 27578-2026</t>
+          <t>A 60803-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2507,10 +2507,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46190</v>
+        <v>45260</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2523,7 +2523,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>6.6</v>
+        <v>1.6</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>

--- a/Översikt YSTAD.xlsx
+++ b/Översikt YSTAD.xlsx
@@ -601,7 +601,7 @@
         <v>44903</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -690,7 +690,7 @@
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 31213-2023</t>
+          <t>A 49546-2025</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -704,10 +704,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>45113</v>
+        <v>45939</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -720,22 +720,22 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>6.5</v>
+        <v>4.4</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -747,56 +747,56 @@
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S3" t="n">
         <v>2</v>
       </c>
       <c r="T3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
-          <t>Skogsveronika
-Skärmstarr</t>
+          <t>Skogsalm
+Igelkottsröksvamp</t>
         </is>
       </c>
       <c r="W3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 31213-2023 artfynd.xlsx", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 49546-2025 artfynd.xlsx", "A 49546-2025")</f>
         <v/>
       </c>
       <c r="X3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 31213-2023 karta.png", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 49546-2025 karta.png", "A 49546-2025")</f>
         <v/>
       </c>
       <c r="Y3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 31213-2023 georefererad karta.tif", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 49546-2025 georefererad karta.tif", "A 49546-2025")</f>
         <v/>
       </c>
       <c r="AA3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 31213-2023 FSC-klagomål.docx", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 49546-2025 FSC-klagomål.docx", "A 49546-2025")</f>
         <v/>
       </c>
       <c r="AB3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 31213-2023 FSC-klagomål mail.docx", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 49546-2025 FSC-klagomål mail.docx", "A 49546-2025")</f>
         <v/>
       </c>
       <c r="AC3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 31213-2023 tillsynsbegäran.docx", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 49546-2025 tillsynsbegäran.docx", "A 49546-2025")</f>
         <v/>
       </c>
       <c r="AD3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 31213-2023 tillsynsbegäran mail.docx", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 49546-2025 tillsynsbegäran mail.docx", "A 49546-2025")</f>
         <v/>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 3253-2025</t>
+          <t>A 31213-2023</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -810,10 +810,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45679</v>
+        <v>45113</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -825,22 +825,17 @@
           <t>YSTAD</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I4" t="n">
-        <v>2.5</v>
+        <v>6.5</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -855,7 +850,7 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -867,47 +862,47 @@
         <v>3</v>
       </c>
       <c r="U4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>Lönnlav
-Strävlosta</t>
+          <t>Skogsveronika
+Skärmstarr</t>
         </is>
       </c>
       <c r="W4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 3253-2025 artfynd.xlsx", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 31213-2023 artfynd.xlsx", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="X4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 3253-2025 karta.png", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 31213-2023 karta.png", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="Y4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 3253-2025 georefererad karta.tif", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 31213-2023 georefererad karta.tif", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="AA4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 3253-2025 FSC-klagomål.docx", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 31213-2023 FSC-klagomål.docx", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="AB4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 3253-2025 FSC-klagomål mail.docx", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 31213-2023 FSC-klagomål mail.docx", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="AC4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 3253-2025 tillsynsbegäran.docx", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 31213-2023 tillsynsbegäran.docx", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="AD4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 3253-2025 tillsynsbegäran mail.docx", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 31213-2023 tillsynsbegäran mail.docx", "A 31213-2023")</f>
         <v/>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 49546-2025</t>
+          <t>A 3253-2025</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -921,10 +916,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>45939</v>
+        <v>45679</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -936,14 +931,19 @@
           <t>YSTAD</t>
         </is>
       </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I5" t="n">
-        <v>4.4</v>
+        <v>2.5</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -952,7 +952,7 @@
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -961,52 +961,52 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
         <v>2</v>
       </c>
       <c r="T5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>Skogsalm
-Igelkottsröksvamp</t>
+          <t>Lönnlav
+Strävlosta</t>
         </is>
       </c>
       <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 49546-2025 artfynd.xlsx", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 3253-2025 artfynd.xlsx", "A 3253-2025")</f>
         <v/>
       </c>
       <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 49546-2025 karta.png", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 3253-2025 karta.png", "A 3253-2025")</f>
         <v/>
       </c>
       <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 49546-2025 georefererad karta.tif", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 3253-2025 georefererad karta.tif", "A 3253-2025")</f>
         <v/>
       </c>
       <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 49546-2025 FSC-klagomål.docx", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 3253-2025 FSC-klagomål.docx", "A 3253-2025")</f>
         <v/>
       </c>
       <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 49546-2025 FSC-klagomål mail.docx", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 3253-2025 FSC-klagomål mail.docx", "A 3253-2025")</f>
         <v/>
       </c>
       <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 49546-2025 tillsynsbegäran.docx", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 3253-2025 tillsynsbegäran.docx", "A 3253-2025")</f>
         <v/>
       </c>
       <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 49546-2025 tillsynsbegäran mail.docx", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 3253-2025 tillsynsbegäran mail.docx", "A 3253-2025")</f>
         <v/>
       </c>
     </row>
@@ -1030,7 +1030,7 @@
         <v>44756</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1135,7 +1135,7 @@
         <v>45265</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 13766-2023</t>
+          <t>A 49543-2025</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1238,14 +1238,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45007</v>
+        <v>45939</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1258,16 +1258,16 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -1282,7 +1282,7 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -1291,49 +1291,49 @@
         <v>1</v>
       </c>
       <c r="T8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U8" t="n">
         <v>0</v>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Svartöra</t>
         </is>
       </c>
       <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 13766-2023 artfynd.xlsx", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 49543-2025 artfynd.xlsx", "A 49543-2025")</f>
         <v/>
       </c>
       <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 13766-2023 karta.png", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 49543-2025 karta.png", "A 49543-2025")</f>
         <v/>
       </c>
       <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 13766-2023 georefererad karta.tif", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 49543-2025 georefererad karta.tif", "A 49543-2025")</f>
         <v/>
       </c>
       <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 13766-2023 FSC-klagomål.docx", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 49543-2025 FSC-klagomål.docx", "A 49543-2025")</f>
         <v/>
       </c>
       <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 13766-2023 FSC-klagomål mail.docx", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 49543-2025 FSC-klagomål mail.docx", "A 49543-2025")</f>
         <v/>
       </c>
       <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 13766-2023 tillsynsbegäran.docx", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 49543-2025 tillsynsbegäran.docx", "A 49543-2025")</f>
         <v/>
       </c>
       <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 13766-2023 tillsynsbegäran mail.docx", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 49543-2025 tillsynsbegäran mail.docx", "A 49543-2025")</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 49543-2025</t>
+          <t>A 49549-2025</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1350,7 +1350,7 @@
         <v>45939</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1363,16 +1363,16 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -1387,7 +1387,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -1396,42 +1396,42 @@
         <v>1</v>
       </c>
       <c r="T9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>Svartöra</t>
+          <t>Noshornsoxe</t>
         </is>
       </c>
       <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 49543-2025 artfynd.xlsx", "A 49543-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 49549-2025 artfynd.xlsx", "A 49549-2025")</f>
         <v/>
       </c>
       <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 49543-2025 karta.png", "A 49543-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 49549-2025 karta.png", "A 49549-2025")</f>
         <v/>
       </c>
       <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 49543-2025 georefererad karta.tif", "A 49543-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 49549-2025 georefererad karta.tif", "A 49549-2025")</f>
         <v/>
       </c>
       <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 49543-2025 FSC-klagomål.docx", "A 49543-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 49549-2025 FSC-klagomål.docx", "A 49549-2025")</f>
         <v/>
       </c>
       <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 49543-2025 FSC-klagomål mail.docx", "A 49543-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 49549-2025 FSC-klagomål mail.docx", "A 49549-2025")</f>
         <v/>
       </c>
       <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 49543-2025 tillsynsbegäran.docx", "A 49543-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 49549-2025 tillsynsbegäran.docx", "A 49549-2025")</f>
         <v/>
       </c>
       <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 49543-2025 tillsynsbegäran mail.docx", "A 49543-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 49549-2025 tillsynsbegäran mail.docx", "A 49549-2025")</f>
         <v/>
       </c>
     </row>
@@ -1455,7 +1455,7 @@
         <v>45525</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1548,7 +1548,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 49549-2025</t>
+          <t>A 13766-2023</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1558,14 +1558,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45939</v>
+        <v>45007</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1578,13 +1578,13 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -1614,39 +1614,39 @@
         <v>1</v>
       </c>
       <c r="U11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Noshornsoxe</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 49549-2025 artfynd.xlsx", "A 49549-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 13766-2023 artfynd.xlsx", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 49549-2025 karta.png", "A 49549-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 13766-2023 karta.png", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 49549-2025 georefererad karta.tif", "A 49549-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 13766-2023 georefererad karta.tif", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 49549-2025 FSC-klagomål.docx", "A 49549-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 13766-2023 FSC-klagomål.docx", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 49549-2025 FSC-klagomål mail.docx", "A 49549-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 13766-2023 FSC-klagomål mail.docx", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 49549-2025 tillsynsbegäran.docx", "A 49549-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 13766-2023 tillsynsbegäran.docx", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 49549-2025 tillsynsbegäran mail.docx", "A 49549-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 13766-2023 tillsynsbegäran mail.docx", "A 13766-2023")</f>
         <v/>
       </c>
     </row>
@@ -1670,7 +1670,7 @@
         <v>45644</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1775,7 +1775,7 @@
         <v>44617</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 38631-2023</t>
+          <t>A 49536-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1845,10 +1845,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45162</v>
+        <v>45939</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1904,7 +1904,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 32596-2024</t>
+          <t>A 22195-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1918,10 +1918,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45513</v>
+        <v>45069</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1933,8 +1933,13 @@
           <t>YSTAD</t>
         </is>
       </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I15" t="n">
-        <v>2.6</v>
+        <v>1.1</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1977,7 +1982,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 22195-2023</t>
+          <t>A 40417-2022</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1991,10 +1996,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45069</v>
+        <v>44823</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2006,13 +2011,8 @@
           <t>YSTAD</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I16" t="n">
-        <v>1.1</v>
+        <v>2.3</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2055,7 +2055,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 34302-2024</t>
+          <t>A 38413-2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2069,10 +2069,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45524</v>
+        <v>46282</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2085,7 +2085,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1.9</v>
+        <v>0.6</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2128,7 +2128,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 49536-2025</t>
+          <t>A 32596-2024</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2142,10 +2142,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45939</v>
+        <v>45513</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2158,7 +2158,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1.5</v>
+        <v>2.6</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2201,7 +2201,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 38413-2026</t>
+          <t>A 34302-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2215,10 +2215,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46282</v>
+        <v>45524</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2231,7 +2231,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.6</v>
+        <v>1.9</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2274,7 +2274,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 40417-2022</t>
+          <t>A 27578-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2288,10 +2288,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44823</v>
+        <v>46190</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>2.3</v>
+        <v>6.6</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2347,7 +2347,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 27578-2026</t>
+          <t>A 60803-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2361,10 +2361,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46190</v>
+        <v>45260</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>6.6</v>
+        <v>1.6</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2420,7 +2420,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 18090-2022</t>
+          <t>A 38631-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2430,14 +2430,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44684</v>
+        <v>45162</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2450,7 +2450,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>4.9</v>
+        <v>0.8</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2493,7 +2493,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 60803-2023</t>
+          <t>A 18090-2022</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2503,14 +2503,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45260</v>
+        <v>44684</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2523,7 +2523,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.6</v>
+        <v>4.9</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>

--- a/Översikt YSTAD.xlsx
+++ b/Översikt YSTAD.xlsx
@@ -601,7 +601,7 @@
         <v>44903</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -707,7 +707,7 @@
         <v>45939</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -813,7 +813,7 @@
         <v>45113</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -919,7 +919,7 @@
         <v>45679</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>44756</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1135,7 +1135,7 @@
         <v>45265</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1245,7 +1245,7 @@
         <v>45939</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
         <v>45939</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         <v>45525</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1565,7 +1565,7 @@
         <v>45007</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1670,7 +1670,7 @@
         <v>45644</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1775,7 +1775,7 @@
         <v>44617</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         <v>45939</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
         <v>45069</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1999,7 +1999,7 @@
         <v>44823</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
         <v>46282</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         <v>45513</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2218,7 +2218,7 @@
         <v>45524</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2291,7 +2291,7 @@
         <v>46190</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         <v>45260</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
         <v>45162</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2510,7 +2510,7 @@
         <v>44684</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>

--- a/Översikt YSTAD.xlsx
+++ b/Översikt YSTAD.xlsx
@@ -601,7 +601,7 @@
         <v>44903</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -707,7 +707,7 @@
         <v>45939</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -813,7 +813,7 @@
         <v>45113</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -919,7 +919,7 @@
         <v>45679</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>44756</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1135,7 +1135,7 @@
         <v>45265</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1245,7 +1245,7 @@
         <v>45939</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
         <v>45939</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         <v>45525</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1565,7 +1565,7 @@
         <v>45007</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1670,7 +1670,7 @@
         <v>45644</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1775,7 +1775,7 @@
         <v>44617</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         <v>45939</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
         <v>45069</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1999,7 +1999,7 @@
         <v>44823</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
         <v>46282</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         <v>45513</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2218,7 +2218,7 @@
         <v>45524</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2291,7 +2291,7 @@
         <v>46190</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         <v>45260</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
         <v>45162</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2510,7 +2510,7 @@
         <v>44684</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>

--- a/Översikt YSTAD.xlsx
+++ b/Översikt YSTAD.xlsx
@@ -584,7 +584,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A 60295-2022</t>
+          <t>A 3253-2025</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -594,14 +594,14 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>44903</v>
+        <v>45679</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -613,14 +613,19 @@
           <t>YSTAD</t>
         </is>
       </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I2" t="n">
-        <v>1.1</v>
+        <v>2.5</v>
       </c>
       <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
         <v>2</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -647,43 +652,43 @@
         <v>2</v>
       </c>
       <c r="T2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="U2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
-          <t>Klockgroda
-Ätlig groda</t>
+          <t>Lönnlav
+Strävlosta</t>
         </is>
       </c>
       <c r="W2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 60295-2022 artfynd.xlsx", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 3253-2025 artfynd.xlsx", "A 3253-2025")</f>
         <v/>
       </c>
       <c r="X2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 60295-2022 karta.png", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 3253-2025 karta.png", "A 3253-2025")</f>
         <v/>
       </c>
       <c r="Y2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 60295-2022 georefererad karta.tif", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 3253-2025 georefererad karta.tif", "A 3253-2025")</f>
         <v/>
       </c>
       <c r="AA2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 60295-2022 FSC-klagomål.docx", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 3253-2025 FSC-klagomål.docx", "A 3253-2025")</f>
         <v/>
       </c>
       <c r="AB2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 60295-2022 FSC-klagomål mail.docx", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 3253-2025 FSC-klagomål mail.docx", "A 3253-2025")</f>
         <v/>
       </c>
       <c r="AC2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 60295-2022 tillsynsbegäran.docx", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 3253-2025 tillsynsbegäran.docx", "A 3253-2025")</f>
         <v/>
       </c>
       <c r="AD2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 60295-2022 tillsynsbegäran mail.docx", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 3253-2025 tillsynsbegäran mail.docx", "A 3253-2025")</f>
         <v/>
       </c>
     </row>
@@ -707,7 +712,7 @@
         <v>45939</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -796,7 +801,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 31213-2023</t>
+          <t>A 60295-2022</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -806,14 +811,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45113</v>
+        <v>44903</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -826,16 +831,16 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>6.5</v>
+        <v>1.1</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -850,7 +855,7 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -859,50 +864,50 @@
         <v>2</v>
       </c>
       <c r="T4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="U4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>Skogsveronika
-Skärmstarr</t>
+          <t>Klockgroda
+Ätlig groda</t>
         </is>
       </c>
       <c r="W4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 31213-2023 artfynd.xlsx", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 60295-2022 artfynd.xlsx", "A 60295-2022")</f>
         <v/>
       </c>
       <c r="X4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 31213-2023 karta.png", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 60295-2022 karta.png", "A 60295-2022")</f>
         <v/>
       </c>
       <c r="Y4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 31213-2023 georefererad karta.tif", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 60295-2022 georefererad karta.tif", "A 60295-2022")</f>
         <v/>
       </c>
       <c r="AA4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 31213-2023 FSC-klagomål.docx", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 60295-2022 FSC-klagomål.docx", "A 60295-2022")</f>
         <v/>
       </c>
       <c r="AB4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 31213-2023 FSC-klagomål mail.docx", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 60295-2022 FSC-klagomål mail.docx", "A 60295-2022")</f>
         <v/>
       </c>
       <c r="AC4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 31213-2023 tillsynsbegäran.docx", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 60295-2022 tillsynsbegäran.docx", "A 60295-2022")</f>
         <v/>
       </c>
       <c r="AD4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 31213-2023 tillsynsbegäran mail.docx", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 60295-2022 tillsynsbegäran mail.docx", "A 60295-2022")</f>
         <v/>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 3253-2025</t>
+          <t>A 31213-2023</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -916,10 +921,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>45679</v>
+        <v>45113</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -931,22 +936,17 @@
           <t>YSTAD</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I5" t="n">
-        <v>2.5</v>
+        <v>6.5</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -961,7 +961,7 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -973,40 +973,40 @@
         <v>3</v>
       </c>
       <c r="U5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>Lönnlav
-Strävlosta</t>
+          <t>Skogsveronika
+Skärmstarr</t>
         </is>
       </c>
       <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 3253-2025 artfynd.xlsx", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 31213-2023 artfynd.xlsx", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 3253-2025 karta.png", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 31213-2023 karta.png", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 3253-2025 georefererad karta.tif", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 31213-2023 georefererad karta.tif", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 3253-2025 FSC-klagomål.docx", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 31213-2023 FSC-klagomål.docx", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 3253-2025 FSC-klagomål mail.docx", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 31213-2023 FSC-klagomål mail.docx", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 3253-2025 tillsynsbegäran.docx", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 31213-2023 tillsynsbegäran.docx", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 3253-2025 tillsynsbegäran mail.docx", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 31213-2023 tillsynsbegäran mail.docx", "A 31213-2023")</f>
         <v/>
       </c>
     </row>
@@ -1030,7 +1030,7 @@
         <v>44756</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1135,7 +1135,7 @@
         <v>45265</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1245,7 +1245,7 @@
         <v>45939</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1333,7 +1333,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 49549-2025</t>
+          <t>A 13766-2023</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1343,14 +1343,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45939</v>
+        <v>45007</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1363,13 +1363,13 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -1399,46 +1399,46 @@
         <v>1</v>
       </c>
       <c r="U9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>Noshornsoxe</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 49549-2025 artfynd.xlsx", "A 49549-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 13766-2023 artfynd.xlsx", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 49549-2025 karta.png", "A 49549-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 13766-2023 karta.png", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 49549-2025 georefererad karta.tif", "A 49549-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 13766-2023 georefererad karta.tif", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 49549-2025 FSC-klagomål.docx", "A 49549-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 13766-2023 FSC-klagomål.docx", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 49549-2025 FSC-klagomål mail.docx", "A 49549-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 13766-2023 FSC-klagomål mail.docx", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 49549-2025 tillsynsbegäran.docx", "A 49549-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 13766-2023 tillsynsbegäran.docx", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 49549-2025 tillsynsbegäran mail.docx", "A 49549-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 13766-2023 tillsynsbegäran mail.docx", "A 13766-2023")</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 34341-2024</t>
+          <t>A 49549-2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1452,10 +1452,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45525</v>
+        <v>45939</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1467,22 +1467,17 @@
           <t>YSTAD</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I10" t="n">
-        <v>14.4</v>
+        <v>0.5</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -1497,7 +1492,7 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -1513,42 +1508,42 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>Desmeknopp</t>
+          <t>Noshornsoxe</t>
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 34341-2024 artfynd.xlsx", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 49549-2025 artfynd.xlsx", "A 49549-2025")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 34341-2024 karta.png", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 49549-2025 karta.png", "A 49549-2025")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 34341-2024 georefererad karta.tif", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 49549-2025 georefererad karta.tif", "A 49549-2025")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 34341-2024 FSC-klagomål.docx", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 49549-2025 FSC-klagomål.docx", "A 49549-2025")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 34341-2024 FSC-klagomål mail.docx", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 49549-2025 FSC-klagomål mail.docx", "A 49549-2025")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 34341-2024 tillsynsbegäran.docx", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 49549-2025 tillsynsbegäran.docx", "A 49549-2025")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 34341-2024 tillsynsbegäran mail.docx", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 49549-2025 tillsynsbegäran mail.docx", "A 49549-2025")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 13766-2023</t>
+          <t>A 60891-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1558,14 +1553,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45007</v>
+        <v>45644</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1578,7 +1573,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0.9</v>
+        <v>16.1</v>
       </c>
       <c r="J11" t="n">
         <v>1</v>
@@ -1618,42 +1613,42 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Lövgroda</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 13766-2023 artfynd.xlsx", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 60891-2024 artfynd.xlsx", "A 60891-2024")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 13766-2023 karta.png", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 60891-2024 karta.png", "A 60891-2024")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 13766-2023 georefererad karta.tif", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 60891-2024 georefererad karta.tif", "A 60891-2024")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 13766-2023 FSC-klagomål.docx", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 60891-2024 FSC-klagomål.docx", "A 60891-2024")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 13766-2023 FSC-klagomål mail.docx", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 60891-2024 FSC-klagomål mail.docx", "A 60891-2024")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 13766-2023 tillsynsbegäran.docx", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 60891-2024 tillsynsbegäran.docx", "A 60891-2024")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 13766-2023 tillsynsbegäran mail.docx", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 60891-2024 tillsynsbegäran mail.docx", "A 60891-2024")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 60891-2024</t>
+          <t>A 34341-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1667,10 +1662,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45644</v>
+        <v>45525</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1682,17 +1677,22 @@
           <t>YSTAD</t>
         </is>
       </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I12" t="n">
-        <v>16.1</v>
+        <v>14.4</v>
       </c>
       <c r="J12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -1707,7 +1707,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -1719,39 +1719,39 @@
         <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Lövgroda</t>
+          <t>Desmeknopp</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 60891-2024 artfynd.xlsx", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 34341-2024 artfynd.xlsx", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 60891-2024 karta.png", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 34341-2024 karta.png", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 60891-2024 georefererad karta.tif", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 34341-2024 georefererad karta.tif", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 60891-2024 FSC-klagomål.docx", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 34341-2024 FSC-klagomål.docx", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 60891-2024 FSC-klagomål mail.docx", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 34341-2024 FSC-klagomål mail.docx", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 60891-2024 tillsynsbegäran.docx", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 34341-2024 tillsynsbegäran.docx", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 60891-2024 tillsynsbegäran mail.docx", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 34341-2024 tillsynsbegäran mail.docx", "A 34341-2024")</f>
         <v/>
       </c>
     </row>
@@ -1775,7 +1775,7 @@
         <v>44617</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 49536-2025</t>
+          <t>A 34302-2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1845,10 +1845,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45939</v>
+        <v>45524</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1904,7 +1904,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 22195-2023</t>
+          <t>A 32596-2024</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1918,10 +1918,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45069</v>
+        <v>45513</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1933,13 +1933,8 @@
           <t>YSTAD</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I15" t="n">
-        <v>1.1</v>
+        <v>2.6</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1999,7 +1994,7 @@
         <v>44823</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2072,7 +2067,7 @@
         <v>46282</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2128,7 +2123,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 32596-2024</t>
+          <t>A 18090-2022</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2138,14 +2133,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45513</v>
+        <v>44684</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2158,7 +2153,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>2.6</v>
+        <v>4.9</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2201,7 +2196,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 34302-2024</t>
+          <t>A 60803-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2215,10 +2210,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45524</v>
+        <v>45260</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2231,7 +2226,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2274,7 +2269,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 27578-2026</t>
+          <t>A 38631-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2288,10 +2283,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46190</v>
+        <v>45162</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2304,7 +2299,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>6.6</v>
+        <v>0.8</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2347,7 +2342,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 60803-2023</t>
+          <t>A 49536-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2361,10 +2356,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45260</v>
+        <v>45939</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2377,7 +2372,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2420,7 +2415,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 38631-2023</t>
+          <t>A 22195-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2434,10 +2429,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45162</v>
+        <v>45069</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2449,8 +2444,13 @@
           <t>YSTAD</t>
         </is>
       </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I22" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2493,7 +2493,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 18090-2022</t>
+          <t>A 27578-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2503,14 +2503,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44684</v>
+        <v>46190</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2523,7 +2523,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>4.9</v>
+        <v>6.6</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>

--- a/Översikt YSTAD.xlsx
+++ b/Översikt YSTAD.xlsx
@@ -584,7 +584,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A 3253-2025</t>
+          <t>A 31213-2023</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>45679</v>
+        <v>45113</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -613,22 +613,17 @@
           <t>YSTAD</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I2" t="n">
-        <v>2.5</v>
+        <v>6.5</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
@@ -643,7 +638,7 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -655,47 +650,47 @@
         <v>3</v>
       </c>
       <c r="U2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
-          <t>Lönnlav
-Strävlosta</t>
+          <t>Skogsveronika
+Skärmstarr</t>
         </is>
       </c>
       <c r="W2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 3253-2025 artfynd.xlsx", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 31213-2023 artfynd.xlsx", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="X2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 3253-2025 karta.png", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 31213-2023 karta.png", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="Y2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 3253-2025 georefererad karta.tif", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 31213-2023 georefererad karta.tif", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="AA2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 3253-2025 FSC-klagomål.docx", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 31213-2023 FSC-klagomål.docx", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="AB2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 3253-2025 FSC-klagomål mail.docx", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 31213-2023 FSC-klagomål mail.docx", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="AC2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 3253-2025 tillsynsbegäran.docx", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 31213-2023 tillsynsbegäran.docx", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="AD2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 3253-2025 tillsynsbegäran mail.docx", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 31213-2023 tillsynsbegäran mail.docx", "A 31213-2023")</f>
         <v/>
       </c>
     </row>
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 49546-2025</t>
+          <t>A 3253-2025</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -709,10 +704,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>45939</v>
+        <v>45679</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -724,14 +719,19 @@
           <t>YSTAD</t>
         </is>
       </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I3" t="n">
-        <v>4.4</v>
+        <v>2.5</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -740,7 +740,7 @@
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -749,52 +749,52 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
         <v>2</v>
       </c>
       <c r="T3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
-          <t>Skogsalm
-Igelkottsröksvamp</t>
+          <t>Lönnlav
+Strävlosta</t>
         </is>
       </c>
       <c r="W3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 49546-2025 artfynd.xlsx", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 3253-2025 artfynd.xlsx", "A 3253-2025")</f>
         <v/>
       </c>
       <c r="X3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 49546-2025 karta.png", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 3253-2025 karta.png", "A 3253-2025")</f>
         <v/>
       </c>
       <c r="Y3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 49546-2025 georefererad karta.tif", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 3253-2025 georefererad karta.tif", "A 3253-2025")</f>
         <v/>
       </c>
       <c r="AA3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 49546-2025 FSC-klagomål.docx", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 3253-2025 FSC-klagomål.docx", "A 3253-2025")</f>
         <v/>
       </c>
       <c r="AB3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 49546-2025 FSC-klagomål mail.docx", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 3253-2025 FSC-klagomål mail.docx", "A 3253-2025")</f>
         <v/>
       </c>
       <c r="AC3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 49546-2025 tillsynsbegäran.docx", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 3253-2025 tillsynsbegäran.docx", "A 3253-2025")</f>
         <v/>
       </c>
       <c r="AD3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 49546-2025 tillsynsbegäran mail.docx", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 3253-2025 tillsynsbegäran mail.docx", "A 3253-2025")</f>
         <v/>
       </c>
     </row>
@@ -818,7 +818,7 @@
         <v>44903</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 31213-2023</t>
+          <t>A 49546-2025</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -921,10 +921,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>45113</v>
+        <v>45939</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -937,22 +937,22 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>6.5</v>
+        <v>4.4</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -964,49 +964,49 @@
         <v>1</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S5" t="n">
         <v>2</v>
       </c>
       <c r="T5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>Skogsveronika
-Skärmstarr</t>
+          <t>Skogsalm
+Igelkottsröksvamp</t>
         </is>
       </c>
       <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 31213-2023 artfynd.xlsx", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 49546-2025 artfynd.xlsx", "A 49546-2025")</f>
         <v/>
       </c>
       <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 31213-2023 karta.png", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 49546-2025 karta.png", "A 49546-2025")</f>
         <v/>
       </c>
       <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 31213-2023 georefererad karta.tif", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 49546-2025 georefererad karta.tif", "A 49546-2025")</f>
         <v/>
       </c>
       <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 31213-2023 FSC-klagomål.docx", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 49546-2025 FSC-klagomål.docx", "A 49546-2025")</f>
         <v/>
       </c>
       <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 31213-2023 FSC-klagomål mail.docx", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 49546-2025 FSC-klagomål mail.docx", "A 49546-2025")</f>
         <v/>
       </c>
       <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 31213-2023 tillsynsbegäran.docx", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 49546-2025 tillsynsbegäran.docx", "A 49546-2025")</f>
         <v/>
       </c>
       <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 31213-2023 tillsynsbegäran mail.docx", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 49546-2025 tillsynsbegäran mail.docx", "A 49546-2025")</f>
         <v/>
       </c>
     </row>
@@ -1030,7 +1030,7 @@
         <v>44756</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1135,7 +1135,7 @@
         <v>45265</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1245,7 +1245,7 @@
         <v>45939</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
         <v>45007</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 49549-2025</t>
+          <t>A 34341-2024</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1452,10 +1452,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45939</v>
+        <v>45525</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1467,17 +1467,22 @@
           <t>YSTAD</t>
         </is>
       </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I10" t="n">
-        <v>0.5</v>
+        <v>14.4</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -1492,7 +1497,7 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -1508,35 +1513,35 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>Noshornsoxe</t>
+          <t>Desmeknopp</t>
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 49549-2025 artfynd.xlsx", "A 49549-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 34341-2024 artfynd.xlsx", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 49549-2025 karta.png", "A 49549-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 34341-2024 karta.png", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 49549-2025 georefererad karta.tif", "A 49549-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 34341-2024 georefererad karta.tif", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 49549-2025 FSC-klagomål.docx", "A 49549-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 34341-2024 FSC-klagomål.docx", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 49549-2025 FSC-klagomål mail.docx", "A 49549-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 34341-2024 FSC-klagomål mail.docx", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 49549-2025 tillsynsbegäran.docx", "A 49549-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 34341-2024 tillsynsbegäran.docx", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 49549-2025 tillsynsbegäran mail.docx", "A 49549-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 34341-2024 tillsynsbegäran mail.docx", "A 34341-2024")</f>
         <v/>
       </c>
     </row>
@@ -1560,7 +1565,7 @@
         <v>45644</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1648,7 +1653,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 34341-2024</t>
+          <t>A 49549-2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1662,10 +1667,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45525</v>
+        <v>45939</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1677,22 +1682,17 @@
           <t>YSTAD</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I12" t="n">
-        <v>14.4</v>
+        <v>0.5</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -1707,7 +1707,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -1723,35 +1723,35 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Desmeknopp</t>
+          <t>Noshornsoxe</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 34341-2024 artfynd.xlsx", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 49549-2025 artfynd.xlsx", "A 49549-2025")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 34341-2024 karta.png", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 49549-2025 karta.png", "A 49549-2025")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 34341-2024 georefererad karta.tif", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 49549-2025 georefererad karta.tif", "A 49549-2025")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 34341-2024 FSC-klagomål.docx", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 49549-2025 FSC-klagomål.docx", "A 49549-2025")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 34341-2024 FSC-klagomål mail.docx", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 49549-2025 FSC-klagomål mail.docx", "A 49549-2025")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 34341-2024 tillsynsbegäran.docx", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 49549-2025 tillsynsbegäran.docx", "A 49549-2025")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 34341-2024 tillsynsbegäran mail.docx", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 49549-2025 tillsynsbegäran mail.docx", "A 49549-2025")</f>
         <v/>
       </c>
     </row>
@@ -1775,7 +1775,7 @@
         <v>44617</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 34302-2024</t>
+          <t>A 22195-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1845,10 +1845,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45524</v>
+        <v>45069</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1860,8 +1860,13 @@
           <t>YSTAD</t>
         </is>
       </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I14" t="n">
-        <v>1.9</v>
+        <v>1.1</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1904,7 +1909,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 32596-2024</t>
+          <t>A 60803-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1918,10 +1923,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45513</v>
+        <v>45260</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1934,7 +1939,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>2.6</v>
+        <v>1.6</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1994,7 +1999,7 @@
         <v>44823</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2050,7 +2055,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 38413-2026</t>
+          <t>A 34302-2024</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2064,10 +2069,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46282</v>
+        <v>45524</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2080,7 +2085,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.6</v>
+        <v>1.9</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2123,7 +2128,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 18090-2022</t>
+          <t>A 38631-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2133,14 +2138,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44684</v>
+        <v>45162</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2153,7 +2158,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>4.9</v>
+        <v>0.8</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2196,7 +2201,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 60803-2023</t>
+          <t>A 18090-2022</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2206,14 +2211,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45260</v>
+        <v>44684</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2226,7 +2231,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1.6</v>
+        <v>4.9</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2269,7 +2274,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 38631-2023</t>
+          <t>A 38413-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2283,10 +2288,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45162</v>
+        <v>46282</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2299,7 +2304,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2342,7 +2347,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 49536-2025</t>
+          <t>A 27578-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2356,10 +2361,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45939</v>
+        <v>46190</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2372,7 +2377,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.5</v>
+        <v>6.6</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2415,7 +2420,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 22195-2023</t>
+          <t>A 32596-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2429,10 +2434,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45069</v>
+        <v>45513</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2444,13 +2449,8 @@
           <t>YSTAD</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I22" t="n">
-        <v>1.1</v>
+        <v>2.6</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2493,7 +2493,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 27578-2026</t>
+          <t>A 49536-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2507,10 +2507,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46190</v>
+        <v>45939</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2523,7 +2523,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>6.6</v>
+        <v>1.5</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>

--- a/Översikt YSTAD.xlsx
+++ b/Översikt YSTAD.xlsx
@@ -584,7 +584,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A 31213-2023</t>
+          <t>A 60295-2022</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -594,14 +594,14 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>45113</v>
+        <v>44903</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -614,16 +614,16 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>6.5</v>
+        <v>1.1</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
@@ -638,7 +638,7 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -647,50 +647,50 @@
         <v>2</v>
       </c>
       <c r="T2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="U2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
-          <t>Skogsveronika
-Skärmstarr</t>
+          <t>Klockgroda
+Ätlig groda</t>
         </is>
       </c>
       <c r="W2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 31213-2023 artfynd.xlsx", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 60295-2022 artfynd.xlsx", "A 60295-2022")</f>
         <v/>
       </c>
       <c r="X2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 31213-2023 karta.png", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 60295-2022 karta.png", "A 60295-2022")</f>
         <v/>
       </c>
       <c r="Y2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 31213-2023 georefererad karta.tif", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 60295-2022 georefererad karta.tif", "A 60295-2022")</f>
         <v/>
       </c>
       <c r="AA2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 31213-2023 FSC-klagomål.docx", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 60295-2022 FSC-klagomål.docx", "A 60295-2022")</f>
         <v/>
       </c>
       <c r="AB2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 31213-2023 FSC-klagomål mail.docx", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 60295-2022 FSC-klagomål mail.docx", "A 60295-2022")</f>
         <v/>
       </c>
       <c r="AC2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 31213-2023 tillsynsbegäran.docx", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 60295-2022 tillsynsbegäran.docx", "A 60295-2022")</f>
         <v/>
       </c>
       <c r="AD2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 31213-2023 tillsynsbegäran mail.docx", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 60295-2022 tillsynsbegäran mail.docx", "A 60295-2022")</f>
         <v/>
       </c>
     </row>
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 3253-2025</t>
+          <t>A 31213-2023</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -704,10 +704,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>45679</v>
+        <v>45113</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -719,22 +719,17 @@
           <t>YSTAD</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I3" t="n">
-        <v>2.5</v>
+        <v>6.5</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
@@ -749,7 +744,7 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -761,47 +756,47 @@
         <v>3</v>
       </c>
       <c r="U3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
-          <t>Lönnlav
-Strävlosta</t>
+          <t>Skogsveronika
+Skärmstarr</t>
         </is>
       </c>
       <c r="W3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 3253-2025 artfynd.xlsx", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 31213-2023 artfynd.xlsx", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="X3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 3253-2025 karta.png", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 31213-2023 karta.png", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="Y3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 3253-2025 georefererad karta.tif", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 31213-2023 georefererad karta.tif", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="AA3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 3253-2025 FSC-klagomål.docx", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 31213-2023 FSC-klagomål.docx", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="AB3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 3253-2025 FSC-klagomål mail.docx", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 31213-2023 FSC-klagomål mail.docx", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="AC3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 3253-2025 tillsynsbegäran.docx", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 31213-2023 tillsynsbegäran.docx", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="AD3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 3253-2025 tillsynsbegäran mail.docx", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 31213-2023 tillsynsbegäran mail.docx", "A 31213-2023")</f>
         <v/>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 60295-2022</t>
+          <t>A 49546-2025</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -811,14 +806,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>44903</v>
+        <v>45939</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -831,13 +826,13 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>1.1</v>
+        <v>4.4</v>
       </c>
       <c r="J4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -846,7 +841,7 @@
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -855,59 +850,59 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S4" t="n">
         <v>2</v>
       </c>
       <c r="T4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="U4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>Klockgroda
-Ätlig groda</t>
+          <t>Skogsalm
+Igelkottsröksvamp</t>
         </is>
       </c>
       <c r="W4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 60295-2022 artfynd.xlsx", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 49546-2025 artfynd.xlsx", "A 49546-2025")</f>
         <v/>
       </c>
       <c r="X4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 60295-2022 karta.png", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 49546-2025 karta.png", "A 49546-2025")</f>
         <v/>
       </c>
       <c r="Y4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 60295-2022 georefererad karta.tif", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 49546-2025 georefererad karta.tif", "A 49546-2025")</f>
         <v/>
       </c>
       <c r="AA4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 60295-2022 FSC-klagomål.docx", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 49546-2025 FSC-klagomål.docx", "A 49546-2025")</f>
         <v/>
       </c>
       <c r="AB4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 60295-2022 FSC-klagomål mail.docx", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 49546-2025 FSC-klagomål mail.docx", "A 49546-2025")</f>
         <v/>
       </c>
       <c r="AC4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 60295-2022 tillsynsbegäran.docx", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 49546-2025 tillsynsbegäran.docx", "A 49546-2025")</f>
         <v/>
       </c>
       <c r="AD4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 60295-2022 tillsynsbegäran mail.docx", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 49546-2025 tillsynsbegäran mail.docx", "A 49546-2025")</f>
         <v/>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 49546-2025</t>
+          <t>A 3253-2025</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -921,10 +916,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>45939</v>
+        <v>45679</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -936,14 +931,19 @@
           <t>YSTAD</t>
         </is>
       </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I5" t="n">
-        <v>4.4</v>
+        <v>2.5</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -952,7 +952,7 @@
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -961,52 +961,52 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
         <v>2</v>
       </c>
       <c r="T5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>Skogsalm
-Igelkottsröksvamp</t>
+          <t>Lönnlav
+Strävlosta</t>
         </is>
       </c>
       <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 49546-2025 artfynd.xlsx", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 3253-2025 artfynd.xlsx", "A 3253-2025")</f>
         <v/>
       </c>
       <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 49546-2025 karta.png", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 3253-2025 karta.png", "A 3253-2025")</f>
         <v/>
       </c>
       <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 49546-2025 georefererad karta.tif", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 3253-2025 georefererad karta.tif", "A 3253-2025")</f>
         <v/>
       </c>
       <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 49546-2025 FSC-klagomål.docx", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 3253-2025 FSC-klagomål.docx", "A 3253-2025")</f>
         <v/>
       </c>
       <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 49546-2025 FSC-klagomål mail.docx", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 3253-2025 FSC-klagomål mail.docx", "A 3253-2025")</f>
         <v/>
       </c>
       <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 49546-2025 tillsynsbegäran.docx", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 3253-2025 tillsynsbegäran.docx", "A 3253-2025")</f>
         <v/>
       </c>
       <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 49546-2025 tillsynsbegäran mail.docx", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 3253-2025 tillsynsbegäran mail.docx", "A 3253-2025")</f>
         <v/>
       </c>
     </row>
@@ -1030,7 +1030,7 @@
         <v>44756</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1135,7 +1135,7 @@
         <v>45265</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1245,7 +1245,7 @@
         <v>45939</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1333,7 +1333,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 13766-2023</t>
+          <t>A 34341-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1343,14 +1343,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45007</v>
+        <v>45525</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1362,17 +1362,22 @@
           <t>YSTAD</t>
         </is>
       </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I9" t="n">
-        <v>0.9</v>
+        <v>14.4</v>
       </c>
       <c r="J9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -1387,7 +1392,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -1399,46 +1404,46 @@
         <v>1</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Desmeknopp</t>
         </is>
       </c>
       <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 13766-2023 artfynd.xlsx", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 34341-2024 artfynd.xlsx", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 13766-2023 karta.png", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 34341-2024 karta.png", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 13766-2023 georefererad karta.tif", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 34341-2024 georefererad karta.tif", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 13766-2023 FSC-klagomål.docx", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 34341-2024 FSC-klagomål.docx", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 13766-2023 FSC-klagomål mail.docx", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 34341-2024 FSC-klagomål mail.docx", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 13766-2023 tillsynsbegäran.docx", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 34341-2024 tillsynsbegäran.docx", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 13766-2023 tillsynsbegäran mail.docx", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 34341-2024 tillsynsbegäran mail.docx", "A 34341-2024")</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 34341-2024</t>
+          <t>A 13766-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1448,14 +1453,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45525</v>
+        <v>45007</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1467,22 +1472,17 @@
           <t>YSTAD</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I10" t="n">
-        <v>14.4</v>
+        <v>0.9</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -1497,7 +1497,7 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -1509,46 +1509,46 @@
         <v>1</v>
       </c>
       <c r="U10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>Desmeknopp</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 34341-2024 artfynd.xlsx", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 13766-2023 artfynd.xlsx", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 34341-2024 karta.png", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 13766-2023 karta.png", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 34341-2024 georefererad karta.tif", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 13766-2023 georefererad karta.tif", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 34341-2024 FSC-klagomål.docx", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 13766-2023 FSC-klagomål.docx", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 34341-2024 FSC-klagomål mail.docx", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 13766-2023 FSC-klagomål mail.docx", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 34341-2024 tillsynsbegäran.docx", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 13766-2023 tillsynsbegäran.docx", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 34341-2024 tillsynsbegäran mail.docx", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 13766-2023 tillsynsbegäran mail.docx", "A 13766-2023")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 60891-2024</t>
+          <t>A 49549-2025</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1562,10 +1562,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45644</v>
+        <v>45939</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1578,13 +1578,13 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>16.1</v>
+        <v>0.5</v>
       </c>
       <c r="J11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -1614,46 +1614,46 @@
         <v>1</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Lövgroda</t>
+          <t>Noshornsoxe</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 60891-2024 artfynd.xlsx", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 49549-2025 artfynd.xlsx", "A 49549-2025")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 60891-2024 karta.png", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 49549-2025 karta.png", "A 49549-2025")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 60891-2024 georefererad karta.tif", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 49549-2025 georefererad karta.tif", "A 49549-2025")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 60891-2024 FSC-klagomål.docx", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 49549-2025 FSC-klagomål.docx", "A 49549-2025")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 60891-2024 FSC-klagomål mail.docx", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 49549-2025 FSC-klagomål mail.docx", "A 49549-2025")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 60891-2024 tillsynsbegäran.docx", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 49549-2025 tillsynsbegäran.docx", "A 49549-2025")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 60891-2024 tillsynsbegäran mail.docx", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 49549-2025 tillsynsbegäran mail.docx", "A 49549-2025")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 49549-2025</t>
+          <t>A 60891-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1667,10 +1667,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45939</v>
+        <v>45644</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1683,13 +1683,13 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.5</v>
+        <v>16.1</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -1719,39 +1719,39 @@
         <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Noshornsoxe</t>
+          <t>Lövgroda</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 49549-2025 artfynd.xlsx", "A 49549-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 60891-2024 artfynd.xlsx", "A 60891-2024")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 49549-2025 karta.png", "A 49549-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 60891-2024 karta.png", "A 60891-2024")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 49549-2025 georefererad karta.tif", "A 49549-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 60891-2024 georefererad karta.tif", "A 60891-2024")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 49549-2025 FSC-klagomål.docx", "A 49549-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 60891-2024 FSC-klagomål.docx", "A 60891-2024")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 49549-2025 FSC-klagomål mail.docx", "A 49549-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 60891-2024 FSC-klagomål mail.docx", "A 60891-2024")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 49549-2025 tillsynsbegäran.docx", "A 49549-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 60891-2024 tillsynsbegäran.docx", "A 60891-2024")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 49549-2025 tillsynsbegäran mail.docx", "A 49549-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 60891-2024 tillsynsbegäran mail.docx", "A 60891-2024")</f>
         <v/>
       </c>
     </row>
@@ -1775,7 +1775,7 @@
         <v>44617</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 22195-2023</t>
+          <t>A 18090-2022</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1841,14 +1841,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45069</v>
+        <v>44684</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1860,13 +1860,8 @@
           <t>YSTAD</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I14" t="n">
-        <v>1.1</v>
+        <v>4.9</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1926,7 +1921,7 @@
         <v>45260</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1982,7 +1977,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 40417-2022</t>
+          <t>A 38631-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1996,10 +1991,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44823</v>
+        <v>45162</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2012,7 +2007,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>2.3</v>
+        <v>0.8</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2055,7 +2050,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 34302-2024</t>
+          <t>A 32596-2024</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2069,10 +2064,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45524</v>
+        <v>45513</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2085,7 +2080,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1.9</v>
+        <v>2.6</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2128,7 +2123,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 38631-2023</t>
+          <t>A 22195-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2142,10 +2137,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45162</v>
+        <v>45069</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2157,8 +2152,13 @@
           <t>YSTAD</t>
         </is>
       </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I18" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2201,7 +2201,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 18090-2022</t>
+          <t>A 49536-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2211,14 +2211,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44684</v>
+        <v>45939</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2231,7 +2231,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>4.9</v>
+        <v>1.5</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2274,7 +2274,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 38413-2026</t>
+          <t>A 34302-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2288,10 +2288,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46282</v>
+        <v>45524</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.6</v>
+        <v>1.9</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2347,7 +2347,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 27578-2026</t>
+          <t>A 38413-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2361,10 +2361,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46190</v>
+        <v>46282</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>6.6</v>
+        <v>0.6</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2420,7 +2420,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 32596-2024</t>
+          <t>A 40417-2022</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2434,10 +2434,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45513</v>
+        <v>44823</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2450,7 +2450,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2493,7 +2493,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 49536-2025</t>
+          <t>A 27578-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2507,10 +2507,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45939</v>
+        <v>46190</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2523,7 +2523,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.5</v>
+        <v>6.6</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>

--- a/Översikt YSTAD.xlsx
+++ b/Översikt YSTAD.xlsx
@@ -584,7 +584,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A 60295-2022</t>
+          <t>A 3253-2025</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -594,14 +594,14 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>44903</v>
+        <v>45679</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -613,14 +613,19 @@
           <t>YSTAD</t>
         </is>
       </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I2" t="n">
-        <v>1.1</v>
+        <v>2.5</v>
       </c>
       <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
         <v>2</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -647,50 +652,50 @@
         <v>2</v>
       </c>
       <c r="T2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="U2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
-          <t>Klockgroda
-Ätlig groda</t>
+          <t>Lönnlav
+Strävlosta</t>
         </is>
       </c>
       <c r="W2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 60295-2022 artfynd.xlsx", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 3253-2025 artfynd.xlsx", "A 3253-2025")</f>
         <v/>
       </c>
       <c r="X2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 60295-2022 karta.png", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 3253-2025 karta.png", "A 3253-2025")</f>
         <v/>
       </c>
       <c r="Y2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 60295-2022 georefererad karta.tif", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 3253-2025 georefererad karta.tif", "A 3253-2025")</f>
         <v/>
       </c>
       <c r="AA2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 60295-2022 FSC-klagomål.docx", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 3253-2025 FSC-klagomål.docx", "A 3253-2025")</f>
         <v/>
       </c>
       <c r="AB2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 60295-2022 FSC-klagomål mail.docx", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 3253-2025 FSC-klagomål mail.docx", "A 3253-2025")</f>
         <v/>
       </c>
       <c r="AC2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 60295-2022 tillsynsbegäran.docx", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 3253-2025 tillsynsbegäran.docx", "A 3253-2025")</f>
         <v/>
       </c>
       <c r="AD2">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 60295-2022 tillsynsbegäran mail.docx", "A 60295-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 3253-2025 tillsynsbegäran mail.docx", "A 3253-2025")</f>
         <v/>
       </c>
     </row>
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 31213-2023</t>
+          <t>A 49546-2025</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -704,10 +709,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>45113</v>
+        <v>45939</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -720,22 +725,22 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>6.5</v>
+        <v>4.4</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -747,56 +752,56 @@
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S3" t="n">
         <v>2</v>
       </c>
       <c r="T3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
-          <t>Skogsveronika
-Skärmstarr</t>
+          <t>Skogsalm
+Igelkottsröksvamp</t>
         </is>
       </c>
       <c r="W3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 31213-2023 artfynd.xlsx", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 49546-2025 artfynd.xlsx", "A 49546-2025")</f>
         <v/>
       </c>
       <c r="X3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 31213-2023 karta.png", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 49546-2025 karta.png", "A 49546-2025")</f>
         <v/>
       </c>
       <c r="Y3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 31213-2023 georefererad karta.tif", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 49546-2025 georefererad karta.tif", "A 49546-2025")</f>
         <v/>
       </c>
       <c r="AA3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 31213-2023 FSC-klagomål.docx", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 49546-2025 FSC-klagomål.docx", "A 49546-2025")</f>
         <v/>
       </c>
       <c r="AB3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 31213-2023 FSC-klagomål mail.docx", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 49546-2025 FSC-klagomål mail.docx", "A 49546-2025")</f>
         <v/>
       </c>
       <c r="AC3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 31213-2023 tillsynsbegäran.docx", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 49546-2025 tillsynsbegäran.docx", "A 49546-2025")</f>
         <v/>
       </c>
       <c r="AD3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 31213-2023 tillsynsbegäran mail.docx", "A 31213-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 49546-2025 tillsynsbegäran mail.docx", "A 49546-2025")</f>
         <v/>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 49546-2025</t>
+          <t>A 60295-2022</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -806,14 +811,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45939</v>
+        <v>44903</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -826,13 +831,13 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>4.4</v>
+        <v>1.1</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -841,7 +846,7 @@
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -850,59 +855,59 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>2</v>
       </c>
       <c r="T4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>Skogsalm
-Igelkottsröksvamp</t>
+          <t>Klockgroda
+Ätlig groda</t>
         </is>
       </c>
       <c r="W4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 49546-2025 artfynd.xlsx", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 60295-2022 artfynd.xlsx", "A 60295-2022")</f>
         <v/>
       </c>
       <c r="X4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 49546-2025 karta.png", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 60295-2022 karta.png", "A 60295-2022")</f>
         <v/>
       </c>
       <c r="Y4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 49546-2025 georefererad karta.tif", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 60295-2022 georefererad karta.tif", "A 60295-2022")</f>
         <v/>
       </c>
       <c r="AA4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 49546-2025 FSC-klagomål.docx", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 60295-2022 FSC-klagomål.docx", "A 60295-2022")</f>
         <v/>
       </c>
       <c r="AB4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 49546-2025 FSC-klagomål mail.docx", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 60295-2022 FSC-klagomål mail.docx", "A 60295-2022")</f>
         <v/>
       </c>
       <c r="AC4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 49546-2025 tillsynsbegäran.docx", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 60295-2022 tillsynsbegäran.docx", "A 60295-2022")</f>
         <v/>
       </c>
       <c r="AD4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 49546-2025 tillsynsbegäran mail.docx", "A 49546-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 60295-2022 tillsynsbegäran mail.docx", "A 60295-2022")</f>
         <v/>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 3253-2025</t>
+          <t>A 31213-2023</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -916,10 +921,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>45679</v>
+        <v>45113</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -931,22 +936,17 @@
           <t>YSTAD</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I5" t="n">
-        <v>2.5</v>
+        <v>6.5</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -961,7 +961,7 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -973,40 +973,40 @@
         <v>3</v>
       </c>
       <c r="U5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>Lönnlav
-Strävlosta</t>
+          <t>Skogsveronika
+Skärmstarr</t>
         </is>
       </c>
       <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 3253-2025 artfynd.xlsx", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 31213-2023 artfynd.xlsx", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 3253-2025 karta.png", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 31213-2023 karta.png", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 3253-2025 georefererad karta.tif", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 31213-2023 georefererad karta.tif", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 3253-2025 FSC-klagomål.docx", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 31213-2023 FSC-klagomål.docx", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 3253-2025 FSC-klagomål mail.docx", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 31213-2023 FSC-klagomål mail.docx", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 3253-2025 tillsynsbegäran.docx", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 31213-2023 tillsynsbegäran.docx", "A 31213-2023")</f>
         <v/>
       </c>
       <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 3253-2025 tillsynsbegäran mail.docx", "A 3253-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 31213-2023 tillsynsbegäran mail.docx", "A 31213-2023")</f>
         <v/>
       </c>
     </row>
@@ -1030,7 +1030,7 @@
         <v>44756</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 61558-2023</t>
+          <t>A 13766-2023</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1128,14 +1128,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45265</v>
+        <v>45007</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1147,16 +1147,11 @@
           <t>YSTAD</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I7" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -1168,7 +1163,7 @@
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1177,10 +1172,10 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1193,42 +1188,42 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 61558-2023 artfynd.xlsx", "A 61558-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 13766-2023 artfynd.xlsx", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 61558-2023 karta.png", "A 61558-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 13766-2023 karta.png", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 61558-2023 georefererad karta.tif", "A 61558-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 13766-2023 georefererad karta.tif", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 61558-2023 FSC-klagomål.docx", "A 61558-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 13766-2023 FSC-klagomål.docx", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 61558-2023 FSC-klagomål mail.docx", "A 61558-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 13766-2023 FSC-klagomål mail.docx", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 61558-2023 tillsynsbegäran.docx", "A 61558-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 13766-2023 tillsynsbegäran.docx", "A 13766-2023")</f>
         <v/>
       </c>
       <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 61558-2023 tillsynsbegäran mail.docx", "A 61558-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 13766-2023 tillsynsbegäran mail.docx", "A 13766-2023")</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 49543-2025</t>
+          <t>A 61558-2023</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1242,10 +1237,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45939</v>
+        <v>45265</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1257,8 +1252,13 @@
           <t>YSTAD</t>
         </is>
       </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I8" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1285,55 +1285,55 @@
         <v>1</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
       </c>
       <c r="T8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U8" t="n">
         <v>0</v>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>Svartöra</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 49543-2025 artfynd.xlsx", "A 49543-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 61558-2023 artfynd.xlsx", "A 61558-2023")</f>
         <v/>
       </c>
       <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 49543-2025 karta.png", "A 49543-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 61558-2023 karta.png", "A 61558-2023")</f>
         <v/>
       </c>
       <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 49543-2025 georefererad karta.tif", "A 49543-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 61558-2023 georefererad karta.tif", "A 61558-2023")</f>
         <v/>
       </c>
       <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 49543-2025 FSC-klagomål.docx", "A 49543-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 61558-2023 FSC-klagomål.docx", "A 61558-2023")</f>
         <v/>
       </c>
       <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 49543-2025 FSC-klagomål mail.docx", "A 49543-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 61558-2023 FSC-klagomål mail.docx", "A 61558-2023")</f>
         <v/>
       </c>
       <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 49543-2025 tillsynsbegäran.docx", "A 49543-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 61558-2023 tillsynsbegäran.docx", "A 61558-2023")</f>
         <v/>
       </c>
       <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 49543-2025 tillsynsbegäran mail.docx", "A 49543-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 61558-2023 tillsynsbegäran mail.docx", "A 61558-2023")</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 34341-2024</t>
+          <t>A 49543-2025</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1347,10 +1347,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45525</v>
+        <v>45939</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1362,13 +1362,8 @@
           <t>YSTAD</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I9" t="n">
-        <v>14.4</v>
+        <v>1.4</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1401,49 +1396,49 @@
         <v>1</v>
       </c>
       <c r="T9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>Desmeknopp</t>
+          <t>Svartöra</t>
         </is>
       </c>
       <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 34341-2024 artfynd.xlsx", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 49543-2025 artfynd.xlsx", "A 49543-2025")</f>
         <v/>
       </c>
       <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 34341-2024 karta.png", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 49543-2025 karta.png", "A 49543-2025")</f>
         <v/>
       </c>
       <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 34341-2024 georefererad karta.tif", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 49543-2025 georefererad karta.tif", "A 49543-2025")</f>
         <v/>
       </c>
       <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 34341-2024 FSC-klagomål.docx", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 49543-2025 FSC-klagomål.docx", "A 49543-2025")</f>
         <v/>
       </c>
       <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 34341-2024 FSC-klagomål mail.docx", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 49543-2025 FSC-klagomål mail.docx", "A 49543-2025")</f>
         <v/>
       </c>
       <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 34341-2024 tillsynsbegäran.docx", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 49543-2025 tillsynsbegäran.docx", "A 49543-2025")</f>
         <v/>
       </c>
       <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 34341-2024 tillsynsbegäran mail.docx", "A 34341-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 49543-2025 tillsynsbegäran mail.docx", "A 49543-2025")</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 13766-2023</t>
+          <t>A 60891-2024</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1453,14 +1448,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45007</v>
+        <v>45644</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1473,7 +1468,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>0.9</v>
+        <v>16.1</v>
       </c>
       <c r="J10" t="n">
         <v>1</v>
@@ -1513,35 +1508,35 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Lövgroda</t>
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 13766-2023 artfynd.xlsx", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 60891-2024 artfynd.xlsx", "A 60891-2024")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 13766-2023 karta.png", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 60891-2024 karta.png", "A 60891-2024")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 13766-2023 georefererad karta.tif", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 60891-2024 georefererad karta.tif", "A 60891-2024")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 13766-2023 FSC-klagomål.docx", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 60891-2024 FSC-klagomål.docx", "A 60891-2024")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 13766-2023 FSC-klagomål mail.docx", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 60891-2024 FSC-klagomål mail.docx", "A 60891-2024")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 13766-2023 tillsynsbegäran.docx", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 60891-2024 tillsynsbegäran.docx", "A 60891-2024")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 13766-2023 tillsynsbegäran mail.docx", "A 13766-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 60891-2024 tillsynsbegäran mail.docx", "A 60891-2024")</f>
         <v/>
       </c>
     </row>
@@ -1565,7 +1560,7 @@
         <v>45939</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1653,7 +1648,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 60891-2024</t>
+          <t>A 34341-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1667,10 +1662,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45644</v>
+        <v>45525</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1682,17 +1677,22 @@
           <t>YSTAD</t>
         </is>
       </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I12" t="n">
-        <v>16.1</v>
+        <v>14.4</v>
       </c>
       <c r="J12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -1707,7 +1707,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -1719,39 +1719,39 @@
         <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Lövgroda</t>
+          <t>Desmeknopp</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 60891-2024 artfynd.xlsx", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/artfynd/A 34341-2024 artfynd.xlsx", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 60891-2024 karta.png", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor/A 34341-2024 karta.png", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 60891-2024 georefererad karta.tif", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/kartor_geotiff/A 34341-2024 georefererad karta.tif", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 60891-2024 FSC-klagomål.docx", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomål/A 34341-2024 FSC-klagomål.docx", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 60891-2024 FSC-klagomål mail.docx", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/klagomålsmail/A 34341-2024 FSC-klagomål mail.docx", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 60891-2024 tillsynsbegäran.docx", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsyn/A 34341-2024 tillsynsbegäran.docx", "A 34341-2024")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 60891-2024 tillsynsbegäran mail.docx", "A 60891-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1286/tillsynsmail/A 34341-2024 tillsynsbegäran mail.docx", "A 34341-2024")</f>
         <v/>
       </c>
     </row>
@@ -1775,7 +1775,7 @@
         <v>44617</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 18090-2022</t>
+          <t>A 32596-2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1841,14 +1841,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44684</v>
+        <v>45513</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>4.9</v>
+        <v>2.6</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1904,7 +1904,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 60803-2023</t>
+          <t>A 40417-2022</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1918,10 +1918,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45260</v>
+        <v>44823</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.6</v>
+        <v>2.3</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1977,7 +1977,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 38631-2023</t>
+          <t>A 18090-2022</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1987,14 +1987,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45162</v>
+        <v>44684</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.8</v>
+        <v>4.9</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2050,7 +2050,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 32596-2024</t>
+          <t>A 60803-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2064,10 +2064,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45513</v>
+        <v>45260</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2080,7 +2080,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>2.6</v>
+        <v>1.6</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2123,7 +2123,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 22195-2023</t>
+          <t>A 38631-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2137,10 +2137,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45069</v>
+        <v>45162</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2152,13 +2152,8 @@
           <t>YSTAD</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I18" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2201,7 +2196,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 49536-2025</t>
+          <t>A 22195-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2215,10 +2210,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45939</v>
+        <v>45069</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2230,8 +2225,13 @@
           <t>YSTAD</t>
         </is>
       </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I19" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2274,7 +2274,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 34302-2024</t>
+          <t>A 49536-2025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2288,10 +2288,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45524</v>
+        <v>45939</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2347,7 +2347,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 38413-2026</t>
+          <t>A 34302-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2361,10 +2361,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46282</v>
+        <v>45524</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.6</v>
+        <v>1.9</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2420,7 +2420,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 40417-2022</t>
+          <t>A 27578-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2434,10 +2434,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44823</v>
+        <v>46190</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2450,7 +2450,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>2.3</v>
+        <v>6.6</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2493,7 +2493,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 27578-2026</t>
+          <t>A 38413-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2507,10 +2507,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46190</v>
+        <v>46282</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2523,7 +2523,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>6.6</v>
+        <v>0.6</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
